--- a/budget_shelters_v2.xlsx
+++ b/budget_shelters_v2.xlsx
@@ -558,7 +558,7 @@
         <v>73000</v>
       </c>
       <c r="C6" t="n">
-        <v>147</v>
+        <v>1</v>
       </c>
       <c r="D6" s="6">
         <f>B6*C6</f>
@@ -573,7 +573,7 @@
         <v>100000</v>
       </c>
       <c r="C7" t="n">
-        <v>122</v>
+        <v>29</v>
       </c>
       <c r="D7" s="6">
         <f>B7*C7</f>
@@ -588,7 +588,7 @@
         <v>150000</v>
       </c>
       <c r="C8" t="n">
-        <v>55</v>
+        <v>200</v>
       </c>
       <c r="D8" s="6">
         <f>B8*C8</f>
@@ -603,7 +603,7 @@
         <v>200000</v>
       </c>
       <c r="C9" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="D9" s="6">
         <f>B9*C9</f>
@@ -618,7 +618,7 @@
         <v>250000</v>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>87</v>
       </c>
       <c r="D10" s="6">
         <f>B10*C10</f>
@@ -875,10 +875,10 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I3" s="13" t="n">
         <v>8000</v>
@@ -890,7 +890,7 @@
         <v>80</v>
       </c>
       <c r="L3" t="n">
-        <v>4.7</v>
+        <v>12.5</v>
       </c>
       <c r="M3" t="n">
         <v>14686</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="G4" s="14" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H4" s="16" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I4" s="17" t="n">
         <v>9000</v>
@@ -937,7 +937,7 @@
         <v>90</v>
       </c>
       <c r="L4" s="14" t="n">
-        <v>5.3</v>
+        <v>14</v>
       </c>
       <c r="M4" s="14" t="n">
         <v>16465</v>
@@ -969,10 +969,10 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>100000</v>
+        <v>250000</v>
       </c>
       <c r="I5" s="13" t="n">
         <v>20000</v>
@@ -984,7 +984,7 @@
         <v>90</v>
       </c>
       <c r="L5" t="n">
-        <v>11.7</v>
+        <v>31.2</v>
       </c>
       <c r="M5" t="n">
         <v>16547</v>
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="G6" s="14" t="n">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="H6" s="16" t="n">
-        <v>100000</v>
+        <v>250000</v>
       </c>
       <c r="I6" s="17" t="n">
         <v>20000</v>
@@ -1031,7 +1031,7 @@
         <v>90</v>
       </c>
       <c r="L6" s="14" t="n">
-        <v>11.7</v>
+        <v>39</v>
       </c>
       <c r="M6" s="14" t="n">
         <v>17553</v>
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="I7" s="13" t="n">
         <v>13000</v>
@@ -1078,7 +1078,7 @@
         <v>90</v>
       </c>
       <c r="L7" t="n">
-        <v>7.6</v>
+        <v>20.3</v>
       </c>
       <c r="M7" t="n">
         <v>12425</v>
@@ -1110,10 +1110,10 @@
         </is>
       </c>
       <c r="G8" s="14" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="H8" s="16" t="n">
-        <v>200000</v>
+        <v>250000</v>
       </c>
       <c r="I8" s="17" t="n">
         <v>18000</v>
@@ -1125,7 +1125,7 @@
         <v>80</v>
       </c>
       <c r="L8" s="14" t="n">
-        <v>10.5</v>
+        <v>35.1</v>
       </c>
       <c r="M8" s="14" t="n">
         <v>51554</v>
@@ -1157,10 +1157,10 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>150000</v>
+        <v>200000</v>
       </c>
       <c r="I9" s="13" t="n">
         <v>4000</v>
@@ -1172,7 +1172,7 @@
         <v>90</v>
       </c>
       <c r="L9" t="n">
-        <v>2.3</v>
+        <v>7.8</v>
       </c>
       <c r="M9" t="n">
         <v>54758</v>
@@ -1204,10 +1204,10 @@
         </is>
       </c>
       <c r="G10" s="14" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H10" s="16" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="I10" s="17" t="n">
         <v>8000</v>
@@ -1219,7 +1219,7 @@
         <v>80</v>
       </c>
       <c r="L10" s="14" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M10" s="14" t="n">
         <v>54291</v>
@@ -1251,10 +1251,10 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I11" s="13" t="n">
         <v>9000</v>
@@ -1266,7 +1266,7 @@
         <v>80</v>
       </c>
       <c r="L11" t="n">
-        <v>5.3</v>
+        <v>14</v>
       </c>
       <c r="M11" t="n">
         <v>16109</v>
@@ -1298,10 +1298,10 @@
         </is>
       </c>
       <c r="G12" s="14" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="H12" s="16" t="n">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="I12" s="17" t="n">
         <v>8000</v>
@@ -1313,7 +1313,7 @@
         <v>90</v>
       </c>
       <c r="L12" s="14" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M12" s="14" t="n">
         <v>39680</v>
@@ -1345,10 +1345,10 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="I13" s="13" t="n">
         <v>8000</v>
@@ -1360,7 +1360,7 @@
         <v>90</v>
       </c>
       <c r="L13" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M13" t="n">
         <v>53735</v>
@@ -1407,7 +1407,7 @@
         <v>90</v>
       </c>
       <c r="L14" s="14" t="n">
-        <v>4.1</v>
+        <v>10.9</v>
       </c>
       <c r="M14" s="14" t="n">
         <v>109</v>
@@ -1454,7 +1454,7 @@
         <v>90</v>
       </c>
       <c r="L15" t="n">
-        <v>17.6</v>
+        <v>58.5</v>
       </c>
       <c r="M15" t="n">
         <v>43621</v>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="G16" s="14" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H16" s="16" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I16" s="17" t="n">
         <v>8000</v>
@@ -1501,7 +1501,7 @@
         <v>50</v>
       </c>
       <c r="L16" s="14" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M16" s="14" t="n">
         <v>16750</v>
@@ -1533,10 +1533,10 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>200000</v>
+        <v>250000</v>
       </c>
       <c r="I17" s="13" t="n">
         <v>40000</v>
@@ -1548,7 +1548,7 @@
         <v>90</v>
       </c>
       <c r="L17" t="n">
-        <v>23.4</v>
+        <v>62.4</v>
       </c>
       <c r="M17" t="n">
         <v>12326</v>
@@ -1580,10 +1580,10 @@
         </is>
       </c>
       <c r="G18" s="14" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="H18" s="16" t="n">
-        <v>200000</v>
+        <v>250000</v>
       </c>
       <c r="I18" s="17" t="n">
         <v>18000</v>
@@ -1595,7 +1595,7 @@
         <v>80</v>
       </c>
       <c r="L18" s="14" t="n">
-        <v>10.5</v>
+        <v>35.1</v>
       </c>
       <c r="M18" s="14" t="n">
         <v>52844</v>
@@ -1627,10 +1627,10 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="I19" s="13" t="n">
         <v>8000</v>
@@ -1642,7 +1642,7 @@
         <v>110</v>
       </c>
       <c r="L19" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M19" t="n">
         <v>52803</v>
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="G20" s="14" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="H20" s="16" t="n">
-        <v>200000</v>
+        <v>250000</v>
       </c>
       <c r="I20" s="17" t="n">
         <v>13000</v>
@@ -1689,7 +1689,7 @@
         <v>110</v>
       </c>
       <c r="L20" s="14" t="n">
-        <v>7.6</v>
+        <v>25.4</v>
       </c>
       <c r="M20" s="14" t="n">
         <v>52692</v>
@@ -1721,10 +1721,10 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I21" s="13" t="n">
         <v>8000</v>
@@ -1736,7 +1736,7 @@
         <v>90</v>
       </c>
       <c r="L21" t="n">
-        <v>4.7</v>
+        <v>12.5</v>
       </c>
       <c r="M21" t="n">
         <v>12418</v>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="G22" s="14" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H22" s="16" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="I22" s="17" t="n">
         <v>8000</v>
@@ -1783,7 +1783,7 @@
         <v>90</v>
       </c>
       <c r="L22" s="14" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M22" s="14" t="n">
         <v>52565</v>
@@ -1815,10 +1815,10 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="I23" s="13" t="n">
         <v>8000</v>
@@ -1830,7 +1830,7 @@
         <v>100</v>
       </c>
       <c r="L23" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M23" t="n">
         <v>52549</v>
@@ -1877,7 +1877,7 @@
         <v>110</v>
       </c>
       <c r="L24" s="14" t="n">
-        <v>23.4</v>
+        <v>78</v>
       </c>
       <c r="M24" s="14" t="n">
         <v>34958</v>
@@ -1909,10 +1909,10 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I25" s="13" t="n">
         <v>8000</v>
@@ -1924,7 +1924,7 @@
         <v>80</v>
       </c>
       <c r="L25" t="n">
-        <v>4.7</v>
+        <v>12.5</v>
       </c>
       <c r="M25" t="n">
         <v>9746</v>
@@ -1956,10 +1956,10 @@
         </is>
       </c>
       <c r="G26" s="14" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H26" s="16" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I26" s="17" t="n">
         <v>8000</v>
@@ -1971,7 +1971,7 @@
         <v>80</v>
       </c>
       <c r="L26" s="14" t="n">
-        <v>4.7</v>
+        <v>12.5</v>
       </c>
       <c r="M26" s="14" t="n">
         <v>109</v>
@@ -2003,10 +2003,10 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="I27" s="13" t="n">
         <v>8000</v>
@@ -2018,7 +2018,7 @@
         <v>90</v>
       </c>
       <c r="L27" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M27" t="n">
         <v>41140</v>
@@ -2050,10 +2050,10 @@
         </is>
       </c>
       <c r="G28" s="14" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="H28" s="16" t="n">
-        <v>200000</v>
+        <v>250000</v>
       </c>
       <c r="I28" s="17" t="n">
         <v>40000</v>
@@ -2065,7 +2065,7 @@
         <v>90</v>
       </c>
       <c r="L28" s="14" t="n">
-        <v>23.4</v>
+        <v>78</v>
       </c>
       <c r="M28" s="14" t="n">
         <v>18384</v>
@@ -2097,10 +2097,10 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="I29" s="13" t="n">
         <v>8000</v>
@@ -2112,7 +2112,7 @@
         <v>80</v>
       </c>
       <c r="L29" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M29" t="n">
         <v>50975</v>
@@ -2159,7 +2159,7 @@
         <v>110</v>
       </c>
       <c r="L30" s="14" t="n">
-        <v>23.4</v>
+        <v>78</v>
       </c>
       <c r="M30" s="14" t="n">
         <v>39021</v>
@@ -2206,7 +2206,7 @@
         <v>90</v>
       </c>
       <c r="L31" t="n">
-        <v>23.4</v>
+        <v>78</v>
       </c>
       <c r="M31" t="n">
         <v>25358</v>
@@ -2253,7 +2253,7 @@
         <v>80</v>
       </c>
       <c r="L32" s="14" t="n">
-        <v>4.1</v>
+        <v>10.9</v>
       </c>
       <c r="M32" s="14" t="n">
         <v>14851</v>
@@ -2285,10 +2285,10 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="I33" s="13" t="n">
         <v>8000</v>
@@ -2300,7 +2300,7 @@
         <v>80</v>
       </c>
       <c r="L33" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M33" t="n">
         <v>49866</v>
@@ -2332,10 +2332,10 @@
         </is>
       </c>
       <c r="G34" s="14" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H34" s="16" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="I34" s="17" t="n">
         <v>8000</v>
@@ -2347,7 +2347,7 @@
         <v>80</v>
       </c>
       <c r="L34" s="14" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M34" s="14" t="n">
         <v>49846</v>
@@ -2379,10 +2379,10 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I35" s="13" t="n">
         <v>8000</v>
@@ -2394,7 +2394,7 @@
         <v>80</v>
       </c>
       <c r="L35" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M35" t="n">
         <v>15756</v>
@@ -2426,10 +2426,10 @@
         </is>
       </c>
       <c r="G36" s="14" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H36" s="16" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="I36" s="17" t="n">
         <v>30000</v>
@@ -2441,7 +2441,7 @@
         <v>90</v>
       </c>
       <c r="L36" s="14" t="n">
-        <v>17.6</v>
+        <v>46.8</v>
       </c>
       <c r="M36" s="14" t="n">
         <v>15658</v>
@@ -2488,7 +2488,7 @@
         <v>90</v>
       </c>
       <c r="L37" t="n">
-        <v>4.1</v>
+        <v>10.9</v>
       </c>
       <c r="M37" t="inlineStr"/>
     </row>
@@ -2518,10 +2518,10 @@
         </is>
       </c>
       <c r="G38" s="14" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="H38" s="16" t="n">
-        <v>200000</v>
+        <v>250000</v>
       </c>
       <c r="I38" s="17" t="n">
         <v>13000</v>
@@ -2533,7 +2533,7 @@
         <v>90</v>
       </c>
       <c r="L38" s="14" t="n">
-        <v>7.6</v>
+        <v>25.4</v>
       </c>
       <c r="M38" s="14" t="n">
         <v>49398</v>
@@ -2565,10 +2565,10 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>200000</v>
+        <v>250000</v>
       </c>
       <c r="I39" s="13" t="n">
         <v>13000</v>
@@ -2580,7 +2580,7 @@
         <v>50</v>
       </c>
       <c r="L39" t="n">
-        <v>7.6</v>
+        <v>25.3</v>
       </c>
       <c r="M39" t="n">
         <v>49394</v>
@@ -2612,10 +2612,10 @@
         </is>
       </c>
       <c r="G40" s="14" t="n">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="H40" s="16" t="n">
-        <v>100000</v>
+        <v>250000</v>
       </c>
       <c r="I40" s="17" t="n">
         <v>20000</v>
@@ -2627,7 +2627,7 @@
         <v>90</v>
       </c>
       <c r="L40" s="14" t="n">
-        <v>11.7</v>
+        <v>39</v>
       </c>
       <c r="M40" s="14" t="n">
         <v>16845</v>
@@ -2659,10 +2659,10 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="I41" s="13" t="n">
         <v>8000</v>
@@ -2674,7 +2674,7 @@
         <v>100</v>
       </c>
       <c r="L41" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M41" t="n">
         <v>49150</v>
@@ -2706,10 +2706,10 @@
         </is>
       </c>
       <c r="G42" s="14" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H42" s="16" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="I42" s="17" t="n">
         <v>30000</v>
@@ -2721,7 +2721,7 @@
         <v>90</v>
       </c>
       <c r="L42" s="14" t="n">
-        <v>17.6</v>
+        <v>58.5</v>
       </c>
       <c r="M42" s="14" t="n">
         <v>18705</v>
@@ -2753,10 +2753,10 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>200000</v>
+        <v>250000</v>
       </c>
       <c r="I43" s="13" t="n">
         <v>40000</v>
@@ -2768,7 +2768,7 @@
         <v>90</v>
       </c>
       <c r="L43" t="n">
-        <v>23.4</v>
+        <v>62.4</v>
       </c>
       <c r="M43" t="n">
         <v>3157</v>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="G44" s="14" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H44" s="16" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I44" s="17" t="n">
         <v>8000</v>
@@ -2815,7 +2815,7 @@
         <v>80</v>
       </c>
       <c r="L44" s="14" t="n">
-        <v>4.7</v>
+        <v>12.5</v>
       </c>
       <c r="M44" s="14" t="n">
         <v>109</v>
@@ -2847,10 +2847,10 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="I45" s="13" t="n">
         <v>8000</v>
@@ -2862,7 +2862,7 @@
         <v>100</v>
       </c>
       <c r="L45" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M45" t="n">
         <v>48224</v>
@@ -2894,10 +2894,10 @@
         </is>
       </c>
       <c r="G46" s="14" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="H46" s="16" t="n">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="I46" s="17" t="n">
         <v>8000</v>
@@ -2909,7 +2909,7 @@
         <v>110</v>
       </c>
       <c r="L46" s="14" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M46" s="14" t="n">
         <v>31956</v>
@@ -2941,10 +2941,10 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="I47" s="13" t="n">
         <v>8000</v>
@@ -2956,7 +2956,7 @@
         <v>90</v>
       </c>
       <c r="L47" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M47" t="n">
         <v>25000</v>
@@ -2988,10 +2988,10 @@
         </is>
       </c>
       <c r="G48" s="14" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H48" s="16" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="I48" s="17" t="n">
         <v>8000</v>
@@ -3003,7 +3003,7 @@
         <v>100</v>
       </c>
       <c r="L48" s="14" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M48" s="14" t="n">
         <v>47623</v>
@@ -3035,10 +3035,10 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H49" s="6" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I49" s="13" t="n">
         <v>8000</v>
@@ -3050,7 +3050,7 @@
         <v>90</v>
       </c>
       <c r="L49" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M49" t="n">
         <v>11993</v>
@@ -3082,10 +3082,10 @@
         </is>
       </c>
       <c r="G50" s="14" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H50" s="16" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I50" s="17" t="n">
         <v>9000</v>
@@ -3097,7 +3097,7 @@
         <v>50</v>
       </c>
       <c r="L50" s="14" t="n">
-        <v>5.3</v>
+        <v>14</v>
       </c>
       <c r="M50" s="14" t="n">
         <v>9934</v>
@@ -3144,7 +3144,7 @@
         <v>80</v>
       </c>
       <c r="L51" t="n">
-        <v>4.1</v>
+        <v>10.9</v>
       </c>
       <c r="M51" t="n">
         <v>620</v>
@@ -3176,10 +3176,10 @@
         </is>
       </c>
       <c r="G52" s="14" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H52" s="16" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I52" s="17" t="n">
         <v>8500</v>
@@ -3191,7 +3191,7 @@
         <v>90</v>
       </c>
       <c r="L52" s="14" t="n">
-        <v>5</v>
+        <v>13.3</v>
       </c>
       <c r="M52" s="14" t="n">
         <v>1082</v>
@@ -3223,10 +3223,10 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H53" s="6" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I53" s="13" t="n">
         <v>9000</v>
@@ -3238,7 +3238,7 @@
         <v>90</v>
       </c>
       <c r="L53" t="n">
-        <v>5.3</v>
+        <v>14</v>
       </c>
       <c r="M53" t="n">
         <v>7954</v>
@@ -3270,10 +3270,10 @@
         </is>
       </c>
       <c r="G54" s="14" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="H54" s="16" t="n">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="I54" s="17" t="n">
         <v>15000</v>
@@ -3285,7 +3285,7 @@
         <v>90</v>
       </c>
       <c r="L54" s="14" t="n">
-        <v>8.800000000000001</v>
+        <v>29.2</v>
       </c>
       <c r="M54" s="14" t="n">
         <v>15064</v>
@@ -3317,10 +3317,10 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="H55" s="6" t="n">
-        <v>100000</v>
+        <v>250000</v>
       </c>
       <c r="I55" s="13" t="n">
         <v>20000</v>
@@ -3332,7 +3332,7 @@
         <v>90</v>
       </c>
       <c r="L55" t="n">
-        <v>11.7</v>
+        <v>39</v>
       </c>
       <c r="M55" t="n">
         <v>16799</v>
@@ -3364,10 +3364,10 @@
         </is>
       </c>
       <c r="G56" s="14" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="H56" s="16" t="n">
-        <v>200000</v>
+        <v>250000</v>
       </c>
       <c r="I56" s="17" t="n">
         <v>18000</v>
@@ -3379,7 +3379,7 @@
         <v>90</v>
       </c>
       <c r="L56" s="14" t="n">
-        <v>10.5</v>
+        <v>35.1</v>
       </c>
       <c r="M56" s="14" t="n">
         <v>45642</v>
@@ -3411,10 +3411,10 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H57" s="6" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I57" s="13" t="n">
         <v>8500</v>
@@ -3426,7 +3426,7 @@
         <v>90</v>
       </c>
       <c r="L57" t="n">
-        <v>5</v>
+        <v>13.3</v>
       </c>
       <c r="M57" t="n">
         <v>620</v>
@@ -3458,10 +3458,10 @@
         </is>
       </c>
       <c r="G58" s="14" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H58" s="16" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I58" s="17" t="n">
         <v>8000</v>
@@ -3473,7 +3473,7 @@
         <v>80</v>
       </c>
       <c r="L58" s="14" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M58" s="14" t="n">
         <v>12417</v>
@@ -3505,10 +3505,10 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H59" s="6" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I59" s="13" t="n">
         <v>8000</v>
@@ -3520,7 +3520,7 @@
         <v>80</v>
       </c>
       <c r="L59" t="n">
-        <v>4.7</v>
+        <v>12.5</v>
       </c>
       <c r="M59" t="inlineStr"/>
     </row>
@@ -3565,7 +3565,7 @@
         <v>80</v>
       </c>
       <c r="L60" s="14" t="n">
-        <v>4.1</v>
+        <v>10.9</v>
       </c>
       <c r="M60" s="14" t="n">
         <v>1562</v>
@@ -3597,10 +3597,10 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H61" s="6" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="I61" s="13" t="n">
         <v>8000</v>
@@ -3612,7 +3612,7 @@
         <v>100</v>
       </c>
       <c r="L61" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M61" t="n">
         <v>41374</v>
@@ -3644,10 +3644,10 @@
         </is>
       </c>
       <c r="G62" s="14" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H62" s="16" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I62" s="17" t="n">
         <v>9000</v>
@@ -3659,7 +3659,7 @@
         <v>60</v>
       </c>
       <c r="L62" s="14" t="n">
-        <v>5.3</v>
+        <v>14</v>
       </c>
       <c r="M62" s="14" t="n">
         <v>8054</v>
@@ -3706,7 +3706,7 @@
         <v>80</v>
       </c>
       <c r="L63" t="n">
-        <v>2</v>
+        <v>5.5</v>
       </c>
       <c r="M63" t="n">
         <v>6933</v>
@@ -3753,7 +3753,7 @@
         <v>90</v>
       </c>
       <c r="L64" s="14" t="n">
-        <v>4.1</v>
+        <v>10.9</v>
       </c>
       <c r="M64" s="14" t="n">
         <v>211</v>
@@ -3785,10 +3785,10 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H65" s="6" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I65" s="13" t="n">
         <v>11000</v>
@@ -3800,7 +3800,7 @@
         <v>90</v>
       </c>
       <c r="L65" t="n">
-        <v>6.4</v>
+        <v>17.2</v>
       </c>
       <c r="M65" t="n">
         <v>6017</v>
@@ -3847,7 +3847,7 @@
         <v>80</v>
       </c>
       <c r="L66" s="14" t="n">
-        <v>4.1</v>
+        <v>10.9</v>
       </c>
       <c r="M66" s="14" t="inlineStr"/>
     </row>
@@ -3877,10 +3877,10 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H67" s="6" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I67" s="13" t="n">
         <v>8000</v>
@@ -3892,7 +3892,7 @@
         <v>60</v>
       </c>
       <c r="L67" t="n">
-        <v>4.7</v>
+        <v>12.5</v>
       </c>
       <c r="M67" t="n">
         <v>7109</v>
@@ -3924,10 +3924,10 @@
         </is>
       </c>
       <c r="G68" s="14" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H68" s="16" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I68" s="17" t="n">
         <v>8000</v>
@@ -3939,7 +3939,7 @@
         <v>80</v>
       </c>
       <c r="L68" s="14" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M68" s="14" t="n">
         <v>13536</v>
@@ -3971,10 +3971,10 @@
         </is>
       </c>
       <c r="G69" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H69" s="6" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I69" s="13" t="n">
         <v>8000</v>
@@ -3986,7 +3986,7 @@
         <v>80</v>
       </c>
       <c r="L69" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M69" t="n">
         <v>13370</v>
@@ -4033,7 +4033,7 @@
         <v>90</v>
       </c>
       <c r="L70" s="14" t="n">
-        <v>17.6</v>
+        <v>58.5</v>
       </c>
       <c r="M70" s="14" t="n">
         <v>40881</v>
@@ -4065,10 +4065,10 @@
         </is>
       </c>
       <c r="G71" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H71" s="6" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="I71" s="13" t="n">
         <v>8000</v>
@@ -4080,7 +4080,7 @@
         <v>80</v>
       </c>
       <c r="L71" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M71" t="n">
         <v>41453</v>
@@ -4112,10 +4112,10 @@
         </is>
       </c>
       <c r="G72" s="14" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H72" s="16" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I72" s="17" t="n">
         <v>8000</v>
@@ -4127,7 +4127,7 @@
         <v>80</v>
       </c>
       <c r="L72" s="14" t="n">
-        <v>4.7</v>
+        <v>12.5</v>
       </c>
       <c r="M72" s="14" t="inlineStr"/>
     </row>
@@ -4172,7 +4172,7 @@
         <v>100</v>
       </c>
       <c r="L73" t="n">
-        <v>23.4</v>
+        <v>78</v>
       </c>
       <c r="M73" t="n">
         <v>41043</v>
@@ -4204,10 +4204,10 @@
         </is>
       </c>
       <c r="G74" s="14" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="H74" s="16" t="n">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="I74" s="17" t="n">
         <v>8000</v>
@@ -4219,7 +4219,7 @@
         <v>80</v>
       </c>
       <c r="L74" s="14" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M74" s="14" t="n">
         <v>28403</v>
@@ -4266,7 +4266,7 @@
         <v>80</v>
       </c>
       <c r="L75" t="n">
-        <v>2.3</v>
+        <v>7.8</v>
       </c>
       <c r="M75" t="n">
         <v>13342</v>
@@ -4298,10 +4298,10 @@
         </is>
       </c>
       <c r="G76" s="14" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H76" s="16" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I76" s="17" t="n">
         <v>9000</v>
@@ -4313,7 +4313,7 @@
         <v>90</v>
       </c>
       <c r="L76" s="14" t="n">
-        <v>5.3</v>
+        <v>17.6</v>
       </c>
       <c r="M76" s="14" t="n">
         <v>6850</v>
@@ -4345,10 +4345,10 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H77" s="6" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I77" s="13" t="n">
         <v>8000</v>
@@ -4360,7 +4360,7 @@
         <v>80</v>
       </c>
       <c r="L77" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M77" t="n">
         <v>5993</v>
@@ -4392,10 +4392,10 @@
         </is>
       </c>
       <c r="G78" s="14" t="n">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="H78" s="16" t="n">
-        <v>100000</v>
+        <v>250000</v>
       </c>
       <c r="I78" s="17" t="n">
         <v>18000</v>
@@ -4407,7 +4407,7 @@
         <v>90</v>
       </c>
       <c r="L78" s="14" t="n">
-        <v>10.5</v>
+        <v>35.1</v>
       </c>
       <c r="M78" s="14" t="n">
         <v>13505</v>
@@ -4439,10 +4439,10 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="H79" s="6" t="n">
-        <v>100000</v>
+        <v>250000</v>
       </c>
       <c r="I79" s="13" t="n">
         <v>20000</v>
@@ -4454,7 +4454,7 @@
         <v>90</v>
       </c>
       <c r="L79" t="n">
-        <v>11.7</v>
+        <v>39</v>
       </c>
       <c r="M79" t="n">
         <v>14475</v>
@@ -4486,10 +4486,10 @@
         </is>
       </c>
       <c r="G80" s="14" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H80" s="16" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I80" s="17" t="n">
         <v>8000</v>
@@ -4501,7 +4501,7 @@
         <v>80</v>
       </c>
       <c r="L80" s="14" t="n">
-        <v>4.7</v>
+        <v>12.5</v>
       </c>
       <c r="M80" s="14" t="n">
         <v>2730</v>
@@ -4533,10 +4533,10 @@
         </is>
       </c>
       <c r="G81" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="H81" s="6" t="n">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="I81" s="13" t="n">
         <v>8000</v>
@@ -4548,7 +4548,7 @@
         <v>70</v>
       </c>
       <c r="L81" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M81" t="n">
         <v>34515</v>
@@ -4580,10 +4580,10 @@
         </is>
       </c>
       <c r="G82" s="14" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="H82" s="16" t="n">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="I82" s="17" t="n">
         <v>8000</v>
@@ -4595,7 +4595,7 @@
         <v>90</v>
       </c>
       <c r="L82" s="14" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M82" s="14" t="n">
         <v>38631</v>
@@ -4627,10 +4627,10 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H83" s="6" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I83" s="13" t="n">
         <v>8000</v>
@@ -4642,7 +4642,7 @@
         <v>80</v>
       </c>
       <c r="L83" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M83" t="n">
         <v>11270</v>
@@ -4674,10 +4674,10 @@
         </is>
       </c>
       <c r="G84" s="14" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H84" s="16" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="I84" s="17" t="n">
         <v>18000</v>
@@ -4689,7 +4689,7 @@
         <v>70</v>
       </c>
       <c r="L84" s="14" t="n">
-        <v>10.5</v>
+        <v>35.1</v>
       </c>
       <c r="M84" s="14" t="n">
         <v>38052</v>
@@ -4736,7 +4736,7 @@
         <v>90</v>
       </c>
       <c r="L85" t="n">
-        <v>4.1</v>
+        <v>10.9</v>
       </c>
       <c r="M85" t="inlineStr"/>
     </row>
@@ -4766,10 +4766,10 @@
         </is>
       </c>
       <c r="G86" s="14" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="H86" s="16" t="n">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="I86" s="17" t="n">
         <v>8000</v>
@@ -4781,7 +4781,7 @@
         <v>80</v>
       </c>
       <c r="L86" s="14" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M86" s="14" t="n">
         <v>37587</v>
@@ -4813,10 +4813,10 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H87" s="6" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I87" s="13" t="n">
         <v>8000</v>
@@ -4828,7 +4828,7 @@
         <v>60</v>
       </c>
       <c r="L87" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M87" t="n">
         <v>7595</v>
@@ -4875,7 +4875,7 @@
         <v>80</v>
       </c>
       <c r="L88" s="14" t="n">
-        <v>2.3</v>
+        <v>7.8</v>
       </c>
       <c r="M88" s="14" t="n">
         <v>12660</v>
@@ -4907,10 +4907,10 @@
         </is>
       </c>
       <c r="G89" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H89" s="6" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I89" s="13" t="n">
         <v>11000</v>
@@ -4922,7 +4922,7 @@
         <v>90</v>
       </c>
       <c r="L89" t="n">
-        <v>6.4</v>
+        <v>17.2</v>
       </c>
       <c r="M89" t="n">
         <v>6284</v>
@@ -4954,10 +4954,10 @@
         </is>
       </c>
       <c r="G90" s="14" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H90" s="16" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="I90" s="17" t="n">
         <v>22000</v>
@@ -4969,7 +4969,7 @@
         <v>90</v>
       </c>
       <c r="L90" s="14" t="n">
-        <v>12.9</v>
+        <v>42.9</v>
       </c>
       <c r="M90" s="14" t="n">
         <v>10448</v>
@@ -5001,10 +5001,10 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H91" s="6" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I91" s="13" t="n">
         <v>8000</v>
@@ -5016,7 +5016,7 @@
         <v>80</v>
       </c>
       <c r="L91" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M91" t="n">
         <v>13745</v>
@@ -5048,10 +5048,10 @@
         </is>
       </c>
       <c r="G92" s="14" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H92" s="16" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I92" s="17" t="n">
         <v>8000</v>
@@ -5063,7 +5063,7 @@
         <v>80</v>
       </c>
       <c r="L92" s="14" t="n">
-        <v>4.7</v>
+        <v>12.5</v>
       </c>
       <c r="M92" s="14" t="n">
         <v>827</v>
@@ -5095,10 +5095,10 @@
         </is>
       </c>
       <c r="G93" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H93" s="6" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="I93" s="13" t="n">
         <v>13000</v>
@@ -5110,7 +5110,7 @@
         <v>90</v>
       </c>
       <c r="L93" t="n">
-        <v>7.6</v>
+        <v>25.4</v>
       </c>
       <c r="M93" t="n">
         <v>35641</v>
@@ -5142,10 +5142,10 @@
         </is>
       </c>
       <c r="G94" s="14" t="n">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="H94" s="16" t="n">
-        <v>100000</v>
+        <v>250000</v>
       </c>
       <c r="I94" s="17" t="n">
         <v>18000</v>
@@ -5157,7 +5157,7 @@
         <v>90</v>
       </c>
       <c r="L94" s="14" t="n">
-        <v>10.5</v>
+        <v>35.1</v>
       </c>
       <c r="M94" s="14" t="n">
         <v>10161</v>
@@ -5189,10 +5189,10 @@
         </is>
       </c>
       <c r="G95" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H95" s="6" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I95" s="13" t="n">
         <v>8000</v>
@@ -5204,7 +5204,7 @@
         <v>80</v>
       </c>
       <c r="L95" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M95" t="n">
         <v>11097</v>
@@ -5251,7 +5251,7 @@
         <v>80</v>
       </c>
       <c r="L96" s="14" t="n">
-        <v>2.3</v>
+        <v>7.8</v>
       </c>
       <c r="M96" s="14" t="n">
         <v>12248</v>
@@ -5283,10 +5283,10 @@
         </is>
       </c>
       <c r="G97" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H97" s="6" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I97" s="13" t="n">
         <v>8000</v>
@@ -5298,7 +5298,7 @@
         <v>110</v>
       </c>
       <c r="L97" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M97" t="n">
         <v>13052</v>
@@ -5330,10 +5330,10 @@
         </is>
       </c>
       <c r="G98" s="14" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H98" s="16" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I98" s="17" t="n">
         <v>9000</v>
@@ -5345,7 +5345,7 @@
         <v>90</v>
       </c>
       <c r="L98" s="14" t="n">
-        <v>5.3</v>
+        <v>17.6</v>
       </c>
       <c r="M98" s="14" t="n">
         <v>5165</v>
@@ -5377,10 +5377,10 @@
         </is>
       </c>
       <c r="G99" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H99" s="6" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I99" s="13" t="n">
         <v>8000</v>
@@ -5392,7 +5392,7 @@
         <v>80</v>
       </c>
       <c r="L99" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M99" t="n">
         <v>10887</v>
@@ -5424,10 +5424,10 @@
         </is>
       </c>
       <c r="G100" s="14" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H100" s="16" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I100" s="17" t="n">
         <v>8000</v>
@@ -5439,7 +5439,7 @@
         <v>90</v>
       </c>
       <c r="L100" s="14" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M100" s="14" t="n">
         <v>789</v>
@@ -5471,10 +5471,10 @@
         </is>
       </c>
       <c r="G101" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="H101" s="6" t="n">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="I101" s="13" t="n">
         <v>13000</v>
@@ -5486,7 +5486,7 @@
         <v>80</v>
       </c>
       <c r="L101" t="n">
-        <v>7.6</v>
+        <v>25.4</v>
       </c>
       <c r="M101" t="n">
         <v>10828</v>
@@ -5518,10 +5518,10 @@
         </is>
       </c>
       <c r="G102" s="14" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H102" s="16" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="I102" s="17" t="n">
         <v>14000</v>
@@ -5533,7 +5533,7 @@
         <v>90</v>
       </c>
       <c r="L102" s="14" t="n">
-        <v>8.199999999999999</v>
+        <v>27.3</v>
       </c>
       <c r="M102" s="14" t="n">
         <v>32451</v>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="G103" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H103" s="6" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I103" s="13" t="n">
         <v>8000</v>
@@ -5580,7 +5580,7 @@
         <v>100</v>
       </c>
       <c r="L103" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M103" t="n">
         <v>11380</v>
@@ -5612,10 +5612,10 @@
         </is>
       </c>
       <c r="G104" s="14" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H104" s="16" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I104" s="17" t="n">
         <v>8000</v>
@@ -5627,7 +5627,7 @@
         <v>80</v>
       </c>
       <c r="L104" s="14" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M104" s="14" t="n">
         <v>8325</v>
@@ -5659,10 +5659,10 @@
         </is>
       </c>
       <c r="G105" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H105" s="6" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I105" s="13" t="n">
         <v>8000</v>
@@ -5674,7 +5674,7 @@
         <v>90</v>
       </c>
       <c r="L105" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M105" t="inlineStr"/>
     </row>
@@ -5704,10 +5704,10 @@
         </is>
       </c>
       <c r="G106" s="14" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H106" s="16" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="I106" s="17" t="n">
         <v>22000</v>
@@ -5719,7 +5719,7 @@
         <v>50</v>
       </c>
       <c r="L106" s="14" t="n">
-        <v>12.9</v>
+        <v>42.9</v>
       </c>
       <c r="M106" s="14" t="n">
         <v>3183</v>
@@ -5751,10 +5751,10 @@
         </is>
       </c>
       <c r="G107" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H107" s="6" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I107" s="13" t="n">
         <v>9000</v>
@@ -5766,7 +5766,7 @@
         <v>90</v>
       </c>
       <c r="L107" t="n">
-        <v>5.3</v>
+        <v>17.6</v>
       </c>
       <c r="M107" t="n">
         <v>4889</v>
@@ -5798,10 +5798,10 @@
         </is>
       </c>
       <c r="G108" s="14" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="H108" s="16" t="n">
-        <v>200000</v>
+        <v>250000</v>
       </c>
       <c r="I108" s="17" t="n">
         <v>35000</v>
@@ -5813,7 +5813,7 @@
         <v>90</v>
       </c>
       <c r="L108" s="14" t="n">
-        <v>20.5</v>
+        <v>68.2</v>
       </c>
       <c r="M108" s="14" t="n">
         <v>8806</v>
@@ -5845,10 +5845,10 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H109" s="6" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I109" s="13" t="n">
         <v>8000</v>
@@ -5860,7 +5860,7 @@
         <v>80</v>
       </c>
       <c r="L109" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M109" t="inlineStr"/>
     </row>
@@ -5905,7 +5905,7 @@
         <v>60</v>
       </c>
       <c r="L110" s="14" t="n">
-        <v>2.3</v>
+        <v>7.8</v>
       </c>
       <c r="M110" s="14" t="n">
         <v>273</v>
@@ -5937,10 +5937,10 @@
         </is>
       </c>
       <c r="G111" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H111" s="6" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I111" s="13" t="n">
         <v>8000</v>
@@ -5952,7 +5952,7 @@
         <v>80</v>
       </c>
       <c r="L111" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M111" t="n">
         <v>9612</v>
@@ -5984,10 +5984,10 @@
         </is>
       </c>
       <c r="G112" s="14" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="H112" s="16" t="n">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="I112" s="17" t="n">
         <v>11000</v>
@@ -5999,7 +5999,7 @@
         <v>90</v>
       </c>
       <c r="L112" s="14" t="n">
-        <v>6.4</v>
+        <v>21.4</v>
       </c>
       <c r="M112" s="14" t="n">
         <v>3110</v>
@@ -6031,10 +6031,10 @@
         </is>
       </c>
       <c r="G113" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H113" s="6" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="I113" s="13" t="n">
         <v>13000</v>
@@ -6046,7 +6046,7 @@
         <v>90</v>
       </c>
       <c r="L113" t="n">
-        <v>7.6</v>
+        <v>25.4</v>
       </c>
       <c r="M113" t="n">
         <v>29500</v>
@@ -6078,10 +6078,10 @@
         </is>
       </c>
       <c r="G114" s="14" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="H114" s="16" t="n">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="I114" s="17" t="n">
         <v>8000</v>
@@ -6093,7 +6093,7 @@
         <v>80</v>
       </c>
       <c r="L114" s="14" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M114" s="14" t="n">
         <v>28965</v>
@@ -6125,10 +6125,10 @@
         </is>
       </c>
       <c r="G115" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H115" s="6" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I115" s="13" t="n">
         <v>8000</v>
@@ -6140,7 +6140,7 @@
         <v>70</v>
       </c>
       <c r="L115" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M115" t="n">
         <v>4723</v>
@@ -6172,10 +6172,10 @@
         </is>
       </c>
       <c r="G116" s="14" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H116" s="16" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I116" s="17" t="n">
         <v>8000</v>
@@ -6187,7 +6187,7 @@
         <v>80</v>
       </c>
       <c r="L116" s="14" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M116" s="14" t="n">
         <v>10861</v>
@@ -6219,10 +6219,10 @@
         </is>
       </c>
       <c r="G117" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H117" s="6" t="n">
-        <v>73000</v>
+        <v>100000</v>
       </c>
       <c r="I117" s="13" t="n">
         <v>4000</v>
@@ -6234,7 +6234,7 @@
         <v>80</v>
       </c>
       <c r="L117" t="n">
-        <v>2.3</v>
+        <v>7.8</v>
       </c>
       <c r="M117" t="n">
         <v>8227</v>
@@ -6266,10 +6266,10 @@
         </is>
       </c>
       <c r="G118" s="14" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="H118" s="16" t="n">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="I118" s="17" t="n">
         <v>8000</v>
@@ -6281,7 +6281,7 @@
         <v>80</v>
       </c>
       <c r="L118" s="14" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M118" s="14" t="n">
         <v>28110</v>
@@ -6313,10 +6313,10 @@
         </is>
       </c>
       <c r="G119" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H119" s="6" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I119" s="13" t="n">
         <v>9000</v>
@@ -6328,7 +6328,7 @@
         <v>90</v>
       </c>
       <c r="L119" t="n">
-        <v>5.3</v>
+        <v>17.6</v>
       </c>
       <c r="M119" t="n">
         <v>4889</v>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="G120" s="14" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H120" s="16" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I120" s="17" t="n">
         <v>8000</v>
@@ -6375,7 +6375,7 @@
         <v>90</v>
       </c>
       <c r="L120" s="14" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M120" s="14" t="n">
         <v>273</v>
@@ -6407,10 +6407,10 @@
         </is>
       </c>
       <c r="G121" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H121" s="6" t="n">
-        <v>73000</v>
+        <v>100000</v>
       </c>
       <c r="I121" s="13" t="n">
         <v>4000</v>
@@ -6422,7 +6422,7 @@
         <v>80</v>
       </c>
       <c r="L121" t="n">
-        <v>2.3</v>
+        <v>7.8</v>
       </c>
       <c r="M121" t="n">
         <v>7107</v>
@@ -6454,10 +6454,10 @@
         </is>
       </c>
       <c r="G122" s="14" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H122" s="16" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I122" s="17" t="n">
         <v>7000</v>
@@ -6469,7 +6469,7 @@
         <v>90</v>
       </c>
       <c r="L122" s="14" t="n">
-        <v>4.1</v>
+        <v>13.7</v>
       </c>
       <c r="M122" s="14" t="n">
         <v>789</v>
@@ -6501,10 +6501,10 @@
         </is>
       </c>
       <c r="G123" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H123" s="6" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I123" s="13" t="n">
         <v>8000</v>
@@ -6516,7 +6516,7 @@
         <v>110</v>
       </c>
       <c r="L123" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M123" t="n">
         <v>1591</v>
@@ -6548,10 +6548,10 @@
         </is>
       </c>
       <c r="G124" s="14" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="H124" s="16" t="n">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="I124" s="17" t="n">
         <v>8000</v>
@@ -6563,7 +6563,7 @@
         <v>80</v>
       </c>
       <c r="L124" s="14" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M124" s="14" t="n">
         <v>26858</v>
@@ -6595,10 +6595,10 @@
         </is>
       </c>
       <c r="G125" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H125" s="6" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I125" s="13" t="n">
         <v>9000</v>
@@ -6610,7 +6610,7 @@
         <v>90</v>
       </c>
       <c r="L125" t="n">
-        <v>5.3</v>
+        <v>17.6</v>
       </c>
       <c r="M125" t="n">
         <v>4665</v>
@@ -6642,10 +6642,10 @@
         </is>
       </c>
       <c r="G126" s="14" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H126" s="16" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I126" s="17" t="n">
         <v>8000</v>
@@ -6657,7 +6657,7 @@
         <v>110</v>
       </c>
       <c r="L126" s="14" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M126" s="14" t="n">
         <v>1839</v>
@@ -6689,10 +6689,10 @@
         </is>
       </c>
       <c r="G127" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H127" s="6" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I127" s="13" t="n">
         <v>8000</v>
@@ -6704,7 +6704,7 @@
         <v>110</v>
       </c>
       <c r="L127" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M127" t="n">
         <v>273</v>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="G128" s="14" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H128" s="16" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I128" s="17" t="n">
         <v>8000</v>
@@ -6751,7 +6751,7 @@
         <v>100</v>
       </c>
       <c r="L128" s="14" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M128" s="14" t="n">
         <v>9128</v>
@@ -6798,7 +6798,7 @@
         <v>90</v>
       </c>
       <c r="L129" t="n">
-        <v>2.3</v>
+        <v>7.8</v>
       </c>
       <c r="M129" t="n">
         <v>1062</v>
@@ -6830,10 +6830,10 @@
         </is>
       </c>
       <c r="G130" s="14" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H130" s="16" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I130" s="17" t="n">
         <v>8000</v>
@@ -6845,7 +6845,7 @@
         <v>80</v>
       </c>
       <c r="L130" s="14" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M130" s="14" t="n">
         <v>5902</v>
@@ -6877,10 +6877,10 @@
         </is>
       </c>
       <c r="G131" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H131" s="6" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I131" s="13" t="n">
         <v>8000</v>
@@ -6892,7 +6892,7 @@
         <v>80</v>
       </c>
       <c r="L131" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M131" t="n">
         <v>524</v>
@@ -6924,10 +6924,10 @@
         </is>
       </c>
       <c r="G132" s="14" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H132" s="16" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I132" s="17" t="n">
         <v>8000</v>
@@ -6939,7 +6939,7 @@
         <v>110</v>
       </c>
       <c r="L132" s="14" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M132" s="14" t="n">
         <v>2062</v>
@@ -6971,10 +6971,10 @@
         </is>
       </c>
       <c r="G133" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H133" s="6" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="I133" s="13" t="n">
         <v>24000</v>
@@ -6986,7 +6986,7 @@
         <v>80</v>
       </c>
       <c r="L133" t="n">
-        <v>14</v>
+        <v>46.8</v>
       </c>
       <c r="M133" t="n">
         <v>4652</v>
@@ -7018,10 +7018,10 @@
         </is>
       </c>
       <c r="G134" s="14" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H134" s="16" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I134" s="17" t="n">
         <v>8000</v>
@@ -7033,7 +7033,7 @@
         <v>80</v>
       </c>
       <c r="L134" s="14" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M134" s="14" t="n">
         <v>5476</v>
@@ -7065,10 +7065,10 @@
         </is>
       </c>
       <c r="G135" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H135" s="6" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="I135" s="13" t="n">
         <v>22000</v>
@@ -7080,7 +7080,7 @@
         <v>90</v>
       </c>
       <c r="L135" t="n">
-        <v>12.9</v>
+        <v>42.9</v>
       </c>
       <c r="M135" t="n">
         <v>1062</v>
@@ -7112,10 +7112,10 @@
         </is>
       </c>
       <c r="G136" s="14" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H136" s="16" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I136" s="17" t="n">
         <v>8000</v>
@@ -7127,7 +7127,7 @@
         <v>70</v>
       </c>
       <c r="L136" s="14" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M136" s="14" t="n">
         <v>789</v>
@@ -7159,10 +7159,10 @@
         </is>
       </c>
       <c r="G137" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H137" s="6" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I137" s="13" t="n">
         <v>8000</v>
@@ -7174,7 +7174,7 @@
         <v>70</v>
       </c>
       <c r="L137" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M137" t="n">
         <v>4303</v>
@@ -7206,10 +7206,10 @@
         </is>
       </c>
       <c r="G138" s="14" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H138" s="16" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I138" s="17" t="n">
         <v>8000</v>
@@ -7221,7 +7221,7 @@
         <v>80</v>
       </c>
       <c r="L138" s="14" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M138" s="14" t="n">
         <v>8545</v>
@@ -7253,10 +7253,10 @@
         </is>
       </c>
       <c r="G139" t="n">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="H139" s="6" t="n">
-        <v>100000</v>
+        <v>250000</v>
       </c>
       <c r="I139" s="13" t="n">
         <v>20000</v>
@@ -7268,7 +7268,7 @@
         <v>90</v>
       </c>
       <c r="L139" t="n">
-        <v>11.7</v>
+        <v>39</v>
       </c>
       <c r="M139" t="n">
         <v>7226</v>
@@ -7300,10 +7300,10 @@
         </is>
       </c>
       <c r="G140" s="14" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="H140" s="16" t="n">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="I140" s="17" t="n">
         <v>8000</v>
@@ -7315,7 +7315,7 @@
         <v>80</v>
       </c>
       <c r="L140" s="14" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M140" s="14" t="n">
         <v>22712</v>
@@ -7347,10 +7347,10 @@
         </is>
       </c>
       <c r="G141" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H141" s="6" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I141" s="13" t="n">
         <v>9000</v>
@@ -7362,7 +7362,7 @@
         <v>90</v>
       </c>
       <c r="L141" t="n">
-        <v>5.3</v>
+        <v>17.6</v>
       </c>
       <c r="M141" t="n">
         <v>3926</v>
@@ -7394,10 +7394,10 @@
         </is>
       </c>
       <c r="G142" s="14" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H142" s="16" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="I142" s="17" t="n">
         <v>18000</v>
@@ -7409,7 +7409,7 @@
         <v>90</v>
       </c>
       <c r="L142" s="14" t="n">
-        <v>10.5</v>
+        <v>35.1</v>
       </c>
       <c r="M142" s="14" t="n">
         <v>21692</v>
@@ -7441,10 +7441,10 @@
         </is>
       </c>
       <c r="G143" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H143" s="6" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I143" s="13" t="n">
         <v>8000</v>
@@ -7456,7 +7456,7 @@
         <v>80</v>
       </c>
       <c r="L143" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M143" t="n">
         <v>10069</v>
@@ -7488,10 +7488,10 @@
         </is>
       </c>
       <c r="G144" s="14" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H144" s="16" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I144" s="17" t="n">
         <v>8000</v>
@@ -7503,7 +7503,7 @@
         <v>80</v>
       </c>
       <c r="L144" s="14" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M144" s="14" t="n">
         <v>5206</v>
@@ -7535,10 +7535,10 @@
         </is>
       </c>
       <c r="G145" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H145" s="6" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I145" s="13" t="n">
         <v>8000</v>
@@ -7550,7 +7550,7 @@
         <v>80</v>
       </c>
       <c r="L145" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M145" t="n">
         <v>6778</v>
@@ -7582,10 +7582,10 @@
         </is>
       </c>
       <c r="G146" s="14" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H146" s="16" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I146" s="17" t="n">
         <v>8000</v>
@@ -7597,7 +7597,7 @@
         <v>110</v>
       </c>
       <c r="L146" s="14" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M146" s="14" t="n">
         <v>1062</v>
@@ -7629,10 +7629,10 @@
         </is>
       </c>
       <c r="G147" t="n">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="H147" s="6" t="n">
-        <v>100000</v>
+        <v>250000</v>
       </c>
       <c r="I147" s="13" t="n">
         <v>19000</v>
@@ -7644,7 +7644,7 @@
         <v>100</v>
       </c>
       <c r="L147" t="n">
-        <v>11.1</v>
+        <v>37</v>
       </c>
       <c r="M147" t="n">
         <v>7336</v>
@@ -7676,10 +7676,10 @@
         </is>
       </c>
       <c r="G148" s="14" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H148" s="16" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="I148" s="17" t="n">
         <v>22000</v>
@@ -7691,7 +7691,7 @@
         <v>100</v>
       </c>
       <c r="L148" s="14" t="n">
-        <v>12.9</v>
+        <v>42.9</v>
       </c>
       <c r="M148" s="14" t="n">
         <v>789</v>
@@ -7723,10 +7723,10 @@
         </is>
       </c>
       <c r="G149" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H149" s="6" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I149" s="13" t="n">
         <v>8000</v>
@@ -7738,7 +7738,7 @@
         <v>90</v>
       </c>
       <c r="L149" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M149" t="n">
         <v>7226</v>
@@ -7770,10 +7770,10 @@
         </is>
       </c>
       <c r="G150" s="14" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H150" s="16" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="I150" s="17" t="n">
         <v>24000</v>
@@ -7785,7 +7785,7 @@
         <v>90</v>
       </c>
       <c r="L150" s="14" t="n">
-        <v>14</v>
+        <v>46.8</v>
       </c>
       <c r="M150" s="14" t="n">
         <v>4044</v>
@@ -7817,10 +7817,10 @@
         </is>
       </c>
       <c r="G151" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H151" s="6" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I151" s="13" t="n">
         <v>8000</v>
@@ -7832,7 +7832,7 @@
         <v>90</v>
       </c>
       <c r="L151" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M151" t="inlineStr"/>
     </row>
@@ -7862,10 +7862,10 @@
         </is>
       </c>
       <c r="G152" s="14" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="H152" s="16" t="n">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="I152" s="17" t="n">
         <v>13000</v>
@@ -7877,7 +7877,7 @@
         <v>90</v>
       </c>
       <c r="L152" s="14" t="n">
-        <v>7.6</v>
+        <v>25.4</v>
       </c>
       <c r="M152" s="14" t="n">
         <v>19378</v>
@@ -7909,10 +7909,10 @@
         </is>
       </c>
       <c r="G153" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H153" s="6" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I153" s="13" t="n">
         <v>8000</v>
@@ -7924,7 +7924,7 @@
         <v>120</v>
       </c>
       <c r="L153" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M153" t="n">
         <v>19020</v>
@@ -7956,10 +7956,10 @@
         </is>
       </c>
       <c r="G154" s="14" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="H154" s="16" t="n">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="I154" s="17" t="n">
         <v>13000</v>
@@ -7971,7 +7971,7 @@
         <v>90</v>
       </c>
       <c r="L154" s="14" t="n">
-        <v>7.6</v>
+        <v>25.4</v>
       </c>
       <c r="M154" s="14" t="n">
         <v>1014</v>
@@ -8003,10 +8003,10 @@
         </is>
       </c>
       <c r="G155" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H155" s="6" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I155" s="13" t="n">
         <v>8000</v>
@@ -8018,7 +8018,7 @@
         <v>80</v>
       </c>
       <c r="L155" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M155" t="n">
         <v>2064</v>
@@ -8050,10 +8050,10 @@
         </is>
       </c>
       <c r="G156" s="14" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H156" s="16" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="I156" s="17" t="n">
         <v>24000</v>
@@ -8065,7 +8065,7 @@
         <v>90</v>
       </c>
       <c r="L156" s="14" t="n">
-        <v>14</v>
+        <v>46.8</v>
       </c>
       <c r="M156" s="14" t="n">
         <v>3872</v>
@@ -8097,10 +8097,10 @@
         </is>
       </c>
       <c r="G157" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H157" s="6" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I157" s="13" t="n">
         <v>8000</v>
@@ -8112,7 +8112,7 @@
         <v>60</v>
       </c>
       <c r="L157" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M157" t="n">
         <v>5880</v>
@@ -8144,10 +8144,10 @@
         </is>
       </c>
       <c r="G158" s="14" t="n">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="H158" s="16" t="n">
-        <v>100000</v>
+        <v>250000</v>
       </c>
       <c r="I158" s="17" t="n">
         <v>18000</v>
@@ -8159,7 +8159,7 @@
         <v>90</v>
       </c>
       <c r="L158" s="14" t="n">
-        <v>10.5</v>
+        <v>35.1</v>
       </c>
       <c r="M158" s="14" t="n">
         <v>6742</v>
@@ -8191,10 +8191,10 @@
         </is>
       </c>
       <c r="G159" t="n">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="H159" s="6" t="n">
-        <v>100000</v>
+        <v>250000</v>
       </c>
       <c r="I159" s="13" t="n">
         <v>19000</v>
@@ -8206,7 +8206,7 @@
         <v>100</v>
       </c>
       <c r="L159" t="n">
-        <v>11.1</v>
+        <v>37</v>
       </c>
       <c r="M159" t="n">
         <v>6486</v>
@@ -8238,10 +8238,10 @@
         </is>
       </c>
       <c r="G160" s="14" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H160" s="16" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I160" s="17" t="n">
         <v>8000</v>
@@ -8253,7 +8253,7 @@
         <v>80</v>
       </c>
       <c r="L160" s="14" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M160" s="14" t="n">
         <v>9768</v>
@@ -8285,10 +8285,10 @@
         </is>
       </c>
       <c r="G161" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H161" s="6" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I161" s="13" t="n">
         <v>8000</v>
@@ -8300,7 +8300,7 @@
         <v>50</v>
       </c>
       <c r="L161" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M161" t="n">
         <v>17117</v>
@@ -8347,7 +8347,7 @@
         <v>80</v>
       </c>
       <c r="L162" s="14" t="n">
-        <v>2.3</v>
+        <v>7.8</v>
       </c>
       <c r="M162" s="14" t="n">
         <v>16937</v>
@@ -8379,10 +8379,10 @@
         </is>
       </c>
       <c r="G163" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H163" s="6" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I163" s="13" t="n">
         <v>8000</v>
@@ -8394,7 +8394,7 @@
         <v>90</v>
       </c>
       <c r="L163" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M163" t="n">
         <v>6095</v>
@@ -8426,10 +8426,10 @@
         </is>
       </c>
       <c r="G164" s="14" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="H164" s="16" t="n">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="I164" s="17" t="n">
         <v>11000</v>
@@ -8441,7 +8441,7 @@
         <v>90</v>
       </c>
       <c r="L164" s="14" t="n">
-        <v>6.4</v>
+        <v>21.4</v>
       </c>
       <c r="M164" s="14" t="n">
         <v>2563</v>
@@ -8473,10 +8473,10 @@
         </is>
       </c>
       <c r="G165" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H165" s="6" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="I165" s="13" t="n">
         <v>22000</v>
@@ -8488,7 +8488,7 @@
         <v>100</v>
       </c>
       <c r="L165" t="n">
-        <v>12.9</v>
+        <v>42.9</v>
       </c>
       <c r="M165" t="n">
         <v>1014</v>
@@ -8520,10 +8520,10 @@
         </is>
       </c>
       <c r="G166" s="14" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H166" s="16" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I166" s="17" t="n">
         <v>8000</v>
@@ -8535,7 +8535,7 @@
         <v>90</v>
       </c>
       <c r="L166" s="14" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M166" s="14" t="n">
         <v>6506</v>
@@ -8567,10 +8567,10 @@
         </is>
       </c>
       <c r="G167" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H167" s="6" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="I167" s="13" t="n">
         <v>24000</v>
@@ -8582,7 +8582,7 @@
         <v>90</v>
       </c>
       <c r="L167" t="n">
-        <v>14</v>
+        <v>46.8</v>
       </c>
       <c r="M167" t="n">
         <v>3998</v>
@@ -8614,10 +8614,10 @@
         </is>
       </c>
       <c r="G168" s="14" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H168" s="16" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="I168" s="17" t="n">
         <v>22000</v>
@@ -8629,7 +8629,7 @@
         <v>90</v>
       </c>
       <c r="L168" s="14" t="n">
-        <v>12.9</v>
+        <v>42.9</v>
       </c>
       <c r="M168" s="14" t="n">
         <v>1014</v>
@@ -8661,10 +8661,10 @@
         </is>
       </c>
       <c r="G169" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H169" s="6" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I169" s="13" t="n">
         <v>8000</v>
@@ -8676,7 +8676,7 @@
         <v>90</v>
       </c>
       <c r="L169" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M169" t="n">
         <v>1276</v>
@@ -8708,10 +8708,10 @@
         </is>
       </c>
       <c r="G170" s="14" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H170" s="16" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I170" s="17" t="n">
         <v>8000</v>
@@ -8723,7 +8723,7 @@
         <v>80</v>
       </c>
       <c r="L170" s="14" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M170" s="14" t="n">
         <v>15450</v>
@@ -8755,10 +8755,10 @@
         </is>
       </c>
       <c r="G171" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H171" s="6" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I171" s="13" t="n">
         <v>8000</v>
@@ -8770,7 +8770,7 @@
         <v>80</v>
       </c>
       <c r="L171" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M171" t="n">
         <v>2007</v>
@@ -8802,10 +8802,10 @@
         </is>
       </c>
       <c r="G172" s="14" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H172" s="16" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I172" s="17" t="n">
         <v>8000</v>
@@ -8817,7 +8817,7 @@
         <v>90</v>
       </c>
       <c r="L172" s="14" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M172" s="14" t="inlineStr"/>
     </row>
@@ -8847,10 +8847,10 @@
         </is>
       </c>
       <c r="G173" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H173" s="6" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I173" s="13" t="n">
         <v>8000</v>
@@ -8862,7 +8862,7 @@
         <v>90</v>
       </c>
       <c r="L173" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M173" t="inlineStr"/>
     </row>
@@ -8892,10 +8892,10 @@
         </is>
       </c>
       <c r="G174" s="14" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H174" s="16" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I174" s="17" t="n">
         <v>9000</v>
@@ -8907,7 +8907,7 @@
         <v>80</v>
       </c>
       <c r="L174" s="14" t="n">
-        <v>5.3</v>
+        <v>17.6</v>
       </c>
       <c r="M174" s="14" t="n">
         <v>1983</v>
@@ -8939,10 +8939,10 @@
         </is>
       </c>
       <c r="G175" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H175" s="6" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I175" s="13" t="n">
         <v>8000</v>
@@ -8954,7 +8954,7 @@
         <v>90</v>
       </c>
       <c r="L175" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M175" t="n">
         <v>14477</v>
@@ -8986,10 +8986,10 @@
         </is>
       </c>
       <c r="G176" s="14" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H176" s="16" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I176" s="17" t="n">
         <v>8000</v>
@@ -9001,7 +9001,7 @@
         <v>80</v>
       </c>
       <c r="L176" s="14" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M176" s="14" t="inlineStr"/>
     </row>
@@ -9031,10 +9031,10 @@
         </is>
       </c>
       <c r="G177" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H177" s="6" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I177" s="13" t="n">
         <v>8000</v>
@@ -9046,7 +9046,7 @@
         <v>90</v>
       </c>
       <c r="L177" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M177" t="n">
         <v>13656</v>
@@ -9078,10 +9078,10 @@
         </is>
       </c>
       <c r="G178" s="14" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H178" s="16" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I178" s="17" t="n">
         <v>6500</v>
@@ -9093,7 +9093,7 @@
         <v>70</v>
       </c>
       <c r="L178" s="14" t="n">
-        <v>3.8</v>
+        <v>12.7</v>
       </c>
       <c r="M178" s="14" t="n">
         <v>1062</v>
@@ -9140,7 +9140,7 @@
         <v>70</v>
       </c>
       <c r="L179" t="n">
-        <v>2.3</v>
+        <v>7.8</v>
       </c>
       <c r="M179" t="n">
         <v>12387</v>
@@ -9172,10 +9172,10 @@
         </is>
       </c>
       <c r="G180" s="14" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H180" s="16" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I180" s="17" t="n">
         <v>8000</v>
@@ -9187,7 +9187,7 @@
         <v>50</v>
       </c>
       <c r="L180" s="14" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M180" s="14" t="n">
         <v>4929</v>
@@ -9219,10 +9219,10 @@
         </is>
       </c>
       <c r="G181" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H181" s="6" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I181" s="13" t="n">
         <v>8000</v>
@@ -9234,7 +9234,7 @@
         <v>80</v>
       </c>
       <c r="L181" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M181" t="n">
         <v>1527</v>
@@ -9266,10 +9266,10 @@
         </is>
       </c>
       <c r="G182" s="14" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="H182" s="16" t="n">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="I182" s="17" t="n">
         <v>14000</v>
@@ -9281,7 +9281,7 @@
         <v>80</v>
       </c>
       <c r="L182" s="14" t="n">
-        <v>8.199999999999999</v>
+        <v>27.3</v>
       </c>
       <c r="M182" s="14" t="n">
         <v>5140</v>
@@ -9313,10 +9313,10 @@
         </is>
       </c>
       <c r="G183" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H183" s="6" t="n">
-        <v>73000</v>
+        <v>100000</v>
       </c>
       <c r="I183" s="13" t="n">
         <v>4000</v>
@@ -9328,7 +9328,7 @@
         <v>80</v>
       </c>
       <c r="L183" t="n">
-        <v>2.3</v>
+        <v>7.8</v>
       </c>
       <c r="M183" t="n">
         <v>1527</v>
@@ -9360,10 +9360,10 @@
         </is>
       </c>
       <c r="G184" s="14" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H184" s="16" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I184" s="17" t="n">
         <v>9000</v>
@@ -9375,7 +9375,7 @@
         <v>80</v>
       </c>
       <c r="L184" s="14" t="n">
-        <v>5.3</v>
+        <v>17.6</v>
       </c>
       <c r="M184" s="14" t="n">
         <v>1983</v>
@@ -9422,7 +9422,7 @@
         <v>60</v>
       </c>
       <c r="L185" t="n">
-        <v>2.3</v>
+        <v>7.8</v>
       </c>
       <c r="M185" t="n">
         <v>12669</v>
@@ -9454,10 +9454,10 @@
         </is>
       </c>
       <c r="G186" s="14" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H186" s="16" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I186" s="17" t="n">
         <v>8000</v>
@@ -9469,7 +9469,7 @@
         <v>90</v>
       </c>
       <c r="L186" s="14" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M186" s="14" t="n">
         <v>12584</v>
@@ -9501,10 +9501,10 @@
         </is>
       </c>
       <c r="G187" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H187" s="6" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I187" s="13" t="n">
         <v>8000</v>
@@ -9516,7 +9516,7 @@
         <v>80</v>
       </c>
       <c r="L187" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M187" t="n">
         <v>2891</v>
@@ -9548,10 +9548,10 @@
         </is>
       </c>
       <c r="G188" s="14" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H188" s="16" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="I188" s="17" t="n">
         <v>22000</v>
@@ -9563,7 +9563,7 @@
         <v>90</v>
       </c>
       <c r="L188" s="14" t="n">
-        <v>12.9</v>
+        <v>42.9</v>
       </c>
       <c r="M188" s="14" t="n">
         <v>1014</v>
@@ -9595,10 +9595,10 @@
         </is>
       </c>
       <c r="G189" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H189" s="6" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I189" s="13" t="n">
         <v>8000</v>
@@ -9610,7 +9610,7 @@
         <v>90</v>
       </c>
       <c r="L189" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M189" t="inlineStr"/>
     </row>
@@ -9640,10 +9640,10 @@
         </is>
       </c>
       <c r="G190" s="14" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H190" s="16" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I190" s="17" t="n">
         <v>8000</v>
@@ -9655,7 +9655,7 @@
         <v>80</v>
       </c>
       <c r="L190" s="14" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M190" s="14" t="n">
         <v>3495</v>
@@ -9702,7 +9702,7 @@
         <v>60</v>
       </c>
       <c r="L191" t="n">
-        <v>2.3</v>
+        <v>7.8</v>
       </c>
       <c r="M191" t="n">
         <v>11583</v>
@@ -9734,10 +9734,10 @@
         </is>
       </c>
       <c r="G192" s="14" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H192" s="16" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I192" s="17" t="n">
         <v>8000</v>
@@ -9749,7 +9749,7 @@
         <v>100</v>
       </c>
       <c r="L192" s="14" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M192" s="14" t="n">
         <v>11283</v>
@@ -9781,10 +9781,10 @@
         </is>
       </c>
       <c r="G193" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H193" s="6" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I193" s="13" t="n">
         <v>8000</v>
@@ -9796,7 +9796,7 @@
         <v>80</v>
       </c>
       <c r="L193" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M193" t="n">
         <v>11155</v>
@@ -9828,10 +9828,10 @@
         </is>
       </c>
       <c r="G194" s="14" t="n">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="H194" s="16" t="n">
-        <v>100000</v>
+        <v>250000</v>
       </c>
       <c r="I194" s="17" t="n">
         <v>16000</v>
@@ -9843,7 +9843,7 @@
         <v>90</v>
       </c>
       <c r="L194" s="14" t="n">
-        <v>9.4</v>
+        <v>31.2</v>
       </c>
       <c r="M194" s="14" t="n">
         <v>1287</v>
@@ -9875,10 +9875,10 @@
         </is>
       </c>
       <c r="G195" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="H195" s="6" t="n">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="I195" s="13" t="n">
         <v>13000</v>
@@ -9890,7 +9890,7 @@
         <v>100</v>
       </c>
       <c r="L195" t="n">
-        <v>7.6</v>
+        <v>25.3</v>
       </c>
       <c r="M195" t="n">
         <v>4459</v>
@@ -9922,10 +9922,10 @@
         </is>
       </c>
       <c r="G196" s="14" t="n">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="H196" s="16" t="n">
-        <v>100000</v>
+        <v>250000</v>
       </c>
       <c r="I196" s="17" t="n">
         <v>19000</v>
@@ -9937,7 +9937,7 @@
         <v>90</v>
       </c>
       <c r="L196" s="14" t="n">
-        <v>11.1</v>
+        <v>37.1</v>
       </c>
       <c r="M196" s="14" t="n">
         <v>2598</v>
@@ -9969,10 +9969,10 @@
         </is>
       </c>
       <c r="G197" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H197" s="6" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I197" s="13" t="n">
         <v>8000</v>
@@ -9984,7 +9984,7 @@
         <v>80</v>
       </c>
       <c r="L197" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M197" t="n">
         <v>1527</v>
@@ -10016,10 +10016,10 @@
         </is>
       </c>
       <c r="G198" s="14" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H198" s="16" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I198" s="17" t="n">
         <v>8000</v>
@@ -10031,7 +10031,7 @@
         <v>80</v>
       </c>
       <c r="L198" s="14" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M198" s="14" t="n">
         <v>1527</v>
@@ -10063,10 +10063,10 @@
         </is>
       </c>
       <c r="G199" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="H199" s="6" t="n">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="I199" s="13" t="n">
         <v>13000</v>
@@ -10078,7 +10078,7 @@
         <v>120</v>
       </c>
       <c r="L199" t="n">
-        <v>7.6</v>
+        <v>25.4</v>
       </c>
       <c r="M199" t="n">
         <v>10091</v>
@@ -10110,10 +10110,10 @@
         </is>
       </c>
       <c r="G200" s="14" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H200" s="16" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I200" s="17" t="n">
         <v>8000</v>
@@ -10125,7 +10125,7 @@
         <v>80</v>
       </c>
       <c r="L200" s="14" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M200" s="14" t="inlineStr"/>
     </row>
@@ -10155,10 +10155,10 @@
         </is>
       </c>
       <c r="G201" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H201" s="6" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I201" s="13" t="n">
         <v>7000</v>
@@ -10170,7 +10170,7 @@
         <v>90</v>
       </c>
       <c r="L201" t="n">
-        <v>4.1</v>
+        <v>13.7</v>
       </c>
       <c r="M201" t="n">
         <v>1014</v>
@@ -10202,10 +10202,10 @@
         </is>
       </c>
       <c r="G202" s="14" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H202" s="16" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I202" s="17" t="n">
         <v>8000</v>
@@ -10217,7 +10217,7 @@
         <v>80</v>
       </c>
       <c r="L202" s="14" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M202" s="14" t="n">
         <v>1527</v>
@@ -10249,10 +10249,10 @@
         </is>
       </c>
       <c r="G203" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H203" s="6" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I203" s="13" t="n">
         <v>8000</v>
@@ -10264,7 +10264,7 @@
         <v>80</v>
       </c>
       <c r="L203" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M203" t="n">
         <v>8965</v>
@@ -10296,10 +10296,10 @@
         </is>
       </c>
       <c r="G204" s="14" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="H204" s="16" t="n">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="I204" s="17" t="n">
         <v>11000</v>
@@ -10311,7 +10311,7 @@
         <v>90</v>
       </c>
       <c r="L204" s="14" t="n">
-        <v>6.4</v>
+        <v>21.4</v>
       </c>
       <c r="M204" s="14" t="n">
         <v>1591</v>
@@ -10343,10 +10343,10 @@
         </is>
       </c>
       <c r="G205" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H205" s="6" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I205" s="13" t="n">
         <v>8000</v>
@@ -10358,7 +10358,7 @@
         <v>80</v>
       </c>
       <c r="L205" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M205" t="n">
         <v>2016</v>
@@ -10390,10 +10390,10 @@
         </is>
       </c>
       <c r="G206" s="14" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H206" s="16" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I206" s="17" t="n">
         <v>8000</v>
@@ -10405,7 +10405,7 @@
         <v>80</v>
       </c>
       <c r="L206" s="14" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M206" s="14" t="n">
         <v>8287</v>
@@ -10437,10 +10437,10 @@
         </is>
       </c>
       <c r="G207" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H207" s="6" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I207" s="13" t="n">
         <v>8000</v>
@@ -10452,7 +10452,7 @@
         <v>90</v>
       </c>
       <c r="L207" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M207" t="n">
         <v>8249</v>
@@ -10484,10 +10484,10 @@
         </is>
       </c>
       <c r="G208" s="14" t="n">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="H208" s="16" t="n">
-        <v>100000</v>
+        <v>250000</v>
       </c>
       <c r="I208" s="17" t="n">
         <v>16000</v>
@@ -10499,7 +10499,7 @@
         <v>90</v>
       </c>
       <c r="L208" s="14" t="n">
-        <v>9.4</v>
+        <v>31.2</v>
       </c>
       <c r="M208" s="14" t="n">
         <v>273</v>
@@ -10531,10 +10531,10 @@
         </is>
       </c>
       <c r="G209" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H209" s="6" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="I209" s="13" t="n">
         <v>22000</v>
@@ -10546,7 +10546,7 @@
         <v>90</v>
       </c>
       <c r="L209" t="n">
-        <v>12.9</v>
+        <v>42.9</v>
       </c>
       <c r="M209" t="inlineStr"/>
     </row>
@@ -10576,10 +10576,10 @@
         </is>
       </c>
       <c r="G210" s="14" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H210" s="16" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="I210" s="17" t="n">
         <v>22000</v>
@@ -10591,7 +10591,7 @@
         <v>80</v>
       </c>
       <c r="L210" s="14" t="n">
-        <v>12.9</v>
+        <v>42.9</v>
       </c>
       <c r="M210" s="14" t="inlineStr"/>
     </row>
@@ -10621,10 +10621,10 @@
         </is>
       </c>
       <c r="G211" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H211" s="6" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I211" s="13" t="n">
         <v>6500</v>
@@ -10636,7 +10636,7 @@
         <v>90</v>
       </c>
       <c r="L211" t="n">
-        <v>3.8</v>
+        <v>12.7</v>
       </c>
       <c r="M211" t="n">
         <v>1231</v>
@@ -10668,10 +10668,10 @@
         </is>
       </c>
       <c r="G212" s="14" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H212" s="16" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I212" s="17" t="n">
         <v>8000</v>
@@ -10683,7 +10683,7 @@
         <v>90</v>
       </c>
       <c r="L212" s="14" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M212" s="14" t="n">
         <v>2017</v>
@@ -10715,10 +10715,10 @@
         </is>
       </c>
       <c r="G213" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H213" s="6" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I213" s="13" t="n">
         <v>8000</v>
@@ -10730,7 +10730,7 @@
         <v>80</v>
       </c>
       <c r="L213" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M213" t="n">
         <v>6387</v>
@@ -10762,10 +10762,10 @@
         </is>
       </c>
       <c r="G214" s="14" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H214" s="16" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I214" s="17" t="n">
         <v>8000</v>
@@ -10777,7 +10777,7 @@
         <v>90</v>
       </c>
       <c r="L214" s="14" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M214" s="14" t="n">
         <v>6118</v>
@@ -10809,10 +10809,10 @@
         </is>
       </c>
       <c r="G215" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H215" s="6" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I215" s="13" t="n">
         <v>8000</v>
@@ -10824,7 +10824,7 @@
         <v>90</v>
       </c>
       <c r="L215" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M215" t="n">
         <v>1254</v>
@@ -10856,10 +10856,10 @@
         </is>
       </c>
       <c r="G216" s="14" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H216" s="16" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="I216" s="17" t="n">
         <v>24000</v>
@@ -10871,7 +10871,7 @@
         <v>90</v>
       </c>
       <c r="L216" s="14" t="n">
-        <v>14</v>
+        <v>46.8</v>
       </c>
       <c r="M216" s="14" t="n">
         <v>580</v>
@@ -10903,10 +10903,10 @@
         </is>
       </c>
       <c r="G217" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H217" s="6" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="I217" s="13" t="n">
         <v>24000</v>
@@ -10918,7 +10918,7 @@
         <v>90</v>
       </c>
       <c r="L217" t="n">
-        <v>14</v>
+        <v>46.8</v>
       </c>
       <c r="M217" t="n">
         <v>5851</v>
@@ -10950,10 +10950,10 @@
         </is>
       </c>
       <c r="G218" s="14" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H218" s="16" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I218" s="17" t="n">
         <v>8000</v>
@@ -10965,7 +10965,7 @@
         <v>90</v>
       </c>
       <c r="L218" s="14" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M218" s="14" t="n">
         <v>348</v>
@@ -10997,10 +10997,10 @@
         </is>
       </c>
       <c r="G219" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H219" s="6" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I219" s="13" t="n">
         <v>8000</v>
@@ -11012,7 +11012,7 @@
         <v>90</v>
       </c>
       <c r="L219" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M219" t="inlineStr"/>
     </row>
@@ -11042,10 +11042,10 @@
         </is>
       </c>
       <c r="G220" s="14" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H220" s="16" t="n">
-        <v>73000</v>
+        <v>100000</v>
       </c>
       <c r="I220" s="17" t="n">
         <v>4000</v>
@@ -11057,7 +11057,7 @@
         <v>80</v>
       </c>
       <c r="L220" s="14" t="n">
-        <v>2.3</v>
+        <v>7.8</v>
       </c>
       <c r="M220" s="14" t="n">
         <v>5557</v>
@@ -11089,10 +11089,10 @@
         </is>
       </c>
       <c r="G221" t="n">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="H221" s="6" t="n">
-        <v>100000</v>
+        <v>250000</v>
       </c>
       <c r="I221" s="13" t="n">
         <v>19000</v>
@@ -11104,7 +11104,7 @@
         <v>90</v>
       </c>
       <c r="L221" t="n">
-        <v>11.1</v>
+        <v>37.1</v>
       </c>
       <c r="M221" t="n">
         <v>348</v>
@@ -11136,10 +11136,10 @@
         </is>
       </c>
       <c r="G222" s="14" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H222" s="16" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I222" s="17" t="n">
         <v>8000</v>
@@ -11151,7 +11151,7 @@
         <v>80</v>
       </c>
       <c r="L222" s="14" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M222" s="14" t="n">
         <v>5230</v>
@@ -11183,10 +11183,10 @@
         </is>
       </c>
       <c r="G223" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H223" s="6" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I223" s="13" t="n">
         <v>8000</v>
@@ -11198,7 +11198,7 @@
         <v>80</v>
       </c>
       <c r="L223" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M223" t="n">
         <v>2419</v>
@@ -11230,10 +11230,10 @@
         </is>
       </c>
       <c r="G224" s="14" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H224" s="16" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I224" s="17" t="n">
         <v>8000</v>
@@ -11245,7 +11245,7 @@
         <v>90</v>
       </c>
       <c r="L224" s="14" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M224" s="14" t="n">
         <v>2013</v>
@@ -11277,10 +11277,10 @@
         </is>
       </c>
       <c r="G225" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H225" s="6" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I225" s="13" t="n">
         <v>8000</v>
@@ -11292,7 +11292,7 @@
         <v>80</v>
       </c>
       <c r="L225" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M225" t="n">
         <v>3911</v>
@@ -11324,10 +11324,10 @@
         </is>
       </c>
       <c r="G226" s="14" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H226" s="16" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I226" s="17" t="n">
         <v>8000</v>
@@ -11339,7 +11339,7 @@
         <v>50</v>
       </c>
       <c r="L226" s="14" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M226" s="14" t="n">
         <v>3267</v>
@@ -11371,10 +11371,10 @@
         </is>
       </c>
       <c r="G227" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H227" s="6" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I227" s="13" t="n">
         <v>8000</v>
@@ -11386,7 +11386,7 @@
         <v>110</v>
       </c>
       <c r="L227" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M227" t="n">
         <v>2956</v>
@@ -11418,10 +11418,10 @@
         </is>
       </c>
       <c r="G228" s="14" t="n">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="H228" s="16" t="n">
-        <v>100000</v>
+        <v>250000</v>
       </c>
       <c r="I228" s="17" t="n">
         <v>16000</v>
@@ -11433,7 +11433,7 @@
         <v>90</v>
       </c>
       <c r="L228" s="14" t="n">
-        <v>9.4</v>
+        <v>31.2</v>
       </c>
       <c r="M228" s="14" t="n">
         <v>1122</v>
@@ -11465,10 +11465,10 @@
         </is>
       </c>
       <c r="G229" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H229" s="6" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I229" s="13" t="n">
         <v>8000</v>
@@ -11480,7 +11480,7 @@
         <v>80</v>
       </c>
       <c r="L229" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M229" t="n">
         <v>2761</v>
@@ -11512,10 +11512,10 @@
         </is>
       </c>
       <c r="G230" s="14" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H230" s="16" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I230" s="17" t="n">
         <v>8000</v>
@@ -11527,7 +11527,7 @@
         <v>110</v>
       </c>
       <c r="L230" s="14" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M230" s="14" t="n">
         <v>2660</v>
@@ -11559,10 +11559,10 @@
         </is>
       </c>
       <c r="G231" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H231" s="6" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I231" s="13" t="n">
         <v>8000</v>
@@ -11574,7 +11574,7 @@
         <v>90</v>
       </c>
       <c r="L231" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M231" t="n">
         <v>662</v>
@@ -11606,10 +11606,10 @@
         </is>
       </c>
       <c r="G232" s="14" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H232" s="16" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="I232" s="17" t="n">
         <v>22000</v>
@@ -11621,7 +11621,7 @@
         <v>90</v>
       </c>
       <c r="L232" s="14" t="n">
-        <v>12.9</v>
+        <v>42.9</v>
       </c>
       <c r="M232" s="14" t="inlineStr"/>
     </row>
@@ -11651,10 +11651,10 @@
         </is>
       </c>
       <c r="G233" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H233" s="6" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I233" s="13" t="n">
         <v>7000</v>
@@ -11666,7 +11666,7 @@
         <v>90</v>
       </c>
       <c r="L233" t="n">
-        <v>4.1</v>
+        <v>13.7</v>
       </c>
       <c r="M233" t="n">
         <v>442</v>
@@ -11698,10 +11698,10 @@
         </is>
       </c>
       <c r="G234" s="14" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H234" s="16" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I234" s="17" t="n">
         <v>8000</v>
@@ -11713,7 +11713,7 @@
         <v>80</v>
       </c>
       <c r="L234" s="14" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M234" s="14" t="n">
         <v>1768</v>
@@ -11745,10 +11745,10 @@
         </is>
       </c>
       <c r="G235" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H235" s="6" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I235" s="13" t="n">
         <v>8000</v>
@@ -11760,7 +11760,7 @@
         <v>60</v>
       </c>
       <c r="L235" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M235" t="inlineStr"/>
     </row>
@@ -11790,10 +11790,10 @@
         </is>
       </c>
       <c r="G236" s="14" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H236" s="16" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I236" s="17" t="n">
         <v>8000</v>
@@ -11805,7 +11805,7 @@
         <v>80</v>
       </c>
       <c r="L236" s="14" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M236" s="14" t="n">
         <v>217</v>
@@ -11837,10 +11837,10 @@
         </is>
       </c>
       <c r="G237" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H237" s="6" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I237" s="13" t="n">
         <v>8000</v>
@@ -11852,7 +11852,7 @@
         <v>120</v>
       </c>
       <c r="L237" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M237" t="n">
         <v>1099</v>
@@ -11884,10 +11884,10 @@
         </is>
       </c>
       <c r="G238" s="14" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H238" s="16" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I238" s="17" t="n">
         <v>8000</v>
@@ -11899,7 +11899,7 @@
         <v>90</v>
       </c>
       <c r="L238" s="14" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M238" s="14" t="n">
         <v>881</v>
@@ -11931,10 +11931,10 @@
         </is>
       </c>
       <c r="G239" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H239" s="6" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I239" s="13" t="n">
         <v>6500</v>
@@ -11946,7 +11946,7 @@
         <v>90</v>
       </c>
       <c r="L239" t="n">
-        <v>3.8</v>
+        <v>12.7</v>
       </c>
       <c r="M239" t="n">
         <v>753</v>
@@ -11978,10 +11978,10 @@
         </is>
       </c>
       <c r="G240" s="14" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H240" s="16" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I240" s="17" t="n">
         <v>8000</v>
@@ -11993,7 +11993,7 @@
         <v>90</v>
       </c>
       <c r="L240" s="14" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M240" s="14" t="n">
         <v>753</v>
@@ -12025,10 +12025,10 @@
         </is>
       </c>
       <c r="G241" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H241" s="6" t="n">
-        <v>73000</v>
+        <v>100000</v>
       </c>
       <c r="I241" s="13" t="n">
         <v>4000</v>
@@ -12040,7 +12040,7 @@
         <v>80</v>
       </c>
       <c r="L241" t="n">
-        <v>2.3</v>
+        <v>7.8</v>
       </c>
       <c r="M241" t="n">
         <v>587</v>
@@ -12072,10 +12072,10 @@
         </is>
       </c>
       <c r="G242" s="14" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H242" s="16" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I242" s="17" t="n">
         <v>8000</v>
@@ -12087,7 +12087,7 @@
         <v>80</v>
       </c>
       <c r="L242" s="14" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M242" s="14" t="n">
         <v>587</v>
@@ -12119,10 +12119,10 @@
         </is>
       </c>
       <c r="G243" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H243" s="6" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I243" s="13" t="n">
         <v>8000</v>
@@ -12134,7 +12134,7 @@
         <v>90</v>
       </c>
       <c r="L243" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M243" t="n">
         <v>536</v>
@@ -12166,10 +12166,10 @@
         </is>
       </c>
       <c r="G244" s="14" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H244" s="16" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I244" s="17" t="n">
         <v>6500</v>
@@ -12181,7 +12181,7 @@
         <v>90</v>
       </c>
       <c r="L244" s="14" t="n">
-        <v>3.8</v>
+        <v>12.7</v>
       </c>
       <c r="M244" s="14" t="n">
         <v>536</v>
@@ -12213,10 +12213,10 @@
         </is>
       </c>
       <c r="G245" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H245" s="6" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I245" s="13" t="n">
         <v>8000</v>
@@ -12228,7 +12228,7 @@
         <v>80</v>
       </c>
       <c r="L245" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M245" t="n">
         <v>536</v>
@@ -12260,10 +12260,10 @@
         </is>
       </c>
       <c r="G246" s="14" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H246" s="16" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I246" s="17" t="n">
         <v>8000</v>
@@ -12275,7 +12275,7 @@
         <v>80</v>
       </c>
       <c r="L246" s="14" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M246" s="14" t="n">
         <v>510</v>
@@ -12307,10 +12307,10 @@
         </is>
       </c>
       <c r="G247" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H247" s="6" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I247" s="13" t="n">
         <v>8000</v>
@@ -12322,7 +12322,7 @@
         <v>90</v>
       </c>
       <c r="L247" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M247" t="n">
         <v>500</v>
@@ -12354,10 +12354,10 @@
         </is>
       </c>
       <c r="G248" s="14" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H248" s="16" t="n">
-        <v>73000</v>
+        <v>100000</v>
       </c>
       <c r="I248" s="17" t="n">
         <v>4000</v>
@@ -12369,7 +12369,7 @@
         <v>90</v>
       </c>
       <c r="L248" s="14" t="n">
-        <v>2.3</v>
+        <v>7.8</v>
       </c>
       <c r="M248" s="14" t="n">
         <v>500</v>
@@ -12401,10 +12401,10 @@
         </is>
       </c>
       <c r="G249" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H249" s="6" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I249" s="13" t="n">
         <v>6500</v>
@@ -12416,7 +12416,7 @@
         <v>90</v>
       </c>
       <c r="L249" t="n">
-        <v>3.8</v>
+        <v>12.7</v>
       </c>
       <c r="M249" t="n">
         <v>500</v>
@@ -12448,10 +12448,10 @@
         </is>
       </c>
       <c r="G250" s="14" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H250" s="16" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I250" s="17" t="n">
         <v>8000</v>
@@ -12463,7 +12463,7 @@
         <v>90</v>
       </c>
       <c r="L250" s="14" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M250" s="14" t="n">
         <v>442</v>
@@ -12495,10 +12495,10 @@
         </is>
       </c>
       <c r="G251" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H251" s="6" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I251" s="13" t="n">
         <v>6500</v>
@@ -12510,7 +12510,7 @@
         <v>90</v>
       </c>
       <c r="L251" t="n">
-        <v>3.8</v>
+        <v>12.7</v>
       </c>
       <c r="M251" t="n">
         <v>442</v>
@@ -12542,10 +12542,10 @@
         </is>
       </c>
       <c r="G252" s="14" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H252" s="16" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I252" s="17" t="n">
         <v>8000</v>
@@ -12557,7 +12557,7 @@
         <v>90</v>
       </c>
       <c r="L252" s="14" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M252" s="14" t="n">
         <v>442</v>
@@ -12589,10 +12589,10 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H253" s="6" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I253" s="13" t="n">
         <v>8000</v>
@@ -12604,7 +12604,7 @@
         <v>80</v>
       </c>
       <c r="L253" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M253" t="n">
         <v>440</v>
@@ -12636,10 +12636,10 @@
         </is>
       </c>
       <c r="G254" s="14" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H254" s="16" t="n">
-        <v>73000</v>
+        <v>100000</v>
       </c>
       <c r="I254" s="17" t="n">
         <v>4000</v>
@@ -12651,7 +12651,7 @@
         <v>80</v>
       </c>
       <c r="L254" s="14" t="n">
-        <v>2.3</v>
+        <v>7.8</v>
       </c>
       <c r="M254" s="14" t="n">
         <v>232</v>
@@ -12683,10 +12683,10 @@
         </is>
       </c>
       <c r="G255" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H255" s="6" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="I255" s="13" t="n">
         <v>22000</v>
@@ -12698,7 +12698,7 @@
         <v>80</v>
       </c>
       <c r="L255" t="n">
-        <v>12.9</v>
+        <v>42.9</v>
       </c>
       <c r="M255" t="n">
         <v>284</v>
@@ -12730,10 +12730,10 @@
         </is>
       </c>
       <c r="G256" s="14" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H256" s="16" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="I256" s="17" t="n">
         <v>22000</v>
@@ -12745,7 +12745,7 @@
         <v>90</v>
       </c>
       <c r="L256" s="14" t="n">
-        <v>12.9</v>
+        <v>42.9</v>
       </c>
       <c r="M256" s="14" t="n">
         <v>284</v>
@@ -12777,10 +12777,10 @@
         </is>
       </c>
       <c r="G257" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H257" s="6" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="I257" s="13" t="n">
         <v>22000</v>
@@ -12792,7 +12792,7 @@
         <v>90</v>
       </c>
       <c r="L257" t="n">
-        <v>12.9</v>
+        <v>42.9</v>
       </c>
       <c r="M257" t="n">
         <v>284</v>
@@ -12824,10 +12824,10 @@
         </is>
       </c>
       <c r="G258" s="14" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H258" s="16" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="I258" s="17" t="n">
         <v>22000</v>
@@ -12839,7 +12839,7 @@
         <v>80</v>
       </c>
       <c r="L258" s="14" t="n">
-        <v>12.9</v>
+        <v>42.9</v>
       </c>
       <c r="M258" s="14" t="n">
         <v>284</v>
@@ -12871,10 +12871,10 @@
         </is>
       </c>
       <c r="G259" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H259" s="6" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="I259" s="13" t="n">
         <v>22000</v>
@@ -12886,7 +12886,7 @@
         <v>90</v>
       </c>
       <c r="L259" t="n">
-        <v>12.9</v>
+        <v>42.9</v>
       </c>
       <c r="M259" t="n">
         <v>284</v>
@@ -12918,10 +12918,10 @@
         </is>
       </c>
       <c r="G260" s="14" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H260" s="16" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I260" s="17" t="n">
         <v>8000</v>
@@ -12933,7 +12933,7 @@
         <v>80</v>
       </c>
       <c r="L260" s="14" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M260" s="14" t="n">
         <v>283</v>
@@ -12965,10 +12965,10 @@
         </is>
       </c>
       <c r="G261" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H261" s="6" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I261" s="13" t="n">
         <v>8000</v>
@@ -12980,7 +12980,7 @@
         <v>80</v>
       </c>
       <c r="L261" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M261" t="n">
         <v>253</v>
@@ -13012,10 +13012,10 @@
         </is>
       </c>
       <c r="G262" s="14" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H262" s="16" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I262" s="17" t="n">
         <v>9000</v>
@@ -13027,7 +13027,7 @@
         <v>80</v>
       </c>
       <c r="L262" s="14" t="n">
-        <v>5.3</v>
+        <v>17.6</v>
       </c>
       <c r="M262" s="14" t="n">
         <v>232</v>
@@ -13059,10 +13059,10 @@
         </is>
       </c>
       <c r="G263" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H263" s="6" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="I263" s="13" t="n">
         <v>24000</v>
@@ -13074,7 +13074,7 @@
         <v>80</v>
       </c>
       <c r="L263" t="n">
-        <v>14</v>
+        <v>46.8</v>
       </c>
       <c r="M263" t="n">
         <v>232</v>
@@ -13106,10 +13106,10 @@
         </is>
       </c>
       <c r="G264" s="14" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H264" s="16" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="I264" s="17" t="n">
         <v>24000</v>
@@ -13121,7 +13121,7 @@
         <v>80</v>
       </c>
       <c r="L264" s="14" t="n">
-        <v>14</v>
+        <v>46.8</v>
       </c>
       <c r="M264" s="14" t="n">
         <v>232</v>
@@ -13153,10 +13153,10 @@
         </is>
       </c>
       <c r="G265" t="n">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="H265" s="6" t="n">
-        <v>100000</v>
+        <v>250000</v>
       </c>
       <c r="I265" s="13" t="n">
         <v>16000</v>
@@ -13168,7 +13168,7 @@
         <v>80</v>
       </c>
       <c r="L265" t="n">
-        <v>9.4</v>
+        <v>31.2</v>
       </c>
       <c r="M265" t="n">
         <v>232</v>
@@ -13200,10 +13200,10 @@
         </is>
       </c>
       <c r="G266" s="14" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H266" s="16" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I266" s="17" t="n">
         <v>8000</v>
@@ -13215,7 +13215,7 @@
         <v>90</v>
       </c>
       <c r="L266" s="14" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M266" s="14" t="n">
         <v>232</v>
@@ -13247,10 +13247,10 @@
         </is>
       </c>
       <c r="G267" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H267" s="6" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I267" s="13" t="n">
         <v>8000</v>
@@ -13262,7 +13262,7 @@
         <v>80</v>
       </c>
       <c r="L267" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M267" t="n">
         <v>232</v>
@@ -13294,10 +13294,10 @@
         </is>
       </c>
       <c r="G268" s="14" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H268" s="16" t="n">
-        <v>73000</v>
+        <v>100000</v>
       </c>
       <c r="I268" s="17" t="n">
         <v>4000</v>
@@ -13309,7 +13309,7 @@
         <v>80</v>
       </c>
       <c r="L268" s="14" t="n">
-        <v>2.3</v>
+        <v>7.8</v>
       </c>
       <c r="M268" s="14" t="n">
         <v>232</v>
@@ -13341,10 +13341,10 @@
         </is>
       </c>
       <c r="G269" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H269" s="6" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I269" s="13" t="n">
         <v>8000</v>
@@ -13356,7 +13356,7 @@
         <v>80</v>
       </c>
       <c r="L269" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M269" t="n">
         <v>232</v>
@@ -13388,10 +13388,10 @@
         </is>
       </c>
       <c r="G270" s="14" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H270" s="16" t="n">
-        <v>73000</v>
+        <v>100000</v>
       </c>
       <c r="I270" s="17" t="n">
         <v>4000</v>
@@ -13403,7 +13403,7 @@
         <v>80</v>
       </c>
       <c r="L270" s="14" t="n">
-        <v>2.3</v>
+        <v>7.8</v>
       </c>
       <c r="M270" s="14" t="n">
         <v>232</v>
@@ -13435,10 +13435,10 @@
         </is>
       </c>
       <c r="G271" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H271" s="6" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I271" s="13" t="n">
         <v>7000</v>
@@ -13450,7 +13450,7 @@
         <v>90</v>
       </c>
       <c r="L271" t="n">
-        <v>4.1</v>
+        <v>13.7</v>
       </c>
       <c r="M271" t="n">
         <v>225</v>
@@ -13482,10 +13482,10 @@
         </is>
       </c>
       <c r="G272" s="14" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H272" s="16" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I272" s="17" t="n">
         <v>8000</v>
@@ -13497,7 +13497,7 @@
         <v>90</v>
       </c>
       <c r="L272" s="14" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M272" s="14" t="inlineStr"/>
     </row>
@@ -13527,10 +13527,10 @@
         </is>
       </c>
       <c r="G273" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H273" s="6" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I273" s="13" t="n">
         <v>8000</v>
@@ -13542,7 +13542,7 @@
         <v>110</v>
       </c>
       <c r="L273" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M273" t="inlineStr"/>
     </row>
@@ -13572,10 +13572,10 @@
         </is>
       </c>
       <c r="G274" s="14" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H274" s="16" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I274" s="17" t="n">
         <v>8000</v>
@@ -13587,7 +13587,7 @@
         <v>110</v>
       </c>
       <c r="L274" s="14" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M274" s="14" t="inlineStr"/>
     </row>
@@ -13617,10 +13617,10 @@
         </is>
       </c>
       <c r="G275" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H275" s="6" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I275" s="13" t="n">
         <v>8000</v>
@@ -13632,7 +13632,7 @@
         <v>110</v>
       </c>
       <c r="L275" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M275" t="inlineStr"/>
     </row>
@@ -13662,10 +13662,10 @@
         </is>
       </c>
       <c r="G276" s="14" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H276" s="16" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I276" s="17" t="n">
         <v>8000</v>
@@ -13677,7 +13677,7 @@
         <v>90</v>
       </c>
       <c r="L276" s="14" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M276" s="14" t="inlineStr"/>
     </row>
@@ -13707,10 +13707,10 @@
         </is>
       </c>
       <c r="G277" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H277" s="6" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I277" s="13" t="n">
         <v>9000</v>
@@ -13722,7 +13722,7 @@
         <v>80</v>
       </c>
       <c r="L277" t="n">
-        <v>5.3</v>
+        <v>17.6</v>
       </c>
       <c r="M277" t="inlineStr"/>
     </row>
@@ -13752,10 +13752,10 @@
         </is>
       </c>
       <c r="G278" s="14" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H278" s="16" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I278" s="17" t="n">
         <v>9000</v>
@@ -13767,7 +13767,7 @@
         <v>60</v>
       </c>
       <c r="L278" s="14" t="n">
-        <v>5.3</v>
+        <v>17.6</v>
       </c>
       <c r="M278" s="14" t="inlineStr"/>
     </row>
@@ -13797,10 +13797,10 @@
         </is>
       </c>
       <c r="G279" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H279" s="6" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I279" s="13" t="n">
         <v>9000</v>
@@ -13812,7 +13812,7 @@
         <v>70</v>
       </c>
       <c r="L279" t="n">
-        <v>5.3</v>
+        <v>17.6</v>
       </c>
       <c r="M279" t="inlineStr"/>
     </row>
@@ -13842,10 +13842,10 @@
         </is>
       </c>
       <c r="G280" s="14" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H280" s="16" t="n">
-        <v>73000</v>
+        <v>100000</v>
       </c>
       <c r="I280" s="17" t="n">
         <v>4000</v>
@@ -13857,7 +13857,7 @@
         <v>90</v>
       </c>
       <c r="L280" s="14" t="n">
-        <v>2.3</v>
+        <v>7.8</v>
       </c>
       <c r="M280" s="14" t="inlineStr"/>
     </row>
@@ -13887,10 +13887,10 @@
         </is>
       </c>
       <c r="G281" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H281" s="6" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I281" s="13" t="n">
         <v>9000</v>
@@ -13902,7 +13902,7 @@
         <v>80</v>
       </c>
       <c r="L281" t="n">
-        <v>5.3</v>
+        <v>17.6</v>
       </c>
       <c r="M281" t="inlineStr"/>
     </row>
@@ -13932,10 +13932,10 @@
         </is>
       </c>
       <c r="G282" s="14" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H282" s="16" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I282" s="17" t="n">
         <v>8000</v>
@@ -13947,7 +13947,7 @@
         <v>90</v>
       </c>
       <c r="L282" s="14" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M282" s="14" t="inlineStr"/>
     </row>
@@ -13977,10 +13977,10 @@
         </is>
       </c>
       <c r="G283" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H283" s="6" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I283" s="13" t="n">
         <v>8000</v>
@@ -13992,7 +13992,7 @@
         <v>30</v>
       </c>
       <c r="L283" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M283" t="inlineStr"/>
     </row>
@@ -14022,10 +14022,10 @@
         </is>
       </c>
       <c r="G284" s="14" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H284" s="16" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I284" s="17" t="n">
         <v>8000</v>
@@ -14037,7 +14037,7 @@
         <v>90</v>
       </c>
       <c r="L284" s="14" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M284" s="14" t="inlineStr"/>
     </row>
@@ -14067,10 +14067,10 @@
         </is>
       </c>
       <c r="G285" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H285" s="6" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="I285" s="13" t="n">
         <v>22000</v>
@@ -14082,7 +14082,7 @@
         <v>80</v>
       </c>
       <c r="L285" t="n">
-        <v>12.9</v>
+        <v>42.9</v>
       </c>
       <c r="M285" t="inlineStr"/>
     </row>
@@ -14112,10 +14112,10 @@
         </is>
       </c>
       <c r="G286" s="14" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H286" s="16" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="I286" s="17" t="n">
         <v>22000</v>
@@ -14127,7 +14127,7 @@
         <v>90</v>
       </c>
       <c r="L286" s="14" t="n">
-        <v>12.9</v>
+        <v>42.9</v>
       </c>
       <c r="M286" s="14" t="inlineStr"/>
     </row>
@@ -14157,10 +14157,10 @@
         </is>
       </c>
       <c r="G287" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H287" s="6" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="I287" s="13" t="n">
         <v>22000</v>
@@ -14172,7 +14172,7 @@
         <v>90</v>
       </c>
       <c r="L287" t="n">
-        <v>12.9</v>
+        <v>42.9</v>
       </c>
       <c r="M287" t="inlineStr"/>
     </row>
@@ -14202,10 +14202,10 @@
         </is>
       </c>
       <c r="G288" s="14" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H288" s="16" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I288" s="17" t="n">
         <v>8000</v>
@@ -14217,7 +14217,7 @@
         <v>90</v>
       </c>
       <c r="L288" s="14" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M288" s="14" t="inlineStr"/>
     </row>
@@ -14247,10 +14247,10 @@
         </is>
       </c>
       <c r="G289" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H289" s="6" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I289" s="13" t="n">
         <v>8000</v>
@@ -14262,7 +14262,7 @@
         <v>80</v>
       </c>
       <c r="L289" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M289" t="inlineStr"/>
     </row>
@@ -14292,10 +14292,10 @@
         </is>
       </c>
       <c r="G290" s="14" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H290" s="16" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I290" s="17" t="n">
         <v>7000</v>
@@ -14307,7 +14307,7 @@
         <v>90</v>
       </c>
       <c r="L290" s="14" t="n">
-        <v>4.1</v>
+        <v>13.7</v>
       </c>
       <c r="M290" s="14" t="inlineStr"/>
     </row>
@@ -14337,10 +14337,10 @@
         </is>
       </c>
       <c r="G291" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H291" s="6" t="n">
-        <v>73000</v>
+        <v>100000</v>
       </c>
       <c r="I291" s="13" t="n">
         <v>4000</v>
@@ -14352,7 +14352,7 @@
         <v>90</v>
       </c>
       <c r="L291" t="n">
-        <v>2.3</v>
+        <v>7.8</v>
       </c>
       <c r="M291" t="inlineStr"/>
     </row>
@@ -14382,10 +14382,10 @@
         </is>
       </c>
       <c r="G292" s="14" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H292" s="16" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I292" s="17" t="n">
         <v>8000</v>
@@ -14397,7 +14397,7 @@
         <v>90</v>
       </c>
       <c r="L292" s="14" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M292" s="14" t="inlineStr"/>
     </row>
@@ -14427,10 +14427,10 @@
         </is>
       </c>
       <c r="G293" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H293" s="6" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I293" s="13" t="n">
         <v>8000</v>
@@ -14442,7 +14442,7 @@
         <v>80</v>
       </c>
       <c r="L293" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M293" t="inlineStr"/>
     </row>
@@ -14472,10 +14472,10 @@
         </is>
       </c>
       <c r="G294" s="14" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H294" s="16" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="I294" s="17" t="n">
         <v>24000</v>
@@ -14487,7 +14487,7 @@
         <v>100</v>
       </c>
       <c r="L294" s="14" t="n">
-        <v>14</v>
+        <v>46.8</v>
       </c>
       <c r="M294" s="14" t="inlineStr"/>
     </row>
@@ -14517,10 +14517,10 @@
         </is>
       </c>
       <c r="G295" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H295" s="6" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I295" s="13" t="n">
         <v>8000</v>
@@ -14532,7 +14532,7 @@
         <v>90</v>
       </c>
       <c r="L295" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M295" t="inlineStr"/>
     </row>
@@ -14562,10 +14562,10 @@
         </is>
       </c>
       <c r="G296" s="14" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H296" s="16" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I296" s="17" t="n">
         <v>8000</v>
@@ -14577,7 +14577,7 @@
         <v>90</v>
       </c>
       <c r="L296" s="14" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M296" s="14" t="inlineStr"/>
     </row>
@@ -14607,10 +14607,10 @@
         </is>
       </c>
       <c r="G297" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H297" s="6" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I297" s="13" t="n">
         <v>8000</v>
@@ -14622,7 +14622,7 @@
         <v>80</v>
       </c>
       <c r="L297" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M297" t="inlineStr"/>
     </row>
@@ -14652,10 +14652,10 @@
         </is>
       </c>
       <c r="G298" s="14" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H298" s="16" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="I298" s="17" t="n">
         <v>22000</v>
@@ -14667,7 +14667,7 @@
         <v>80</v>
       </c>
       <c r="L298" s="14" t="n">
-        <v>12.9</v>
+        <v>42.9</v>
       </c>
       <c r="M298" s="14" t="inlineStr"/>
     </row>
@@ -14697,10 +14697,10 @@
         </is>
       </c>
       <c r="G299" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H299" s="6" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I299" s="13" t="n">
         <v>8000</v>
@@ -14712,7 +14712,7 @@
         <v>100</v>
       </c>
       <c r="L299" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M299" t="inlineStr"/>
     </row>
@@ -14742,10 +14742,10 @@
         </is>
       </c>
       <c r="G300" s="14" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H300" s="16" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I300" s="17" t="n">
         <v>8000</v>
@@ -14757,7 +14757,7 @@
         <v>80</v>
       </c>
       <c r="L300" s="14" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M300" s="14" t="inlineStr"/>
     </row>
@@ -14787,10 +14787,10 @@
         </is>
       </c>
       <c r="G301" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H301" s="6" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I301" s="13" t="n">
         <v>8000</v>
@@ -14802,7 +14802,7 @@
         <v>70</v>
       </c>
       <c r="L301" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M301" t="inlineStr"/>
     </row>
@@ -14832,10 +14832,10 @@
         </is>
       </c>
       <c r="G302" s="14" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H302" s="16" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I302" s="17" t="n">
         <v>8000</v>
@@ -14847,7 +14847,7 @@
         <v>100</v>
       </c>
       <c r="L302" s="14" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M302" s="14" t="inlineStr"/>
     </row>
@@ -14877,10 +14877,10 @@
         </is>
       </c>
       <c r="G303" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H303" s="6" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I303" s="13" t="n">
         <v>8000</v>
@@ -14892,7 +14892,7 @@
         <v>90</v>
       </c>
       <c r="L303" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M303" t="inlineStr"/>
     </row>
@@ -14922,10 +14922,10 @@
         </is>
       </c>
       <c r="G304" s="14" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H304" s="16" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I304" s="17" t="n">
         <v>8000</v>
@@ -14937,7 +14937,7 @@
         <v>80</v>
       </c>
       <c r="L304" s="14" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M304" s="14" t="inlineStr"/>
     </row>
@@ -14967,10 +14967,10 @@
         </is>
       </c>
       <c r="G305" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H305" s="6" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I305" s="13" t="n">
         <v>7000</v>
@@ -14982,7 +14982,7 @@
         <v>90</v>
       </c>
       <c r="L305" t="n">
-        <v>4.1</v>
+        <v>13.7</v>
       </c>
       <c r="M305" t="inlineStr"/>
     </row>
@@ -15012,10 +15012,10 @@
         </is>
       </c>
       <c r="G306" s="14" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H306" s="16" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I306" s="17" t="n">
         <v>8000</v>
@@ -15027,7 +15027,7 @@
         <v>90</v>
       </c>
       <c r="L306" s="14" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M306" s="14" t="inlineStr"/>
     </row>
@@ -15057,10 +15057,10 @@
         </is>
       </c>
       <c r="G307" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H307" s="6" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="I307" s="13" t="n">
         <v>22000</v>
@@ -15072,7 +15072,7 @@
         <v>90</v>
       </c>
       <c r="L307" t="n">
-        <v>12.9</v>
+        <v>42.9</v>
       </c>
       <c r="M307" t="inlineStr"/>
     </row>
@@ -15102,10 +15102,10 @@
         </is>
       </c>
       <c r="G308" s="14" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H308" s="16" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="I308" s="17" t="n">
         <v>22000</v>
@@ -15117,7 +15117,7 @@
         <v>90</v>
       </c>
       <c r="L308" s="14" t="n">
-        <v>12.9</v>
+        <v>42.9</v>
       </c>
       <c r="M308" s="14" t="inlineStr"/>
     </row>
@@ -15147,10 +15147,10 @@
         </is>
       </c>
       <c r="G309" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H309" s="6" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I309" s="13" t="n">
         <v>9000</v>
@@ -15162,7 +15162,7 @@
         <v>80</v>
       </c>
       <c r="L309" t="n">
-        <v>5.3</v>
+        <v>17.6</v>
       </c>
       <c r="M309" t="inlineStr"/>
     </row>
@@ -15192,10 +15192,10 @@
         </is>
       </c>
       <c r="G310" s="14" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H310" s="16" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I310" s="17" t="n">
         <v>8000</v>
@@ -15207,7 +15207,7 @@
         <v>90</v>
       </c>
       <c r="L310" s="14" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M310" s="14" t="inlineStr"/>
     </row>
@@ -15237,10 +15237,10 @@
         </is>
       </c>
       <c r="G311" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H311" s="6" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I311" s="13" t="n">
         <v>8000</v>
@@ -15252,7 +15252,7 @@
         <v>90</v>
       </c>
       <c r="L311" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M311" t="inlineStr"/>
     </row>
@@ -15282,10 +15282,10 @@
         </is>
       </c>
       <c r="G312" s="14" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H312" s="16" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="I312" s="17" t="n">
         <v>22000</v>
@@ -15297,7 +15297,7 @@
         <v>90</v>
       </c>
       <c r="L312" s="14" t="n">
-        <v>12.9</v>
+        <v>42.9</v>
       </c>
       <c r="M312" s="14" t="inlineStr"/>
     </row>
@@ -15327,10 +15327,10 @@
         </is>
       </c>
       <c r="G313" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H313" s="6" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I313" s="13" t="n">
         <v>8000</v>
@@ -15342,7 +15342,7 @@
         <v>80</v>
       </c>
       <c r="L313" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M313" t="inlineStr"/>
     </row>
@@ -15372,10 +15372,10 @@
         </is>
       </c>
       <c r="G314" s="14" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H314" s="16" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I314" s="17" t="n">
         <v>8000</v>
@@ -15387,7 +15387,7 @@
         <v>100</v>
       </c>
       <c r="L314" s="14" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M314" s="14" t="inlineStr"/>
     </row>
@@ -15417,10 +15417,10 @@
         </is>
       </c>
       <c r="G315" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H315" s="6" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I315" s="13" t="n">
         <v>8000</v>
@@ -15432,7 +15432,7 @@
         <v>70</v>
       </c>
       <c r="L315" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M315" t="inlineStr"/>
     </row>
@@ -15462,10 +15462,10 @@
         </is>
       </c>
       <c r="G316" s="14" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H316" s="16" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="I316" s="17" t="n">
         <v>24000</v>
@@ -15477,7 +15477,7 @@
         <v>100</v>
       </c>
       <c r="L316" s="14" t="n">
-        <v>14</v>
+        <v>46.8</v>
       </c>
       <c r="M316" s="14" t="inlineStr"/>
     </row>
@@ -15507,10 +15507,10 @@
         </is>
       </c>
       <c r="G317" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H317" s="6" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I317" s="13" t="n">
         <v>8000</v>
@@ -15522,7 +15522,7 @@
         <v>80</v>
       </c>
       <c r="L317" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M317" t="inlineStr"/>
     </row>
@@ -15552,10 +15552,10 @@
         </is>
       </c>
       <c r="G318" s="14" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H318" s="16" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I318" s="17" t="n">
         <v>8000</v>
@@ -15567,7 +15567,7 @@
         <v>80</v>
       </c>
       <c r="L318" s="14" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M318" s="14" t="inlineStr"/>
     </row>
@@ -15597,10 +15597,10 @@
         </is>
       </c>
       <c r="G319" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H319" s="6" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I319" s="13" t="n">
         <v>8000</v>
@@ -15612,7 +15612,7 @@
         <v>90</v>
       </c>
       <c r="L319" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M319" t="inlineStr"/>
     </row>
@@ -15642,10 +15642,10 @@
         </is>
       </c>
       <c r="G320" s="14" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H320" s="16" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I320" s="17" t="n">
         <v>8000</v>
@@ -15657,7 +15657,7 @@
         <v>80</v>
       </c>
       <c r="L320" s="14" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M320" s="14" t="inlineStr"/>
     </row>
@@ -15687,10 +15687,10 @@
         </is>
       </c>
       <c r="G321" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H321" s="6" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I321" s="13" t="n">
         <v>8000</v>
@@ -15702,7 +15702,7 @@
         <v>90</v>
       </c>
       <c r="L321" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M321" t="inlineStr"/>
     </row>
@@ -15732,10 +15732,10 @@
         </is>
       </c>
       <c r="G322" s="14" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H322" s="16" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I322" s="17" t="n">
         <v>8000</v>
@@ -15747,7 +15747,7 @@
         <v>100</v>
       </c>
       <c r="L322" s="14" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M322" s="14" t="inlineStr"/>
     </row>
@@ -15777,10 +15777,10 @@
         </is>
       </c>
       <c r="G323" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H323" s="6" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="I323" s="13" t="n">
         <v>24000</v>
@@ -15792,7 +15792,7 @@
         <v>100</v>
       </c>
       <c r="L323" t="n">
-        <v>14</v>
+        <v>46.8</v>
       </c>
       <c r="M323" t="inlineStr"/>
     </row>
@@ -15822,10 +15822,10 @@
         </is>
       </c>
       <c r="G324" s="14" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H324" s="16" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I324" s="17" t="n">
         <v>8000</v>
@@ -15837,7 +15837,7 @@
         <v>90</v>
       </c>
       <c r="L324" s="14" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M324" s="14" t="inlineStr"/>
     </row>
@@ -15867,10 +15867,10 @@
         </is>
       </c>
       <c r="G325" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H325" s="6" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I325" s="13" t="n">
         <v>8000</v>
@@ -15882,7 +15882,7 @@
         <v>80</v>
       </c>
       <c r="L325" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M325" t="inlineStr"/>
     </row>
@@ -15912,10 +15912,10 @@
         </is>
       </c>
       <c r="G326" s="14" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H326" s="16" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I326" s="17" t="n">
         <v>8000</v>
@@ -15927,7 +15927,7 @@
         <v>80</v>
       </c>
       <c r="L326" s="14" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M326" s="14" t="inlineStr"/>
     </row>
@@ -15957,10 +15957,10 @@
         </is>
       </c>
       <c r="G327" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H327" s="6" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I327" s="13" t="n">
         <v>8000</v>
@@ -15972,7 +15972,7 @@
         <v>80</v>
       </c>
       <c r="L327" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M327" t="inlineStr"/>
     </row>
@@ -16002,10 +16002,10 @@
         </is>
       </c>
       <c r="G328" s="14" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H328" s="16" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I328" s="17" t="n">
         <v>8000</v>
@@ -16017,7 +16017,7 @@
         <v>80</v>
       </c>
       <c r="L328" s="14" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M328" s="14" t="inlineStr"/>
     </row>
@@ -16047,10 +16047,10 @@
         </is>
       </c>
       <c r="G329" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H329" s="6" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I329" s="13" t="n">
         <v>8000</v>
@@ -16062,7 +16062,7 @@
         <v>80</v>
       </c>
       <c r="L329" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M329" t="inlineStr"/>
     </row>
@@ -16092,10 +16092,10 @@
         </is>
       </c>
       <c r="G330" s="14" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H330" s="16" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I330" s="17" t="n">
         <v>8000</v>
@@ -16107,7 +16107,7 @@
         <v>90</v>
       </c>
       <c r="L330" s="14" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M330" s="14" t="inlineStr"/>
     </row>
@@ -16137,10 +16137,10 @@
         </is>
       </c>
       <c r="G331" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H331" s="6" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I331" s="13" t="n">
         <v>8000</v>
@@ -16152,7 +16152,7 @@
         <v>60</v>
       </c>
       <c r="L331" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M331" t="inlineStr"/>
     </row>
@@ -16182,10 +16182,10 @@
         </is>
       </c>
       <c r="G332" s="14" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H332" s="16" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I332" s="17" t="n">
         <v>8000</v>
@@ -16197,7 +16197,7 @@
         <v>80</v>
       </c>
       <c r="L332" s="14" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M332" s="14" t="inlineStr"/>
     </row>
@@ -16227,10 +16227,10 @@
         </is>
       </c>
       <c r="G333" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H333" s="6" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I333" s="13" t="n">
         <v>8000</v>
@@ -16242,7 +16242,7 @@
         <v>90</v>
       </c>
       <c r="L333" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M333" t="inlineStr"/>
     </row>
@@ -16272,10 +16272,10 @@
         </is>
       </c>
       <c r="G334" s="14" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H334" s="16" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I334" s="17" t="n">
         <v>8000</v>
@@ -16287,7 +16287,7 @@
         <v>80</v>
       </c>
       <c r="L334" s="14" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M334" s="14" t="inlineStr"/>
     </row>
@@ -16317,10 +16317,10 @@
         </is>
       </c>
       <c r="G335" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H335" s="6" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I335" s="13" t="n">
         <v>8000</v>
@@ -16332,7 +16332,7 @@
         <v>80</v>
       </c>
       <c r="L335" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M335" t="inlineStr"/>
     </row>
@@ -16362,10 +16362,10 @@
         </is>
       </c>
       <c r="G336" s="14" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H336" s="16" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I336" s="17" t="n">
         <v>8000</v>
@@ -16377,7 +16377,7 @@
         <v>80</v>
       </c>
       <c r="L336" s="14" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M336" s="14" t="inlineStr"/>
     </row>
@@ -16407,10 +16407,10 @@
         </is>
       </c>
       <c r="G337" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H337" s="6" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I337" s="13" t="n">
         <v>8000</v>
@@ -16422,7 +16422,7 @@
         <v>80</v>
       </c>
       <c r="L337" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M337" t="inlineStr"/>
     </row>
@@ -16452,10 +16452,10 @@
         </is>
       </c>
       <c r="G338" s="14" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H338" s="16" t="n">
-        <v>73000</v>
+        <v>100000</v>
       </c>
       <c r="I338" s="17" t="n">
         <v>4000</v>
@@ -16467,7 +16467,7 @@
         <v>50</v>
       </c>
       <c r="L338" s="14" t="n">
-        <v>2.3</v>
+        <v>7.8</v>
       </c>
       <c r="M338" s="14" t="inlineStr"/>
     </row>
@@ -16497,10 +16497,10 @@
         </is>
       </c>
       <c r="G339" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H339" s="6" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I339" s="13" t="n">
         <v>8000</v>
@@ -16512,7 +16512,7 @@
         <v>80</v>
       </c>
       <c r="L339" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M339" t="inlineStr"/>
     </row>
@@ -16542,10 +16542,10 @@
         </is>
       </c>
       <c r="G340" s="14" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H340" s="16" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I340" s="17" t="n">
         <v>8000</v>
@@ -16557,7 +16557,7 @@
         <v>80</v>
       </c>
       <c r="L340" s="14" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M340" s="14" t="inlineStr"/>
     </row>
@@ -16587,10 +16587,10 @@
         </is>
       </c>
       <c r="G341" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H341" s="6" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I341" s="13" t="n">
         <v>8000</v>
@@ -16602,7 +16602,7 @@
         <v>80</v>
       </c>
       <c r="L341" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M341" t="inlineStr"/>
     </row>
@@ -16632,10 +16632,10 @@
         </is>
       </c>
       <c r="G342" s="14" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H342" s="16" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="I342" s="17" t="n">
         <v>8000</v>
@@ -16647,7 +16647,7 @@
         <v>80</v>
       </c>
       <c r="L342" s="14" t="n">
-        <v>4.7</v>
+        <v>15.6</v>
       </c>
       <c r="M342" s="14" t="inlineStr"/>
     </row>
@@ -16719,13 +16719,13 @@
         <v>107</v>
       </c>
       <c r="C3" s="6" t="n">
-        <v>9449000</v>
+        <v>18100000</v>
       </c>
       <c r="D3" t="n">
         <v>31.5</v>
       </c>
       <c r="E3" t="n">
-        <v>27.2</v>
+        <v>30.5</v>
       </c>
     </row>
     <row r="4">
@@ -16738,13 +16738,13 @@
         <v>53</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>7157000</v>
+        <v>10650000</v>
       </c>
       <c r="D4" t="n">
         <v>15.6</v>
       </c>
       <c r="E4" t="n">
-        <v>20.6</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5">
@@ -16757,13 +16757,13 @@
         <v>36</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>4284000</v>
+        <v>7000000</v>
       </c>
       <c r="D5" t="n">
         <v>10.6</v>
       </c>
       <c r="E5" t="n">
-        <v>12.4</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="6">
@@ -16776,13 +16776,13 @@
         <v>71</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>5853000</v>
+        <v>11500000</v>
       </c>
       <c r="D6" t="n">
         <v>20.9</v>
       </c>
       <c r="E6" t="n">
-        <v>16.9</v>
+        <v>19.4</v>
       </c>
     </row>
     <row r="7">
@@ -16795,13 +16795,13 @@
         <v>61</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>6900000</v>
+        <v>10350000</v>
       </c>
       <c r="D7" t="n">
         <v>17.9</v>
       </c>
       <c r="E7" t="n">
-        <v>19.9</v>
+        <v>17.4</v>
       </c>
     </row>
     <row r="8">
@@ -16814,13 +16814,13 @@
         <v>12</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>1038000</v>
+        <v>1723000</v>
       </c>
       <c r="D8" t="n">
         <v>3.5</v>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="9">
@@ -16833,7 +16833,7 @@
         <v>340</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>34681000</v>
+        <v>59323000</v>
       </c>
     </row>
   </sheetData>
@@ -16896,16 +16896,16 @@
         <v>6</v>
       </c>
       <c r="B3" t="n">
-        <v>147</v>
+        <v>1</v>
       </c>
       <c r="C3" s="6" t="n">
         <v>73000</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>10731000</v>
+        <v>73000</v>
       </c>
       <c r="E3" t="n">
-        <v>43.2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="4">
@@ -16913,16 +16913,16 @@
         <v>12</v>
       </c>
       <c r="B4" t="n">
-        <v>122</v>
+        <v>29</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>100000</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>12200000</v>
+        <v>2900000</v>
       </c>
       <c r="E4" t="n">
-        <v>35.9</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="5">
@@ -16930,16 +16930,16 @@
         <v>20</v>
       </c>
       <c r="B5" t="n">
-        <v>55</v>
+        <v>200</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>150000</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>8250000</v>
+        <v>30000000</v>
       </c>
       <c r="E5" t="n">
-        <v>16.2</v>
+        <v>58.8</v>
       </c>
     </row>
     <row r="6">
@@ -16947,16 +16947,16 @@
         <v>30</v>
       </c>
       <c r="B6" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>200000</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>2000000</v>
+        <v>4600000</v>
       </c>
       <c r="E6" t="n">
-        <v>2.9</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="7">
@@ -16964,16 +16964,16 @@
         <v>50</v>
       </c>
       <c r="B7" t="n">
-        <v>6</v>
+        <v>87</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>250000</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>1500000</v>
+        <v>21750000</v>
       </c>
       <c r="E7" t="n">
-        <v>1.8</v>
+        <v>25.6</v>
       </c>
     </row>
     <row r="8">
@@ -16986,7 +16986,7 @@
         <v>340</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>34681000</v>
+        <v>59323000</v>
       </c>
     </row>
   </sheetData>

--- a/budget_shelters_v2.xlsx
+++ b/budget_shelters_v2.xlsx
@@ -588,7 +588,7 @@
         <v>150000</v>
       </c>
       <c r="C8" t="n">
-        <v>200</v>
+        <v>183</v>
       </c>
       <c r="D8" s="6">
         <f>B8*C8</f>
@@ -618,7 +618,7 @@
         <v>250000</v>
       </c>
       <c r="C10" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D10" s="6">
         <f>B10*C10</f>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>340</v>
+        <v>322</v>
       </c>
     </row>
     <row r="19">
@@ -716,11 +716,11 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>עלות תחזוקה שנתית (340 מיגוניות)</t>
+          <t>עלות תחזוקה שנתית (322 מיגוניות)</t>
         </is>
       </c>
       <c r="B22" s="6">
-        <f>B15*340</f>
+        <f>B15*322</f>
         <v/>
       </c>
     </row>
@@ -731,14 +731,14 @@
         </is>
       </c>
       <c r="B23" s="7">
-        <f>D11*(1+B14/100)+B15*340*10</f>
+        <f>D11*(1+B14/100)+B15*322*10</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>הערות: עלויות ללא מע"מ. מבוסס על אלגוריתם Gonzalez k-center | תקן 5 דקות | 340 מיגוניות | ישראל בלבד (קו ירוק 1967) | קיבולת מחושבת לפי תנועה בשעת שיא בזמן מלחמה (10% מתנועה רגילה)</t>
+          <t>הערות: עלויות ללא מע"מ. מבוסס על אלגוריתם Gonzalez k-center | תקן 5 דקות | 322 מיגוניות | ישראל בלבד (קו ירוק 1967) | קיבולת מחושבת לפי תנועה בשעת שיא בזמן מלחמה (10% מתנועה רגילה)</t>
         </is>
       </c>
     </row>
@@ -757,7 +757,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M342"/>
+  <dimension ref="A1:M324"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -778,7 +778,7 @@
     <row r="1">
       <c r="A1" s="10" t="inlineStr">
         <is>
-          <t>רשימת מיגוניות מלאה — 340 יחידות</t>
+          <t>רשימת מיגוניות מלאה — 322 יחידות</t>
         </is>
       </c>
     </row>
@@ -8684,17 +8684,17 @@
     </row>
     <row r="170">
       <c r="A170" s="14" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B170" s="15" t="n">
-        <v>31.73761</v>
+        <v>32.90057</v>
       </c>
       <c r="C170" s="15" t="n">
-        <v>35.15143</v>
+        <v>35.61115</v>
       </c>
       <c r="D170" s="14" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>87</t>
         </is>
       </c>
       <c r="E170" s="14" t="inlineStr">
@@ -8704,7 +8704,7 @@
       </c>
       <c r="F170" s="14" t="inlineStr">
         <is>
-          <t>ירושלים / שפלה</t>
+          <t>חיפה / כרמל</t>
         </is>
       </c>
       <c r="G170" s="14" t="n">
@@ -8726,32 +8726,32 @@
         <v>15.6</v>
       </c>
       <c r="M170" s="14" t="n">
-        <v>15450</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B171" s="12" t="n">
-        <v>32.90057</v>
+        <v>30.93828</v>
       </c>
       <c r="C171" s="12" t="n">
-        <v>35.61115</v>
+        <v>34.58878</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>211</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>רגיל</t>
+          <t>עוטף עזה</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>חיפה / כרמל</t>
+          <t>עוטף עזה / הנגב המערבי</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -8767,24 +8767,22 @@
         <v>800</v>
       </c>
       <c r="K171" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="L171" t="n">
         <v>15.6</v>
       </c>
-      <c r="M171" t="n">
-        <v>2007</v>
-      </c>
+      <c r="M171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="14" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B172" s="15" t="n">
-        <v>30.93828</v>
+        <v>30.90461</v>
       </c>
       <c r="C172" s="15" t="n">
-        <v>34.58878</v>
+        <v>34.49691</v>
       </c>
       <c r="D172" s="14" t="inlineStr">
         <is>
@@ -8823,27 +8821,27 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B173" s="12" t="n">
-        <v>30.90461</v>
+        <v>32.87232</v>
       </c>
       <c r="C173" s="12" t="n">
-        <v>34.49691</v>
+        <v>35.54062</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>90</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>עוטף עזה</t>
+          <t>רגיל</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>עוטף עזה / הנגב המערבי</t>
+          <t>חיפה / כרמל</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -8853,32 +8851,34 @@
         <v>150000</v>
       </c>
       <c r="I173" s="13" t="n">
-        <v>8000</v>
+        <v>9000</v>
       </c>
       <c r="J173" s="13" t="n">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="K173" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="L173" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="M173" t="inlineStr"/>
+        <v>17.6</v>
+      </c>
+      <c r="M173" t="n">
+        <v>1983</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="14" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B174" s="15" t="n">
-        <v>32.87232</v>
+        <v>32.35022</v>
       </c>
       <c r="C174" s="15" t="n">
-        <v>35.54062</v>
+        <v>35.00667</v>
       </c>
       <c r="D174" s="14" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>582</t>
         </is>
       </c>
       <c r="E174" s="14" t="inlineStr">
@@ -8888,7 +8888,7 @@
       </c>
       <c r="F174" s="14" t="inlineStr">
         <is>
-          <t>חיפה / כרמל</t>
+          <t>מרכז (שרון / גוש דן)</t>
         </is>
       </c>
       <c r="G174" s="14" t="n">
@@ -8898,44 +8898,44 @@
         <v>150000</v>
       </c>
       <c r="I174" s="17" t="n">
-        <v>9000</v>
+        <v>8000</v>
       </c>
       <c r="J174" s="17" t="n">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="K174" s="14" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="L174" s="14" t="n">
-        <v>17.6</v>
+        <v>15.6</v>
       </c>
       <c r="M174" s="14" t="n">
-        <v>1983</v>
+        <v>14477</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B175" s="12" t="n">
-        <v>32.35022</v>
+        <v>30.8825</v>
       </c>
       <c r="C175" s="12" t="n">
-        <v>35.00667</v>
+        <v>34.39305</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>רגיל</t>
+          <t>עוטף עזה</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>מרכז (שרון / גוש דן)</t>
+          <t>עוטף עזה / הנגב המערבי</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -8951,38 +8951,36 @@
         <v>800</v>
       </c>
       <c r="K175" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="L175" t="n">
         <v>15.6</v>
       </c>
-      <c r="M175" t="n">
-        <v>14477</v>
-      </c>
+      <c r="M175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="14" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B176" s="15" t="n">
-        <v>30.8825</v>
+        <v>32.36079</v>
       </c>
       <c r="C176" s="15" t="n">
-        <v>34.39305</v>
+        <v>34.86679</v>
       </c>
       <c r="D176" s="14" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>כביש החוף</t>
         </is>
       </c>
       <c r="E176" s="14" t="inlineStr">
         <is>
-          <t>עוטף עזה</t>
+          <t>רגיל</t>
         </is>
       </c>
       <c r="F176" s="14" t="inlineStr">
         <is>
-          <t>עוטף עזה / הנגב המערבי</t>
+          <t>מרכז (שרון / גוש דן)</t>
         </is>
       </c>
       <c r="G176" s="14" t="n">
@@ -8998,36 +8996,38 @@
         <v>800</v>
       </c>
       <c r="K176" s="14" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="L176" s="14" t="n">
         <v>15.6</v>
       </c>
-      <c r="M176" s="14" t="inlineStr"/>
+      <c r="M176" s="14" t="n">
+        <v>13656</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B177" s="12" t="n">
-        <v>32.36079</v>
+        <v>31.32146</v>
       </c>
       <c r="C177" s="12" t="n">
-        <v>34.86679</v>
+        <v>34.88618</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>כביש החוף</t>
+          <t>31</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>רגיל</t>
+          <t>עוטף עזה</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>מרכז (שרון / גוש דן)</t>
+          <t>עוטף עזה / הנגב המערבי</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -9037,81 +9037,81 @@
         <v>150000</v>
       </c>
       <c r="I177" s="13" t="n">
-        <v>8000</v>
+        <v>6500</v>
       </c>
       <c r="J177" s="13" t="n">
-        <v>800</v>
+        <v>650</v>
       </c>
       <c r="K177" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="L177" t="n">
-        <v>15.6</v>
+        <v>12.7</v>
       </c>
       <c r="M177" t="n">
-        <v>13656</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="14" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B178" s="15" t="n">
-        <v>31.32146</v>
+        <v>31.69666</v>
       </c>
       <c r="C178" s="15" t="n">
-        <v>34.88618</v>
+        <v>35.01068</v>
       </c>
       <c r="D178" s="14" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>עוקף בית שמש</t>
         </is>
       </c>
       <c r="E178" s="14" t="inlineStr">
         <is>
-          <t>עוטף עזה</t>
+          <t>רגיל</t>
         </is>
       </c>
       <c r="F178" s="14" t="inlineStr">
         <is>
-          <t>עוטף עזה / הנגב המערבי</t>
+          <t>ירושלים / שפלה</t>
         </is>
       </c>
       <c r="G178" s="14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H178" s="16" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I178" s="17" t="n">
-        <v>6500</v>
+        <v>4000</v>
       </c>
       <c r="J178" s="17" t="n">
-        <v>650</v>
+        <v>400</v>
       </c>
       <c r="K178" s="14" t="n">
         <v>70</v>
       </c>
       <c r="L178" s="14" t="n">
-        <v>12.7</v>
+        <v>7.8</v>
       </c>
       <c r="M178" s="14" t="n">
-        <v>1062</v>
+        <v>12387</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B179" s="12" t="n">
-        <v>31.69666</v>
+        <v>32.68643</v>
       </c>
       <c r="C179" s="12" t="n">
-        <v>35.01068</v>
+        <v>35.06666</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>עוקף בית שמש</t>
+          <t>672</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -9121,44 +9121,44 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>ירושלים / שפלה</t>
+          <t>חיפה / כרמל</t>
         </is>
       </c>
       <c r="G179" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H179" s="6" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I179" s="13" t="n">
-        <v>4000</v>
+        <v>8000</v>
       </c>
       <c r="J179" s="13" t="n">
-        <v>400</v>
+        <v>800</v>
       </c>
       <c r="K179" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="L179" t="n">
-        <v>7.8</v>
+        <v>15.6</v>
       </c>
       <c r="M179" t="n">
-        <v>12387</v>
+        <v>4929</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="14" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B180" s="15" t="n">
-        <v>32.68643</v>
+        <v>31.45936</v>
       </c>
       <c r="C180" s="15" t="n">
-        <v>35.06666</v>
+        <v>34.91479</v>
       </c>
       <c r="D180" s="14" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>358</t>
         </is>
       </c>
       <c r="E180" s="14" t="inlineStr">
@@ -9168,7 +9168,7 @@
       </c>
       <c r="F180" s="14" t="inlineStr">
         <is>
-          <t>חיפה / כרמל</t>
+          <t>נגב / ערבה</t>
         </is>
       </c>
       <c r="G180" s="14" t="n">
@@ -9184,28 +9184,28 @@
         <v>800</v>
       </c>
       <c r="K180" s="14" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="L180" s="14" t="n">
         <v>15.6</v>
       </c>
       <c r="M180" s="14" t="n">
-        <v>4929</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B181" s="12" t="n">
-        <v>31.45936</v>
+        <v>32.70048</v>
       </c>
       <c r="C181" s="12" t="n">
-        <v>34.91479</v>
+        <v>35.20778</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>דרך העמקים</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -9215,44 +9215,44 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>נגב / ערבה</t>
+          <t>חיפה / כרמל</t>
         </is>
       </c>
       <c r="G181" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H181" s="6" t="n">
-        <v>150000</v>
+        <v>200000</v>
       </c>
       <c r="I181" s="13" t="n">
-        <v>8000</v>
+        <v>14000</v>
       </c>
       <c r="J181" s="13" t="n">
-        <v>800</v>
+        <v>1400</v>
       </c>
       <c r="K181" t="n">
         <v>80</v>
       </c>
       <c r="L181" t="n">
-        <v>15.6</v>
+        <v>27.3</v>
       </c>
       <c r="M181" t="n">
-        <v>1527</v>
+        <v>5140</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="14" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B182" s="15" t="n">
-        <v>32.70048</v>
+        <v>31.5361</v>
       </c>
       <c r="C182" s="15" t="n">
-        <v>35.20778</v>
+        <v>34.92017</v>
       </c>
       <c r="D182" s="14" t="inlineStr">
         <is>
-          <t>דרך העמקים</t>
+          <t>358</t>
         </is>
       </c>
       <c r="E182" s="14" t="inlineStr">
@@ -9262,44 +9262,44 @@
       </c>
       <c r="F182" s="14" t="inlineStr">
         <is>
-          <t>חיפה / כרמל</t>
+          <t>ירושלים / שפלה</t>
         </is>
       </c>
       <c r="G182" s="14" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="H182" s="16" t="n">
-        <v>200000</v>
+        <v>100000</v>
       </c>
       <c r="I182" s="17" t="n">
-        <v>14000</v>
+        <v>4000</v>
       </c>
       <c r="J182" s="17" t="n">
-        <v>1400</v>
+        <v>400</v>
       </c>
       <c r="K182" s="14" t="n">
         <v>80</v>
       </c>
       <c r="L182" s="14" t="n">
-        <v>27.3</v>
+        <v>7.8</v>
       </c>
       <c r="M182" s="14" t="n">
-        <v>5140</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B183" s="12" t="n">
-        <v>31.5361</v>
+        <v>32.8454</v>
       </c>
       <c r="C183" s="12" t="n">
-        <v>34.92017</v>
+        <v>35.51626</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>90</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -9309,44 +9309,44 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>ירושלים / שפלה</t>
+          <t>חיפה / כרמל</t>
         </is>
       </c>
       <c r="G183" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H183" s="6" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I183" s="13" t="n">
-        <v>4000</v>
+        <v>9000</v>
       </c>
       <c r="J183" s="13" t="n">
-        <v>400</v>
+        <v>900</v>
       </c>
       <c r="K183" t="n">
         <v>80</v>
       </c>
       <c r="L183" t="n">
-        <v>7.8</v>
+        <v>17.6</v>
       </c>
       <c r="M183" t="n">
-        <v>1527</v>
+        <v>1983</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="14" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B184" s="15" t="n">
-        <v>32.8454</v>
+        <v>32.38111</v>
       </c>
       <c r="C184" s="15" t="n">
-        <v>35.51626</v>
+        <v>34.99238</v>
       </c>
       <c r="D184" s="14" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>581</t>
         </is>
       </c>
       <c r="E184" s="14" t="inlineStr">
@@ -9356,44 +9356,44 @@
       </c>
       <c r="F184" s="14" t="inlineStr">
         <is>
-          <t>חיפה / כרמל</t>
+          <t>מרכז (שרון / גוש דן)</t>
         </is>
       </c>
       <c r="G184" s="14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H184" s="16" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I184" s="17" t="n">
-        <v>9000</v>
+        <v>4000</v>
       </c>
       <c r="J184" s="17" t="n">
-        <v>900</v>
+        <v>400</v>
       </c>
       <c r="K184" s="14" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="L184" s="14" t="n">
-        <v>17.6</v>
+        <v>7.8</v>
       </c>
       <c r="M184" s="14" t="n">
-        <v>1983</v>
+        <v>12669</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B185" s="12" t="n">
-        <v>32.38111</v>
+        <v>32.38041</v>
       </c>
       <c r="C185" s="12" t="n">
-        <v>34.99238</v>
+        <v>34.90748</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>כביש חיפה רעננה</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -9407,40 +9407,40 @@
         </is>
       </c>
       <c r="G185" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H185" s="6" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I185" s="13" t="n">
-        <v>4000</v>
+        <v>8000</v>
       </c>
       <c r="J185" s="13" t="n">
-        <v>400</v>
+        <v>800</v>
       </c>
       <c r="K185" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="L185" t="n">
-        <v>7.8</v>
+        <v>15.6</v>
       </c>
       <c r="M185" t="n">
-        <v>12669</v>
+        <v>12584</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="14" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B186" s="15" t="n">
-        <v>32.38041</v>
+        <v>32.70974</v>
       </c>
       <c r="C186" s="15" t="n">
-        <v>34.90748</v>
+        <v>34.95217</v>
       </c>
       <c r="D186" s="14" t="inlineStr">
         <is>
-          <t>כביש חיפה רעננה</t>
+          <t>כביש החוף</t>
         </is>
       </c>
       <c r="E186" s="14" t="inlineStr">
@@ -9450,7 +9450,7 @@
       </c>
       <c r="F186" s="14" t="inlineStr">
         <is>
-          <t>מרכז (שרון / גוש דן)</t>
+          <t>חיפה / כרמל</t>
         </is>
       </c>
       <c r="G186" s="14" t="n">
@@ -9466,75 +9466,75 @@
         <v>800</v>
       </c>
       <c r="K186" s="14" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="L186" s="14" t="n">
         <v>15.6</v>
       </c>
       <c r="M186" s="14" t="n">
-        <v>12584</v>
+        <v>2891</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B187" s="12" t="n">
-        <v>32.70974</v>
+        <v>31.11922</v>
       </c>
       <c r="C187" s="12" t="n">
-        <v>34.95217</v>
+        <v>34.81323</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>כביש החוף</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>רגיל</t>
+          <t>עוטף עזה</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>חיפה / כרמל</t>
+          <t>עוטף עזה / הנגב המערבי</t>
         </is>
       </c>
       <c r="G187" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H187" s="6" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="I187" s="13" t="n">
-        <v>8000</v>
+        <v>22000</v>
       </c>
       <c r="J187" s="13" t="n">
-        <v>800</v>
+        <v>2200</v>
       </c>
       <c r="K187" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="L187" t="n">
-        <v>15.6</v>
+        <v>42.9</v>
       </c>
       <c r="M187" t="n">
-        <v>2891</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="14" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B188" s="15" t="n">
-        <v>31.11922</v>
+        <v>30.95655</v>
       </c>
       <c r="C188" s="15" t="n">
-        <v>34.81323</v>
+        <v>34.67235</v>
       </c>
       <c r="D188" s="14" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>211</t>
         </is>
       </c>
       <c r="E188" s="14" t="inlineStr">
@@ -9548,50 +9548,48 @@
         </is>
       </c>
       <c r="G188" s="14" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H188" s="16" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="I188" s="17" t="n">
-        <v>22000</v>
+        <v>8000</v>
       </c>
       <c r="J188" s="17" t="n">
-        <v>2200</v>
+        <v>800</v>
       </c>
       <c r="K188" s="14" t="n">
         <v>90</v>
       </c>
       <c r="L188" s="14" t="n">
-        <v>42.9</v>
-      </c>
-      <c r="M188" s="14" t="n">
-        <v>1014</v>
-      </c>
+        <v>15.6</v>
+      </c>
+      <c r="M188" s="14" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B189" s="12" t="n">
-        <v>30.95655</v>
+        <v>32.75307</v>
       </c>
       <c r="C189" s="12" t="n">
-        <v>34.67235</v>
+        <v>35.34331</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>754</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>עוטף עזה</t>
+          <t>רגיל</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>עוטף עזה / הנגב המערבי</t>
+          <t>חיפה / כרמל</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -9607,26 +9605,28 @@
         <v>800</v>
       </c>
       <c r="K189" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="L189" t="n">
         <v>15.6</v>
       </c>
-      <c r="M189" t="inlineStr"/>
+      <c r="M189" t="n">
+        <v>3495</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="14" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B190" s="15" t="n">
-        <v>32.75307</v>
+        <v>32.39689</v>
       </c>
       <c r="C190" s="15" t="n">
-        <v>35.34331</v>
+        <v>34.92828</v>
       </c>
       <c r="D190" s="14" t="inlineStr">
         <is>
-          <t>754</t>
+          <t>581</t>
         </is>
       </c>
       <c r="E190" s="14" t="inlineStr">
@@ -9636,44 +9636,44 @@
       </c>
       <c r="F190" s="14" t="inlineStr">
         <is>
-          <t>חיפה / כרמל</t>
+          <t>מרכז (שרון / גוש דן)</t>
         </is>
       </c>
       <c r="G190" s="14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H190" s="16" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I190" s="17" t="n">
-        <v>8000</v>
+        <v>4000</v>
       </c>
       <c r="J190" s="17" t="n">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="K190" s="14" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="L190" s="14" t="n">
-        <v>15.6</v>
+        <v>7.8</v>
       </c>
       <c r="M190" s="14" t="n">
-        <v>3495</v>
+        <v>11583</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B191" s="12" t="n">
-        <v>32.39689</v>
+        <v>32.395</v>
       </c>
       <c r="C191" s="12" t="n">
-        <v>34.92828</v>
+        <v>34.87165</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>כביש החוף</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -9687,40 +9687,40 @@
         </is>
       </c>
       <c r="G191" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H191" s="6" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I191" s="13" t="n">
-        <v>4000</v>
+        <v>8000</v>
       </c>
       <c r="J191" s="13" t="n">
-        <v>400</v>
+        <v>800</v>
       </c>
       <c r="K191" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="L191" t="n">
-        <v>7.8</v>
+        <v>15.6</v>
       </c>
       <c r="M191" t="n">
-        <v>11583</v>
+        <v>11283</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="14" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B192" s="15" t="n">
-        <v>32.395</v>
+        <v>32.36165</v>
       </c>
       <c r="C192" s="15" t="n">
-        <v>34.87165</v>
+        <v>35.02999</v>
       </c>
       <c r="D192" s="14" t="inlineStr">
         <is>
-          <t>כביש החוף</t>
+          <t>574</t>
         </is>
       </c>
       <c r="E192" s="14" t="inlineStr">
@@ -9746,28 +9746,28 @@
         <v>800</v>
       </c>
       <c r="K192" s="14" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="L192" s="14" t="n">
         <v>15.6</v>
       </c>
       <c r="M192" s="14" t="n">
-        <v>11283</v>
+        <v>11155</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B193" s="12" t="n">
-        <v>32.36165</v>
+        <v>31.31604</v>
       </c>
       <c r="C193" s="12" t="n">
-        <v>35.02999</v>
+        <v>34.91218</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>574</t>
+          <t>60</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -9777,44 +9777,44 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>מרכז (שרון / גוש דן)</t>
+          <t>נגב / ערבה</t>
         </is>
       </c>
       <c r="G193" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H193" s="6" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="I193" s="13" t="n">
-        <v>8000</v>
+        <v>16000</v>
       </c>
       <c r="J193" s="13" t="n">
-        <v>800</v>
+        <v>1600</v>
       </c>
       <c r="K193" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="L193" t="n">
-        <v>15.6</v>
+        <v>31.2</v>
       </c>
       <c r="M193" t="n">
-        <v>11155</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="14" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B194" s="15" t="n">
-        <v>31.31604</v>
+        <v>32.67418</v>
       </c>
       <c r="C194" s="15" t="n">
-        <v>34.91218</v>
+        <v>35.10376</v>
       </c>
       <c r="D194" s="14" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>כביש חוצה ישראל</t>
         </is>
       </c>
       <c r="E194" s="14" t="inlineStr">
@@ -9824,44 +9824,44 @@
       </c>
       <c r="F194" s="14" t="inlineStr">
         <is>
-          <t>נגב / ערבה</t>
+          <t>חיפה / כרמל</t>
         </is>
       </c>
       <c r="G194" s="14" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H194" s="16" t="n">
-        <v>250000</v>
+        <v>200000</v>
       </c>
       <c r="I194" s="17" t="n">
-        <v>16000</v>
+        <v>13000</v>
       </c>
       <c r="J194" s="17" t="n">
-        <v>1600</v>
+        <v>1300</v>
       </c>
       <c r="K194" s="14" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="L194" s="14" t="n">
-        <v>31.2</v>
+        <v>25.3</v>
       </c>
       <c r="M194" s="14" t="n">
-        <v>1287</v>
+        <v>4459</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B195" s="12" t="n">
-        <v>32.67418</v>
+        <v>32.76387</v>
       </c>
       <c r="C195" s="12" t="n">
-        <v>35.10376</v>
+        <v>35.37519</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>כביש חוצה ישראל</t>
+          <t>77</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -9875,40 +9875,40 @@
         </is>
       </c>
       <c r="G195" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="H195" s="6" t="n">
-        <v>200000</v>
+        <v>250000</v>
       </c>
       <c r="I195" s="13" t="n">
-        <v>13000</v>
+        <v>19000</v>
       </c>
       <c r="J195" s="13" t="n">
-        <v>1300</v>
+        <v>1900</v>
       </c>
       <c r="K195" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="L195" t="n">
-        <v>25.3</v>
+        <v>37.1</v>
       </c>
       <c r="M195" t="n">
-        <v>4459</v>
+        <v>2598</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="14" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B196" s="15" t="n">
-        <v>32.76387</v>
+        <v>31.50673</v>
       </c>
       <c r="C196" s="15" t="n">
-        <v>35.37519</v>
+        <v>34.94324</v>
       </c>
       <c r="D196" s="14" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>358</t>
         </is>
       </c>
       <c r="E196" s="14" t="inlineStr">
@@ -9918,44 +9918,44 @@
       </c>
       <c r="F196" s="14" t="inlineStr">
         <is>
-          <t>חיפה / כרמל</t>
+          <t>ירושלים / שפלה</t>
         </is>
       </c>
       <c r="G196" s="14" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H196" s="16" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="I196" s="17" t="n">
-        <v>19000</v>
+        <v>8000</v>
       </c>
       <c r="J196" s="17" t="n">
-        <v>1900</v>
+        <v>800</v>
       </c>
       <c r="K196" s="14" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="L196" s="14" t="n">
-        <v>37.1</v>
+        <v>15.6</v>
       </c>
       <c r="M196" s="14" t="n">
-        <v>2598</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B197" s="12" t="n">
-        <v>31.50673</v>
+        <v>32.3855</v>
       </c>
       <c r="C197" s="12" t="n">
-        <v>34.94324</v>
+        <v>35.01922</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>כביש חוצה ישראל</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -9965,54 +9965,54 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>ירושלים / שפלה</t>
+          <t>מרכז (שרון / גוש דן)</t>
         </is>
       </c>
       <c r="G197" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H197" s="6" t="n">
-        <v>150000</v>
+        <v>200000</v>
       </c>
       <c r="I197" s="13" t="n">
-        <v>8000</v>
+        <v>13000</v>
       </c>
       <c r="J197" s="13" t="n">
-        <v>800</v>
+        <v>1300</v>
       </c>
       <c r="K197" t="n">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="L197" t="n">
-        <v>15.6</v>
+        <v>25.4</v>
       </c>
       <c r="M197" t="n">
-        <v>1527</v>
+        <v>10091</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="14" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B198" s="15" t="n">
-        <v>31.41642</v>
+        <v>30.96492</v>
       </c>
       <c r="C198" s="15" t="n">
-        <v>34.93574</v>
+        <v>34.71583</v>
       </c>
       <c r="D198" s="14" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>211</t>
         </is>
       </c>
       <c r="E198" s="14" t="inlineStr">
         <is>
-          <t>רגיל</t>
+          <t>עוטף עזה</t>
         </is>
       </c>
       <c r="F198" s="14" t="inlineStr">
         <is>
-          <t>נגב / ערבה</t>
+          <t>עוטף עזה / הנגב המערבי</t>
         </is>
       </c>
       <c r="G198" s="14" t="n">
@@ -10033,80 +10033,78 @@
       <c r="L198" s="14" t="n">
         <v>15.6</v>
       </c>
-      <c r="M198" s="14" t="n">
-        <v>1527</v>
-      </c>
+      <c r="M198" s="14" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="B199" s="12" t="n">
-        <v>32.3855</v>
+        <v>31.20745</v>
       </c>
       <c r="C199" s="12" t="n">
-        <v>35.01922</v>
+        <v>34.89689</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>כביש חוצה ישראל</t>
+          <t>25</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>רגיל</t>
+          <t>עוטף עזה</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>מרכז (שרון / גוש דן)</t>
+          <t>עוטף עזה / הנגב המערבי</t>
         </is>
       </c>
       <c r="G199" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H199" s="6" t="n">
-        <v>200000</v>
+        <v>150000</v>
       </c>
       <c r="I199" s="13" t="n">
-        <v>13000</v>
+        <v>7000</v>
       </c>
       <c r="J199" s="13" t="n">
-        <v>1300</v>
+        <v>700</v>
       </c>
       <c r="K199" t="n">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="L199" t="n">
-        <v>25.4</v>
+        <v>13.7</v>
       </c>
       <c r="M199" t="n">
-        <v>10091</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="14" t="n">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B200" s="15" t="n">
-        <v>30.96492</v>
+        <v>31.67529</v>
       </c>
       <c r="C200" s="15" t="n">
-        <v>34.71583</v>
+        <v>35.03189</v>
       </c>
       <c r="D200" s="14" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>367</t>
         </is>
       </c>
       <c r="E200" s="14" t="inlineStr">
         <is>
-          <t>עוטף עזה</t>
+          <t>רגיל</t>
         </is>
       </c>
       <c r="F200" s="14" t="inlineStr">
         <is>
-          <t>עוטף עזה / הנגב המערבי</t>
+          <t>ירושלים / שפלה</t>
         </is>
       </c>
       <c r="G200" s="14" t="n">
@@ -10127,68 +10125,70 @@
       <c r="L200" s="14" t="n">
         <v>15.6</v>
       </c>
-      <c r="M200" s="14" t="inlineStr"/>
+      <c r="M200" s="14" t="n">
+        <v>8965</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="B201" s="12" t="n">
-        <v>31.20745</v>
+        <v>31.593</v>
       </c>
       <c r="C201" s="12" t="n">
-        <v>34.89689</v>
+        <v>34.96153</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>35</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>עוטף עזה</t>
+          <t>רגיל</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>עוטף עזה / הנגב המערבי</t>
+          <t>ירושלים / שפלה</t>
         </is>
       </c>
       <c r="G201" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H201" s="6" t="n">
-        <v>150000</v>
+        <v>200000</v>
       </c>
       <c r="I201" s="13" t="n">
-        <v>7000</v>
+        <v>11000</v>
       </c>
       <c r="J201" s="13" t="n">
-        <v>700</v>
+        <v>1100</v>
       </c>
       <c r="K201" t="n">
         <v>90</v>
       </c>
       <c r="L201" t="n">
-        <v>13.7</v>
+        <v>21.4</v>
       </c>
       <c r="M201" t="n">
-        <v>1014</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="14" t="n">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B202" s="15" t="n">
-        <v>31.48628</v>
+        <v>32.72877</v>
       </c>
       <c r="C202" s="15" t="n">
-        <v>34.95581</v>
+        <v>35.32292</v>
       </c>
       <c r="D202" s="14" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>79</t>
         </is>
       </c>
       <c r="E202" s="14" t="inlineStr">
@@ -10198,7 +10198,7 @@
       </c>
       <c r="F202" s="14" t="inlineStr">
         <is>
-          <t>נגב / ערבה</t>
+          <t>חיפה / כרמל</t>
         </is>
       </c>
       <c r="G202" s="14" t="n">
@@ -10220,22 +10220,22 @@
         <v>15.6</v>
       </c>
       <c r="M202" s="14" t="n">
-        <v>1527</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B203" s="12" t="n">
-        <v>31.67529</v>
+        <v>32.39496</v>
       </c>
       <c r="C203" s="12" t="n">
-        <v>35.03189</v>
+        <v>35.04624</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>574</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -10245,7 +10245,7 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>ירושלים / שפלה</t>
+          <t>מרכז (שרון / גוש דן)</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -10267,22 +10267,22 @@
         <v>15.6</v>
       </c>
       <c r="M203" t="n">
-        <v>8965</v>
+        <v>8287</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="14" t="n">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="B204" s="15" t="n">
-        <v>31.593</v>
+        <v>32.41182</v>
       </c>
       <c r="C204" s="15" t="n">
-        <v>34.96153</v>
+        <v>35.01958</v>
       </c>
       <c r="D204" s="14" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E204" s="14" t="inlineStr">
@@ -10292,44 +10292,44 @@
       </c>
       <c r="F204" s="14" t="inlineStr">
         <is>
-          <t>ירושלים / שפלה</t>
+          <t>מרכז (שרון / גוש דן)</t>
         </is>
       </c>
       <c r="G204" s="14" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H204" s="16" t="n">
-        <v>200000</v>
+        <v>150000</v>
       </c>
       <c r="I204" s="17" t="n">
-        <v>11000</v>
+        <v>8000</v>
       </c>
       <c r="J204" s="17" t="n">
-        <v>1100</v>
+        <v>800</v>
       </c>
       <c r="K204" s="14" t="n">
         <v>90</v>
       </c>
       <c r="L204" s="14" t="n">
-        <v>21.4</v>
+        <v>15.6</v>
       </c>
       <c r="M204" s="14" t="n">
-        <v>1591</v>
+        <v>8249</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="B205" s="12" t="n">
-        <v>32.72877</v>
+        <v>31.34204</v>
       </c>
       <c r="C205" s="12" t="n">
-        <v>35.32292</v>
+        <v>34.93297</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>60</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -10339,138 +10339,134 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>חיפה / כרמל</t>
+          <t>נגב / ערבה</t>
         </is>
       </c>
       <c r="G205" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H205" s="6" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="I205" s="13" t="n">
-        <v>8000</v>
+        <v>16000</v>
       </c>
       <c r="J205" s="13" t="n">
-        <v>800</v>
+        <v>1600</v>
       </c>
       <c r="K205" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="L205" t="n">
-        <v>15.6</v>
+        <v>31.2</v>
       </c>
       <c r="M205" t="n">
-        <v>2016</v>
+        <v>273</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="14" t="n">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B206" s="15" t="n">
-        <v>32.39496</v>
+        <v>31.00948</v>
       </c>
       <c r="C206" s="15" t="n">
-        <v>35.04624</v>
+        <v>34.7797</v>
       </c>
       <c r="D206" s="14" t="inlineStr">
         <is>
-          <t>574</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E206" s="14" t="inlineStr">
         <is>
-          <t>רגיל</t>
+          <t>עוטף עזה</t>
         </is>
       </c>
       <c r="F206" s="14" t="inlineStr">
         <is>
-          <t>מרכז (שרון / גוש דן)</t>
+          <t>עוטף עזה / הנגב המערבי</t>
         </is>
       </c>
       <c r="G206" s="14" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H206" s="16" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="I206" s="17" t="n">
-        <v>8000</v>
+        <v>22000</v>
       </c>
       <c r="J206" s="17" t="n">
-        <v>800</v>
+        <v>2200</v>
       </c>
       <c r="K206" s="14" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="L206" s="14" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="M206" s="14" t="n">
-        <v>8287</v>
-      </c>
+        <v>42.9</v>
+      </c>
+      <c r="M206" s="14" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="B207" s="12" t="n">
-        <v>32.41182</v>
+        <v>30.98717</v>
       </c>
       <c r="C207" s="12" t="n">
-        <v>35.01958</v>
+        <v>34.76682</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>רגיל</t>
+          <t>עוטף עזה</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>מרכז (שרון / גוש דן)</t>
+          <t>עוטף עזה / הנגב המערבי</t>
         </is>
       </c>
       <c r="G207" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H207" s="6" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="I207" s="13" t="n">
-        <v>8000</v>
+        <v>22000</v>
       </c>
       <c r="J207" s="13" t="n">
-        <v>800</v>
+        <v>2200</v>
       </c>
       <c r="K207" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="L207" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="M207" t="n">
-        <v>8249</v>
-      </c>
+        <v>42.9</v>
+      </c>
+      <c r="M207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" s="14" t="n">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B208" s="15" t="n">
-        <v>31.34204</v>
+        <v>31.27477</v>
       </c>
       <c r="C208" s="15" t="n">
-        <v>34.93297</v>
+        <v>34.94342</v>
       </c>
       <c r="D208" s="14" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>31</t>
         </is>
       </c>
       <c r="E208" s="14" t="inlineStr">
@@ -10484,130 +10480,134 @@
         </is>
       </c>
       <c r="G208" s="14" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H208" s="16" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="I208" s="17" t="n">
-        <v>16000</v>
+        <v>6500</v>
       </c>
       <c r="J208" s="17" t="n">
-        <v>1600</v>
+        <v>650</v>
       </c>
       <c r="K208" s="14" t="n">
         <v>90</v>
       </c>
       <c r="L208" s="14" t="n">
-        <v>31.2</v>
+        <v>12.7</v>
       </c>
       <c r="M208" s="14" t="n">
-        <v>273</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B209" s="12" t="n">
-        <v>31.00948</v>
+        <v>32.70875</v>
       </c>
       <c r="C209" s="12" t="n">
-        <v>34.7797</v>
+        <v>35.30998</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>דרך הציונות</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>עוטף עזה</t>
+          <t>רגיל</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>עוטף עזה / הנגב המערבי</t>
+          <t>חיפה / כרמל</t>
         </is>
       </c>
       <c r="G209" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H209" s="6" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="I209" s="13" t="n">
-        <v>22000</v>
+        <v>8000</v>
       </c>
       <c r="J209" s="13" t="n">
-        <v>2200</v>
+        <v>800</v>
       </c>
       <c r="K209" t="n">
         <v>90</v>
       </c>
       <c r="L209" t="n">
-        <v>42.9</v>
-      </c>
-      <c r="M209" t="inlineStr"/>
+        <v>15.6</v>
+      </c>
+      <c r="M209" t="n">
+        <v>2017</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="14" t="n">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="B210" s="15" t="n">
-        <v>30.98717</v>
+        <v>32.45118</v>
       </c>
       <c r="C210" s="15" t="n">
-        <v>34.76682</v>
+        <v>34.8932</v>
       </c>
       <c r="D210" s="14" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>כביש החוף</t>
         </is>
       </c>
       <c r="E210" s="14" t="inlineStr">
         <is>
-          <t>עוטף עזה</t>
+          <t>רגיל</t>
         </is>
       </c>
       <c r="F210" s="14" t="inlineStr">
         <is>
-          <t>עוטף עזה / הנגב המערבי</t>
+          <t>מרכז (שרון / גוש דן)</t>
         </is>
       </c>
       <c r="G210" s="14" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H210" s="16" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="I210" s="17" t="n">
-        <v>22000</v>
+        <v>8000</v>
       </c>
       <c r="J210" s="17" t="n">
-        <v>2200</v>
+        <v>800</v>
       </c>
       <c r="K210" s="14" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="L210" s="14" t="n">
-        <v>42.9</v>
-      </c>
-      <c r="M210" s="14" t="inlineStr"/>
+        <v>15.6</v>
+      </c>
+      <c r="M210" s="14" t="n">
+        <v>6118</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="B211" s="12" t="n">
-        <v>31.27477</v>
+        <v>31.57389</v>
       </c>
       <c r="C211" s="12" t="n">
-        <v>34.94342</v>
+        <v>34.9817</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>חוצה יהודה</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -10617,7 +10617,7 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>נגב / ערבה</t>
+          <t>ירושלים / שפלה</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -10627,34 +10627,34 @@
         <v>150000</v>
       </c>
       <c r="I211" s="13" t="n">
-        <v>6500</v>
+        <v>8000</v>
       </c>
       <c r="J211" s="13" t="n">
-        <v>650</v>
+        <v>800</v>
       </c>
       <c r="K211" t="n">
         <v>90</v>
       </c>
       <c r="L211" t="n">
-        <v>12.7</v>
+        <v>15.6</v>
       </c>
       <c r="M211" t="n">
-        <v>1231</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="14" t="n">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="B212" s="15" t="n">
-        <v>32.70875</v>
+        <v>32.75386</v>
       </c>
       <c r="C212" s="15" t="n">
-        <v>35.30998</v>
+        <v>35.41108</v>
       </c>
       <c r="D212" s="14" t="inlineStr">
         <is>
-          <t>דרך הציונות</t>
+          <t>65</t>
         </is>
       </c>
       <c r="E212" s="14" t="inlineStr">
@@ -10668,40 +10668,40 @@
         </is>
       </c>
       <c r="G212" s="14" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H212" s="16" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="I212" s="17" t="n">
-        <v>8000</v>
+        <v>24000</v>
       </c>
       <c r="J212" s="17" t="n">
-        <v>800</v>
+        <v>2400</v>
       </c>
       <c r="K212" s="14" t="n">
         <v>90</v>
       </c>
       <c r="L212" s="14" t="n">
-        <v>15.6</v>
+        <v>46.8</v>
       </c>
       <c r="M212" s="14" t="n">
-        <v>2017</v>
+        <v>580</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="B213" s="12" t="n">
-        <v>31.66644</v>
+        <v>32.45257</v>
       </c>
       <c r="C213" s="12" t="n">
-        <v>35.10938</v>
+        <v>34.97321</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>65</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -10711,44 +10711,44 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>ירושלים / שפלה</t>
+          <t>מרכז (שרון / גוש דן)</t>
         </is>
       </c>
       <c r="G213" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H213" s="6" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="I213" s="13" t="n">
-        <v>8000</v>
+        <v>24000</v>
       </c>
       <c r="J213" s="13" t="n">
-        <v>800</v>
+        <v>2400</v>
       </c>
       <c r="K213" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="L213" t="n">
-        <v>15.6</v>
+        <v>46.8</v>
       </c>
       <c r="M213" t="n">
-        <v>6387</v>
+        <v>5851</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="14" t="n">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="B214" s="15" t="n">
-        <v>32.45118</v>
+        <v>32.79894</v>
       </c>
       <c r="C214" s="15" t="n">
-        <v>34.8932</v>
+        <v>35.52056</v>
       </c>
       <c r="D214" s="14" t="inlineStr">
         <is>
-          <t>כביש החוף</t>
+          <t>מנחם בגין</t>
         </is>
       </c>
       <c r="E214" s="14" t="inlineStr">
@@ -10758,7 +10758,7 @@
       </c>
       <c r="F214" s="14" t="inlineStr">
         <is>
-          <t>מרכז (שרון / גוש דן)</t>
+          <t>חיפה / כרמל</t>
         </is>
       </c>
       <c r="G214" s="14" t="n">
@@ -10780,32 +10780,32 @@
         <v>15.6</v>
       </c>
       <c r="M214" s="14" t="n">
-        <v>6118</v>
+        <v>348</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="B215" s="12" t="n">
-        <v>31.57389</v>
+        <v>31.06652</v>
       </c>
       <c r="C215" s="12" t="n">
-        <v>34.9817</v>
+        <v>34.83841</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>חוצה יהודה</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>רגיל</t>
+          <t>עוטף עזה</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>ירושלים / שפלה</t>
+          <t>עוטף עזה / הנגב המערבי</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -10826,23 +10826,21 @@
       <c r="L215" t="n">
         <v>15.6</v>
       </c>
-      <c r="M215" t="n">
-        <v>1254</v>
-      </c>
+      <c r="M215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" s="14" t="n">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B216" s="15" t="n">
-        <v>32.75386</v>
+        <v>32.43746</v>
       </c>
       <c r="C216" s="15" t="n">
-        <v>35.41108</v>
+        <v>35.02462</v>
       </c>
       <c r="D216" s="14" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>574</t>
         </is>
       </c>
       <c r="E216" s="14" t="inlineStr">
@@ -10852,44 +10850,44 @@
       </c>
       <c r="F216" s="14" t="inlineStr">
         <is>
-          <t>חיפה / כרמל</t>
+          <t>מרכז (שרון / גוש דן)</t>
         </is>
       </c>
       <c r="G216" s="14" t="n">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="H216" s="16" t="n">
-        <v>250000</v>
+        <v>100000</v>
       </c>
       <c r="I216" s="17" t="n">
-        <v>24000</v>
+        <v>4000</v>
       </c>
       <c r="J216" s="17" t="n">
-        <v>2400</v>
+        <v>400</v>
       </c>
       <c r="K216" s="14" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="L216" s="14" t="n">
-        <v>46.8</v>
+        <v>7.8</v>
       </c>
       <c r="M216" s="14" t="n">
-        <v>580</v>
+        <v>5557</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="B217" s="12" t="n">
-        <v>32.45257</v>
+        <v>32.78596</v>
       </c>
       <c r="C217" s="12" t="n">
-        <v>34.97321</v>
+        <v>35.49496</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>מנחם בגין</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -10899,7 +10897,7 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>מרכז (שרון / גוש דן)</t>
+          <t>חיפה / כרמל</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -10909,34 +10907,34 @@
         <v>250000</v>
       </c>
       <c r="I217" s="13" t="n">
-        <v>24000</v>
+        <v>19000</v>
       </c>
       <c r="J217" s="13" t="n">
-        <v>2400</v>
+        <v>1900</v>
       </c>
       <c r="K217" t="n">
         <v>90</v>
       </c>
       <c r="L217" t="n">
-        <v>46.8</v>
+        <v>37.1</v>
       </c>
       <c r="M217" t="n">
-        <v>5851</v>
+        <v>348</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="14" t="n">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="B218" s="15" t="n">
-        <v>32.79894</v>
+        <v>31.65044</v>
       </c>
       <c r="C218" s="15" t="n">
-        <v>35.52056</v>
+        <v>35.06612</v>
       </c>
       <c r="D218" s="14" t="inlineStr">
         <is>
-          <t>מנחם בגין</t>
+          <t>Downtown - Schools</t>
         </is>
       </c>
       <c r="E218" s="14" t="inlineStr">
@@ -10946,7 +10944,7 @@
       </c>
       <c r="F218" s="14" t="inlineStr">
         <is>
-          <t>חיפה / כרמל</t>
+          <t>ירושלים / שפלה</t>
         </is>
       </c>
       <c r="G218" s="14" t="n">
@@ -10962,38 +10960,38 @@
         <v>800</v>
       </c>
       <c r="K218" s="14" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="L218" s="14" t="n">
         <v>15.6</v>
       </c>
       <c r="M218" s="14" t="n">
-        <v>348</v>
+        <v>5230</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="B219" s="12" t="n">
-        <v>31.06652</v>
+        <v>32.6423</v>
       </c>
       <c r="C219" s="12" t="n">
-        <v>34.83841</v>
+        <v>35.05813</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>672</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>עוטף עזה</t>
+          <t>רגיל</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>עוטף עזה / הנגב המערבי</t>
+          <t>חיפה / כרמל</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -11009,26 +11007,28 @@
         <v>800</v>
       </c>
       <c r="K219" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="L219" t="n">
         <v>15.6</v>
       </c>
-      <c r="M219" t="inlineStr"/>
+      <c r="M219" t="n">
+        <v>2419</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="14" t="n">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B220" s="15" t="n">
-        <v>32.43746</v>
+        <v>32.66137</v>
       </c>
       <c r="C220" s="15" t="n">
-        <v>35.02462</v>
+        <v>35.23909</v>
       </c>
       <c r="D220" s="14" t="inlineStr">
         <is>
-          <t>574</t>
+          <t>73</t>
         </is>
       </c>
       <c r="E220" s="14" t="inlineStr">
@@ -11038,44 +11038,44 @@
       </c>
       <c r="F220" s="14" t="inlineStr">
         <is>
-          <t>מרכז (שרון / גוש דן)</t>
+          <t>חיפה / כרמל</t>
         </is>
       </c>
       <c r="G220" s="14" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H220" s="16" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I220" s="17" t="n">
-        <v>4000</v>
+        <v>8000</v>
       </c>
       <c r="J220" s="17" t="n">
-        <v>400</v>
+        <v>800</v>
       </c>
       <c r="K220" s="14" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="L220" s="14" t="n">
-        <v>7.8</v>
+        <v>15.6</v>
       </c>
       <c r="M220" s="14" t="n">
-        <v>5557</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="B221" s="12" t="n">
-        <v>32.78596</v>
+        <v>32.47901</v>
       </c>
       <c r="C221" s="12" t="n">
-        <v>35.49496</v>
+        <v>34.95591</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>מנחם בגין</t>
+          <t>הים</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -11085,44 +11085,44 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>חיפה / כרמל</t>
+          <t>מרכז (שרון / גוש דן)</t>
         </is>
       </c>
       <c r="G221" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H221" s="6" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="I221" s="13" t="n">
-        <v>19000</v>
+        <v>8000</v>
       </c>
       <c r="J221" s="13" t="n">
-        <v>1900</v>
+        <v>800</v>
       </c>
       <c r="K221" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="L221" t="n">
-        <v>37.1</v>
+        <v>15.6</v>
       </c>
       <c r="M221" t="n">
-        <v>348</v>
+        <v>3911</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="14" t="n">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="B222" s="15" t="n">
-        <v>31.65044</v>
+        <v>32.45671</v>
       </c>
       <c r="C222" s="15" t="n">
-        <v>35.06612</v>
+        <v>35.04691</v>
       </c>
       <c r="D222" s="14" t="inlineStr">
         <is>
-          <t>Downtown - Schools</t>
+          <t>האחווה</t>
         </is>
       </c>
       <c r="E222" s="14" t="inlineStr">
@@ -11132,7 +11132,7 @@
       </c>
       <c r="F222" s="14" t="inlineStr">
         <is>
-          <t>ירושלים / שפלה</t>
+          <t>מרכז (שרון / גוש דן)</t>
         </is>
       </c>
       <c r="G222" s="14" t="n">
@@ -11148,28 +11148,28 @@
         <v>800</v>
       </c>
       <c r="K222" s="14" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="L222" s="14" t="n">
         <v>15.6</v>
       </c>
       <c r="M222" s="14" t="n">
-        <v>5230</v>
+        <v>3267</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="B223" s="12" t="n">
-        <v>32.6423</v>
+        <v>32.50474</v>
       </c>
       <c r="C223" s="12" t="n">
-        <v>35.05813</v>
+        <v>34.91422</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>כביש החוף</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -11195,28 +11195,28 @@
         <v>800</v>
       </c>
       <c r="K223" t="n">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="L223" t="n">
         <v>15.6</v>
       </c>
       <c r="M223" t="n">
-        <v>2419</v>
+        <v>2956</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="14" t="n">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="B224" s="15" t="n">
-        <v>32.66137</v>
+        <v>32.67574</v>
       </c>
       <c r="C224" s="15" t="n">
-        <v>35.23909</v>
+        <v>35.29197</v>
       </c>
       <c r="D224" s="14" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>60</t>
         </is>
       </c>
       <c r="E224" s="14" t="inlineStr">
@@ -11230,40 +11230,40 @@
         </is>
       </c>
       <c r="G224" s="14" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H224" s="16" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="I224" s="17" t="n">
-        <v>8000</v>
+        <v>16000</v>
       </c>
       <c r="J224" s="17" t="n">
-        <v>800</v>
+        <v>1600</v>
       </c>
       <c r="K224" s="14" t="n">
         <v>90</v>
       </c>
       <c r="L224" s="14" t="n">
-        <v>15.6</v>
+        <v>31.2</v>
       </c>
       <c r="M224" s="14" t="n">
-        <v>2013</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="B225" s="12" t="n">
-        <v>32.47901</v>
+        <v>32.48213</v>
       </c>
       <c r="C225" s="12" t="n">
-        <v>34.95591</v>
+        <v>35.03479</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>הים</t>
+          <t>כביש חוצה ישראל</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -11289,28 +11289,28 @@
         <v>800</v>
       </c>
       <c r="K225" t="n">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="L225" t="n">
         <v>15.6</v>
       </c>
       <c r="M225" t="n">
-        <v>3911</v>
+        <v>2660</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="14" t="n">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="B226" s="15" t="n">
-        <v>32.45671</v>
+        <v>32.64337</v>
       </c>
       <c r="C226" s="15" t="n">
-        <v>35.04691</v>
+        <v>34.95866</v>
       </c>
       <c r="D226" s="14" t="inlineStr">
         <is>
-          <t>האחווה</t>
+          <t>כביש חיפה רעננה</t>
         </is>
       </c>
       <c r="E226" s="14" t="inlineStr">
@@ -11320,7 +11320,7 @@
       </c>
       <c r="F226" s="14" t="inlineStr">
         <is>
-          <t>מרכז (שרון / גוש דן)</t>
+          <t>חיפה / כרמל</t>
         </is>
       </c>
       <c r="G226" s="14" t="n">
@@ -11336,75 +11336,73 @@
         <v>800</v>
       </c>
       <c r="K226" s="14" t="n">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="L226" s="14" t="n">
         <v>15.6</v>
       </c>
       <c r="M226" s="14" t="n">
-        <v>3267</v>
+        <v>662</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="B227" s="12" t="n">
-        <v>32.50474</v>
+        <v>30.93868</v>
       </c>
       <c r="C227" s="12" t="n">
-        <v>34.91422</v>
+        <v>34.78511</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>כביש החוף</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>רגיל</t>
+          <t>עוטף עזה</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>חיפה / כרמל</t>
+          <t>עוטף עזה / הנגב המערבי</t>
         </is>
       </c>
       <c r="G227" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H227" s="6" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="I227" s="13" t="n">
-        <v>8000</v>
+        <v>22000</v>
       </c>
       <c r="J227" s="13" t="n">
-        <v>800</v>
+        <v>2200</v>
       </c>
       <c r="K227" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="L227" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="M227" t="n">
-        <v>2956</v>
-      </c>
+        <v>42.9</v>
+      </c>
+      <c r="M227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" s="14" t="n">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="B228" s="15" t="n">
-        <v>32.67574</v>
+        <v>31.1853</v>
       </c>
       <c r="C228" s="15" t="n">
-        <v>35.29197</v>
+        <v>34.95695</v>
       </c>
       <c r="D228" s="14" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>25</t>
         </is>
       </c>
       <c r="E228" s="14" t="inlineStr">
@@ -11414,44 +11412,44 @@
       </c>
       <c r="F228" s="14" t="inlineStr">
         <is>
-          <t>חיפה / כרמל</t>
+          <t>נגב / ערבה</t>
         </is>
       </c>
       <c r="G228" s="14" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H228" s="16" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="I228" s="17" t="n">
-        <v>16000</v>
+        <v>7000</v>
       </c>
       <c r="J228" s="17" t="n">
-        <v>1600</v>
+        <v>700</v>
       </c>
       <c r="K228" s="14" t="n">
         <v>90</v>
       </c>
       <c r="L228" s="14" t="n">
-        <v>31.2</v>
+        <v>13.7</v>
       </c>
       <c r="M228" s="14" t="n">
-        <v>1122</v>
+        <v>442</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="B229" s="12" t="n">
-        <v>31.60979</v>
+        <v>32.5173</v>
       </c>
       <c r="C229" s="12" t="n">
-        <v>35.0419</v>
+        <v>34.99246</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Tarqumia - Surif</t>
+          <t>654</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -11461,7 +11459,7 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>ירושלים / שפלה</t>
+          <t>חיפה / כרמל</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -11483,22 +11481,22 @@
         <v>15.6</v>
       </c>
       <c r="M229" t="n">
-        <v>2761</v>
+        <v>1768</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="14" t="n">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="B230" s="15" t="n">
-        <v>32.48213</v>
+        <v>32.77382</v>
       </c>
       <c r="C230" s="15" t="n">
-        <v>35.03479</v>
+        <v>35.54631</v>
       </c>
       <c r="D230" s="14" t="inlineStr">
         <is>
-          <t>כביש חוצה ישראל</t>
+          <t>שדרות אליעזר קפלן</t>
         </is>
       </c>
       <c r="E230" s="14" t="inlineStr">
@@ -11508,7 +11506,7 @@
       </c>
       <c r="F230" s="14" t="inlineStr">
         <is>
-          <t>מרכז (שרון / גוש דן)</t>
+          <t>חיפה / כרמל</t>
         </is>
       </c>
       <c r="G230" s="14" t="n">
@@ -11524,28 +11522,26 @@
         <v>800</v>
       </c>
       <c r="K230" s="14" t="n">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="L230" s="14" t="n">
         <v>15.6</v>
       </c>
-      <c r="M230" s="14" t="n">
-        <v>2660</v>
-      </c>
+      <c r="M230" s="14" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="B231" s="12" t="n">
-        <v>32.64337</v>
+        <v>31.31285</v>
       </c>
       <c r="C231" s="12" t="n">
-        <v>34.95866</v>
+        <v>34.99488</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>כביש חיפה רעננה</t>
+          <t>316</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -11555,7 +11551,7 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>חיפה / כרמל</t>
+          <t>נגב / ערבה</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -11571,73 +11567,75 @@
         <v>800</v>
       </c>
       <c r="K231" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="L231" t="n">
         <v>15.6</v>
       </c>
       <c r="M231" t="n">
-        <v>662</v>
+        <v>217</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="14" t="n">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="B232" s="15" t="n">
-        <v>30.93868</v>
+        <v>32.61908</v>
       </c>
       <c r="C232" s="15" t="n">
-        <v>34.78511</v>
+        <v>35.05488</v>
       </c>
       <c r="D232" s="14" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>כביש חוצה ישראל</t>
         </is>
       </c>
       <c r="E232" s="14" t="inlineStr">
         <is>
-          <t>עוטף עזה</t>
+          <t>רגיל</t>
         </is>
       </c>
       <c r="F232" s="14" t="inlineStr">
         <is>
-          <t>עוטף עזה / הנגב המערבי</t>
+          <t>חיפה / כרמל</t>
         </is>
       </c>
       <c r="G232" s="14" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H232" s="16" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="I232" s="17" t="n">
-        <v>22000</v>
+        <v>8000</v>
       </c>
       <c r="J232" s="17" t="n">
-        <v>2200</v>
+        <v>800</v>
       </c>
       <c r="K232" s="14" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="L232" s="14" t="n">
-        <v>42.9</v>
-      </c>
-      <c r="M232" s="14" t="inlineStr"/>
+        <v>15.6</v>
+      </c>
+      <c r="M232" s="14" t="n">
+        <v>1099</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="B233" s="12" t="n">
-        <v>31.1853</v>
+        <v>32.53646</v>
       </c>
       <c r="C233" s="12" t="n">
-        <v>34.95695</v>
+        <v>34.92907</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>כביש חיפה רעננה</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -11647,7 +11645,7 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>נגב / ערבה</t>
+          <t>חיפה / כרמל</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -11657,34 +11655,34 @@
         <v>150000</v>
       </c>
       <c r="I233" s="13" t="n">
-        <v>7000</v>
+        <v>8000</v>
       </c>
       <c r="J233" s="13" t="n">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="K233" t="n">
         <v>90</v>
       </c>
       <c r="L233" t="n">
-        <v>13.7</v>
+        <v>15.6</v>
       </c>
       <c r="M233" t="n">
-        <v>442</v>
+        <v>881</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="14" t="n">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="B234" s="15" t="n">
-        <v>32.5173</v>
+        <v>31.25485</v>
       </c>
       <c r="C234" s="15" t="n">
-        <v>34.99246</v>
+        <v>35.21055</v>
       </c>
       <c r="D234" s="14" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>31</t>
         </is>
       </c>
       <c r="E234" s="14" t="inlineStr">
@@ -11694,7 +11692,7 @@
       </c>
       <c r="F234" s="14" t="inlineStr">
         <is>
-          <t>חיפה / כרמל</t>
+          <t>נגב / ערבה</t>
         </is>
       </c>
       <c r="G234" s="14" t="n">
@@ -11704,34 +11702,34 @@
         <v>150000</v>
       </c>
       <c r="I234" s="17" t="n">
-        <v>8000</v>
+        <v>6500</v>
       </c>
       <c r="J234" s="17" t="n">
-        <v>800</v>
+        <v>650</v>
       </c>
       <c r="K234" s="14" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="L234" s="14" t="n">
-        <v>15.6</v>
+        <v>12.7</v>
       </c>
       <c r="M234" s="14" t="n">
-        <v>1768</v>
+        <v>753</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="B235" s="12" t="n">
-        <v>32.77382</v>
+        <v>31.29801</v>
       </c>
       <c r="C235" s="12" t="n">
-        <v>35.54631</v>
+        <v>35.13199</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>שדרות אליעזר קפלן</t>
+          <t>80</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -11741,7 +11739,7 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>חיפה / כרמל</t>
+          <t>נגב / ערבה</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -11757,26 +11755,28 @@
         <v>800</v>
       </c>
       <c r="K235" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="L235" t="n">
         <v>15.6</v>
       </c>
-      <c r="M235" t="inlineStr"/>
+      <c r="M235" t="n">
+        <v>753</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" s="14" t="n">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="B236" s="15" t="n">
-        <v>31.31285</v>
+        <v>32.56323</v>
       </c>
       <c r="C236" s="15" t="n">
-        <v>34.99488</v>
+        <v>34.95873</v>
       </c>
       <c r="D236" s="14" t="inlineStr">
         <is>
-          <t>316</t>
+          <t>652</t>
         </is>
       </c>
       <c r="E236" s="14" t="inlineStr">
@@ -11786,44 +11786,44 @@
       </c>
       <c r="F236" s="14" t="inlineStr">
         <is>
-          <t>נגב / ערבה</t>
+          <t>חיפה / כרמל</t>
         </is>
       </c>
       <c r="G236" s="14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H236" s="16" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I236" s="17" t="n">
-        <v>8000</v>
+        <v>4000</v>
       </c>
       <c r="J236" s="17" t="n">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="K236" s="14" t="n">
         <v>80</v>
       </c>
       <c r="L236" s="14" t="n">
-        <v>15.6</v>
+        <v>7.8</v>
       </c>
       <c r="M236" s="14" t="n">
-        <v>217</v>
+        <v>587</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="B237" s="12" t="n">
-        <v>32.61908</v>
+        <v>32.52426</v>
       </c>
       <c r="C237" s="12" t="n">
-        <v>35.05488</v>
+        <v>35.02544</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>כביש חוצה ישראל</t>
+          <t>653</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -11849,28 +11849,28 @@
         <v>800</v>
       </c>
       <c r="K237" t="n">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="L237" t="n">
         <v>15.6</v>
       </c>
       <c r="M237" t="n">
-        <v>1099</v>
+        <v>587</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="14" t="n">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="B238" s="15" t="n">
-        <v>32.53646</v>
+        <v>31.2012</v>
       </c>
       <c r="C238" s="15" t="n">
-        <v>34.92907</v>
+        <v>35.35995</v>
       </c>
       <c r="D238" s="14" t="inlineStr">
         <is>
-          <t>כביש חיפה רעננה</t>
+          <t>דרך ים המלח</t>
         </is>
       </c>
       <c r="E238" s="14" t="inlineStr">
@@ -11880,7 +11880,7 @@
       </c>
       <c r="F238" s="14" t="inlineStr">
         <is>
-          <t>חיפה / כרמל</t>
+          <t>נגב / ערבה</t>
         </is>
       </c>
       <c r="G238" s="14" t="n">
@@ -11902,18 +11902,18 @@
         <v>15.6</v>
       </c>
       <c r="M238" s="14" t="n">
-        <v>881</v>
+        <v>536</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="B239" s="12" t="n">
-        <v>31.25485</v>
+        <v>31.19194</v>
       </c>
       <c r="C239" s="12" t="n">
-        <v>35.21055</v>
+        <v>35.28031</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -11949,22 +11949,22 @@
         <v>12.7</v>
       </c>
       <c r="M239" t="n">
-        <v>753</v>
+        <v>536</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="14" t="n">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="B240" s="15" t="n">
-        <v>31.29801</v>
+        <v>31.25015</v>
       </c>
       <c r="C240" s="15" t="n">
-        <v>35.13199</v>
+        <v>35.36307</v>
       </c>
       <c r="D240" s="14" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>דרך ים המלח</t>
         </is>
       </c>
       <c r="E240" s="14" t="inlineStr">
@@ -11990,28 +11990,28 @@
         <v>800</v>
       </c>
       <c r="K240" s="14" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="L240" s="14" t="n">
         <v>15.6</v>
       </c>
       <c r="M240" s="14" t="n">
-        <v>753</v>
+        <v>536</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="B241" s="12" t="n">
-        <v>32.56323</v>
+        <v>32.5864</v>
       </c>
       <c r="C241" s="12" t="n">
-        <v>34.95873</v>
+        <v>35.43541</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>717</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -12025,40 +12025,40 @@
         </is>
       </c>
       <c r="G241" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H241" s="6" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I241" s="13" t="n">
-        <v>4000</v>
+        <v>8000</v>
       </c>
       <c r="J241" s="13" t="n">
-        <v>400</v>
+        <v>800</v>
       </c>
       <c r="K241" t="n">
         <v>80</v>
       </c>
       <c r="L241" t="n">
-        <v>7.8</v>
+        <v>15.6</v>
       </c>
       <c r="M241" t="n">
-        <v>587</v>
+        <v>510</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="14" t="n">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="B242" s="15" t="n">
-        <v>32.52426</v>
+        <v>31.25249</v>
       </c>
       <c r="C242" s="15" t="n">
-        <v>35.02544</v>
+        <v>35.12599</v>
       </c>
       <c r="D242" s="14" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>80</t>
         </is>
       </c>
       <c r="E242" s="14" t="inlineStr">
@@ -12068,7 +12068,7 @@
       </c>
       <c r="F242" s="14" t="inlineStr">
         <is>
-          <t>חיפה / כרמל</t>
+          <t>נגב / ערבה</t>
         </is>
       </c>
       <c r="G242" s="14" t="n">
@@ -12084,28 +12084,28 @@
         <v>800</v>
       </c>
       <c r="K242" s="14" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="L242" s="14" t="n">
         <v>15.6</v>
       </c>
       <c r="M242" s="14" t="n">
-        <v>587</v>
+        <v>500</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="B243" s="12" t="n">
-        <v>31.2012</v>
+        <v>31.2344</v>
       </c>
       <c r="C243" s="12" t="n">
-        <v>35.35995</v>
+        <v>35.10819</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>דרך ים המלח</t>
+          <t>80</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -12119,36 +12119,36 @@
         </is>
       </c>
       <c r="G243" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H243" s="6" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I243" s="13" t="n">
-        <v>8000</v>
+        <v>4000</v>
       </c>
       <c r="J243" s="13" t="n">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="K243" t="n">
         <v>90</v>
       </c>
       <c r="L243" t="n">
-        <v>15.6</v>
+        <v>7.8</v>
       </c>
       <c r="M243" t="n">
-        <v>536</v>
+        <v>500</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="14" t="n">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="B244" s="15" t="n">
-        <v>31.19194</v>
+        <v>31.2565</v>
       </c>
       <c r="C244" s="15" t="n">
-        <v>35.28031</v>
+        <v>35.09862</v>
       </c>
       <c r="D244" s="14" t="inlineStr">
         <is>
@@ -12184,22 +12184,22 @@
         <v>12.7</v>
       </c>
       <c r="M244" s="14" t="n">
-        <v>536</v>
+        <v>500</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="B245" s="12" t="n">
-        <v>31.25015</v>
+        <v>31.16767</v>
       </c>
       <c r="C245" s="12" t="n">
-        <v>35.36307</v>
+        <v>35.04596</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>דרך ים המלח</t>
+          <t>80</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -12225,28 +12225,28 @@
         <v>800</v>
       </c>
       <c r="K245" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="L245" t="n">
         <v>15.6</v>
       </c>
       <c r="M245" t="n">
-        <v>536</v>
+        <v>442</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="14" t="n">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="B246" s="15" t="n">
-        <v>32.5864</v>
+        <v>31.26291</v>
       </c>
       <c r="C246" s="15" t="n">
-        <v>35.43541</v>
+        <v>35.02142</v>
       </c>
       <c r="D246" s="14" t="inlineStr">
         <is>
-          <t>717</t>
+          <t>31</t>
         </is>
       </c>
       <c r="E246" s="14" t="inlineStr">
@@ -12256,7 +12256,7 @@
       </c>
       <c r="F246" s="14" t="inlineStr">
         <is>
-          <t>חיפה / כרמל</t>
+          <t>נגב / ערבה</t>
         </is>
       </c>
       <c r="G246" s="14" t="n">
@@ -12266,30 +12266,30 @@
         <v>150000</v>
       </c>
       <c r="I246" s="17" t="n">
-        <v>8000</v>
+        <v>6500</v>
       </c>
       <c r="J246" s="17" t="n">
-        <v>800</v>
+        <v>650</v>
       </c>
       <c r="K246" s="14" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="L246" s="14" t="n">
-        <v>15.6</v>
+        <v>12.7</v>
       </c>
       <c r="M246" s="14" t="n">
-        <v>510</v>
+        <v>442</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="B247" s="12" t="n">
-        <v>31.25249</v>
+        <v>31.15683</v>
       </c>
       <c r="C247" s="12" t="n">
-        <v>35.12599</v>
+        <v>34.995</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -12325,22 +12325,22 @@
         <v>15.6</v>
       </c>
       <c r="M247" t="n">
-        <v>500</v>
+        <v>442</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="14" t="n">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="B248" s="15" t="n">
-        <v>31.2344</v>
+        <v>32.60198</v>
       </c>
       <c r="C248" s="15" t="n">
-        <v>35.10819</v>
+        <v>35.08464</v>
       </c>
       <c r="D248" s="14" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>672</t>
         </is>
       </c>
       <c r="E248" s="14" t="inlineStr">
@@ -12350,44 +12350,44 @@
       </c>
       <c r="F248" s="14" t="inlineStr">
         <is>
-          <t>נגב / ערבה</t>
+          <t>חיפה / כרמל</t>
         </is>
       </c>
       <c r="G248" s="14" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H248" s="16" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I248" s="17" t="n">
-        <v>4000</v>
+        <v>8000</v>
       </c>
       <c r="J248" s="17" t="n">
-        <v>400</v>
+        <v>800</v>
       </c>
       <c r="K248" s="14" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="L248" s="14" t="n">
-        <v>7.8</v>
+        <v>15.6</v>
       </c>
       <c r="M248" s="14" t="n">
-        <v>500</v>
+        <v>440</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="B249" s="12" t="n">
-        <v>31.2565</v>
+        <v>32.71782</v>
       </c>
       <c r="C249" s="12" t="n">
-        <v>35.09862</v>
+        <v>35.43847</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>דרך המושבות</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
@@ -12397,185 +12397,185 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>נגב / ערבה</t>
+          <t>חיפה / כרמל</t>
         </is>
       </c>
       <c r="G249" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H249" s="6" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I249" s="13" t="n">
-        <v>6500</v>
+        <v>4000</v>
       </c>
       <c r="J249" s="13" t="n">
-        <v>650</v>
+        <v>400</v>
       </c>
       <c r="K249" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="L249" t="n">
-        <v>12.7</v>
+        <v>7.8</v>
       </c>
       <c r="M249" t="n">
-        <v>500</v>
+        <v>232</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="14" t="n">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="B250" s="15" t="n">
-        <v>31.16767</v>
+        <v>30.61281</v>
       </c>
       <c r="C250" s="15" t="n">
-        <v>35.04596</v>
+        <v>34.85762</v>
       </c>
       <c r="D250" s="14" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E250" s="14" t="inlineStr">
         <is>
-          <t>רגיל</t>
+          <t>עוטף עזה</t>
         </is>
       </c>
       <c r="F250" s="14" t="inlineStr">
         <is>
-          <t>נגב / ערבה</t>
+          <t>עוטף עזה / הנגב המערבי</t>
         </is>
       </c>
       <c r="G250" s="14" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H250" s="16" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="I250" s="17" t="n">
-        <v>8000</v>
+        <v>22000</v>
       </c>
       <c r="J250" s="17" t="n">
-        <v>800</v>
+        <v>2200</v>
       </c>
       <c r="K250" s="14" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="L250" s="14" t="n">
-        <v>15.6</v>
+        <v>42.9</v>
       </c>
       <c r="M250" s="14" t="n">
-        <v>442</v>
+        <v>284</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B251" s="12" t="n">
-        <v>31.26291</v>
+        <v>30.62719</v>
       </c>
       <c r="C251" s="12" t="n">
-        <v>35.02142</v>
+        <v>34.80473</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>רגיל</t>
+          <t>עוטף עזה</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>נגב / ערבה</t>
+          <t>עוטף עזה / הנגב המערבי</t>
         </is>
       </c>
       <c r="G251" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H251" s="6" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="I251" s="13" t="n">
-        <v>6500</v>
+        <v>22000</v>
       </c>
       <c r="J251" s="13" t="n">
-        <v>650</v>
+        <v>2200</v>
       </c>
       <c r="K251" t="n">
         <v>90</v>
       </c>
       <c r="L251" t="n">
-        <v>12.7</v>
+        <v>42.9</v>
       </c>
       <c r="M251" t="n">
-        <v>442</v>
+        <v>284</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="14" t="n">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="B252" s="15" t="n">
-        <v>31.15683</v>
+        <v>30.6616</v>
       </c>
       <c r="C252" s="15" t="n">
-        <v>34.995</v>
+        <v>34.80929</v>
       </c>
       <c r="D252" s="14" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E252" s="14" t="inlineStr">
         <is>
-          <t>רגיל</t>
+          <t>עוטף עזה</t>
         </is>
       </c>
       <c r="F252" s="14" t="inlineStr">
         <is>
-          <t>נגב / ערבה</t>
+          <t>עוטף עזה / הנגב המערבי</t>
         </is>
       </c>
       <c r="G252" s="14" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H252" s="16" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="I252" s="17" t="n">
-        <v>8000</v>
+        <v>22000</v>
       </c>
       <c r="J252" s="17" t="n">
-        <v>800</v>
+        <v>2200</v>
       </c>
       <c r="K252" s="14" t="n">
         <v>90</v>
       </c>
       <c r="L252" s="14" t="n">
-        <v>15.6</v>
+        <v>42.9</v>
       </c>
       <c r="M252" s="14" t="n">
-        <v>442</v>
+        <v>284</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="B253" s="12" t="n">
-        <v>32.60198</v>
+        <v>30.5665</v>
       </c>
       <c r="C253" s="12" t="n">
-        <v>35.08464</v>
+        <v>34.90431</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -12585,232 +12585,232 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>חיפה / כרמל</t>
+          <t>נגב / ערבה</t>
         </is>
       </c>
       <c r="G253" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H253" s="6" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="I253" s="13" t="n">
-        <v>8000</v>
+        <v>22000</v>
       </c>
       <c r="J253" s="13" t="n">
-        <v>800</v>
+        <v>2200</v>
       </c>
       <c r="K253" t="n">
         <v>80</v>
       </c>
       <c r="L253" t="n">
-        <v>15.6</v>
+        <v>42.9</v>
       </c>
       <c r="M253" t="n">
-        <v>440</v>
+        <v>284</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="14" t="n">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="B254" s="15" t="n">
-        <v>32.71782</v>
+        <v>30.72685</v>
       </c>
       <c r="C254" s="15" t="n">
-        <v>35.43847</v>
+        <v>34.77465</v>
       </c>
       <c r="D254" s="14" t="inlineStr">
         <is>
-          <t>דרך המושבות</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E254" s="14" t="inlineStr">
         <is>
-          <t>רגיל</t>
+          <t>עוטף עזה</t>
         </is>
       </c>
       <c r="F254" s="14" t="inlineStr">
         <is>
-          <t>חיפה / כרמל</t>
+          <t>עוטף עזה / הנגב המערבי</t>
         </is>
       </c>
       <c r="G254" s="14" t="n">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="H254" s="16" t="n">
-        <v>100000</v>
+        <v>250000</v>
       </c>
       <c r="I254" s="17" t="n">
-        <v>4000</v>
+        <v>22000</v>
       </c>
       <c r="J254" s="17" t="n">
-        <v>400</v>
+        <v>2200</v>
       </c>
       <c r="K254" s="14" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="L254" s="14" t="n">
-        <v>7.8</v>
+        <v>42.9</v>
       </c>
       <c r="M254" s="14" t="n">
-        <v>232</v>
+        <v>284</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="B255" s="12" t="n">
-        <v>30.61281</v>
+        <v>31.14917</v>
       </c>
       <c r="C255" s="12" t="n">
-        <v>34.85762</v>
+        <v>35.22181</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>258</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>עוטף עזה</t>
+          <t>רגיל</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>עוטף עזה / הנגב המערבי</t>
+          <t>נגב / ערבה</t>
         </is>
       </c>
       <c r="G255" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H255" s="6" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="I255" s="13" t="n">
-        <v>22000</v>
+        <v>8000</v>
       </c>
       <c r="J255" s="13" t="n">
-        <v>2200</v>
+        <v>800</v>
       </c>
       <c r="K255" t="n">
         <v>80</v>
       </c>
       <c r="L255" t="n">
-        <v>42.9</v>
+        <v>15.6</v>
       </c>
       <c r="M255" t="n">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="14" t="n">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="B256" s="15" t="n">
-        <v>30.62719</v>
+        <v>31.31343</v>
       </c>
       <c r="C256" s="15" t="n">
-        <v>34.80473</v>
+        <v>35.38376</v>
       </c>
       <c r="D256" s="14" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>דרך ים המלח</t>
         </is>
       </c>
       <c r="E256" s="14" t="inlineStr">
         <is>
-          <t>עוטף עזה</t>
+          <t>רגיל</t>
         </is>
       </c>
       <c r="F256" s="14" t="inlineStr">
         <is>
-          <t>עוטף עזה / הנגב המערבי</t>
+          <t>נגב / ערבה</t>
         </is>
       </c>
       <c r="G256" s="14" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H256" s="16" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="I256" s="17" t="n">
-        <v>22000</v>
+        <v>8000</v>
       </c>
       <c r="J256" s="17" t="n">
-        <v>2200</v>
+        <v>800</v>
       </c>
       <c r="K256" s="14" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="L256" s="14" t="n">
-        <v>42.9</v>
+        <v>15.6</v>
       </c>
       <c r="M256" s="14" t="n">
-        <v>284</v>
+        <v>253</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="B257" s="12" t="n">
-        <v>30.6616</v>
+        <v>32.6126</v>
       </c>
       <c r="C257" s="12" t="n">
-        <v>34.80929</v>
+        <v>35.54892</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>90</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>עוטף עזה</t>
+          <t>רגיל</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>עוטף עזה / הנגב המערבי</t>
+          <t>חיפה / כרמל</t>
         </is>
       </c>
       <c r="G257" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H257" s="6" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="I257" s="13" t="n">
-        <v>22000</v>
+        <v>9000</v>
       </c>
       <c r="J257" s="13" t="n">
-        <v>2200</v>
+        <v>900</v>
       </c>
       <c r="K257" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="L257" t="n">
-        <v>42.9</v>
+        <v>17.6</v>
       </c>
       <c r="M257" t="n">
-        <v>284</v>
+        <v>232</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="14" t="n">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="B258" s="15" t="n">
-        <v>30.5665</v>
+        <v>32.70236</v>
       </c>
       <c r="C258" s="15" t="n">
-        <v>34.90431</v>
+        <v>35.41203</v>
       </c>
       <c r="D258" s="14" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>65</t>
         </is>
       </c>
       <c r="E258" s="14" t="inlineStr">
@@ -12820,7 +12820,7 @@
       </c>
       <c r="F258" s="14" t="inlineStr">
         <is>
-          <t>נגב / ערבה</t>
+          <t>חיפה / כרמל</t>
         </is>
       </c>
       <c r="G258" s="14" t="n">
@@ -12830,44 +12830,44 @@
         <v>250000</v>
       </c>
       <c r="I258" s="17" t="n">
-        <v>22000</v>
+        <v>24000</v>
       </c>
       <c r="J258" s="17" t="n">
-        <v>2200</v>
+        <v>2400</v>
       </c>
       <c r="K258" s="14" t="n">
         <v>80</v>
       </c>
       <c r="L258" s="14" t="n">
-        <v>42.9</v>
+        <v>46.8</v>
       </c>
       <c r="M258" s="14" t="n">
-        <v>284</v>
+        <v>232</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="B259" s="12" t="n">
-        <v>30.72685</v>
+        <v>32.66478</v>
       </c>
       <c r="C259" s="12" t="n">
-        <v>34.77465</v>
+        <v>35.39644</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>65</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>עוטף עזה</t>
+          <t>רגיל</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>עוטף עזה / הנגב המערבי</t>
+          <t>חיפה / כרמל</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -12877,34 +12877,34 @@
         <v>250000</v>
       </c>
       <c r="I259" s="13" t="n">
-        <v>22000</v>
+        <v>24000</v>
       </c>
       <c r="J259" s="13" t="n">
-        <v>2200</v>
+        <v>2400</v>
       </c>
       <c r="K259" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="L259" t="n">
-        <v>42.9</v>
+        <v>46.8</v>
       </c>
       <c r="M259" t="n">
-        <v>284</v>
+        <v>232</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="14" t="n">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="B260" s="15" t="n">
-        <v>31.14917</v>
+        <v>32.59074</v>
       </c>
       <c r="C260" s="15" t="n">
-        <v>35.22181</v>
+        <v>35.2921</v>
       </c>
       <c r="D260" s="14" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>60</t>
         </is>
       </c>
       <c r="E260" s="14" t="inlineStr">
@@ -12914,44 +12914,44 @@
       </c>
       <c r="F260" s="14" t="inlineStr">
         <is>
-          <t>נגב / ערבה</t>
+          <t>חיפה / כרמל</t>
         </is>
       </c>
       <c r="G260" s="14" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H260" s="16" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="I260" s="17" t="n">
-        <v>8000</v>
+        <v>16000</v>
       </c>
       <c r="J260" s="17" t="n">
-        <v>800</v>
+        <v>1600</v>
       </c>
       <c r="K260" s="14" t="n">
         <v>80</v>
       </c>
       <c r="L260" s="14" t="n">
-        <v>15.6</v>
+        <v>31.2</v>
       </c>
       <c r="M260" s="14" t="n">
-        <v>283</v>
+        <v>232</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="B261" s="12" t="n">
-        <v>31.31343</v>
+        <v>32.64101</v>
       </c>
       <c r="C261" s="12" t="n">
-        <v>35.38376</v>
+        <v>35.32434</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>דרך ים המלח</t>
+          <t>כביש עוקף עפולה מזרח</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
@@ -12961,7 +12961,7 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>נגב / ערבה</t>
+          <t>חיפה / כרמל</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -12977,28 +12977,28 @@
         <v>800</v>
       </c>
       <c r="K261" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="L261" t="n">
         <v>15.6</v>
       </c>
       <c r="M261" t="n">
-        <v>253</v>
+        <v>232</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="14" t="n">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="B262" s="15" t="n">
-        <v>32.6126</v>
+        <v>32.56021</v>
       </c>
       <c r="C262" s="15" t="n">
-        <v>35.54892</v>
+        <v>35.35378</v>
       </c>
       <c r="D262" s="14" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>675</t>
         </is>
       </c>
       <c r="E262" s="14" t="inlineStr">
@@ -13018,16 +13018,16 @@
         <v>150000</v>
       </c>
       <c r="I262" s="17" t="n">
-        <v>9000</v>
+        <v>8000</v>
       </c>
       <c r="J262" s="17" t="n">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="K262" s="14" t="n">
         <v>80</v>
       </c>
       <c r="L262" s="14" t="n">
-        <v>17.6</v>
+        <v>15.6</v>
       </c>
       <c r="M262" s="14" t="n">
         <v>232</v>
@@ -13035,17 +13035,17 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="B263" s="12" t="n">
-        <v>32.70236</v>
+        <v>32.5798</v>
       </c>
       <c r="C263" s="12" t="n">
-        <v>35.41203</v>
+        <v>35.39895</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>716</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
@@ -13059,22 +13059,22 @@
         </is>
       </c>
       <c r="G263" t="n">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="H263" s="6" t="n">
-        <v>250000</v>
+        <v>100000</v>
       </c>
       <c r="I263" s="13" t="n">
-        <v>24000</v>
+        <v>4000</v>
       </c>
       <c r="J263" s="13" t="n">
-        <v>2400</v>
+        <v>400</v>
       </c>
       <c r="K263" t="n">
         <v>80</v>
       </c>
       <c r="L263" t="n">
-        <v>46.8</v>
+        <v>7.8</v>
       </c>
       <c r="M263" t="n">
         <v>232</v>
@@ -13082,17 +13082,17 @@
     </row>
     <row r="264">
       <c r="A264" s="14" t="n">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="B264" s="15" t="n">
-        <v>32.66478</v>
+        <v>32.63534</v>
       </c>
       <c r="C264" s="15" t="n">
-        <v>35.39644</v>
+        <v>35.39574</v>
       </c>
       <c r="D264" s="14" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>716</t>
         </is>
       </c>
       <c r="E264" s="14" t="inlineStr">
@@ -13106,22 +13106,22 @@
         </is>
       </c>
       <c r="G264" s="14" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H264" s="16" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="I264" s="17" t="n">
-        <v>24000</v>
+        <v>8000</v>
       </c>
       <c r="J264" s="17" t="n">
-        <v>2400</v>
+        <v>800</v>
       </c>
       <c r="K264" s="14" t="n">
         <v>80</v>
       </c>
       <c r="L264" s="14" t="n">
-        <v>46.8</v>
+        <v>15.6</v>
       </c>
       <c r="M264" s="14" t="n">
         <v>232</v>
@@ -13129,17 +13129,17 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="B265" s="12" t="n">
-        <v>32.59074</v>
+        <v>32.71608</v>
       </c>
       <c r="C265" s="12" t="n">
-        <v>35.2921</v>
+        <v>35.46579</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>דרך המושבות</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
@@ -13153,22 +13153,22 @@
         </is>
       </c>
       <c r="G265" t="n">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="H265" s="6" t="n">
-        <v>250000</v>
+        <v>100000</v>
       </c>
       <c r="I265" s="13" t="n">
-        <v>16000</v>
+        <v>4000</v>
       </c>
       <c r="J265" s="13" t="n">
-        <v>1600</v>
+        <v>400</v>
       </c>
       <c r="K265" t="n">
         <v>80</v>
       </c>
       <c r="L265" t="n">
-        <v>31.2</v>
+        <v>7.8</v>
       </c>
       <c r="M265" t="n">
         <v>232</v>
@@ -13176,17 +13176,17 @@
     </row>
     <row r="266">
       <c r="A266" s="14" t="n">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="B266" s="15" t="n">
-        <v>32.64101</v>
+        <v>31.12478</v>
       </c>
       <c r="C266" s="15" t="n">
-        <v>35.32434</v>
+        <v>35.01084</v>
       </c>
       <c r="D266" s="14" t="inlineStr">
         <is>
-          <t>כביש עוקף עפולה מזרח</t>
+          <t>25</t>
         </is>
       </c>
       <c r="E266" s="14" t="inlineStr">
@@ -13196,7 +13196,7 @@
       </c>
       <c r="F266" s="14" t="inlineStr">
         <is>
-          <t>חיפה / כרמל</t>
+          <t>נגב / ערבה</t>
         </is>
       </c>
       <c r="G266" s="14" t="n">
@@ -13206,34 +13206,34 @@
         <v>150000</v>
       </c>
       <c r="I266" s="17" t="n">
-        <v>8000</v>
+        <v>7000</v>
       </c>
       <c r="J266" s="17" t="n">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="K266" s="14" t="n">
         <v>90</v>
       </c>
       <c r="L266" s="14" t="n">
-        <v>15.6</v>
+        <v>13.7</v>
       </c>
       <c r="M266" s="14" t="n">
-        <v>232</v>
+        <v>225</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="B267" s="12" t="n">
-        <v>32.56021</v>
+        <v>32.55248</v>
       </c>
       <c r="C267" s="12" t="n">
-        <v>35.35378</v>
+        <v>35.0312</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>כביש חוצה ישראל</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
@@ -13259,28 +13259,26 @@
         <v>800</v>
       </c>
       <c r="K267" t="n">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="L267" t="n">
         <v>15.6</v>
       </c>
-      <c r="M267" t="n">
-        <v>232</v>
-      </c>
+      <c r="M267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" s="14" t="n">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="B268" s="15" t="n">
-        <v>32.5798</v>
+        <v>32.58001</v>
       </c>
       <c r="C268" s="15" t="n">
-        <v>35.39895</v>
+        <v>35.04577</v>
       </c>
       <c r="D268" s="14" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>כביש חוצה ישראל</t>
         </is>
       </c>
       <c r="E268" s="14" t="inlineStr">
@@ -13294,40 +13292,38 @@
         </is>
       </c>
       <c r="G268" s="14" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H268" s="16" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I268" s="17" t="n">
-        <v>4000</v>
+        <v>8000</v>
       </c>
       <c r="J268" s="17" t="n">
-        <v>400</v>
+        <v>800</v>
       </c>
       <c r="K268" s="14" t="n">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="L268" s="14" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="M268" s="14" t="n">
-        <v>232</v>
-      </c>
+        <v>15.6</v>
+      </c>
+      <c r="M268" s="14" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="B269" s="12" t="n">
-        <v>32.63534</v>
+        <v>32.61043</v>
       </c>
       <c r="C269" s="12" t="n">
-        <v>35.39574</v>
+        <v>34.92748</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>כביש החוף</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
@@ -13353,28 +13349,26 @@
         <v>800</v>
       </c>
       <c r="K269" t="n">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="L269" t="n">
         <v>15.6</v>
       </c>
-      <c r="M269" t="n">
-        <v>232</v>
-      </c>
+      <c r="M269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" s="14" t="n">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="B270" s="15" t="n">
-        <v>32.71608</v>
+        <v>32.58656</v>
       </c>
       <c r="C270" s="15" t="n">
-        <v>35.46579</v>
+        <v>34.92636</v>
       </c>
       <c r="D270" s="14" t="inlineStr">
         <is>
-          <t>דרך המושבות</t>
+          <t>כביש החוף</t>
         </is>
       </c>
       <c r="E270" s="14" t="inlineStr">
@@ -13388,40 +13382,38 @@
         </is>
       </c>
       <c r="G270" s="14" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H270" s="16" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I270" s="17" t="n">
-        <v>4000</v>
+        <v>8000</v>
       </c>
       <c r="J270" s="17" t="n">
-        <v>400</v>
+        <v>800</v>
       </c>
       <c r="K270" s="14" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="L270" s="14" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="M270" s="14" t="n">
-        <v>232</v>
-      </c>
+        <v>15.6</v>
+      </c>
+      <c r="M270" s="14" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="B271" s="12" t="n">
-        <v>31.12478</v>
+        <v>32.74157</v>
       </c>
       <c r="C271" s="12" t="n">
-        <v>35.01084</v>
+        <v>35.56785</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>90</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
@@ -13431,7 +13423,7 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>נגב / ערבה</t>
+          <t>חיפה / כרמל</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -13441,34 +13433,32 @@
         <v>150000</v>
       </c>
       <c r="I271" s="13" t="n">
-        <v>7000</v>
+        <v>9000</v>
       </c>
       <c r="J271" s="13" t="n">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="K271" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="L271" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="M271" t="n">
-        <v>225</v>
-      </c>
+        <v>17.6</v>
+      </c>
+      <c r="M271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" s="14" t="n">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="B272" s="15" t="n">
-        <v>29.54367</v>
+        <v>31.14138</v>
       </c>
       <c r="C272" s="15" t="n">
-        <v>35.13064</v>
+        <v>35.36025</v>
       </c>
       <c r="D272" s="14" t="inlineStr">
         <is>
-          <t>Aqaba Back Road Hight Way</t>
+          <t>90</t>
         </is>
       </c>
       <c r="E272" s="14" t="inlineStr">
@@ -13488,32 +13478,32 @@
         <v>150000</v>
       </c>
       <c r="I272" s="17" t="n">
-        <v>8000</v>
+        <v>9000</v>
       </c>
       <c r="J272" s="17" t="n">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="K272" s="14" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="L272" s="14" t="n">
-        <v>15.6</v>
+        <v>17.6</v>
       </c>
       <c r="M272" s="14" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="B273" s="12" t="n">
-        <v>32.55248</v>
+        <v>29.5441</v>
       </c>
       <c r="C273" s="12" t="n">
-        <v>35.0312</v>
+        <v>34.95027</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>כביש חוצה ישראל</t>
+          <t>90</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
@@ -13523,7 +13513,7 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>חיפה / כרמל</t>
+          <t>נגב / ערבה</t>
         </is>
       </c>
       <c r="G273" t="n">
@@ -13533,32 +13523,32 @@
         <v>150000</v>
       </c>
       <c r="I273" s="13" t="n">
-        <v>8000</v>
+        <v>9000</v>
       </c>
       <c r="J273" s="13" t="n">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="K273" t="n">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="L273" t="n">
-        <v>15.6</v>
+        <v>17.6</v>
       </c>
       <c r="M273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" s="14" t="n">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="B274" s="15" t="n">
-        <v>32.58001</v>
+        <v>32.70484</v>
       </c>
       <c r="C274" s="15" t="n">
-        <v>35.04577</v>
+        <v>35.58641</v>
       </c>
       <c r="D274" s="14" t="inlineStr">
         <is>
-          <t>כביש חוצה ישראל</t>
+          <t>90</t>
         </is>
       </c>
       <c r="E274" s="14" t="inlineStr">
@@ -13572,38 +13562,38 @@
         </is>
       </c>
       <c r="G274" s="14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H274" s="16" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I274" s="17" t="n">
-        <v>8000</v>
+        <v>4000</v>
       </c>
       <c r="J274" s="17" t="n">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="K274" s="14" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="L274" s="14" t="n">
-        <v>15.6</v>
+        <v>7.8</v>
       </c>
       <c r="M274" s="14" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="B275" s="12" t="n">
-        <v>32.61043</v>
+        <v>32.67837</v>
       </c>
       <c r="C275" s="12" t="n">
-        <v>34.92748</v>
+        <v>35.5805</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>כביש החוף</t>
+          <t>90</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
@@ -13623,32 +13613,32 @@
         <v>150000</v>
       </c>
       <c r="I275" s="13" t="n">
-        <v>8000</v>
+        <v>9000</v>
       </c>
       <c r="J275" s="13" t="n">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="K275" t="n">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="L275" t="n">
-        <v>15.6</v>
+        <v>17.6</v>
       </c>
       <c r="M275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" s="14" t="n">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="B276" s="15" t="n">
-        <v>32.58656</v>
+        <v>29.57788</v>
       </c>
       <c r="C276" s="15" t="n">
-        <v>34.92636</v>
+        <v>34.96757</v>
       </c>
       <c r="D276" s="14" t="inlineStr">
         <is>
-          <t>כביש החוף</t>
+          <t>הערבה</t>
         </is>
       </c>
       <c r="E276" s="14" t="inlineStr">
@@ -13658,7 +13648,7 @@
       </c>
       <c r="F276" s="14" t="inlineStr">
         <is>
-          <t>חיפה / כרמל</t>
+          <t>נגב / ערבה</t>
         </is>
       </c>
       <c r="G276" s="14" t="n">
@@ -13683,17 +13673,17 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="B277" s="12" t="n">
-        <v>32.74157</v>
+        <v>29.60913</v>
       </c>
       <c r="C277" s="12" t="n">
-        <v>35.56785</v>
+        <v>34.98382</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>הערבה</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
@@ -13703,7 +13693,7 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>חיפה / כרמל</t>
+          <t>נגב / ערבה</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -13713,32 +13703,32 @@
         <v>150000</v>
       </c>
       <c r="I277" s="13" t="n">
-        <v>9000</v>
+        <v>8000</v>
       </c>
       <c r="J277" s="13" t="n">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="K277" t="n">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="L277" t="n">
-        <v>17.6</v>
+        <v>15.6</v>
       </c>
       <c r="M277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" s="14" t="n">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="B278" s="15" t="n">
-        <v>31.14138</v>
+        <v>29.76344</v>
       </c>
       <c r="C278" s="15" t="n">
-        <v>35.36025</v>
+        <v>35.01411</v>
       </c>
       <c r="D278" s="14" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>הערבה</t>
         </is>
       </c>
       <c r="E278" s="14" t="inlineStr">
@@ -13758,32 +13748,32 @@
         <v>150000</v>
       </c>
       <c r="I278" s="17" t="n">
-        <v>9000</v>
+        <v>8000</v>
       </c>
       <c r="J278" s="17" t="n">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="K278" s="14" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="L278" s="14" t="n">
-        <v>17.6</v>
+        <v>15.6</v>
       </c>
       <c r="M278" s="14" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="B279" s="12" t="n">
-        <v>29.5441</v>
+        <v>30.28384</v>
       </c>
       <c r="C279" s="12" t="n">
-        <v>34.95027</v>
+        <v>34.99975</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
@@ -13797,128 +13787,128 @@
         </is>
       </c>
       <c r="G279" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H279" s="6" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="I279" s="13" t="n">
-        <v>9000</v>
+        <v>22000</v>
       </c>
       <c r="J279" s="13" t="n">
-        <v>900</v>
+        <v>2200</v>
       </c>
       <c r="K279" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="L279" t="n">
-        <v>17.6</v>
+        <v>42.9</v>
       </c>
       <c r="M279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" s="14" t="n">
-        <v>293</v>
+        <v>304</v>
       </c>
       <c r="B280" s="15" t="n">
-        <v>32.70484</v>
+        <v>30.81704</v>
       </c>
       <c r="C280" s="15" t="n">
-        <v>35.58641</v>
+        <v>34.75609</v>
       </c>
       <c r="D280" s="14" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E280" s="14" t="inlineStr">
         <is>
-          <t>רגיל</t>
+          <t>עוטף עזה</t>
         </is>
       </c>
       <c r="F280" s="14" t="inlineStr">
         <is>
-          <t>חיפה / כרמל</t>
+          <t>עוטף עזה / הנגב המערבי</t>
         </is>
       </c>
       <c r="G280" s="14" t="n">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="H280" s="16" t="n">
-        <v>100000</v>
+        <v>250000</v>
       </c>
       <c r="I280" s="17" t="n">
-        <v>4000</v>
+        <v>22000</v>
       </c>
       <c r="J280" s="17" t="n">
-        <v>400</v>
+        <v>2200</v>
       </c>
       <c r="K280" s="14" t="n">
         <v>90</v>
       </c>
       <c r="L280" s="14" t="n">
-        <v>7.8</v>
+        <v>42.9</v>
       </c>
       <c r="M280" s="14" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="B281" s="12" t="n">
-        <v>32.67837</v>
+        <v>30.78002</v>
       </c>
       <c r="C281" s="12" t="n">
-        <v>35.5805</v>
+        <v>34.76921</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>רגיל</t>
+          <t>עוטף עזה</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>חיפה / כרמל</t>
+          <t>עוטף עזה / הנגב המערבי</t>
         </is>
       </c>
       <c r="G281" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H281" s="6" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="I281" s="13" t="n">
-        <v>9000</v>
+        <v>22000</v>
       </c>
       <c r="J281" s="13" t="n">
-        <v>900</v>
+        <v>2200</v>
       </c>
       <c r="K281" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="L281" t="n">
-        <v>17.6</v>
+        <v>42.9</v>
       </c>
       <c r="M281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" s="14" t="n">
-        <v>296</v>
+        <v>310</v>
       </c>
       <c r="B282" s="15" t="n">
-        <v>29.57788</v>
+        <v>30.04781</v>
       </c>
       <c r="C282" s="15" t="n">
-        <v>34.96757</v>
+        <v>35.01047</v>
       </c>
       <c r="D282" s="14" t="inlineStr">
         <is>
-          <t>הערבה</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E282" s="14" t="inlineStr">
@@ -13944,7 +13934,7 @@
         <v>800</v>
       </c>
       <c r="K282" s="14" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="L282" s="14" t="n">
         <v>15.6</v>
@@ -13953,17 +13943,17 @@
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>297</v>
+        <v>311</v>
       </c>
       <c r="B283" s="12" t="n">
-        <v>29.60913</v>
+        <v>31.05359</v>
       </c>
       <c r="C283" s="12" t="n">
-        <v>34.98382</v>
+        <v>35.03088</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>הערבה</t>
+          <t>25</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -13983,32 +13973,32 @@
         <v>150000</v>
       </c>
       <c r="I283" s="13" t="n">
-        <v>8000</v>
+        <v>7000</v>
       </c>
       <c r="J283" s="13" t="n">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="K283" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="L283" t="n">
-        <v>15.6</v>
+        <v>13.7</v>
       </c>
       <c r="M283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" s="14" t="n">
-        <v>300</v>
+        <v>312</v>
       </c>
       <c r="B284" s="15" t="n">
-        <v>29.76344</v>
+        <v>31.06829</v>
       </c>
       <c r="C284" s="15" t="n">
-        <v>35.01411</v>
+        <v>35.00661</v>
       </c>
       <c r="D284" s="14" t="inlineStr">
         <is>
-          <t>הערבה</t>
+          <t>25</t>
         </is>
       </c>
       <c r="E284" s="14" t="inlineStr">
@@ -14022,38 +14012,38 @@
         </is>
       </c>
       <c r="G284" s="14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H284" s="16" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I284" s="17" t="n">
-        <v>8000</v>
+        <v>4000</v>
       </c>
       <c r="J284" s="17" t="n">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="K284" s="14" t="n">
         <v>90</v>
       </c>
       <c r="L284" s="14" t="n">
-        <v>15.6</v>
+        <v>7.8</v>
       </c>
       <c r="M284" s="14" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>303</v>
+        <v>317</v>
       </c>
       <c r="B285" s="12" t="n">
-        <v>30.28384</v>
+        <v>29.83364</v>
       </c>
       <c r="C285" s="12" t="n">
-        <v>34.99975</v>
+        <v>35.02882</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>הערבה</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -14067,38 +14057,38 @@
         </is>
       </c>
       <c r="G285" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H285" s="6" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="I285" s="13" t="n">
-        <v>22000</v>
+        <v>8000</v>
       </c>
       <c r="J285" s="13" t="n">
-        <v>2200</v>
+        <v>800</v>
       </c>
       <c r="K285" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="L285" t="n">
-        <v>42.9</v>
+        <v>15.6</v>
       </c>
       <c r="M285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" s="14" t="n">
-        <v>304</v>
+        <v>318</v>
       </c>
       <c r="B286" s="15" t="n">
-        <v>30.81704</v>
+        <v>29.63183</v>
       </c>
       <c r="C286" s="15" t="n">
-        <v>34.75609</v>
+        <v>34.88065</v>
       </c>
       <c r="D286" s="14" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>כביש הגבול המערבי</t>
         </is>
       </c>
       <c r="E286" s="14" t="inlineStr">
@@ -14112,48 +14102,48 @@
         </is>
       </c>
       <c r="G286" s="14" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H286" s="16" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="I286" s="17" t="n">
-        <v>22000</v>
+        <v>8000</v>
       </c>
       <c r="J286" s="17" t="n">
-        <v>2200</v>
+        <v>800</v>
       </c>
       <c r="K286" s="14" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="L286" s="14" t="n">
-        <v>42.9</v>
+        <v>15.6</v>
       </c>
       <c r="M286" s="14" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>305</v>
+        <v>319</v>
       </c>
       <c r="B287" s="12" t="n">
-        <v>30.78002</v>
+        <v>29.77754</v>
       </c>
       <c r="C287" s="12" t="n">
-        <v>34.76921</v>
+        <v>35.05858</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>Jordan Valley Highway</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>עוטף עזה</t>
+          <t>רגיל</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>עוטף עזה / הנגב המערבי</t>
+          <t>נגב / ערבה</t>
         </is>
       </c>
       <c r="G287" t="n">
@@ -14163,32 +14153,32 @@
         <v>250000</v>
       </c>
       <c r="I287" s="13" t="n">
-        <v>22000</v>
+        <v>24000</v>
       </c>
       <c r="J287" s="13" t="n">
-        <v>2200</v>
+        <v>2400</v>
       </c>
       <c r="K287" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="L287" t="n">
-        <v>42.9</v>
+        <v>46.8</v>
       </c>
       <c r="M287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" s="14" t="n">
-        <v>309</v>
+        <v>320</v>
       </c>
       <c r="B288" s="15" t="n">
-        <v>29.52232</v>
+        <v>30.13754</v>
       </c>
       <c r="C288" s="15" t="n">
-        <v>35.00277</v>
+        <v>35.138</v>
       </c>
       <c r="D288" s="14" t="inlineStr">
         <is>
-          <t>شارع الملك حسين</t>
+          <t>הערבה</t>
         </is>
       </c>
       <c r="E288" s="14" t="inlineStr">
@@ -14223,13 +14213,13 @@
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="B289" s="12" t="n">
-        <v>30.04781</v>
+        <v>29.84431</v>
       </c>
       <c r="C289" s="12" t="n">
-        <v>35.01047</v>
+        <v>34.83819</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -14238,12 +14228,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>רגיל</t>
+          <t>עוטף עזה</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>נגב / ערבה</t>
+          <t>עוטף עזה / הנגב המערבי</t>
         </is>
       </c>
       <c r="G289" t="n">
@@ -14268,17 +14258,17 @@
     </row>
     <row r="290">
       <c r="A290" s="14" t="n">
-        <v>311</v>
+        <v>324</v>
       </c>
       <c r="B290" s="15" t="n">
-        <v>31.05359</v>
+        <v>30.48576</v>
       </c>
       <c r="C290" s="15" t="n">
-        <v>35.03088</v>
+        <v>34.93315</v>
       </c>
       <c r="D290" s="14" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E290" s="14" t="inlineStr">
@@ -14292,38 +14282,38 @@
         </is>
       </c>
       <c r="G290" s="14" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H290" s="16" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="I290" s="17" t="n">
-        <v>7000</v>
+        <v>22000</v>
       </c>
       <c r="J290" s="17" t="n">
-        <v>700</v>
+        <v>2200</v>
       </c>
       <c r="K290" s="14" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="L290" s="14" t="n">
-        <v>13.7</v>
+        <v>42.9</v>
       </c>
       <c r="M290" s="14" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>312</v>
+        <v>330</v>
       </c>
       <c r="B291" s="12" t="n">
-        <v>31.06829</v>
+        <v>29.94978</v>
       </c>
       <c r="C291" s="12" t="n">
-        <v>35.00661</v>
+        <v>34.91844</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
@@ -14337,34 +14327,34 @@
         </is>
       </c>
       <c r="G291" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H291" s="6" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I291" s="13" t="n">
-        <v>4000</v>
+        <v>8000</v>
       </c>
       <c r="J291" s="13" t="n">
-        <v>400</v>
+        <v>800</v>
       </c>
       <c r="K291" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="L291" t="n">
-        <v>7.8</v>
+        <v>15.6</v>
       </c>
       <c r="M291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" s="14" t="n">
-        <v>317</v>
+        <v>331</v>
       </c>
       <c r="B292" s="15" t="n">
-        <v>29.83364</v>
+        <v>29.96941</v>
       </c>
       <c r="C292" s="15" t="n">
-        <v>35.02882</v>
+        <v>35.06507</v>
       </c>
       <c r="D292" s="14" t="inlineStr">
         <is>
@@ -14394,7 +14384,7 @@
         <v>800</v>
       </c>
       <c r="K292" s="14" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="L292" s="14" t="n">
         <v>15.6</v>
@@ -14403,27 +14393,27 @@
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>318</v>
+        <v>333</v>
       </c>
       <c r="B293" s="12" t="n">
-        <v>29.63183</v>
+        <v>30.26971</v>
       </c>
       <c r="C293" s="12" t="n">
-        <v>34.88065</v>
+        <v>35.13539</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>כביש הגבול המערבי</t>
+          <t>הערבה</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>עוטף עזה</t>
+          <t>רגיל</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>עוטף עזה / הנגב המערבי</t>
+          <t>נגב / ערבה</t>
         </is>
       </c>
       <c r="G293" t="n">
@@ -14439,7 +14429,7 @@
         <v>800</v>
       </c>
       <c r="K293" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="L293" t="n">
         <v>15.6</v>
@@ -14448,62 +14438,62 @@
     </row>
     <row r="294">
       <c r="A294" s="14" t="n">
-        <v>319</v>
+        <v>334</v>
       </c>
       <c r="B294" s="15" t="n">
-        <v>29.77754</v>
+        <v>29.73907</v>
       </c>
       <c r="C294" s="15" t="n">
-        <v>35.05858</v>
+        <v>34.85312</v>
       </c>
       <c r="D294" s="14" t="inlineStr">
         <is>
-          <t>Jordan Valley Highway</t>
+          <t>כביש הגבול המערבי</t>
         </is>
       </c>
       <c r="E294" s="14" t="inlineStr">
         <is>
-          <t>רגיל</t>
+          <t>עוטף עזה</t>
         </is>
       </c>
       <c r="F294" s="14" t="inlineStr">
         <is>
-          <t>נגב / ערבה</t>
+          <t>עוטף עזה / הנגב המערבי</t>
         </is>
       </c>
       <c r="G294" s="14" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H294" s="16" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="I294" s="17" t="n">
-        <v>24000</v>
+        <v>8000</v>
       </c>
       <c r="J294" s="17" t="n">
-        <v>2400</v>
+        <v>800</v>
       </c>
       <c r="K294" s="14" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="L294" s="14" t="n">
-        <v>46.8</v>
+        <v>15.6</v>
       </c>
       <c r="M294" s="14" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>320</v>
+        <v>335</v>
       </c>
       <c r="B295" s="12" t="n">
-        <v>30.13754</v>
+        <v>31.03923</v>
       </c>
       <c r="C295" s="12" t="n">
-        <v>35.138</v>
+        <v>35.16624</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>הערבה</t>
+          <t>25</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
@@ -14523,32 +14513,32 @@
         <v>150000</v>
       </c>
       <c r="I295" s="13" t="n">
-        <v>8000</v>
+        <v>7000</v>
       </c>
       <c r="J295" s="13" t="n">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="K295" t="n">
         <v>90</v>
       </c>
       <c r="L295" t="n">
-        <v>15.6</v>
+        <v>13.7</v>
       </c>
       <c r="M295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" s="14" t="n">
-        <v>321</v>
+        <v>336</v>
       </c>
       <c r="B296" s="15" t="n">
-        <v>32.51782</v>
+        <v>29.70652</v>
       </c>
       <c r="C296" s="15" t="n">
-        <v>35.12337</v>
+        <v>34.99732</v>
       </c>
       <c r="D296" s="14" t="inlineStr">
         <is>
-          <t>ואדי עארה</t>
+          <t>הערבה</t>
         </is>
       </c>
       <c r="E296" s="14" t="inlineStr">
@@ -14558,7 +14548,7 @@
       </c>
       <c r="F296" s="14" t="inlineStr">
         <is>
-          <t>חיפה / כרמל</t>
+          <t>נגב / ערבה</t>
         </is>
       </c>
       <c r="G296" s="14" t="n">
@@ -14583,58 +14573,58 @@
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>322</v>
+        <v>337</v>
       </c>
       <c r="B297" s="12" t="n">
-        <v>29.84431</v>
+        <v>30.37038</v>
       </c>
       <c r="C297" s="12" t="n">
-        <v>34.83819</v>
+        <v>34.96243</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>עוטף עזה</t>
+          <t>רגיל</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>עוטף עזה / הנגב המערבי</t>
+          <t>נגב / ערבה</t>
         </is>
       </c>
       <c r="G297" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H297" s="6" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="I297" s="13" t="n">
-        <v>8000</v>
+        <v>22000</v>
       </c>
       <c r="J297" s="13" t="n">
-        <v>800</v>
+        <v>2200</v>
       </c>
       <c r="K297" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="L297" t="n">
-        <v>15.6</v>
+        <v>42.9</v>
       </c>
       <c r="M297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" s="14" t="n">
-        <v>324</v>
+        <v>338</v>
       </c>
       <c r="B298" s="15" t="n">
-        <v>30.48576</v>
+        <v>30.16144</v>
       </c>
       <c r="C298" s="15" t="n">
-        <v>34.93315</v>
+        <v>35.01743</v>
       </c>
       <c r="D298" s="14" t="inlineStr">
         <is>
@@ -14664,7 +14654,7 @@
         <v>2200</v>
       </c>
       <c r="K298" s="14" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="L298" s="14" t="n">
         <v>42.9</v>
@@ -14673,17 +14663,17 @@
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>327</v>
+        <v>343</v>
       </c>
       <c r="B299" s="12" t="n">
-        <v>29.63123</v>
+        <v>31.07234</v>
       </c>
       <c r="C299" s="12" t="n">
-        <v>35.03926</v>
+        <v>35.3971</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>Jordan Valley Highway</t>
+          <t>90</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
@@ -14703,32 +14693,32 @@
         <v>150000</v>
       </c>
       <c r="I299" s="13" t="n">
-        <v>8000</v>
+        <v>9000</v>
       </c>
       <c r="J299" s="13" t="n">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="K299" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="L299" t="n">
-        <v>15.6</v>
+        <v>17.6</v>
       </c>
       <c r="M299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" s="14" t="n">
-        <v>330</v>
+        <v>345</v>
       </c>
       <c r="B300" s="15" t="n">
-        <v>29.94978</v>
+        <v>29.89666</v>
       </c>
       <c r="C300" s="15" t="n">
-        <v>34.91844</v>
+        <v>35.06371</v>
       </c>
       <c r="D300" s="14" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>הערבה</t>
         </is>
       </c>
       <c r="E300" s="14" t="inlineStr">
@@ -14754,7 +14744,7 @@
         <v>800</v>
       </c>
       <c r="K300" s="14" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="L300" s="14" t="n">
         <v>15.6</v>
@@ -14763,13 +14753,13 @@
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>331</v>
+        <v>346</v>
       </c>
       <c r="B301" s="12" t="n">
-        <v>29.96941</v>
+        <v>30.05335</v>
       </c>
       <c r="C301" s="12" t="n">
-        <v>35.06507</v>
+        <v>35.11309</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -14799,7 +14789,7 @@
         <v>800</v>
       </c>
       <c r="K301" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="L301" t="n">
         <v>15.6</v>
@@ -14808,62 +14798,62 @@
     </row>
     <row r="302">
       <c r="A302" s="14" t="n">
-        <v>332</v>
+        <v>347</v>
       </c>
       <c r="B302" s="15" t="n">
-        <v>29.90251</v>
+        <v>30.87527</v>
       </c>
       <c r="C302" s="15" t="n">
-        <v>35.11642</v>
+        <v>34.78662</v>
       </c>
       <c r="D302" s="14" t="inlineStr">
         <is>
-          <t>Jordan Valley Highway</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E302" s="14" t="inlineStr">
         <is>
-          <t>רגיל</t>
+          <t>עוטף עזה</t>
         </is>
       </c>
       <c r="F302" s="14" t="inlineStr">
         <is>
-          <t>נגב / ערבה</t>
+          <t>עוטף עזה / הנגב המערבי</t>
         </is>
       </c>
       <c r="G302" s="14" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H302" s="16" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="I302" s="17" t="n">
-        <v>8000</v>
+        <v>22000</v>
       </c>
       <c r="J302" s="17" t="n">
-        <v>800</v>
+        <v>2200</v>
       </c>
       <c r="K302" s="14" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="L302" s="14" t="n">
-        <v>15.6</v>
+        <v>42.9</v>
       </c>
       <c r="M302" s="14" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>333</v>
+        <v>350</v>
       </c>
       <c r="B303" s="12" t="n">
-        <v>30.26971</v>
+        <v>32.5894</v>
       </c>
       <c r="C303" s="12" t="n">
-        <v>35.13539</v>
+        <v>34.98374</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>הערבה</t>
+          <t>ואדי מילק</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
@@ -14873,7 +14863,7 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>נגב / ערבה</t>
+          <t>חיפה / כרמל</t>
         </is>
       </c>
       <c r="G303" t="n">
@@ -14889,7 +14879,7 @@
         <v>800</v>
       </c>
       <c r="K303" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="L303" t="n">
         <v>15.6</v>
@@ -14898,17 +14888,17 @@
     </row>
     <row r="304">
       <c r="A304" s="14" t="n">
-        <v>334</v>
+        <v>357</v>
       </c>
       <c r="B304" s="15" t="n">
-        <v>29.73907</v>
+        <v>29.90423</v>
       </c>
       <c r="C304" s="15" t="n">
-        <v>34.85312</v>
+        <v>34.86291</v>
       </c>
       <c r="D304" s="14" t="inlineStr">
         <is>
-          <t>כביש הגבול המערבי</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E304" s="14" t="inlineStr">
@@ -14943,17 +14933,17 @@
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>335</v>
+        <v>358</v>
       </c>
       <c r="B305" s="12" t="n">
-        <v>31.03923</v>
+        <v>30.00362</v>
       </c>
       <c r="C305" s="12" t="n">
-        <v>35.16624</v>
+        <v>34.9552</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
@@ -14973,28 +14963,28 @@
         <v>150000</v>
       </c>
       <c r="I305" s="13" t="n">
-        <v>7000</v>
+        <v>8000</v>
       </c>
       <c r="J305" s="13" t="n">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="K305" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="L305" t="n">
-        <v>13.7</v>
+        <v>15.6</v>
       </c>
       <c r="M305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" s="14" t="n">
-        <v>336</v>
+        <v>361</v>
       </c>
       <c r="B306" s="15" t="n">
-        <v>29.70652</v>
+        <v>29.65814</v>
       </c>
       <c r="C306" s="15" t="n">
-        <v>34.99732</v>
+        <v>34.99038</v>
       </c>
       <c r="D306" s="14" t="inlineStr">
         <is>
@@ -15033,17 +15023,17 @@
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>337</v>
+        <v>363</v>
       </c>
       <c r="B307" s="12" t="n">
-        <v>30.37038</v>
+        <v>30.20251</v>
       </c>
       <c r="C307" s="12" t="n">
-        <v>34.96243</v>
+        <v>35.13549</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>הערבה</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
@@ -15057,38 +15047,38 @@
         </is>
       </c>
       <c r="G307" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H307" s="6" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="I307" s="13" t="n">
-        <v>22000</v>
+        <v>8000</v>
       </c>
       <c r="J307" s="13" t="n">
-        <v>2200</v>
+        <v>800</v>
       </c>
       <c r="K307" t="n">
         <v>90</v>
       </c>
       <c r="L307" t="n">
-        <v>42.9</v>
+        <v>15.6</v>
       </c>
       <c r="M307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" s="14" t="n">
-        <v>338</v>
+        <v>365</v>
       </c>
       <c r="B308" s="15" t="n">
-        <v>30.16144</v>
+        <v>29.72945</v>
       </c>
       <c r="C308" s="15" t="n">
-        <v>35.01743</v>
+        <v>35.03561</v>
       </c>
       <c r="D308" s="14" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>Jordan Valley Highway</t>
         </is>
       </c>
       <c r="E308" s="14" t="inlineStr">
@@ -15108,32 +15098,32 @@
         <v>250000</v>
       </c>
       <c r="I308" s="17" t="n">
-        <v>22000</v>
+        <v>24000</v>
       </c>
       <c r="J308" s="17" t="n">
-        <v>2200</v>
+        <v>2400</v>
       </c>
       <c r="K308" s="14" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="L308" s="14" t="n">
-        <v>42.9</v>
+        <v>46.8</v>
       </c>
       <c r="M308" s="14" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>343</v>
+        <v>366</v>
       </c>
       <c r="B309" s="12" t="n">
-        <v>31.07234</v>
+        <v>30.29091</v>
       </c>
       <c r="C309" s="12" t="n">
-        <v>35.3971</v>
+        <v>35.09632</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
@@ -15153,32 +15143,32 @@
         <v>150000</v>
       </c>
       <c r="I309" s="13" t="n">
-        <v>9000</v>
+        <v>8000</v>
       </c>
       <c r="J309" s="13" t="n">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="K309" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="L309" t="n">
-        <v>17.6</v>
+        <v>15.6</v>
       </c>
       <c r="M309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" s="14" t="n">
-        <v>345</v>
+        <v>367</v>
       </c>
       <c r="B310" s="15" t="n">
-        <v>29.89666</v>
+        <v>30.9957</v>
       </c>
       <c r="C310" s="15" t="n">
-        <v>35.06371</v>
+        <v>34.92368</v>
       </c>
       <c r="D310" s="14" t="inlineStr">
         <is>
-          <t>הערבה</t>
+          <t>204</t>
         </is>
       </c>
       <c r="E310" s="14" t="inlineStr">
@@ -15204,7 +15194,7 @@
         <v>800</v>
       </c>
       <c r="K310" s="14" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="L310" s="14" t="n">
         <v>15.6</v>
@@ -15213,17 +15203,17 @@
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>346</v>
+        <v>368</v>
       </c>
       <c r="B311" s="12" t="n">
-        <v>30.05335</v>
+        <v>32.57236</v>
       </c>
       <c r="C311" s="12" t="n">
-        <v>35.11309</v>
+        <v>35.07668</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>הערבה</t>
+          <t>672</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
@@ -15233,7 +15223,7 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>נגב / ערבה</t>
+          <t>חיפה / כרמל</t>
         </is>
       </c>
       <c r="G311" t="n">
@@ -15249,7 +15239,7 @@
         <v>800</v>
       </c>
       <c r="K311" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="L311" t="n">
         <v>15.6</v>
@@ -15258,72 +15248,72 @@
     </row>
     <row r="312">
       <c r="A312" s="14" t="n">
-        <v>347</v>
+        <v>369</v>
       </c>
       <c r="B312" s="15" t="n">
-        <v>30.87527</v>
+        <v>32.56674</v>
       </c>
       <c r="C312" s="15" t="n">
-        <v>34.78662</v>
+        <v>35.26239</v>
       </c>
       <c r="D312" s="14" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>675</t>
         </is>
       </c>
       <c r="E312" s="14" t="inlineStr">
         <is>
-          <t>עוטף עזה</t>
+          <t>רגיל</t>
         </is>
       </c>
       <c r="F312" s="14" t="inlineStr">
         <is>
-          <t>עוטף עזה / הנגב המערבי</t>
+          <t>חיפה / כרמל</t>
         </is>
       </c>
       <c r="G312" s="14" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H312" s="16" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="I312" s="17" t="n">
-        <v>22000</v>
+        <v>8000</v>
       </c>
       <c r="J312" s="17" t="n">
-        <v>2200</v>
+        <v>800</v>
       </c>
       <c r="K312" s="14" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="L312" s="14" t="n">
-        <v>42.9</v>
+        <v>15.6</v>
       </c>
       <c r="M312" s="14" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>348</v>
+        <v>370</v>
       </c>
       <c r="B313" s="12" t="n">
-        <v>29.47292</v>
+        <v>30.91157</v>
       </c>
       <c r="C313" s="12" t="n">
-        <v>34.98165</v>
+        <v>34.84372</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>شارع الملك حسين</t>
+          <t>204</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>רגיל</t>
+          <t>עוטף עזה</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>נגב / ערבה</t>
+          <t>עוטף עזה / הנגב המערבי</t>
         </is>
       </c>
       <c r="G313" t="n">
@@ -15348,17 +15338,17 @@
     </row>
     <row r="314">
       <c r="A314" s="14" t="n">
-        <v>350</v>
+        <v>371</v>
       </c>
       <c r="B314" s="15" t="n">
-        <v>32.5894</v>
+        <v>29.55534</v>
       </c>
       <c r="C314" s="15" t="n">
-        <v>34.98374</v>
+        <v>34.91334</v>
       </c>
       <c r="D314" s="14" t="inlineStr">
         <is>
-          <t>ואדי מילק</t>
+          <t>דרך החוגגים</t>
         </is>
       </c>
       <c r="E314" s="14" t="inlineStr">
@@ -15368,7 +15358,7 @@
       </c>
       <c r="F314" s="14" t="inlineStr">
         <is>
-          <t>חיפה / כרמל</t>
+          <t>נגב / ערבה</t>
         </is>
       </c>
       <c r="G314" s="14" t="n">
@@ -15384,7 +15374,7 @@
         <v>800</v>
       </c>
       <c r="K314" s="14" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="L314" s="14" t="n">
         <v>15.6</v>
@@ -15393,17 +15383,17 @@
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>351</v>
+        <v>374</v>
       </c>
       <c r="B315" s="12" t="n">
-        <v>29.57155</v>
+        <v>32.59429</v>
       </c>
       <c r="C315" s="12" t="n">
-        <v>35.01651</v>
+        <v>35.18035</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>Jordan Valley Highway</t>
+          <t>66</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
@@ -15413,7 +15403,7 @@
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>נגב / ערבה</t>
+          <t>חיפה / כרמל</t>
         </is>
       </c>
       <c r="G315" t="n">
@@ -15429,7 +15419,7 @@
         <v>800</v>
       </c>
       <c r="K315" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="L315" t="n">
         <v>15.6</v>
@@ -15438,17 +15428,17 @@
     </row>
     <row r="316">
       <c r="A316" s="14" t="n">
-        <v>355</v>
+        <v>375</v>
       </c>
       <c r="B316" s="15" t="n">
-        <v>29.95947</v>
+        <v>31.00401</v>
       </c>
       <c r="C316" s="15" t="n">
-        <v>35.13153</v>
+        <v>35.27512</v>
       </c>
       <c r="D316" s="14" t="inlineStr">
         <is>
-          <t>Jordan Valley Highway</t>
+          <t>מעלה תמר</t>
         </is>
       </c>
       <c r="E316" s="14" t="inlineStr">
@@ -15462,48 +15452,48 @@
         </is>
       </c>
       <c r="G316" s="14" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H316" s="16" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="I316" s="17" t="n">
-        <v>24000</v>
+        <v>8000</v>
       </c>
       <c r="J316" s="17" t="n">
-        <v>2400</v>
+        <v>800</v>
       </c>
       <c r="K316" s="14" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="L316" s="14" t="n">
-        <v>46.8</v>
+        <v>15.6</v>
       </c>
       <c r="M316" s="14" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>357</v>
+        <v>377</v>
       </c>
       <c r="B317" s="12" t="n">
-        <v>29.90423</v>
+        <v>30.92485</v>
       </c>
       <c r="C317" s="12" t="n">
-        <v>34.86291</v>
+        <v>35.02487</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>206</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>עוטף עזה</t>
+          <t>רגיל</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>עוטף עזה / הנגב המערבי</t>
+          <t>נגב / ערבה</t>
         </is>
       </c>
       <c r="G317" t="n">
@@ -15528,17 +15518,17 @@
     </row>
     <row r="318">
       <c r="A318" s="14" t="n">
-        <v>358</v>
+        <v>378</v>
       </c>
       <c r="B318" s="15" t="n">
-        <v>30.00362</v>
+        <v>32.71419</v>
       </c>
       <c r="C318" s="15" t="n">
-        <v>34.9552</v>
+        <v>35.54642</v>
       </c>
       <c r="D318" s="14" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>767</t>
         </is>
       </c>
       <c r="E318" s="14" t="inlineStr">
@@ -15548,7 +15538,7 @@
       </c>
       <c r="F318" s="14" t="inlineStr">
         <is>
-          <t>נגב / ערבה</t>
+          <t>חיפה / כרמל</t>
         </is>
       </c>
       <c r="G318" s="14" t="n">
@@ -15573,17 +15563,17 @@
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>361</v>
+        <v>380</v>
       </c>
       <c r="B319" s="12" t="n">
-        <v>29.65814</v>
+        <v>30.93723</v>
       </c>
       <c r="C319" s="12" t="n">
-        <v>34.99038</v>
+        <v>35.11694</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>הערבה</t>
+          <t>227</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
@@ -15609,7 +15599,7 @@
         <v>800</v>
       </c>
       <c r="K319" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="L319" t="n">
         <v>15.6</v>
@@ -15618,17 +15608,17 @@
     </row>
     <row r="320">
       <c r="A320" s="14" t="n">
-        <v>362</v>
+        <v>381</v>
       </c>
       <c r="B320" s="15" t="n">
-        <v>32.55072</v>
+        <v>30.95248</v>
       </c>
       <c r="C320" s="15" t="n">
-        <v>35.16414</v>
+        <v>35.01187</v>
       </c>
       <c r="D320" s="14" t="inlineStr">
         <is>
-          <t>ואדי עארה</t>
+          <t>225</t>
         </is>
       </c>
       <c r="E320" s="14" t="inlineStr">
@@ -15638,42 +15628,42 @@
       </c>
       <c r="F320" s="14" t="inlineStr">
         <is>
-          <t>חיפה / כרמל</t>
+          <t>נגב / ערבה</t>
         </is>
       </c>
       <c r="G320" s="14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H320" s="16" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I320" s="17" t="n">
-        <v>8000</v>
+        <v>4000</v>
       </c>
       <c r="J320" s="17" t="n">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="K320" s="14" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="L320" s="14" t="n">
-        <v>15.6</v>
+        <v>7.8</v>
       </c>
       <c r="M320" s="14" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>363</v>
+        <v>382</v>
       </c>
       <c r="B321" s="12" t="n">
-        <v>30.20251</v>
+        <v>31.01151</v>
       </c>
       <c r="C321" s="12" t="n">
-        <v>35.13549</v>
+        <v>35.07848</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>הערבה</t>
+          <t>206</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
@@ -15699,7 +15689,7 @@
         <v>800</v>
       </c>
       <c r="K321" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="L321" t="n">
         <v>15.6</v>
@@ -15708,17 +15698,17 @@
     </row>
     <row r="322">
       <c r="A322" s="14" t="n">
-        <v>364</v>
+        <v>383</v>
       </c>
       <c r="B322" s="15" t="n">
-        <v>29.8365</v>
+        <v>30.88774</v>
       </c>
       <c r="C322" s="15" t="n">
-        <v>35.10101</v>
+        <v>35.13939</v>
       </c>
       <c r="D322" s="14" t="inlineStr">
         <is>
-          <t>Jordan Valley Highway</t>
+          <t>227</t>
         </is>
       </c>
       <c r="E322" s="14" t="inlineStr">
@@ -15744,7 +15734,7 @@
         <v>800</v>
       </c>
       <c r="K322" s="14" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="L322" s="14" t="n">
         <v>15.6</v>
@@ -15753,17 +15743,17 @@
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>365</v>
+        <v>384</v>
       </c>
       <c r="B323" s="12" t="n">
-        <v>29.72945</v>
+        <v>30.9633</v>
       </c>
       <c r="C323" s="12" t="n">
-        <v>35.03561</v>
+        <v>35.04934</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>Jordan Valley Highway</t>
+          <t>227</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
@@ -15777,38 +15767,38 @@
         </is>
       </c>
       <c r="G323" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H323" s="6" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="I323" s="13" t="n">
-        <v>24000</v>
+        <v>8000</v>
       </c>
       <c r="J323" s="13" t="n">
-        <v>2400</v>
+        <v>800</v>
       </c>
       <c r="K323" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="L323" t="n">
-        <v>46.8</v>
+        <v>15.6</v>
       </c>
       <c r="M323" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" s="14" t="n">
-        <v>366</v>
+        <v>385</v>
       </c>
       <c r="B324" s="15" t="n">
-        <v>30.29091</v>
+        <v>31.08317</v>
       </c>
       <c r="C324" s="15" t="n">
-        <v>35.09632</v>
+        <v>35.21114</v>
       </c>
       <c r="D324" s="14" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>258</t>
         </is>
       </c>
       <c r="E324" s="14" t="inlineStr">
@@ -15834,822 +15824,12 @@
         <v>800</v>
       </c>
       <c r="K324" s="14" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="L324" s="14" t="n">
         <v>15.6</v>
       </c>
       <c r="M324" s="14" t="inlineStr"/>
-    </row>
-    <row r="325">
-      <c r="A325" t="n">
-        <v>367</v>
-      </c>
-      <c r="B325" s="12" t="n">
-        <v>30.9957</v>
-      </c>
-      <c r="C325" s="12" t="n">
-        <v>34.92368</v>
-      </c>
-      <c r="D325" t="inlineStr">
-        <is>
-          <t>204</t>
-        </is>
-      </c>
-      <c r="E325" t="inlineStr">
-        <is>
-          <t>רגיל</t>
-        </is>
-      </c>
-      <c r="F325" t="inlineStr">
-        <is>
-          <t>נגב / ערבה</t>
-        </is>
-      </c>
-      <c r="G325" t="n">
-        <v>20</v>
-      </c>
-      <c r="H325" s="6" t="n">
-        <v>150000</v>
-      </c>
-      <c r="I325" s="13" t="n">
-        <v>8000</v>
-      </c>
-      <c r="J325" s="13" t="n">
-        <v>800</v>
-      </c>
-      <c r="K325" t="n">
-        <v>80</v>
-      </c>
-      <c r="L325" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="M325" t="inlineStr"/>
-    </row>
-    <row r="326">
-      <c r="A326" s="14" t="n">
-        <v>368</v>
-      </c>
-      <c r="B326" s="15" t="n">
-        <v>32.57236</v>
-      </c>
-      <c r="C326" s="15" t="n">
-        <v>35.07668</v>
-      </c>
-      <c r="D326" s="14" t="inlineStr">
-        <is>
-          <t>672</t>
-        </is>
-      </c>
-      <c r="E326" s="14" t="inlineStr">
-        <is>
-          <t>רגיל</t>
-        </is>
-      </c>
-      <c r="F326" s="14" t="inlineStr">
-        <is>
-          <t>חיפה / כרמל</t>
-        </is>
-      </c>
-      <c r="G326" s="14" t="n">
-        <v>20</v>
-      </c>
-      <c r="H326" s="16" t="n">
-        <v>150000</v>
-      </c>
-      <c r="I326" s="17" t="n">
-        <v>8000</v>
-      </c>
-      <c r="J326" s="17" t="n">
-        <v>800</v>
-      </c>
-      <c r="K326" s="14" t="n">
-        <v>80</v>
-      </c>
-      <c r="L326" s="14" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="M326" s="14" t="inlineStr"/>
-    </row>
-    <row r="327">
-      <c r="A327" t="n">
-        <v>369</v>
-      </c>
-      <c r="B327" s="12" t="n">
-        <v>32.56674</v>
-      </c>
-      <c r="C327" s="12" t="n">
-        <v>35.26239</v>
-      </c>
-      <c r="D327" t="inlineStr">
-        <is>
-          <t>675</t>
-        </is>
-      </c>
-      <c r="E327" t="inlineStr">
-        <is>
-          <t>רגיל</t>
-        </is>
-      </c>
-      <c r="F327" t="inlineStr">
-        <is>
-          <t>חיפה / כרמל</t>
-        </is>
-      </c>
-      <c r="G327" t="n">
-        <v>20</v>
-      </c>
-      <c r="H327" s="6" t="n">
-        <v>150000</v>
-      </c>
-      <c r="I327" s="13" t="n">
-        <v>8000</v>
-      </c>
-      <c r="J327" s="13" t="n">
-        <v>800</v>
-      </c>
-      <c r="K327" t="n">
-        <v>80</v>
-      </c>
-      <c r="L327" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="M327" t="inlineStr"/>
-    </row>
-    <row r="328">
-      <c r="A328" s="14" t="n">
-        <v>370</v>
-      </c>
-      <c r="B328" s="15" t="n">
-        <v>30.91157</v>
-      </c>
-      <c r="C328" s="15" t="n">
-        <v>34.84372</v>
-      </c>
-      <c r="D328" s="14" t="inlineStr">
-        <is>
-          <t>204</t>
-        </is>
-      </c>
-      <c r="E328" s="14" t="inlineStr">
-        <is>
-          <t>עוטף עזה</t>
-        </is>
-      </c>
-      <c r="F328" s="14" t="inlineStr">
-        <is>
-          <t>עוטף עזה / הנגב המערבי</t>
-        </is>
-      </c>
-      <c r="G328" s="14" t="n">
-        <v>20</v>
-      </c>
-      <c r="H328" s="16" t="n">
-        <v>150000</v>
-      </c>
-      <c r="I328" s="17" t="n">
-        <v>8000</v>
-      </c>
-      <c r="J328" s="17" t="n">
-        <v>800</v>
-      </c>
-      <c r="K328" s="14" t="n">
-        <v>80</v>
-      </c>
-      <c r="L328" s="14" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="M328" s="14" t="inlineStr"/>
-    </row>
-    <row r="329">
-      <c r="A329" t="n">
-        <v>371</v>
-      </c>
-      <c r="B329" s="12" t="n">
-        <v>29.55534</v>
-      </c>
-      <c r="C329" s="12" t="n">
-        <v>34.91334</v>
-      </c>
-      <c r="D329" t="inlineStr">
-        <is>
-          <t>דרך החוגגים</t>
-        </is>
-      </c>
-      <c r="E329" t="inlineStr">
-        <is>
-          <t>רגיל</t>
-        </is>
-      </c>
-      <c r="F329" t="inlineStr">
-        <is>
-          <t>נגב / ערבה</t>
-        </is>
-      </c>
-      <c r="G329" t="n">
-        <v>20</v>
-      </c>
-      <c r="H329" s="6" t="n">
-        <v>150000</v>
-      </c>
-      <c r="I329" s="13" t="n">
-        <v>8000</v>
-      </c>
-      <c r="J329" s="13" t="n">
-        <v>800</v>
-      </c>
-      <c r="K329" t="n">
-        <v>80</v>
-      </c>
-      <c r="L329" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="M329" t="inlineStr"/>
-    </row>
-    <row r="330">
-      <c r="A330" s="14" t="n">
-        <v>372</v>
-      </c>
-      <c r="B330" s="15" t="n">
-        <v>29.45665</v>
-      </c>
-      <c r="C330" s="15" t="n">
-        <v>35.03705</v>
-      </c>
-      <c r="D330" s="14" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="E330" s="14" t="inlineStr">
-        <is>
-          <t>רגיל</t>
-        </is>
-      </c>
-      <c r="F330" s="14" t="inlineStr">
-        <is>
-          <t>נגב / ערבה</t>
-        </is>
-      </c>
-      <c r="G330" s="14" t="n">
-        <v>20</v>
-      </c>
-      <c r="H330" s="16" t="n">
-        <v>150000</v>
-      </c>
-      <c r="I330" s="17" t="n">
-        <v>8000</v>
-      </c>
-      <c r="J330" s="17" t="n">
-        <v>800</v>
-      </c>
-      <c r="K330" s="14" t="n">
-        <v>90</v>
-      </c>
-      <c r="L330" s="14" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="M330" s="14" t="inlineStr"/>
-    </row>
-    <row r="331">
-      <c r="A331" t="n">
-        <v>374</v>
-      </c>
-      <c r="B331" s="12" t="n">
-        <v>32.59429</v>
-      </c>
-      <c r="C331" s="12" t="n">
-        <v>35.18035</v>
-      </c>
-      <c r="D331" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="E331" t="inlineStr">
-        <is>
-          <t>רגיל</t>
-        </is>
-      </c>
-      <c r="F331" t="inlineStr">
-        <is>
-          <t>חיפה / כרמל</t>
-        </is>
-      </c>
-      <c r="G331" t="n">
-        <v>20</v>
-      </c>
-      <c r="H331" s="6" t="n">
-        <v>150000</v>
-      </c>
-      <c r="I331" s="13" t="n">
-        <v>8000</v>
-      </c>
-      <c r="J331" s="13" t="n">
-        <v>800</v>
-      </c>
-      <c r="K331" t="n">
-        <v>60</v>
-      </c>
-      <c r="L331" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="M331" t="inlineStr"/>
-    </row>
-    <row r="332">
-      <c r="A332" s="14" t="n">
-        <v>375</v>
-      </c>
-      <c r="B332" s="15" t="n">
-        <v>31.00401</v>
-      </c>
-      <c r="C332" s="15" t="n">
-        <v>35.27512</v>
-      </c>
-      <c r="D332" s="14" t="inlineStr">
-        <is>
-          <t>מעלה תמר</t>
-        </is>
-      </c>
-      <c r="E332" s="14" t="inlineStr">
-        <is>
-          <t>רגיל</t>
-        </is>
-      </c>
-      <c r="F332" s="14" t="inlineStr">
-        <is>
-          <t>נגב / ערבה</t>
-        </is>
-      </c>
-      <c r="G332" s="14" t="n">
-        <v>20</v>
-      </c>
-      <c r="H332" s="16" t="n">
-        <v>150000</v>
-      </c>
-      <c r="I332" s="17" t="n">
-        <v>8000</v>
-      </c>
-      <c r="J332" s="17" t="n">
-        <v>800</v>
-      </c>
-      <c r="K332" s="14" t="n">
-        <v>80</v>
-      </c>
-      <c r="L332" s="14" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="M332" s="14" t="inlineStr"/>
-    </row>
-    <row r="333">
-      <c r="A333" t="n">
-        <v>376</v>
-      </c>
-      <c r="B333" s="12" t="n">
-        <v>29.49429</v>
-      </c>
-      <c r="C333" s="12" t="n">
-        <v>35.08565</v>
-      </c>
-      <c r="D333" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="E333" t="inlineStr">
-        <is>
-          <t>רגיל</t>
-        </is>
-      </c>
-      <c r="F333" t="inlineStr">
-        <is>
-          <t>נגב / ערבה</t>
-        </is>
-      </c>
-      <c r="G333" t="n">
-        <v>20</v>
-      </c>
-      <c r="H333" s="6" t="n">
-        <v>150000</v>
-      </c>
-      <c r="I333" s="13" t="n">
-        <v>8000</v>
-      </c>
-      <c r="J333" s="13" t="n">
-        <v>800</v>
-      </c>
-      <c r="K333" t="n">
-        <v>90</v>
-      </c>
-      <c r="L333" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="M333" t="inlineStr"/>
-    </row>
-    <row r="334">
-      <c r="A334" s="14" t="n">
-        <v>377</v>
-      </c>
-      <c r="B334" s="15" t="n">
-        <v>30.92485</v>
-      </c>
-      <c r="C334" s="15" t="n">
-        <v>35.02487</v>
-      </c>
-      <c r="D334" s="14" t="inlineStr">
-        <is>
-          <t>206</t>
-        </is>
-      </c>
-      <c r="E334" s="14" t="inlineStr">
-        <is>
-          <t>רגיל</t>
-        </is>
-      </c>
-      <c r="F334" s="14" t="inlineStr">
-        <is>
-          <t>נגב / ערבה</t>
-        </is>
-      </c>
-      <c r="G334" s="14" t="n">
-        <v>20</v>
-      </c>
-      <c r="H334" s="16" t="n">
-        <v>150000</v>
-      </c>
-      <c r="I334" s="17" t="n">
-        <v>8000</v>
-      </c>
-      <c r="J334" s="17" t="n">
-        <v>800</v>
-      </c>
-      <c r="K334" s="14" t="n">
-        <v>80</v>
-      </c>
-      <c r="L334" s="14" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="M334" s="14" t="inlineStr"/>
-    </row>
-    <row r="335">
-      <c r="A335" t="n">
-        <v>378</v>
-      </c>
-      <c r="B335" s="12" t="n">
-        <v>32.71419</v>
-      </c>
-      <c r="C335" s="12" t="n">
-        <v>35.54642</v>
-      </c>
-      <c r="D335" t="inlineStr">
-        <is>
-          <t>767</t>
-        </is>
-      </c>
-      <c r="E335" t="inlineStr">
-        <is>
-          <t>רגיל</t>
-        </is>
-      </c>
-      <c r="F335" t="inlineStr">
-        <is>
-          <t>חיפה / כרמל</t>
-        </is>
-      </c>
-      <c r="G335" t="n">
-        <v>20</v>
-      </c>
-      <c r="H335" s="6" t="n">
-        <v>150000</v>
-      </c>
-      <c r="I335" s="13" t="n">
-        <v>8000</v>
-      </c>
-      <c r="J335" s="13" t="n">
-        <v>800</v>
-      </c>
-      <c r="K335" t="n">
-        <v>80</v>
-      </c>
-      <c r="L335" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="M335" t="inlineStr"/>
-    </row>
-    <row r="336">
-      <c r="A336" s="14" t="n">
-        <v>379</v>
-      </c>
-      <c r="B336" s="15" t="n">
-        <v>32.49564</v>
-      </c>
-      <c r="C336" s="15" t="n">
-        <v>35.15476</v>
-      </c>
-      <c r="D336" s="14" t="inlineStr">
-        <is>
-          <t>596</t>
-        </is>
-      </c>
-      <c r="E336" s="14" t="inlineStr">
-        <is>
-          <t>רגיל</t>
-        </is>
-      </c>
-      <c r="F336" s="14" t="inlineStr">
-        <is>
-          <t>מרכז (שרון / גוש דן)</t>
-        </is>
-      </c>
-      <c r="G336" s="14" t="n">
-        <v>20</v>
-      </c>
-      <c r="H336" s="16" t="n">
-        <v>150000</v>
-      </c>
-      <c r="I336" s="17" t="n">
-        <v>8000</v>
-      </c>
-      <c r="J336" s="17" t="n">
-        <v>800</v>
-      </c>
-      <c r="K336" s="14" t="n">
-        <v>80</v>
-      </c>
-      <c r="L336" s="14" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="M336" s="14" t="inlineStr"/>
-    </row>
-    <row r="337">
-      <c r="A337" t="n">
-        <v>380</v>
-      </c>
-      <c r="B337" s="12" t="n">
-        <v>30.93723</v>
-      </c>
-      <c r="C337" s="12" t="n">
-        <v>35.11694</v>
-      </c>
-      <c r="D337" t="inlineStr">
-        <is>
-          <t>227</t>
-        </is>
-      </c>
-      <c r="E337" t="inlineStr">
-        <is>
-          <t>רגיל</t>
-        </is>
-      </c>
-      <c r="F337" t="inlineStr">
-        <is>
-          <t>נגב / ערבה</t>
-        </is>
-      </c>
-      <c r="G337" t="n">
-        <v>20</v>
-      </c>
-      <c r="H337" s="6" t="n">
-        <v>150000</v>
-      </c>
-      <c r="I337" s="13" t="n">
-        <v>8000</v>
-      </c>
-      <c r="J337" s="13" t="n">
-        <v>800</v>
-      </c>
-      <c r="K337" t="n">
-        <v>80</v>
-      </c>
-      <c r="L337" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="M337" t="inlineStr"/>
-    </row>
-    <row r="338">
-      <c r="A338" s="14" t="n">
-        <v>381</v>
-      </c>
-      <c r="B338" s="15" t="n">
-        <v>30.95248</v>
-      </c>
-      <c r="C338" s="15" t="n">
-        <v>35.01187</v>
-      </c>
-      <c r="D338" s="14" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
-      <c r="E338" s="14" t="inlineStr">
-        <is>
-          <t>רגיל</t>
-        </is>
-      </c>
-      <c r="F338" s="14" t="inlineStr">
-        <is>
-          <t>נגב / ערבה</t>
-        </is>
-      </c>
-      <c r="G338" s="14" t="n">
-        <v>12</v>
-      </c>
-      <c r="H338" s="16" t="n">
-        <v>100000</v>
-      </c>
-      <c r="I338" s="17" t="n">
-        <v>4000</v>
-      </c>
-      <c r="J338" s="17" t="n">
-        <v>400</v>
-      </c>
-      <c r="K338" s="14" t="n">
-        <v>50</v>
-      </c>
-      <c r="L338" s="14" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="M338" s="14" t="inlineStr"/>
-    </row>
-    <row r="339">
-      <c r="A339" t="n">
-        <v>382</v>
-      </c>
-      <c r="B339" s="12" t="n">
-        <v>31.01151</v>
-      </c>
-      <c r="C339" s="12" t="n">
-        <v>35.07848</v>
-      </c>
-      <c r="D339" t="inlineStr">
-        <is>
-          <t>206</t>
-        </is>
-      </c>
-      <c r="E339" t="inlineStr">
-        <is>
-          <t>רגיל</t>
-        </is>
-      </c>
-      <c r="F339" t="inlineStr">
-        <is>
-          <t>נגב / ערבה</t>
-        </is>
-      </c>
-      <c r="G339" t="n">
-        <v>20</v>
-      </c>
-      <c r="H339" s="6" t="n">
-        <v>150000</v>
-      </c>
-      <c r="I339" s="13" t="n">
-        <v>8000</v>
-      </c>
-      <c r="J339" s="13" t="n">
-        <v>800</v>
-      </c>
-      <c r="K339" t="n">
-        <v>80</v>
-      </c>
-      <c r="L339" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="M339" t="inlineStr"/>
-    </row>
-    <row r="340">
-      <c r="A340" s="14" t="n">
-        <v>383</v>
-      </c>
-      <c r="B340" s="15" t="n">
-        <v>30.88774</v>
-      </c>
-      <c r="C340" s="15" t="n">
-        <v>35.13939</v>
-      </c>
-      <c r="D340" s="14" t="inlineStr">
-        <is>
-          <t>227</t>
-        </is>
-      </c>
-      <c r="E340" s="14" t="inlineStr">
-        <is>
-          <t>רגיל</t>
-        </is>
-      </c>
-      <c r="F340" s="14" t="inlineStr">
-        <is>
-          <t>נגב / ערבה</t>
-        </is>
-      </c>
-      <c r="G340" s="14" t="n">
-        <v>20</v>
-      </c>
-      <c r="H340" s="16" t="n">
-        <v>150000</v>
-      </c>
-      <c r="I340" s="17" t="n">
-        <v>8000</v>
-      </c>
-      <c r="J340" s="17" t="n">
-        <v>800</v>
-      </c>
-      <c r="K340" s="14" t="n">
-        <v>80</v>
-      </c>
-      <c r="L340" s="14" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="M340" s="14" t="inlineStr"/>
-    </row>
-    <row r="341">
-      <c r="A341" t="n">
-        <v>384</v>
-      </c>
-      <c r="B341" s="12" t="n">
-        <v>30.9633</v>
-      </c>
-      <c r="C341" s="12" t="n">
-        <v>35.04934</v>
-      </c>
-      <c r="D341" t="inlineStr">
-        <is>
-          <t>227</t>
-        </is>
-      </c>
-      <c r="E341" t="inlineStr">
-        <is>
-          <t>רגיל</t>
-        </is>
-      </c>
-      <c r="F341" t="inlineStr">
-        <is>
-          <t>נגב / ערבה</t>
-        </is>
-      </c>
-      <c r="G341" t="n">
-        <v>20</v>
-      </c>
-      <c r="H341" s="6" t="n">
-        <v>150000</v>
-      </c>
-      <c r="I341" s="13" t="n">
-        <v>8000</v>
-      </c>
-      <c r="J341" s="13" t="n">
-        <v>800</v>
-      </c>
-      <c r="K341" t="n">
-        <v>80</v>
-      </c>
-      <c r="L341" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="M341" t="inlineStr"/>
-    </row>
-    <row r="342">
-      <c r="A342" s="14" t="n">
-        <v>385</v>
-      </c>
-      <c r="B342" s="15" t="n">
-        <v>31.08317</v>
-      </c>
-      <c r="C342" s="15" t="n">
-        <v>35.21114</v>
-      </c>
-      <c r="D342" s="14" t="inlineStr">
-        <is>
-          <t>258</t>
-        </is>
-      </c>
-      <c r="E342" s="14" t="inlineStr">
-        <is>
-          <t>רגיל</t>
-        </is>
-      </c>
-      <c r="F342" s="14" t="inlineStr">
-        <is>
-          <t>נגב / ערבה</t>
-        </is>
-      </c>
-      <c r="G342" s="14" t="n">
-        <v>20</v>
-      </c>
-      <c r="H342" s="16" t="n">
-        <v>150000</v>
-      </c>
-      <c r="I342" s="17" t="n">
-        <v>8000</v>
-      </c>
-      <c r="J342" s="17" t="n">
-        <v>800</v>
-      </c>
-      <c r="K342" s="14" t="n">
-        <v>80</v>
-      </c>
-      <c r="L342" s="14" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="M342" s="14" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -16716,16 +15896,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C3" s="6" t="n">
-        <v>18100000</v>
+        <v>17800000</v>
       </c>
       <c r="D3" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="E3" t="n">
         <v>31.5</v>
-      </c>
-      <c r="E3" t="n">
-        <v>30.5</v>
       </c>
     </row>
     <row r="4">
@@ -16735,13 +15915,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>10650000</v>
+        <v>10200000</v>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>15.5</v>
       </c>
       <c r="E4" t="n">
         <v>18</v>
@@ -16754,16 +15934,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>7000000</v>
+        <v>6850000</v>
       </c>
       <c r="D5" t="n">
-        <v>10.6</v>
+        <v>10.9</v>
       </c>
       <c r="E5" t="n">
-        <v>11.8</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="6">
@@ -16773,16 +15953,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>11500000</v>
+        <v>9600000</v>
       </c>
       <c r="D6" t="n">
-        <v>20.9</v>
+        <v>18.3</v>
       </c>
       <c r="E6" t="n">
-        <v>19.4</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7">
@@ -16798,10 +15978,10 @@
         <v>10350000</v>
       </c>
       <c r="D7" t="n">
-        <v>17.9</v>
+        <v>18.9</v>
       </c>
       <c r="E7" t="n">
-        <v>17.4</v>
+        <v>18.3</v>
       </c>
     </row>
     <row r="8">
@@ -16817,10 +15997,10 @@
         <v>1723000</v>
       </c>
       <c r="D8" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="E8" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -16830,10 +16010,10 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>340</v>
+        <v>322</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>59323000</v>
+        <v>56523000</v>
       </c>
     </row>
   </sheetData>
@@ -16922,7 +16102,7 @@
         <v>2900000</v>
       </c>
       <c r="E4" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
@@ -16930,16 +16110,16 @@
         <v>20</v>
       </c>
       <c r="B5" t="n">
-        <v>200</v>
+        <v>183</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>150000</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>30000000</v>
+        <v>27450000</v>
       </c>
       <c r="E5" t="n">
-        <v>58.8</v>
+        <v>56.8</v>
       </c>
     </row>
     <row r="6">
@@ -16956,7 +16136,7 @@
         <v>4600000</v>
       </c>
       <c r="E6" t="n">
-        <v>6.8</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="7">
@@ -16964,16 +16144,16 @@
         <v>50</v>
       </c>
       <c r="B7" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>250000</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>21750000</v>
+        <v>21500000</v>
       </c>
       <c r="E7" t="n">
-        <v>25.6</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="8">
@@ -16983,10 +16163,10 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>340</v>
+        <v>322</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>59323000</v>
+        <v>56523000</v>
       </c>
     </row>
   </sheetData>

--- a/budget_shelters_v2.xlsx
+++ b/budget_shelters_v2.xlsx
@@ -588,7 +588,7 @@
         <v>150000</v>
       </c>
       <c r="C8" t="n">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D8" s="6">
         <f>B8*C8</f>
@@ -603,7 +603,7 @@
         <v>200000</v>
       </c>
       <c r="C9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D9" s="6">
         <f>B9*C9</f>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="19">
@@ -716,11 +716,11 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>עלות תחזוקה שנתית (322 מיגוניות)</t>
+          <t>עלות תחזוקה שנתית (319 מיגוניות)</t>
         </is>
       </c>
       <c r="B22" s="6">
-        <f>B15*322</f>
+        <f>B15*319</f>
         <v/>
       </c>
     </row>
@@ -731,14 +731,14 @@
         </is>
       </c>
       <c r="B23" s="7">
-        <f>D11*(1+B14/100)+B15*322*10</f>
+        <f>D11*(1+B14/100)+B15*319*10</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>הערות: עלויות ללא מע"מ. מבוסס על אלגוריתם Gonzalez k-center | תקן 5 דקות | 322 מיגוניות | ישראל בלבד (קו ירוק 1967) | קיבולת מחושבת לפי תנועה בשעת שיא בזמן מלחמה (10% מתנועה רגילה)</t>
+          <t>הערות: עלויות ללא מע"מ. מבוסס על אלגוריתם Gonzalez k-center | תקן 5 דקות | 319 מיגוניות | ישראל בלבד (קו ירוק 1967) | קיבולת מחושבת לפי תנועה בשעת שיא בזמן מלחמה (10% מתנועה רגילה)</t>
         </is>
       </c>
     </row>
@@ -757,7 +757,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M324"/>
+  <dimension ref="A1:M321"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -778,7 +778,7 @@
     <row r="1">
       <c r="A1" s="10" t="inlineStr">
         <is>
-          <t>רשימת מיגוניות מלאה — 322 יחידות</t>
+          <t>רשימת מיגוניות מלאה — 319 יחידות</t>
         </is>
       </c>
     </row>
@@ -10131,17 +10131,17 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B201" s="12" t="n">
-        <v>31.593</v>
+        <v>32.72877</v>
       </c>
       <c r="C201" s="12" t="n">
-        <v>34.96153</v>
+        <v>35.32292</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>79</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -10151,44 +10151,44 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>ירושלים / שפלה</t>
+          <t>חיפה / כרמל</t>
         </is>
       </c>
       <c r="G201" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H201" s="6" t="n">
-        <v>200000</v>
+        <v>150000</v>
       </c>
       <c r="I201" s="13" t="n">
-        <v>11000</v>
+        <v>8000</v>
       </c>
       <c r="J201" s="13" t="n">
-        <v>1100</v>
+        <v>800</v>
       </c>
       <c r="K201" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="L201" t="n">
-        <v>21.4</v>
+        <v>15.6</v>
       </c>
       <c r="M201" t="n">
-        <v>1591</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="14" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B202" s="15" t="n">
-        <v>32.72877</v>
+        <v>32.39496</v>
       </c>
       <c r="C202" s="15" t="n">
-        <v>35.32292</v>
+        <v>35.04624</v>
       </c>
       <c r="D202" s="14" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>574</t>
         </is>
       </c>
       <c r="E202" s="14" t="inlineStr">
@@ -10198,7 +10198,7 @@
       </c>
       <c r="F202" s="14" t="inlineStr">
         <is>
-          <t>חיפה / כרמל</t>
+          <t>מרכז (שרון / גוש דן)</t>
         </is>
       </c>
       <c r="G202" s="14" t="n">
@@ -10220,22 +10220,22 @@
         <v>15.6</v>
       </c>
       <c r="M202" s="14" t="n">
-        <v>2016</v>
+        <v>8287</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B203" s="12" t="n">
-        <v>32.39496</v>
+        <v>32.41182</v>
       </c>
       <c r="C203" s="12" t="n">
-        <v>35.04624</v>
+        <v>35.01958</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>574</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -10261,28 +10261,28 @@
         <v>800</v>
       </c>
       <c r="K203" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="L203" t="n">
         <v>15.6</v>
       </c>
       <c r="M203" t="n">
-        <v>8287</v>
+        <v>8249</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="14" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B204" s="15" t="n">
-        <v>32.41182</v>
+        <v>31.34204</v>
       </c>
       <c r="C204" s="15" t="n">
-        <v>35.01958</v>
+        <v>34.93297</v>
       </c>
       <c r="D204" s="14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>60</t>
         </is>
       </c>
       <c r="E204" s="14" t="inlineStr">
@@ -10292,54 +10292,54 @@
       </c>
       <c r="F204" s="14" t="inlineStr">
         <is>
-          <t>מרכז (שרון / גוש דן)</t>
+          <t>נגב / ערבה</t>
         </is>
       </c>
       <c r="G204" s="14" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H204" s="16" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="I204" s="17" t="n">
-        <v>8000</v>
+        <v>16000</v>
       </c>
       <c r="J204" s="17" t="n">
-        <v>800</v>
+        <v>1600</v>
       </c>
       <c r="K204" s="14" t="n">
         <v>90</v>
       </c>
       <c r="L204" s="14" t="n">
-        <v>15.6</v>
+        <v>31.2</v>
       </c>
       <c r="M204" s="14" t="n">
-        <v>8249</v>
+        <v>273</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B205" s="12" t="n">
-        <v>31.34204</v>
+        <v>31.00948</v>
       </c>
       <c r="C205" s="12" t="n">
-        <v>34.93297</v>
+        <v>34.7797</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>רגיל</t>
+          <t>עוטף עזה</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>נגב / ערבה</t>
+          <t>עוטף עזה / הנגב המערבי</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -10349,30 +10349,28 @@
         <v>250000</v>
       </c>
       <c r="I205" s="13" t="n">
-        <v>16000</v>
+        <v>22000</v>
       </c>
       <c r="J205" s="13" t="n">
-        <v>1600</v>
+        <v>2200</v>
       </c>
       <c r="K205" t="n">
         <v>90</v>
       </c>
       <c r="L205" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="M205" t="n">
-        <v>273</v>
-      </c>
+        <v>42.9</v>
+      </c>
+      <c r="M205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" s="14" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B206" s="15" t="n">
-        <v>31.00948</v>
+        <v>30.98717</v>
       </c>
       <c r="C206" s="15" t="n">
-        <v>34.7797</v>
+        <v>34.76682</v>
       </c>
       <c r="D206" s="14" t="inlineStr">
         <is>
@@ -10402,7 +10400,7 @@
         <v>2200</v>
       </c>
       <c r="K206" s="14" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="L206" s="14" t="n">
         <v>42.9</v>
@@ -10411,62 +10409,64 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B207" s="12" t="n">
-        <v>30.98717</v>
+        <v>31.27477</v>
       </c>
       <c r="C207" s="12" t="n">
-        <v>34.76682</v>
+        <v>34.94342</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>31</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>עוטף עזה</t>
+          <t>רגיל</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>עוטף עזה / הנגב המערבי</t>
+          <t>נגב / ערבה</t>
         </is>
       </c>
       <c r="G207" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H207" s="6" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="I207" s="13" t="n">
-        <v>22000</v>
+        <v>6500</v>
       </c>
       <c r="J207" s="13" t="n">
-        <v>2200</v>
+        <v>650</v>
       </c>
       <c r="K207" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="L207" t="n">
-        <v>42.9</v>
-      </c>
-      <c r="M207" t="inlineStr"/>
+        <v>12.7</v>
+      </c>
+      <c r="M207" t="n">
+        <v>1231</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="14" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B208" s="15" t="n">
-        <v>31.27477</v>
+        <v>32.70875</v>
       </c>
       <c r="C208" s="15" t="n">
-        <v>34.94342</v>
+        <v>35.30998</v>
       </c>
       <c r="D208" s="14" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>דרך הציונות</t>
         </is>
       </c>
       <c r="E208" s="14" t="inlineStr">
@@ -10476,7 +10476,7 @@
       </c>
       <c r="F208" s="14" t="inlineStr">
         <is>
-          <t>נגב / ערבה</t>
+          <t>חיפה / כרמל</t>
         </is>
       </c>
       <c r="G208" s="14" t="n">
@@ -10486,34 +10486,34 @@
         <v>150000</v>
       </c>
       <c r="I208" s="17" t="n">
-        <v>6500</v>
+        <v>8000</v>
       </c>
       <c r="J208" s="17" t="n">
-        <v>650</v>
+        <v>800</v>
       </c>
       <c r="K208" s="14" t="n">
         <v>90</v>
       </c>
       <c r="L208" s="14" t="n">
-        <v>12.7</v>
+        <v>15.6</v>
       </c>
       <c r="M208" s="14" t="n">
-        <v>1231</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B209" s="12" t="n">
-        <v>32.70875</v>
+        <v>32.45118</v>
       </c>
       <c r="C209" s="12" t="n">
-        <v>35.30998</v>
+        <v>34.8932</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>דרך הציונות</t>
+          <t>כביש החוף</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -10523,7 +10523,7 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>חיפה / כרמל</t>
+          <t>מרכז (שרון / גוש דן)</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -10545,22 +10545,22 @@
         <v>15.6</v>
       </c>
       <c r="M209" t="n">
-        <v>2017</v>
+        <v>6118</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="14" t="n">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B210" s="15" t="n">
-        <v>32.45118</v>
+        <v>32.75386</v>
       </c>
       <c r="C210" s="15" t="n">
-        <v>34.8932</v>
+        <v>35.41108</v>
       </c>
       <c r="D210" s="14" t="inlineStr">
         <is>
-          <t>כביש החוף</t>
+          <t>65</t>
         </is>
       </c>
       <c r="E210" s="14" t="inlineStr">
@@ -10570,44 +10570,44 @@
       </c>
       <c r="F210" s="14" t="inlineStr">
         <is>
-          <t>מרכז (שרון / גוש דן)</t>
+          <t>חיפה / כרמל</t>
         </is>
       </c>
       <c r="G210" s="14" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H210" s="16" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="I210" s="17" t="n">
-        <v>8000</v>
+        <v>24000</v>
       </c>
       <c r="J210" s="17" t="n">
-        <v>800</v>
+        <v>2400</v>
       </c>
       <c r="K210" s="14" t="n">
         <v>90</v>
       </c>
       <c r="L210" s="14" t="n">
-        <v>15.6</v>
+        <v>46.8</v>
       </c>
       <c r="M210" s="14" t="n">
-        <v>6118</v>
+        <v>580</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B211" s="12" t="n">
-        <v>31.57389</v>
+        <v>32.45257</v>
       </c>
       <c r="C211" s="12" t="n">
-        <v>34.9817</v>
+        <v>34.97321</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>חוצה יהודה</t>
+          <t>65</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -10617,44 +10617,44 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>ירושלים / שפלה</t>
+          <t>מרכז (שרון / גוש דן)</t>
         </is>
       </c>
       <c r="G211" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H211" s="6" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="I211" s="13" t="n">
-        <v>8000</v>
+        <v>24000</v>
       </c>
       <c r="J211" s="13" t="n">
-        <v>800</v>
+        <v>2400</v>
       </c>
       <c r="K211" t="n">
         <v>90</v>
       </c>
       <c r="L211" t="n">
-        <v>15.6</v>
+        <v>46.8</v>
       </c>
       <c r="M211" t="n">
-        <v>1254</v>
+        <v>5851</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="14" t="n">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B212" s="15" t="n">
-        <v>32.75386</v>
+        <v>32.79894</v>
       </c>
       <c r="C212" s="15" t="n">
-        <v>35.41108</v>
+        <v>35.52056</v>
       </c>
       <c r="D212" s="14" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>מנחם בגין</t>
         </is>
       </c>
       <c r="E212" s="14" t="inlineStr">
@@ -10668,87 +10668,85 @@
         </is>
       </c>
       <c r="G212" s="14" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H212" s="16" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="I212" s="17" t="n">
-        <v>24000</v>
+        <v>8000</v>
       </c>
       <c r="J212" s="17" t="n">
-        <v>2400</v>
+        <v>800</v>
       </c>
       <c r="K212" s="14" t="n">
         <v>90</v>
       </c>
       <c r="L212" s="14" t="n">
-        <v>46.8</v>
+        <v>15.6</v>
       </c>
       <c r="M212" s="14" t="n">
-        <v>580</v>
+        <v>348</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B213" s="12" t="n">
-        <v>32.45257</v>
+        <v>31.06652</v>
       </c>
       <c r="C213" s="12" t="n">
-        <v>34.97321</v>
+        <v>34.83841</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>רגיל</t>
+          <t>עוטף עזה</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>מרכז (שרון / גוש דן)</t>
+          <t>עוטף עזה / הנגב המערבי</t>
         </is>
       </c>
       <c r="G213" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H213" s="6" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="I213" s="13" t="n">
-        <v>24000</v>
+        <v>8000</v>
       </c>
       <c r="J213" s="13" t="n">
-        <v>2400</v>
+        <v>800</v>
       </c>
       <c r="K213" t="n">
         <v>90</v>
       </c>
       <c r="L213" t="n">
-        <v>46.8</v>
-      </c>
-      <c r="M213" t="n">
-        <v>5851</v>
-      </c>
+        <v>15.6</v>
+      </c>
+      <c r="M213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" s="14" t="n">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B214" s="15" t="n">
-        <v>32.79894</v>
+        <v>32.43746</v>
       </c>
       <c r="C214" s="15" t="n">
-        <v>35.52056</v>
+        <v>35.02462</v>
       </c>
       <c r="D214" s="14" t="inlineStr">
         <is>
-          <t>מנחם בגין</t>
+          <t>574</t>
         </is>
       </c>
       <c r="E214" s="14" t="inlineStr">
@@ -10758,89 +10756,91 @@
       </c>
       <c r="F214" s="14" t="inlineStr">
         <is>
-          <t>חיפה / כרמל</t>
+          <t>מרכז (שרון / גוש דן)</t>
         </is>
       </c>
       <c r="G214" s="14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H214" s="16" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I214" s="17" t="n">
-        <v>8000</v>
+        <v>4000</v>
       </c>
       <c r="J214" s="17" t="n">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="K214" s="14" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="L214" s="14" t="n">
-        <v>15.6</v>
+        <v>7.8</v>
       </c>
       <c r="M214" s="14" t="n">
-        <v>348</v>
+        <v>5557</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B215" s="12" t="n">
-        <v>31.06652</v>
+        <v>32.78596</v>
       </c>
       <c r="C215" s="12" t="n">
-        <v>34.83841</v>
+        <v>35.49496</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>מנחם בגין</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>עוטף עזה</t>
+          <t>רגיל</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>עוטף עזה / הנגב המערבי</t>
+          <t>חיפה / כרמל</t>
         </is>
       </c>
       <c r="G215" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H215" s="6" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="I215" s="13" t="n">
-        <v>8000</v>
+        <v>19000</v>
       </c>
       <c r="J215" s="13" t="n">
-        <v>800</v>
+        <v>1900</v>
       </c>
       <c r="K215" t="n">
         <v>90</v>
       </c>
       <c r="L215" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="M215" t="inlineStr"/>
+        <v>37.1</v>
+      </c>
+      <c r="M215" t="n">
+        <v>348</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="14" t="n">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B216" s="15" t="n">
-        <v>32.43746</v>
+        <v>32.6423</v>
       </c>
       <c r="C216" s="15" t="n">
-        <v>35.02462</v>
+        <v>35.05813</v>
       </c>
       <c r="D216" s="14" t="inlineStr">
         <is>
-          <t>574</t>
+          <t>672</t>
         </is>
       </c>
       <c r="E216" s="14" t="inlineStr">
@@ -10850,44 +10850,44 @@
       </c>
       <c r="F216" s="14" t="inlineStr">
         <is>
-          <t>מרכז (שרון / גוש דן)</t>
+          <t>חיפה / כרמל</t>
         </is>
       </c>
       <c r="G216" s="14" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H216" s="16" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I216" s="17" t="n">
-        <v>4000</v>
+        <v>8000</v>
       </c>
       <c r="J216" s="17" t="n">
-        <v>400</v>
+        <v>800</v>
       </c>
       <c r="K216" s="14" t="n">
         <v>80</v>
       </c>
       <c r="L216" s="14" t="n">
-        <v>7.8</v>
+        <v>15.6</v>
       </c>
       <c r="M216" s="14" t="n">
-        <v>5557</v>
+        <v>2419</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="B217" s="12" t="n">
-        <v>32.78596</v>
+        <v>32.66137</v>
       </c>
       <c r="C217" s="12" t="n">
-        <v>35.49496</v>
+        <v>35.23909</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>מנחם בגין</t>
+          <t>73</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -10901,40 +10901,40 @@
         </is>
       </c>
       <c r="G217" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H217" s="6" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="I217" s="13" t="n">
-        <v>19000</v>
+        <v>8000</v>
       </c>
       <c r="J217" s="13" t="n">
-        <v>1900</v>
+        <v>800</v>
       </c>
       <c r="K217" t="n">
         <v>90</v>
       </c>
       <c r="L217" t="n">
-        <v>37.1</v>
+        <v>15.6</v>
       </c>
       <c r="M217" t="n">
-        <v>348</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="14" t="n">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B218" s="15" t="n">
-        <v>31.65044</v>
+        <v>32.47901</v>
       </c>
       <c r="C218" s="15" t="n">
-        <v>35.06612</v>
+        <v>34.95591</v>
       </c>
       <c r="D218" s="14" t="inlineStr">
         <is>
-          <t>Downtown - Schools</t>
+          <t>הים</t>
         </is>
       </c>
       <c r="E218" s="14" t="inlineStr">
@@ -10944,7 +10944,7 @@
       </c>
       <c r="F218" s="14" t="inlineStr">
         <is>
-          <t>ירושלים / שפלה</t>
+          <t>מרכז (שרון / גוש דן)</t>
         </is>
       </c>
       <c r="G218" s="14" t="n">
@@ -10966,22 +10966,22 @@
         <v>15.6</v>
       </c>
       <c r="M218" s="14" t="n">
-        <v>5230</v>
+        <v>3911</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="B219" s="12" t="n">
-        <v>32.6423</v>
+        <v>32.45671</v>
       </c>
       <c r="C219" s="12" t="n">
-        <v>35.05813</v>
+        <v>35.04691</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>האחווה</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -10991,7 +10991,7 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>חיפה / כרמל</t>
+          <t>מרכז (שרון / גוש דן)</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -11007,28 +11007,28 @@
         <v>800</v>
       </c>
       <c r="K219" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="L219" t="n">
         <v>15.6</v>
       </c>
       <c r="M219" t="n">
-        <v>2419</v>
+        <v>3267</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="14" t="n">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="B220" s="15" t="n">
-        <v>32.66137</v>
+        <v>32.50474</v>
       </c>
       <c r="C220" s="15" t="n">
-        <v>35.23909</v>
+        <v>34.91422</v>
       </c>
       <c r="D220" s="14" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>כביש החוף</t>
         </is>
       </c>
       <c r="E220" s="14" t="inlineStr">
@@ -11054,28 +11054,28 @@
         <v>800</v>
       </c>
       <c r="K220" s="14" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="L220" s="14" t="n">
         <v>15.6</v>
       </c>
       <c r="M220" s="14" t="n">
-        <v>2013</v>
+        <v>2956</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="B221" s="12" t="n">
-        <v>32.47901</v>
+        <v>32.67574</v>
       </c>
       <c r="C221" s="12" t="n">
-        <v>34.95591</v>
+        <v>35.29197</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>הים</t>
+          <t>60</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -11085,44 +11085,44 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>מרכז (שרון / גוש דן)</t>
+          <t>חיפה / כרמל</t>
         </is>
       </c>
       <c r="G221" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H221" s="6" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="I221" s="13" t="n">
-        <v>8000</v>
+        <v>16000</v>
       </c>
       <c r="J221" s="13" t="n">
-        <v>800</v>
+        <v>1600</v>
       </c>
       <c r="K221" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="L221" t="n">
-        <v>15.6</v>
+        <v>31.2</v>
       </c>
       <c r="M221" t="n">
-        <v>3911</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="14" t="n">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="B222" s="15" t="n">
-        <v>32.45671</v>
+        <v>32.48213</v>
       </c>
       <c r="C222" s="15" t="n">
-        <v>35.04691</v>
+        <v>35.03479</v>
       </c>
       <c r="D222" s="14" t="inlineStr">
         <is>
-          <t>האחווה</t>
+          <t>כביש חוצה ישראל</t>
         </is>
       </c>
       <c r="E222" s="14" t="inlineStr">
@@ -11148,28 +11148,28 @@
         <v>800</v>
       </c>
       <c r="K222" s="14" t="n">
-        <v>50</v>
+        <v>110</v>
       </c>
       <c r="L222" s="14" t="n">
         <v>15.6</v>
       </c>
       <c r="M222" s="14" t="n">
-        <v>3267</v>
+        <v>2660</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="B223" s="12" t="n">
-        <v>32.50474</v>
+        <v>32.64337</v>
       </c>
       <c r="C223" s="12" t="n">
-        <v>34.91422</v>
+        <v>34.95866</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>כביש החוף</t>
+          <t>כביש חיפה רעננה</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -11195,38 +11195,38 @@
         <v>800</v>
       </c>
       <c r="K223" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="L223" t="n">
         <v>15.6</v>
       </c>
       <c r="M223" t="n">
-        <v>2956</v>
+        <v>662</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="14" t="n">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="B224" s="15" t="n">
-        <v>32.67574</v>
+        <v>30.93868</v>
       </c>
       <c r="C224" s="15" t="n">
-        <v>35.29197</v>
+        <v>34.78511</v>
       </c>
       <c r="D224" s="14" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E224" s="14" t="inlineStr">
         <is>
-          <t>רגיל</t>
+          <t>עוטף עזה</t>
         </is>
       </c>
       <c r="F224" s="14" t="inlineStr">
         <is>
-          <t>חיפה / כרמל</t>
+          <t>עוטף עזה / הנגב המערבי</t>
         </is>
       </c>
       <c r="G224" s="14" t="n">
@@ -11236,34 +11236,32 @@
         <v>250000</v>
       </c>
       <c r="I224" s="17" t="n">
-        <v>16000</v>
+        <v>22000</v>
       </c>
       <c r="J224" s="17" t="n">
-        <v>1600</v>
+        <v>2200</v>
       </c>
       <c r="K224" s="14" t="n">
         <v>90</v>
       </c>
       <c r="L224" s="14" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="M224" s="14" t="n">
-        <v>1122</v>
-      </c>
+        <v>42.9</v>
+      </c>
+      <c r="M224" s="14" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="B225" s="12" t="n">
-        <v>32.48213</v>
+        <v>31.1853</v>
       </c>
       <c r="C225" s="12" t="n">
-        <v>35.03479</v>
+        <v>34.95695</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>כביש חוצה ישראל</t>
+          <t>25</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -11273,7 +11271,7 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>מרכז (שרון / גוש דן)</t>
+          <t>נגב / ערבה</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -11283,34 +11281,34 @@
         <v>150000</v>
       </c>
       <c r="I225" s="13" t="n">
-        <v>8000</v>
+        <v>7000</v>
       </c>
       <c r="J225" s="13" t="n">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="K225" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="L225" t="n">
-        <v>15.6</v>
+        <v>13.7</v>
       </c>
       <c r="M225" t="n">
-        <v>2660</v>
+        <v>442</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="14" t="n">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="B226" s="15" t="n">
-        <v>32.64337</v>
+        <v>32.5173</v>
       </c>
       <c r="C226" s="15" t="n">
-        <v>34.95866</v>
+        <v>34.99246</v>
       </c>
       <c r="D226" s="14" t="inlineStr">
         <is>
-          <t>כביש חיפה רעננה</t>
+          <t>654</t>
         </is>
       </c>
       <c r="E226" s="14" t="inlineStr">
@@ -11336,73 +11334,73 @@
         <v>800</v>
       </c>
       <c r="K226" s="14" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="L226" s="14" t="n">
         <v>15.6</v>
       </c>
       <c r="M226" s="14" t="n">
-        <v>662</v>
+        <v>1768</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="B227" s="12" t="n">
-        <v>30.93868</v>
+        <v>32.77382</v>
       </c>
       <c r="C227" s="12" t="n">
-        <v>34.78511</v>
+        <v>35.54631</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>שדרות אליעזר קפלן</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>עוטף עזה</t>
+          <t>רגיל</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>עוטף עזה / הנגב המערבי</t>
+          <t>חיפה / כרמל</t>
         </is>
       </c>
       <c r="G227" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H227" s="6" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="I227" s="13" t="n">
-        <v>22000</v>
+        <v>8000</v>
       </c>
       <c r="J227" s="13" t="n">
-        <v>2200</v>
+        <v>800</v>
       </c>
       <c r="K227" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="L227" t="n">
-        <v>42.9</v>
+        <v>15.6</v>
       </c>
       <c r="M227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" s="14" t="n">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="B228" s="15" t="n">
-        <v>31.1853</v>
+        <v>31.31285</v>
       </c>
       <c r="C228" s="15" t="n">
-        <v>34.95695</v>
+        <v>34.99488</v>
       </c>
       <c r="D228" s="14" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>316</t>
         </is>
       </c>
       <c r="E228" s="14" t="inlineStr">
@@ -11422,34 +11420,34 @@
         <v>150000</v>
       </c>
       <c r="I228" s="17" t="n">
-        <v>7000</v>
+        <v>8000</v>
       </c>
       <c r="J228" s="17" t="n">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="K228" s="14" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="L228" s="14" t="n">
-        <v>13.7</v>
+        <v>15.6</v>
       </c>
       <c r="M228" s="14" t="n">
-        <v>442</v>
+        <v>217</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="B229" s="12" t="n">
-        <v>32.5173</v>
+        <v>32.61908</v>
       </c>
       <c r="C229" s="12" t="n">
-        <v>34.99246</v>
+        <v>35.05488</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>כביש חוצה ישראל</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -11475,28 +11473,28 @@
         <v>800</v>
       </c>
       <c r="K229" t="n">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="L229" t="n">
         <v>15.6</v>
       </c>
       <c r="M229" t="n">
-        <v>1768</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="14" t="n">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="B230" s="15" t="n">
-        <v>32.77382</v>
+        <v>32.53646</v>
       </c>
       <c r="C230" s="15" t="n">
-        <v>35.54631</v>
+        <v>34.92907</v>
       </c>
       <c r="D230" s="14" t="inlineStr">
         <is>
-          <t>שדרות אליעזר קפלן</t>
+          <t>כביש חיפה רעננה</t>
         </is>
       </c>
       <c r="E230" s="14" t="inlineStr">
@@ -11522,26 +11520,28 @@
         <v>800</v>
       </c>
       <c r="K230" s="14" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="L230" s="14" t="n">
         <v>15.6</v>
       </c>
-      <c r="M230" s="14" t="inlineStr"/>
+      <c r="M230" s="14" t="n">
+        <v>881</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="B231" s="12" t="n">
-        <v>31.31285</v>
+        <v>31.25485</v>
       </c>
       <c r="C231" s="12" t="n">
-        <v>34.99488</v>
+        <v>35.21055</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>316</t>
+          <t>31</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -11561,34 +11561,34 @@
         <v>150000</v>
       </c>
       <c r="I231" s="13" t="n">
-        <v>8000</v>
+        <v>6500</v>
       </c>
       <c r="J231" s="13" t="n">
-        <v>800</v>
+        <v>650</v>
       </c>
       <c r="K231" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="L231" t="n">
-        <v>15.6</v>
+        <v>12.7</v>
       </c>
       <c r="M231" t="n">
-        <v>217</v>
+        <v>753</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="14" t="n">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B232" s="15" t="n">
-        <v>32.61908</v>
+        <v>31.29801</v>
       </c>
       <c r="C232" s="15" t="n">
-        <v>35.05488</v>
+        <v>35.13199</v>
       </c>
       <c r="D232" s="14" t="inlineStr">
         <is>
-          <t>כביש חוצה ישראל</t>
+          <t>80</t>
         </is>
       </c>
       <c r="E232" s="14" t="inlineStr">
@@ -11598,7 +11598,7 @@
       </c>
       <c r="F232" s="14" t="inlineStr">
         <is>
-          <t>חיפה / כרמל</t>
+          <t>נגב / ערבה</t>
         </is>
       </c>
       <c r="G232" s="14" t="n">
@@ -11614,28 +11614,28 @@
         <v>800</v>
       </c>
       <c r="K232" s="14" t="n">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="L232" s="14" t="n">
         <v>15.6</v>
       </c>
       <c r="M232" s="14" t="n">
-        <v>1099</v>
+        <v>753</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="B233" s="12" t="n">
-        <v>32.53646</v>
+        <v>32.56323</v>
       </c>
       <c r="C233" s="12" t="n">
-        <v>34.92907</v>
+        <v>34.95873</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>כביש חיפה רעננה</t>
+          <t>652</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -11649,40 +11649,40 @@
         </is>
       </c>
       <c r="G233" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H233" s="6" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I233" s="13" t="n">
-        <v>8000</v>
+        <v>4000</v>
       </c>
       <c r="J233" s="13" t="n">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="K233" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="L233" t="n">
-        <v>15.6</v>
+        <v>7.8</v>
       </c>
       <c r="M233" t="n">
-        <v>881</v>
+        <v>587</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="14" t="n">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="B234" s="15" t="n">
-        <v>31.25485</v>
+        <v>32.52426</v>
       </c>
       <c r="C234" s="15" t="n">
-        <v>35.21055</v>
+        <v>35.02544</v>
       </c>
       <c r="D234" s="14" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>653</t>
         </is>
       </c>
       <c r="E234" s="14" t="inlineStr">
@@ -11692,7 +11692,7 @@
       </c>
       <c r="F234" s="14" t="inlineStr">
         <is>
-          <t>נגב / ערבה</t>
+          <t>חיפה / כרמל</t>
         </is>
       </c>
       <c r="G234" s="14" t="n">
@@ -11702,34 +11702,34 @@
         <v>150000</v>
       </c>
       <c r="I234" s="17" t="n">
-        <v>6500</v>
+        <v>8000</v>
       </c>
       <c r="J234" s="17" t="n">
-        <v>650</v>
+        <v>800</v>
       </c>
       <c r="K234" s="14" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="L234" s="14" t="n">
-        <v>12.7</v>
+        <v>15.6</v>
       </c>
       <c r="M234" s="14" t="n">
-        <v>753</v>
+        <v>587</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="B235" s="12" t="n">
-        <v>31.29801</v>
+        <v>31.2012</v>
       </c>
       <c r="C235" s="12" t="n">
-        <v>35.13199</v>
+        <v>35.35995</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>דרך ים המלח</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -11761,22 +11761,22 @@
         <v>15.6</v>
       </c>
       <c r="M235" t="n">
-        <v>753</v>
+        <v>536</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="14" t="n">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="B236" s="15" t="n">
-        <v>32.56323</v>
+        <v>31.19194</v>
       </c>
       <c r="C236" s="15" t="n">
-        <v>34.95873</v>
+        <v>35.28031</v>
       </c>
       <c r="D236" s="14" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>31</t>
         </is>
       </c>
       <c r="E236" s="14" t="inlineStr">
@@ -11786,44 +11786,44 @@
       </c>
       <c r="F236" s="14" t="inlineStr">
         <is>
-          <t>חיפה / כרמל</t>
+          <t>נגב / ערבה</t>
         </is>
       </c>
       <c r="G236" s="14" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H236" s="16" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I236" s="17" t="n">
-        <v>4000</v>
+        <v>6500</v>
       </c>
       <c r="J236" s="17" t="n">
-        <v>400</v>
+        <v>650</v>
       </c>
       <c r="K236" s="14" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="L236" s="14" t="n">
-        <v>7.8</v>
+        <v>12.7</v>
       </c>
       <c r="M236" s="14" t="n">
-        <v>587</v>
+        <v>536</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="B237" s="12" t="n">
-        <v>32.52426</v>
+        <v>31.25015</v>
       </c>
       <c r="C237" s="12" t="n">
-        <v>35.02544</v>
+        <v>35.36307</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>דרך ים המלח</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -11833,7 +11833,7 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>חיפה / כרמל</t>
+          <t>נגב / ערבה</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -11855,22 +11855,22 @@
         <v>15.6</v>
       </c>
       <c r="M237" t="n">
-        <v>587</v>
+        <v>536</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="14" t="n">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="B238" s="15" t="n">
-        <v>31.2012</v>
+        <v>32.5864</v>
       </c>
       <c r="C238" s="15" t="n">
-        <v>35.35995</v>
+        <v>35.43541</v>
       </c>
       <c r="D238" s="14" t="inlineStr">
         <is>
-          <t>דרך ים המלח</t>
+          <t>717</t>
         </is>
       </c>
       <c r="E238" s="14" t="inlineStr">
@@ -11880,7 +11880,7 @@
       </c>
       <c r="F238" s="14" t="inlineStr">
         <is>
-          <t>נגב / ערבה</t>
+          <t>חיפה / כרמל</t>
         </is>
       </c>
       <c r="G238" s="14" t="n">
@@ -11896,28 +11896,28 @@
         <v>800</v>
       </c>
       <c r="K238" s="14" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="L238" s="14" t="n">
         <v>15.6</v>
       </c>
       <c r="M238" s="14" t="n">
-        <v>536</v>
+        <v>510</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="B239" s="12" t="n">
-        <v>31.19194</v>
+        <v>31.25249</v>
       </c>
       <c r="C239" s="12" t="n">
-        <v>35.28031</v>
+        <v>35.12599</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>80</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -11937,34 +11937,34 @@
         <v>150000</v>
       </c>
       <c r="I239" s="13" t="n">
-        <v>6500</v>
+        <v>8000</v>
       </c>
       <c r="J239" s="13" t="n">
-        <v>650</v>
+        <v>800</v>
       </c>
       <c r="K239" t="n">
         <v>90</v>
       </c>
       <c r="L239" t="n">
-        <v>12.7</v>
+        <v>15.6</v>
       </c>
       <c r="M239" t="n">
-        <v>536</v>
+        <v>500</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="14" t="n">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="B240" s="15" t="n">
-        <v>31.25015</v>
+        <v>31.2344</v>
       </c>
       <c r="C240" s="15" t="n">
-        <v>35.36307</v>
+        <v>35.10819</v>
       </c>
       <c r="D240" s="14" t="inlineStr">
         <is>
-          <t>דרך ים המלח</t>
+          <t>80</t>
         </is>
       </c>
       <c r="E240" s="14" t="inlineStr">
@@ -11978,40 +11978,40 @@
         </is>
       </c>
       <c r="G240" s="14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H240" s="16" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I240" s="17" t="n">
-        <v>8000</v>
+        <v>4000</v>
       </c>
       <c r="J240" s="17" t="n">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="K240" s="14" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="L240" s="14" t="n">
-        <v>15.6</v>
+        <v>7.8</v>
       </c>
       <c r="M240" s="14" t="n">
-        <v>536</v>
+        <v>500</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B241" s="12" t="n">
-        <v>32.5864</v>
+        <v>31.2565</v>
       </c>
       <c r="C241" s="12" t="n">
-        <v>35.43541</v>
+        <v>35.09862</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>717</t>
+          <t>31</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -12021,7 +12021,7 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>חיפה / כרמל</t>
+          <t>נגב / ערבה</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -12031,30 +12031,30 @@
         <v>150000</v>
       </c>
       <c r="I241" s="13" t="n">
-        <v>8000</v>
+        <v>6500</v>
       </c>
       <c r="J241" s="13" t="n">
-        <v>800</v>
+        <v>650</v>
       </c>
       <c r="K241" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="L241" t="n">
-        <v>15.6</v>
+        <v>12.7</v>
       </c>
       <c r="M241" t="n">
-        <v>510</v>
+        <v>500</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="14" t="n">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="B242" s="15" t="n">
-        <v>31.25249</v>
+        <v>31.16767</v>
       </c>
       <c r="C242" s="15" t="n">
-        <v>35.12599</v>
+        <v>35.04596</v>
       </c>
       <c r="D242" s="14" t="inlineStr">
         <is>
@@ -12090,22 +12090,22 @@
         <v>15.6</v>
       </c>
       <c r="M242" s="14" t="n">
-        <v>500</v>
+        <v>442</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="B243" s="12" t="n">
-        <v>31.2344</v>
+        <v>31.26291</v>
       </c>
       <c r="C243" s="12" t="n">
-        <v>35.10819</v>
+        <v>35.02142</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>31</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -12119,40 +12119,40 @@
         </is>
       </c>
       <c r="G243" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H243" s="6" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I243" s="13" t="n">
-        <v>4000</v>
+        <v>6500</v>
       </c>
       <c r="J243" s="13" t="n">
-        <v>400</v>
+        <v>650</v>
       </c>
       <c r="K243" t="n">
         <v>90</v>
       </c>
       <c r="L243" t="n">
-        <v>7.8</v>
+        <v>12.7</v>
       </c>
       <c r="M243" t="n">
-        <v>500</v>
+        <v>442</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="14" t="n">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B244" s="15" t="n">
-        <v>31.2565</v>
+        <v>31.15683</v>
       </c>
       <c r="C244" s="15" t="n">
-        <v>35.09862</v>
+        <v>34.995</v>
       </c>
       <c r="D244" s="14" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>80</t>
         </is>
       </c>
       <c r="E244" s="14" t="inlineStr">
@@ -12172,34 +12172,34 @@
         <v>150000</v>
       </c>
       <c r="I244" s="17" t="n">
-        <v>6500</v>
+        <v>8000</v>
       </c>
       <c r="J244" s="17" t="n">
-        <v>650</v>
+        <v>800</v>
       </c>
       <c r="K244" s="14" t="n">
         <v>90</v>
       </c>
       <c r="L244" s="14" t="n">
-        <v>12.7</v>
+        <v>15.6</v>
       </c>
       <c r="M244" s="14" t="n">
-        <v>500</v>
+        <v>442</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B245" s="12" t="n">
-        <v>31.16767</v>
+        <v>32.60198</v>
       </c>
       <c r="C245" s="12" t="n">
-        <v>35.04596</v>
+        <v>35.08464</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>672</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -12209,7 +12209,7 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>נגב / ערבה</t>
+          <t>חיפה / כרמל</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -12225,28 +12225,28 @@
         <v>800</v>
       </c>
       <c r="K245" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="L245" t="n">
         <v>15.6</v>
       </c>
       <c r="M245" t="n">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="14" t="n">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="B246" s="15" t="n">
-        <v>31.26291</v>
+        <v>32.71782</v>
       </c>
       <c r="C246" s="15" t="n">
-        <v>35.02142</v>
+        <v>35.43847</v>
       </c>
       <c r="D246" s="14" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>דרך המושבות</t>
         </is>
       </c>
       <c r="E246" s="14" t="inlineStr">
@@ -12256,181 +12256,181 @@
       </c>
       <c r="F246" s="14" t="inlineStr">
         <is>
-          <t>נגב / ערבה</t>
+          <t>חיפה / כרמל</t>
         </is>
       </c>
       <c r="G246" s="14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H246" s="16" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I246" s="17" t="n">
-        <v>6500</v>
+        <v>4000</v>
       </c>
       <c r="J246" s="17" t="n">
-        <v>650</v>
+        <v>400</v>
       </c>
       <c r="K246" s="14" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="L246" s="14" t="n">
-        <v>12.7</v>
+        <v>7.8</v>
       </c>
       <c r="M246" s="14" t="n">
-        <v>442</v>
+        <v>232</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="B247" s="12" t="n">
-        <v>31.15683</v>
+        <v>30.61281</v>
       </c>
       <c r="C247" s="12" t="n">
-        <v>34.995</v>
+        <v>34.85762</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>רגיל</t>
+          <t>עוטף עזה</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>נגב / ערבה</t>
+          <t>עוטף עזה / הנגב המערבי</t>
         </is>
       </c>
       <c r="G247" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H247" s="6" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="I247" s="13" t="n">
-        <v>8000</v>
+        <v>22000</v>
       </c>
       <c r="J247" s="13" t="n">
-        <v>800</v>
+        <v>2200</v>
       </c>
       <c r="K247" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="L247" t="n">
-        <v>15.6</v>
+        <v>42.9</v>
       </c>
       <c r="M247" t="n">
-        <v>442</v>
+        <v>284</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="14" t="n">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="B248" s="15" t="n">
-        <v>32.60198</v>
+        <v>30.62719</v>
       </c>
       <c r="C248" s="15" t="n">
-        <v>35.08464</v>
+        <v>34.80473</v>
       </c>
       <c r="D248" s="14" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E248" s="14" t="inlineStr">
         <is>
-          <t>רגיל</t>
+          <t>עוטף עזה</t>
         </is>
       </c>
       <c r="F248" s="14" t="inlineStr">
         <is>
-          <t>חיפה / כרמל</t>
+          <t>עוטף עזה / הנגב המערבי</t>
         </is>
       </c>
       <c r="G248" s="14" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H248" s="16" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="I248" s="17" t="n">
-        <v>8000</v>
+        <v>22000</v>
       </c>
       <c r="J248" s="17" t="n">
-        <v>800</v>
+        <v>2200</v>
       </c>
       <c r="K248" s="14" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="L248" s="14" t="n">
-        <v>15.6</v>
+        <v>42.9</v>
       </c>
       <c r="M248" s="14" t="n">
-        <v>440</v>
+        <v>284</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="B249" s="12" t="n">
-        <v>32.71782</v>
+        <v>30.6616</v>
       </c>
       <c r="C249" s="12" t="n">
-        <v>35.43847</v>
+        <v>34.80929</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>דרך המושבות</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>רגיל</t>
+          <t>עוטף עזה</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>חיפה / כרמל</t>
+          <t>עוטף עזה / הנגב המערבי</t>
         </is>
       </c>
       <c r="G249" t="n">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="H249" s="6" t="n">
-        <v>100000</v>
+        <v>250000</v>
       </c>
       <c r="I249" s="13" t="n">
-        <v>4000</v>
+        <v>22000</v>
       </c>
       <c r="J249" s="13" t="n">
-        <v>400</v>
+        <v>2200</v>
       </c>
       <c r="K249" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="L249" t="n">
-        <v>7.8</v>
+        <v>42.9</v>
       </c>
       <c r="M249" t="n">
-        <v>232</v>
+        <v>284</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="14" t="n">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="B250" s="15" t="n">
-        <v>30.61281</v>
+        <v>30.5665</v>
       </c>
       <c r="C250" s="15" t="n">
-        <v>34.85762</v>
+        <v>34.90431</v>
       </c>
       <c r="D250" s="14" t="inlineStr">
         <is>
@@ -12439,12 +12439,12 @@
       </c>
       <c r="E250" s="14" t="inlineStr">
         <is>
-          <t>עוטף עזה</t>
+          <t>רגיל</t>
         </is>
       </c>
       <c r="F250" s="14" t="inlineStr">
         <is>
-          <t>עוטף עזה / הנגב המערבי</t>
+          <t>נגב / ערבה</t>
         </is>
       </c>
       <c r="G250" s="14" t="n">
@@ -12471,13 +12471,13 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="B251" s="12" t="n">
-        <v>30.62719</v>
+        <v>30.72685</v>
       </c>
       <c r="C251" s="12" t="n">
-        <v>34.80473</v>
+        <v>34.77465</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -12518,64 +12518,64 @@
     </row>
     <row r="252">
       <c r="A252" s="14" t="n">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B252" s="15" t="n">
-        <v>30.6616</v>
+        <v>31.14917</v>
       </c>
       <c r="C252" s="15" t="n">
-        <v>34.80929</v>
+        <v>35.22181</v>
       </c>
       <c r="D252" s="14" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>258</t>
         </is>
       </c>
       <c r="E252" s="14" t="inlineStr">
         <is>
-          <t>עוטף עזה</t>
+          <t>רגיל</t>
         </is>
       </c>
       <c r="F252" s="14" t="inlineStr">
         <is>
-          <t>עוטף עזה / הנגב המערבי</t>
+          <t>נגב / ערבה</t>
         </is>
       </c>
       <c r="G252" s="14" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H252" s="16" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="I252" s="17" t="n">
-        <v>22000</v>
+        <v>8000</v>
       </c>
       <c r="J252" s="17" t="n">
-        <v>2200</v>
+        <v>800</v>
       </c>
       <c r="K252" s="14" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="L252" s="14" t="n">
-        <v>42.9</v>
+        <v>15.6</v>
       </c>
       <c r="M252" s="14" t="n">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B253" s="12" t="n">
-        <v>30.5665</v>
+        <v>31.31343</v>
       </c>
       <c r="C253" s="12" t="n">
-        <v>34.90431</v>
+        <v>35.38376</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>דרך ים המלח</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -12589,87 +12589,87 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H253" s="6" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="I253" s="13" t="n">
-        <v>22000</v>
+        <v>8000</v>
       </c>
       <c r="J253" s="13" t="n">
-        <v>2200</v>
+        <v>800</v>
       </c>
       <c r="K253" t="n">
         <v>80</v>
       </c>
       <c r="L253" t="n">
-        <v>42.9</v>
+        <v>15.6</v>
       </c>
       <c r="M253" t="n">
-        <v>284</v>
+        <v>253</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="14" t="n">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="B254" s="15" t="n">
-        <v>30.72685</v>
+        <v>32.6126</v>
       </c>
       <c r="C254" s="15" t="n">
-        <v>34.77465</v>
+        <v>35.54892</v>
       </c>
       <c r="D254" s="14" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>90</t>
         </is>
       </c>
       <c r="E254" s="14" t="inlineStr">
         <is>
-          <t>עוטף עזה</t>
+          <t>רגיל</t>
         </is>
       </c>
       <c r="F254" s="14" t="inlineStr">
         <is>
-          <t>עוטף עזה / הנגב המערבי</t>
+          <t>חיפה / כרמל</t>
         </is>
       </c>
       <c r="G254" s="14" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H254" s="16" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="I254" s="17" t="n">
-        <v>22000</v>
+        <v>9000</v>
       </c>
       <c r="J254" s="17" t="n">
-        <v>2200</v>
+        <v>900</v>
       </c>
       <c r="K254" s="14" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="L254" s="14" t="n">
-        <v>42.9</v>
+        <v>17.6</v>
       </c>
       <c r="M254" s="14" t="n">
-        <v>284</v>
+        <v>232</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="B255" s="12" t="n">
-        <v>31.14917</v>
+        <v>32.70236</v>
       </c>
       <c r="C255" s="12" t="n">
-        <v>35.22181</v>
+        <v>35.41203</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>65</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -12679,44 +12679,44 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>נגב / ערבה</t>
+          <t>חיפה / כרמל</t>
         </is>
       </c>
       <c r="G255" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H255" s="6" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="I255" s="13" t="n">
-        <v>8000</v>
+        <v>24000</v>
       </c>
       <c r="J255" s="13" t="n">
-        <v>800</v>
+        <v>2400</v>
       </c>
       <c r="K255" t="n">
         <v>80</v>
       </c>
       <c r="L255" t="n">
-        <v>15.6</v>
+        <v>46.8</v>
       </c>
       <c r="M255" t="n">
-        <v>283</v>
+        <v>232</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="14" t="n">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="B256" s="15" t="n">
-        <v>31.31343</v>
+        <v>32.66478</v>
       </c>
       <c r="C256" s="15" t="n">
-        <v>35.38376</v>
+        <v>35.39644</v>
       </c>
       <c r="D256" s="14" t="inlineStr">
         <is>
-          <t>דרך ים המלח</t>
+          <t>65</t>
         </is>
       </c>
       <c r="E256" s="14" t="inlineStr">
@@ -12726,44 +12726,44 @@
       </c>
       <c r="F256" s="14" t="inlineStr">
         <is>
-          <t>נגב / ערבה</t>
+          <t>חיפה / כרמל</t>
         </is>
       </c>
       <c r="G256" s="14" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H256" s="16" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="I256" s="17" t="n">
-        <v>8000</v>
+        <v>24000</v>
       </c>
       <c r="J256" s="17" t="n">
-        <v>800</v>
+        <v>2400</v>
       </c>
       <c r="K256" s="14" t="n">
         <v>80</v>
       </c>
       <c r="L256" s="14" t="n">
-        <v>15.6</v>
+        <v>46.8</v>
       </c>
       <c r="M256" s="14" t="n">
-        <v>253</v>
+        <v>232</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="B257" s="12" t="n">
-        <v>32.6126</v>
+        <v>32.59074</v>
       </c>
       <c r="C257" s="12" t="n">
-        <v>35.54892</v>
+        <v>35.2921</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>60</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -12777,22 +12777,22 @@
         </is>
       </c>
       <c r="G257" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H257" s="6" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="I257" s="13" t="n">
-        <v>9000</v>
+        <v>16000</v>
       </c>
       <c r="J257" s="13" t="n">
-        <v>900</v>
+        <v>1600</v>
       </c>
       <c r="K257" t="n">
         <v>80</v>
       </c>
       <c r="L257" t="n">
-        <v>17.6</v>
+        <v>31.2</v>
       </c>
       <c r="M257" t="n">
         <v>232</v>
@@ -12800,17 +12800,17 @@
     </row>
     <row r="258">
       <c r="A258" s="14" t="n">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="B258" s="15" t="n">
-        <v>32.70236</v>
+        <v>32.64101</v>
       </c>
       <c r="C258" s="15" t="n">
-        <v>35.41203</v>
+        <v>35.32434</v>
       </c>
       <c r="D258" s="14" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>כביש עוקף עפולה מזרח</t>
         </is>
       </c>
       <c r="E258" s="14" t="inlineStr">
@@ -12824,22 +12824,22 @@
         </is>
       </c>
       <c r="G258" s="14" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H258" s="16" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="I258" s="17" t="n">
-        <v>24000</v>
+        <v>8000</v>
       </c>
       <c r="J258" s="17" t="n">
-        <v>2400</v>
+        <v>800</v>
       </c>
       <c r="K258" s="14" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="L258" s="14" t="n">
-        <v>46.8</v>
+        <v>15.6</v>
       </c>
       <c r="M258" s="14" t="n">
         <v>232</v>
@@ -12847,17 +12847,17 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B259" s="12" t="n">
-        <v>32.66478</v>
+        <v>32.56021</v>
       </c>
       <c r="C259" s="12" t="n">
-        <v>35.39644</v>
+        <v>35.35378</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>675</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -12871,22 +12871,22 @@
         </is>
       </c>
       <c r="G259" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H259" s="6" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="I259" s="13" t="n">
-        <v>24000</v>
+        <v>8000</v>
       </c>
       <c r="J259" s="13" t="n">
-        <v>2400</v>
+        <v>800</v>
       </c>
       <c r="K259" t="n">
         <v>80</v>
       </c>
       <c r="L259" t="n">
-        <v>46.8</v>
+        <v>15.6</v>
       </c>
       <c r="M259" t="n">
         <v>232</v>
@@ -12894,17 +12894,17 @@
     </row>
     <row r="260">
       <c r="A260" s="14" t="n">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="B260" s="15" t="n">
-        <v>32.59074</v>
+        <v>32.5798</v>
       </c>
       <c r="C260" s="15" t="n">
-        <v>35.2921</v>
+        <v>35.39895</v>
       </c>
       <c r="D260" s="14" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>716</t>
         </is>
       </c>
       <c r="E260" s="14" t="inlineStr">
@@ -12918,22 +12918,22 @@
         </is>
       </c>
       <c r="G260" s="14" t="n">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="H260" s="16" t="n">
-        <v>250000</v>
+        <v>100000</v>
       </c>
       <c r="I260" s="17" t="n">
-        <v>16000</v>
+        <v>4000</v>
       </c>
       <c r="J260" s="17" t="n">
-        <v>1600</v>
+        <v>400</v>
       </c>
       <c r="K260" s="14" t="n">
         <v>80</v>
       </c>
       <c r="L260" s="14" t="n">
-        <v>31.2</v>
+        <v>7.8</v>
       </c>
       <c r="M260" s="14" t="n">
         <v>232</v>
@@ -12941,17 +12941,17 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="B261" s="12" t="n">
-        <v>32.64101</v>
+        <v>32.63534</v>
       </c>
       <c r="C261" s="12" t="n">
-        <v>35.32434</v>
+        <v>35.39574</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>כביש עוקף עפולה מזרח</t>
+          <t>716</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
@@ -12977,7 +12977,7 @@
         <v>800</v>
       </c>
       <c r="K261" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="L261" t="n">
         <v>15.6</v>
@@ -12988,17 +12988,17 @@
     </row>
     <row r="262">
       <c r="A262" s="14" t="n">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="B262" s="15" t="n">
-        <v>32.56021</v>
+        <v>32.71608</v>
       </c>
       <c r="C262" s="15" t="n">
-        <v>35.35378</v>
+        <v>35.46579</v>
       </c>
       <c r="D262" s="14" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>דרך המושבות</t>
         </is>
       </c>
       <c r="E262" s="14" t="inlineStr">
@@ -13012,22 +13012,22 @@
         </is>
       </c>
       <c r="G262" s="14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H262" s="16" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I262" s="17" t="n">
-        <v>8000</v>
+        <v>4000</v>
       </c>
       <c r="J262" s="17" t="n">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="K262" s="14" t="n">
         <v>80</v>
       </c>
       <c r="L262" s="14" t="n">
-        <v>15.6</v>
+        <v>7.8</v>
       </c>
       <c r="M262" s="14" t="n">
         <v>232</v>
@@ -13035,17 +13035,17 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="B263" s="12" t="n">
-        <v>32.5798</v>
+        <v>31.12478</v>
       </c>
       <c r="C263" s="12" t="n">
-        <v>35.39895</v>
+        <v>35.01084</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>25</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
@@ -13055,44 +13055,44 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>חיפה / כרמל</t>
+          <t>נגב / ערבה</t>
         </is>
       </c>
       <c r="G263" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H263" s="6" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I263" s="13" t="n">
-        <v>4000</v>
+        <v>7000</v>
       </c>
       <c r="J263" s="13" t="n">
-        <v>400</v>
+        <v>700</v>
       </c>
       <c r="K263" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="L263" t="n">
-        <v>7.8</v>
+        <v>13.7</v>
       </c>
       <c r="M263" t="n">
-        <v>232</v>
+        <v>225</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="14" t="n">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="B264" s="15" t="n">
-        <v>32.63534</v>
+        <v>32.55248</v>
       </c>
       <c r="C264" s="15" t="n">
-        <v>35.39574</v>
+        <v>35.0312</v>
       </c>
       <c r="D264" s="14" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>כביש חוצה ישראל</t>
         </is>
       </c>
       <c r="E264" s="14" t="inlineStr">
@@ -13118,28 +13118,26 @@
         <v>800</v>
       </c>
       <c r="K264" s="14" t="n">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="L264" s="14" t="n">
         <v>15.6</v>
       </c>
-      <c r="M264" s="14" t="n">
-        <v>232</v>
-      </c>
+      <c r="M264" s="14" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="B265" s="12" t="n">
-        <v>32.71608</v>
+        <v>32.58001</v>
       </c>
       <c r="C265" s="12" t="n">
-        <v>35.46579</v>
+        <v>35.04577</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>דרך המושבות</t>
+          <t>כביש חוצה ישראל</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
@@ -13153,40 +13151,38 @@
         </is>
       </c>
       <c r="G265" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H265" s="6" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I265" s="13" t="n">
-        <v>4000</v>
+        <v>8000</v>
       </c>
       <c r="J265" s="13" t="n">
-        <v>400</v>
+        <v>800</v>
       </c>
       <c r="K265" t="n">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="L265" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="M265" t="n">
-        <v>232</v>
-      </c>
+        <v>15.6</v>
+      </c>
+      <c r="M265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" s="14" t="n">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="B266" s="15" t="n">
-        <v>31.12478</v>
+        <v>32.61043</v>
       </c>
       <c r="C266" s="15" t="n">
-        <v>35.01084</v>
+        <v>34.92748</v>
       </c>
       <c r="D266" s="14" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>כביש החוף</t>
         </is>
       </c>
       <c r="E266" s="14" t="inlineStr">
@@ -13196,7 +13192,7 @@
       </c>
       <c r="F266" s="14" t="inlineStr">
         <is>
-          <t>נגב / ערבה</t>
+          <t>חיפה / כרמל</t>
         </is>
       </c>
       <c r="G266" s="14" t="n">
@@ -13206,34 +13202,32 @@
         <v>150000</v>
       </c>
       <c r="I266" s="17" t="n">
-        <v>7000</v>
+        <v>8000</v>
       </c>
       <c r="J266" s="17" t="n">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="K266" s="14" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="L266" s="14" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="M266" s="14" t="n">
-        <v>225</v>
-      </c>
+        <v>15.6</v>
+      </c>
+      <c r="M266" s="14" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="B267" s="12" t="n">
-        <v>32.55248</v>
+        <v>32.58656</v>
       </c>
       <c r="C267" s="12" t="n">
-        <v>35.0312</v>
+        <v>34.92636</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>כביש חוצה ישראל</t>
+          <t>כביש החוף</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
@@ -13259,7 +13253,7 @@
         <v>800</v>
       </c>
       <c r="K267" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="L267" t="n">
         <v>15.6</v>
@@ -13268,17 +13262,17 @@
     </row>
     <row r="268">
       <c r="A268" s="14" t="n">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="B268" s="15" t="n">
-        <v>32.58001</v>
+        <v>32.74157</v>
       </c>
       <c r="C268" s="15" t="n">
-        <v>35.04577</v>
+        <v>35.56785</v>
       </c>
       <c r="D268" s="14" t="inlineStr">
         <is>
-          <t>כביש חוצה ישראל</t>
+          <t>90</t>
         </is>
       </c>
       <c r="E268" s="14" t="inlineStr">
@@ -13298,32 +13292,32 @@
         <v>150000</v>
       </c>
       <c r="I268" s="17" t="n">
-        <v>8000</v>
+        <v>9000</v>
       </c>
       <c r="J268" s="17" t="n">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="K268" s="14" t="n">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="L268" s="14" t="n">
-        <v>15.6</v>
+        <v>17.6</v>
       </c>
       <c r="M268" s="14" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="B269" s="12" t="n">
-        <v>32.61043</v>
+        <v>31.14138</v>
       </c>
       <c r="C269" s="12" t="n">
-        <v>34.92748</v>
+        <v>35.36025</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>כביש החוף</t>
+          <t>90</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
@@ -13333,7 +13327,7 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>חיפה / כרמל</t>
+          <t>נגב / ערבה</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -13343,32 +13337,32 @@
         <v>150000</v>
       </c>
       <c r="I269" s="13" t="n">
-        <v>8000</v>
+        <v>9000</v>
       </c>
       <c r="J269" s="13" t="n">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="K269" t="n">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="L269" t="n">
-        <v>15.6</v>
+        <v>17.6</v>
       </c>
       <c r="M269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" s="14" t="n">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="B270" s="15" t="n">
-        <v>32.58656</v>
+        <v>29.5441</v>
       </c>
       <c r="C270" s="15" t="n">
-        <v>34.92636</v>
+        <v>34.95027</v>
       </c>
       <c r="D270" s="14" t="inlineStr">
         <is>
-          <t>כביש החוף</t>
+          <t>90</t>
         </is>
       </c>
       <c r="E270" s="14" t="inlineStr">
@@ -13378,7 +13372,7 @@
       </c>
       <c r="F270" s="14" t="inlineStr">
         <is>
-          <t>חיפה / כרמל</t>
+          <t>נגב / ערבה</t>
         </is>
       </c>
       <c r="G270" s="14" t="n">
@@ -13388,28 +13382,28 @@
         <v>150000</v>
       </c>
       <c r="I270" s="17" t="n">
-        <v>8000</v>
+        <v>9000</v>
       </c>
       <c r="J270" s="17" t="n">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="K270" s="14" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="L270" s="14" t="n">
-        <v>15.6</v>
+        <v>17.6</v>
       </c>
       <c r="M270" s="14" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="B271" s="12" t="n">
-        <v>32.74157</v>
+        <v>32.70484</v>
       </c>
       <c r="C271" s="12" t="n">
-        <v>35.56785</v>
+        <v>35.58641</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -13427,34 +13421,34 @@
         </is>
       </c>
       <c r="G271" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H271" s="6" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I271" s="13" t="n">
-        <v>9000</v>
+        <v>4000</v>
       </c>
       <c r="J271" s="13" t="n">
-        <v>900</v>
+        <v>400</v>
       </c>
       <c r="K271" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="L271" t="n">
-        <v>17.6</v>
+        <v>7.8</v>
       </c>
       <c r="M271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" s="14" t="n">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="B272" s="15" t="n">
-        <v>31.14138</v>
+        <v>32.67837</v>
       </c>
       <c r="C272" s="15" t="n">
-        <v>35.36025</v>
+        <v>35.5805</v>
       </c>
       <c r="D272" s="14" t="inlineStr">
         <is>
@@ -13468,7 +13462,7 @@
       </c>
       <c r="F272" s="14" t="inlineStr">
         <is>
-          <t>נגב / ערבה</t>
+          <t>חיפה / כרמל</t>
         </is>
       </c>
       <c r="G272" s="14" t="n">
@@ -13484,7 +13478,7 @@
         <v>900</v>
       </c>
       <c r="K272" s="14" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="L272" s="14" t="n">
         <v>17.6</v>
@@ -13493,17 +13487,17 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="B273" s="12" t="n">
-        <v>29.5441</v>
+        <v>29.57788</v>
       </c>
       <c r="C273" s="12" t="n">
-        <v>34.95027</v>
+        <v>34.96757</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>הערבה</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
@@ -13523,32 +13517,32 @@
         <v>150000</v>
       </c>
       <c r="I273" s="13" t="n">
-        <v>9000</v>
+        <v>8000</v>
       </c>
       <c r="J273" s="13" t="n">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="K273" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="L273" t="n">
-        <v>17.6</v>
+        <v>15.6</v>
       </c>
       <c r="M273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" s="14" t="n">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="B274" s="15" t="n">
-        <v>32.70484</v>
+        <v>29.60913</v>
       </c>
       <c r="C274" s="15" t="n">
-        <v>35.58641</v>
+        <v>34.98382</v>
       </c>
       <c r="D274" s="14" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>הערבה</t>
         </is>
       </c>
       <c r="E274" s="14" t="inlineStr">
@@ -13558,42 +13552,42 @@
       </c>
       <c r="F274" s="14" t="inlineStr">
         <is>
-          <t>חיפה / כרמל</t>
+          <t>נגב / ערבה</t>
         </is>
       </c>
       <c r="G274" s="14" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H274" s="16" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I274" s="17" t="n">
-        <v>4000</v>
+        <v>8000</v>
       </c>
       <c r="J274" s="17" t="n">
-        <v>400</v>
+        <v>800</v>
       </c>
       <c r="K274" s="14" t="n">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="L274" s="14" t="n">
-        <v>7.8</v>
+        <v>15.6</v>
       </c>
       <c r="M274" s="14" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="B275" s="12" t="n">
-        <v>32.67837</v>
+        <v>29.76344</v>
       </c>
       <c r="C275" s="12" t="n">
-        <v>35.5805</v>
+        <v>35.01411</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>הערבה</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
@@ -13603,7 +13597,7 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>חיפה / כרמל</t>
+          <t>נגב / ערבה</t>
         </is>
       </c>
       <c r="G275" t="n">
@@ -13613,32 +13607,32 @@
         <v>150000</v>
       </c>
       <c r="I275" s="13" t="n">
-        <v>9000</v>
+        <v>8000</v>
       </c>
       <c r="J275" s="13" t="n">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="K275" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="L275" t="n">
-        <v>17.6</v>
+        <v>15.6</v>
       </c>
       <c r="M275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" s="14" t="n">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="B276" s="15" t="n">
-        <v>29.57788</v>
+        <v>30.28384</v>
       </c>
       <c r="C276" s="15" t="n">
-        <v>34.96757</v>
+        <v>34.99975</v>
       </c>
       <c r="D276" s="14" t="inlineStr">
         <is>
-          <t>הערבה</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E276" s="14" t="inlineStr">
@@ -13652,128 +13646,128 @@
         </is>
       </c>
       <c r="G276" s="14" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H276" s="16" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="I276" s="17" t="n">
-        <v>8000</v>
+        <v>22000</v>
       </c>
       <c r="J276" s="17" t="n">
-        <v>800</v>
+        <v>2200</v>
       </c>
       <c r="K276" s="14" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="L276" s="14" t="n">
-        <v>15.6</v>
+        <v>42.9</v>
       </c>
       <c r="M276" s="14" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="B277" s="12" t="n">
-        <v>29.60913</v>
+        <v>30.81704</v>
       </c>
       <c r="C277" s="12" t="n">
-        <v>34.98382</v>
+        <v>34.75609</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>הערבה</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>רגיל</t>
+          <t>עוטף עזה</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>נגב / ערבה</t>
+          <t>עוטף עזה / הנגב המערבי</t>
         </is>
       </c>
       <c r="G277" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H277" s="6" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="I277" s="13" t="n">
-        <v>8000</v>
+        <v>22000</v>
       </c>
       <c r="J277" s="13" t="n">
-        <v>800</v>
+        <v>2200</v>
       </c>
       <c r="K277" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="L277" t="n">
-        <v>15.6</v>
+        <v>42.9</v>
       </c>
       <c r="M277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" s="14" t="n">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="B278" s="15" t="n">
-        <v>29.76344</v>
+        <v>30.78002</v>
       </c>
       <c r="C278" s="15" t="n">
-        <v>35.01411</v>
+        <v>34.76921</v>
       </c>
       <c r="D278" s="14" t="inlineStr">
         <is>
-          <t>הערבה</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E278" s="14" t="inlineStr">
         <is>
-          <t>רגיל</t>
+          <t>עוטף עזה</t>
         </is>
       </c>
       <c r="F278" s="14" t="inlineStr">
         <is>
-          <t>נגב / ערבה</t>
+          <t>עוטף עזה / הנגב המערבי</t>
         </is>
       </c>
       <c r="G278" s="14" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H278" s="16" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="I278" s="17" t="n">
-        <v>8000</v>
+        <v>22000</v>
       </c>
       <c r="J278" s="17" t="n">
-        <v>800</v>
+        <v>2200</v>
       </c>
       <c r="K278" s="14" t="n">
         <v>90</v>
       </c>
       <c r="L278" s="14" t="n">
-        <v>15.6</v>
+        <v>42.9</v>
       </c>
       <c r="M278" s="14" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="B279" s="12" t="n">
-        <v>30.28384</v>
+        <v>30.04781</v>
       </c>
       <c r="C279" s="12" t="n">
-        <v>34.99975</v>
+        <v>35.01047</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
@@ -13787,128 +13781,128 @@
         </is>
       </c>
       <c r="G279" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H279" s="6" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="I279" s="13" t="n">
-        <v>22000</v>
+        <v>8000</v>
       </c>
       <c r="J279" s="13" t="n">
-        <v>2200</v>
+        <v>800</v>
       </c>
       <c r="K279" t="n">
         <v>80</v>
       </c>
       <c r="L279" t="n">
-        <v>42.9</v>
+        <v>15.6</v>
       </c>
       <c r="M279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" s="14" t="n">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="B280" s="15" t="n">
-        <v>30.81704</v>
+        <v>31.05359</v>
       </c>
       <c r="C280" s="15" t="n">
-        <v>34.75609</v>
+        <v>35.03088</v>
       </c>
       <c r="D280" s="14" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>25</t>
         </is>
       </c>
       <c r="E280" s="14" t="inlineStr">
         <is>
-          <t>עוטף עזה</t>
+          <t>רגיל</t>
         </is>
       </c>
       <c r="F280" s="14" t="inlineStr">
         <is>
-          <t>עוטף עזה / הנגב המערבי</t>
+          <t>נגב / ערבה</t>
         </is>
       </c>
       <c r="G280" s="14" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H280" s="16" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="I280" s="17" t="n">
-        <v>22000</v>
+        <v>7000</v>
       </c>
       <c r="J280" s="17" t="n">
-        <v>2200</v>
+        <v>700</v>
       </c>
       <c r="K280" s="14" t="n">
         <v>90</v>
       </c>
       <c r="L280" s="14" t="n">
-        <v>42.9</v>
+        <v>13.7</v>
       </c>
       <c r="M280" s="14" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="B281" s="12" t="n">
-        <v>30.78002</v>
+        <v>31.06829</v>
       </c>
       <c r="C281" s="12" t="n">
-        <v>34.76921</v>
+        <v>35.00661</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>25</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>עוטף עזה</t>
+          <t>רגיל</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>עוטף עזה / הנגב המערבי</t>
+          <t>נגב / ערבה</t>
         </is>
       </c>
       <c r="G281" t="n">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="H281" s="6" t="n">
-        <v>250000</v>
+        <v>100000</v>
       </c>
       <c r="I281" s="13" t="n">
-        <v>22000</v>
+        <v>4000</v>
       </c>
       <c r="J281" s="13" t="n">
-        <v>2200</v>
+        <v>400</v>
       </c>
       <c r="K281" t="n">
         <v>90</v>
       </c>
       <c r="L281" t="n">
-        <v>42.9</v>
+        <v>7.8</v>
       </c>
       <c r="M281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" s="14" t="n">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="B282" s="15" t="n">
-        <v>30.04781</v>
+        <v>29.83364</v>
       </c>
       <c r="C282" s="15" t="n">
-        <v>35.01047</v>
+        <v>35.02882</v>
       </c>
       <c r="D282" s="14" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>הערבה</t>
         </is>
       </c>
       <c r="E282" s="14" t="inlineStr">
@@ -13934,7 +13928,7 @@
         <v>800</v>
       </c>
       <c r="K282" s="14" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="L282" s="14" t="n">
         <v>15.6</v>
@@ -13943,27 +13937,27 @@
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="B283" s="12" t="n">
-        <v>31.05359</v>
+        <v>29.63183</v>
       </c>
       <c r="C283" s="12" t="n">
-        <v>35.03088</v>
+        <v>34.88065</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>כביש הגבול המערבי</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>רגיל</t>
+          <t>עוטף עזה</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>נגב / ערבה</t>
+          <t>עוטף עזה / הנגב המערבי</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -13973,32 +13967,32 @@
         <v>150000</v>
       </c>
       <c r="I283" s="13" t="n">
-        <v>7000</v>
+        <v>8000</v>
       </c>
       <c r="J283" s="13" t="n">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="K283" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="L283" t="n">
-        <v>13.7</v>
+        <v>15.6</v>
       </c>
       <c r="M283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" s="14" t="n">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="B284" s="15" t="n">
-        <v>31.06829</v>
+        <v>29.77754</v>
       </c>
       <c r="C284" s="15" t="n">
-        <v>35.00661</v>
+        <v>35.05858</v>
       </c>
       <c r="D284" s="14" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>Jordan Valley Highway</t>
         </is>
       </c>
       <c r="E284" s="14" t="inlineStr">
@@ -14012,34 +14006,34 @@
         </is>
       </c>
       <c r="G284" s="14" t="n">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="H284" s="16" t="n">
-        <v>100000</v>
+        <v>250000</v>
       </c>
       <c r="I284" s="17" t="n">
-        <v>4000</v>
+        <v>24000</v>
       </c>
       <c r="J284" s="17" t="n">
-        <v>400</v>
+        <v>2400</v>
       </c>
       <c r="K284" s="14" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="L284" s="14" t="n">
-        <v>7.8</v>
+        <v>46.8</v>
       </c>
       <c r="M284" s="14" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="B285" s="12" t="n">
-        <v>29.83364</v>
+        <v>30.13754</v>
       </c>
       <c r="C285" s="12" t="n">
-        <v>35.02882</v>
+        <v>35.138</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -14078,17 +14072,17 @@
     </row>
     <row r="286">
       <c r="A286" s="14" t="n">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="B286" s="15" t="n">
-        <v>29.63183</v>
+        <v>29.84431</v>
       </c>
       <c r="C286" s="15" t="n">
-        <v>34.88065</v>
+        <v>34.83819</v>
       </c>
       <c r="D286" s="14" t="inlineStr">
         <is>
-          <t>כביש הגבול המערבי</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E286" s="14" t="inlineStr">
@@ -14123,17 +14117,17 @@
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="B287" s="12" t="n">
-        <v>29.77754</v>
+        <v>30.48576</v>
       </c>
       <c r="C287" s="12" t="n">
-        <v>35.05858</v>
+        <v>34.93315</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>Jordan Valley Highway</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
@@ -14153,32 +14147,32 @@
         <v>250000</v>
       </c>
       <c r="I287" s="13" t="n">
-        <v>24000</v>
+        <v>22000</v>
       </c>
       <c r="J287" s="13" t="n">
-        <v>2400</v>
+        <v>2200</v>
       </c>
       <c r="K287" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="L287" t="n">
-        <v>46.8</v>
+        <v>42.9</v>
       </c>
       <c r="M287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" s="14" t="n">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="B288" s="15" t="n">
-        <v>30.13754</v>
+        <v>29.94978</v>
       </c>
       <c r="C288" s="15" t="n">
-        <v>35.138</v>
+        <v>34.91844</v>
       </c>
       <c r="D288" s="14" t="inlineStr">
         <is>
-          <t>הערבה</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E288" s="14" t="inlineStr">
@@ -14204,7 +14198,7 @@
         <v>800</v>
       </c>
       <c r="K288" s="14" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="L288" s="14" t="n">
         <v>15.6</v>
@@ -14213,27 +14207,27 @@
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="B289" s="12" t="n">
-        <v>29.84431</v>
+        <v>29.96941</v>
       </c>
       <c r="C289" s="12" t="n">
-        <v>34.83819</v>
+        <v>35.06507</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>הערבה</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>עוטף עזה</t>
+          <t>רגיל</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>עוטף עזה / הנגב המערבי</t>
+          <t>נגב / ערבה</t>
         </is>
       </c>
       <c r="G289" t="n">
@@ -14249,7 +14243,7 @@
         <v>800</v>
       </c>
       <c r="K289" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="L289" t="n">
         <v>15.6</v>
@@ -14258,17 +14252,17 @@
     </row>
     <row r="290">
       <c r="A290" s="14" t="n">
-        <v>324</v>
+        <v>333</v>
       </c>
       <c r="B290" s="15" t="n">
-        <v>30.48576</v>
+        <v>30.26971</v>
       </c>
       <c r="C290" s="15" t="n">
-        <v>34.93315</v>
+        <v>35.13539</v>
       </c>
       <c r="D290" s="14" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>הערבה</t>
         </is>
       </c>
       <c r="E290" s="14" t="inlineStr">
@@ -14282,48 +14276,48 @@
         </is>
       </c>
       <c r="G290" s="14" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H290" s="16" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="I290" s="17" t="n">
-        <v>22000</v>
+        <v>8000</v>
       </c>
       <c r="J290" s="17" t="n">
-        <v>2200</v>
+        <v>800</v>
       </c>
       <c r="K290" s="14" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="L290" s="14" t="n">
-        <v>42.9</v>
+        <v>15.6</v>
       </c>
       <c r="M290" s="14" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="B291" s="12" t="n">
-        <v>29.94978</v>
+        <v>29.73907</v>
       </c>
       <c r="C291" s="12" t="n">
-        <v>34.91844</v>
+        <v>34.85312</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>כביש הגבול המערבי</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>רגיל</t>
+          <t>עוטף עזה</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>נגב / ערבה</t>
+          <t>עוטף עזה / הנגב המערבי</t>
         </is>
       </c>
       <c r="G291" t="n">
@@ -14348,17 +14342,17 @@
     </row>
     <row r="292">
       <c r="A292" s="14" t="n">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="B292" s="15" t="n">
-        <v>29.96941</v>
+        <v>31.03923</v>
       </c>
       <c r="C292" s="15" t="n">
-        <v>35.06507</v>
+        <v>35.16624</v>
       </c>
       <c r="D292" s="14" t="inlineStr">
         <is>
-          <t>הערבה</t>
+          <t>25</t>
         </is>
       </c>
       <c r="E292" s="14" t="inlineStr">
@@ -14378,28 +14372,28 @@
         <v>150000</v>
       </c>
       <c r="I292" s="17" t="n">
-        <v>8000</v>
+        <v>7000</v>
       </c>
       <c r="J292" s="17" t="n">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="K292" s="14" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="L292" s="14" t="n">
-        <v>15.6</v>
+        <v>13.7</v>
       </c>
       <c r="M292" s="14" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B293" s="12" t="n">
-        <v>30.26971</v>
+        <v>29.70652</v>
       </c>
       <c r="C293" s="12" t="n">
-        <v>35.13539</v>
+        <v>34.99732</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -14438,62 +14432,62 @@
     </row>
     <row r="294">
       <c r="A294" s="14" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="B294" s="15" t="n">
-        <v>29.73907</v>
+        <v>30.37038</v>
       </c>
       <c r="C294" s="15" t="n">
-        <v>34.85312</v>
+        <v>34.96243</v>
       </c>
       <c r="D294" s="14" t="inlineStr">
         <is>
-          <t>כביש הגבול המערבי</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E294" s="14" t="inlineStr">
         <is>
-          <t>עוטף עזה</t>
+          <t>רגיל</t>
         </is>
       </c>
       <c r="F294" s="14" t="inlineStr">
         <is>
-          <t>עוטף עזה / הנגב המערבי</t>
+          <t>נגב / ערבה</t>
         </is>
       </c>
       <c r="G294" s="14" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H294" s="16" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="I294" s="17" t="n">
-        <v>8000</v>
+        <v>22000</v>
       </c>
       <c r="J294" s="17" t="n">
-        <v>800</v>
+        <v>2200</v>
       </c>
       <c r="K294" s="14" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="L294" s="14" t="n">
-        <v>15.6</v>
+        <v>42.9</v>
       </c>
       <c r="M294" s="14" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="B295" s="12" t="n">
-        <v>31.03923</v>
+        <v>30.16144</v>
       </c>
       <c r="C295" s="12" t="n">
-        <v>35.16624</v>
+        <v>35.01743</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
@@ -14507,38 +14501,38 @@
         </is>
       </c>
       <c r="G295" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H295" s="6" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="I295" s="13" t="n">
-        <v>7000</v>
+        <v>22000</v>
       </c>
       <c r="J295" s="13" t="n">
-        <v>700</v>
+        <v>2200</v>
       </c>
       <c r="K295" t="n">
         <v>90</v>
       </c>
       <c r="L295" t="n">
-        <v>13.7</v>
+        <v>42.9</v>
       </c>
       <c r="M295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" s="14" t="n">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="B296" s="15" t="n">
-        <v>29.70652</v>
+        <v>31.07234</v>
       </c>
       <c r="C296" s="15" t="n">
-        <v>34.99732</v>
+        <v>35.3971</v>
       </c>
       <c r="D296" s="14" t="inlineStr">
         <is>
-          <t>הערבה</t>
+          <t>90</t>
         </is>
       </c>
       <c r="E296" s="14" t="inlineStr">
@@ -14558,32 +14552,32 @@
         <v>150000</v>
       </c>
       <c r="I296" s="17" t="n">
-        <v>8000</v>
+        <v>9000</v>
       </c>
       <c r="J296" s="17" t="n">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="K296" s="14" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="L296" s="14" t="n">
-        <v>15.6</v>
+        <v>17.6</v>
       </c>
       <c r="M296" s="14" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="B297" s="12" t="n">
-        <v>30.37038</v>
+        <v>29.89666</v>
       </c>
       <c r="C297" s="12" t="n">
-        <v>34.96243</v>
+        <v>35.06371</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>הערבה</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
@@ -14597,38 +14591,38 @@
         </is>
       </c>
       <c r="G297" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H297" s="6" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="I297" s="13" t="n">
-        <v>22000</v>
+        <v>8000</v>
       </c>
       <c r="J297" s="13" t="n">
-        <v>2200</v>
+        <v>800</v>
       </c>
       <c r="K297" t="n">
         <v>90</v>
       </c>
       <c r="L297" t="n">
-        <v>42.9</v>
+        <v>15.6</v>
       </c>
       <c r="M297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" s="14" t="n">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="B298" s="15" t="n">
-        <v>30.16144</v>
+        <v>30.05335</v>
       </c>
       <c r="C298" s="15" t="n">
-        <v>35.01743</v>
+        <v>35.11309</v>
       </c>
       <c r="D298" s="14" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>הערבה</t>
         </is>
       </c>
       <c r="E298" s="14" t="inlineStr">
@@ -14642,83 +14636,83 @@
         </is>
       </c>
       <c r="G298" s="14" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H298" s="16" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="I298" s="17" t="n">
-        <v>22000</v>
+        <v>8000</v>
       </c>
       <c r="J298" s="17" t="n">
-        <v>2200</v>
+        <v>800</v>
       </c>
       <c r="K298" s="14" t="n">
         <v>90</v>
       </c>
       <c r="L298" s="14" t="n">
-        <v>42.9</v>
+        <v>15.6</v>
       </c>
       <c r="M298" s="14" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="B299" s="12" t="n">
-        <v>31.07234</v>
+        <v>30.87527</v>
       </c>
       <c r="C299" s="12" t="n">
-        <v>35.3971</v>
+        <v>34.78662</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>רגיל</t>
+          <t>עוטף עזה</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>נגב / ערבה</t>
+          <t>עוטף עזה / הנגב המערבי</t>
         </is>
       </c>
       <c r="G299" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H299" s="6" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="I299" s="13" t="n">
-        <v>9000</v>
+        <v>22000</v>
       </c>
       <c r="J299" s="13" t="n">
-        <v>900</v>
+        <v>2200</v>
       </c>
       <c r="K299" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="L299" t="n">
-        <v>17.6</v>
+        <v>42.9</v>
       </c>
       <c r="M299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" s="14" t="n">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="B300" s="15" t="n">
-        <v>29.89666</v>
+        <v>32.5894</v>
       </c>
       <c r="C300" s="15" t="n">
-        <v>35.06371</v>
+        <v>34.98374</v>
       </c>
       <c r="D300" s="14" t="inlineStr">
         <is>
-          <t>הערבה</t>
+          <t>ואדי מילק</t>
         </is>
       </c>
       <c r="E300" s="14" t="inlineStr">
@@ -14728,7 +14722,7 @@
       </c>
       <c r="F300" s="14" t="inlineStr">
         <is>
-          <t>נגב / ערבה</t>
+          <t>חיפה / כרמל</t>
         </is>
       </c>
       <c r="G300" s="14" t="n">
@@ -14744,7 +14738,7 @@
         <v>800</v>
       </c>
       <c r="K300" s="14" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="L300" s="14" t="n">
         <v>15.6</v>
@@ -14753,27 +14747,27 @@
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>346</v>
+        <v>357</v>
       </c>
       <c r="B301" s="12" t="n">
-        <v>30.05335</v>
+        <v>29.90423</v>
       </c>
       <c r="C301" s="12" t="n">
-        <v>35.11309</v>
+        <v>34.86291</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>הערבה</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>רגיל</t>
+          <t>עוטף עזה</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>נגב / ערבה</t>
+          <t>עוטף עזה / הנגב המערבי</t>
         </is>
       </c>
       <c r="G301" t="n">
@@ -14789,7 +14783,7 @@
         <v>800</v>
       </c>
       <c r="K301" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="L301" t="n">
         <v>15.6</v>
@@ -14798,62 +14792,62 @@
     </row>
     <row r="302">
       <c r="A302" s="14" t="n">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="B302" s="15" t="n">
-        <v>30.87527</v>
+        <v>30.00362</v>
       </c>
       <c r="C302" s="15" t="n">
-        <v>34.78662</v>
+        <v>34.9552</v>
       </c>
       <c r="D302" s="14" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E302" s="14" t="inlineStr">
         <is>
-          <t>עוטף עזה</t>
+          <t>רגיל</t>
         </is>
       </c>
       <c r="F302" s="14" t="inlineStr">
         <is>
-          <t>עוטף עזה / הנגב המערבי</t>
+          <t>נגב / ערבה</t>
         </is>
       </c>
       <c r="G302" s="14" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H302" s="16" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="I302" s="17" t="n">
-        <v>22000</v>
+        <v>8000</v>
       </c>
       <c r="J302" s="17" t="n">
-        <v>2200</v>
+        <v>800</v>
       </c>
       <c r="K302" s="14" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="L302" s="14" t="n">
-        <v>42.9</v>
+        <v>15.6</v>
       </c>
       <c r="M302" s="14" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>350</v>
+        <v>361</v>
       </c>
       <c r="B303" s="12" t="n">
-        <v>32.5894</v>
+        <v>29.65814</v>
       </c>
       <c r="C303" s="12" t="n">
-        <v>34.98374</v>
+        <v>34.99038</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>ואדי מילק</t>
+          <t>הערבה</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
@@ -14863,7 +14857,7 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>חיפה / כרמל</t>
+          <t>נגב / ערבה</t>
         </is>
       </c>
       <c r="G303" t="n">
@@ -14879,7 +14873,7 @@
         <v>800</v>
       </c>
       <c r="K303" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="L303" t="n">
         <v>15.6</v>
@@ -14888,27 +14882,27 @@
     </row>
     <row r="304">
       <c r="A304" s="14" t="n">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="B304" s="15" t="n">
-        <v>29.90423</v>
+        <v>30.20251</v>
       </c>
       <c r="C304" s="15" t="n">
-        <v>34.86291</v>
+        <v>35.13549</v>
       </c>
       <c r="D304" s="14" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>הערבה</t>
         </is>
       </c>
       <c r="E304" s="14" t="inlineStr">
         <is>
-          <t>עוטף עזה</t>
+          <t>רגיל</t>
         </is>
       </c>
       <c r="F304" s="14" t="inlineStr">
         <is>
-          <t>עוטף עזה / הנגב המערבי</t>
+          <t>נגב / ערבה</t>
         </is>
       </c>
       <c r="G304" s="14" t="n">
@@ -14924,7 +14918,7 @@
         <v>800</v>
       </c>
       <c r="K304" s="14" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="L304" s="14" t="n">
         <v>15.6</v>
@@ -14933,17 +14927,17 @@
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="B305" s="12" t="n">
-        <v>30.00362</v>
+        <v>29.72945</v>
       </c>
       <c r="C305" s="12" t="n">
-        <v>34.9552</v>
+        <v>35.03561</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>Jordan Valley Highway</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
@@ -14957,38 +14951,38 @@
         </is>
       </c>
       <c r="G305" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H305" s="6" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="I305" s="13" t="n">
-        <v>8000</v>
+        <v>24000</v>
       </c>
       <c r="J305" s="13" t="n">
-        <v>800</v>
+        <v>2400</v>
       </c>
       <c r="K305" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="L305" t="n">
-        <v>15.6</v>
+        <v>46.8</v>
       </c>
       <c r="M305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" s="14" t="n">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="B306" s="15" t="n">
-        <v>29.65814</v>
+        <v>30.29091</v>
       </c>
       <c r="C306" s="15" t="n">
-        <v>34.99038</v>
+        <v>35.09632</v>
       </c>
       <c r="D306" s="14" t="inlineStr">
         <is>
-          <t>הערבה</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E306" s="14" t="inlineStr">
@@ -15023,17 +15017,17 @@
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="B307" s="12" t="n">
-        <v>30.20251</v>
+        <v>30.9957</v>
       </c>
       <c r="C307" s="12" t="n">
-        <v>35.13549</v>
+        <v>34.92368</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>הערבה</t>
+          <t>204</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
@@ -15059,7 +15053,7 @@
         <v>800</v>
       </c>
       <c r="K307" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="L307" t="n">
         <v>15.6</v>
@@ -15068,17 +15062,17 @@
     </row>
     <row r="308">
       <c r="A308" s="14" t="n">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B308" s="15" t="n">
-        <v>29.72945</v>
+        <v>32.57236</v>
       </c>
       <c r="C308" s="15" t="n">
-        <v>35.03561</v>
+        <v>35.07668</v>
       </c>
       <c r="D308" s="14" t="inlineStr">
         <is>
-          <t>Jordan Valley Highway</t>
+          <t>672</t>
         </is>
       </c>
       <c r="E308" s="14" t="inlineStr">
@@ -15088,42 +15082,42 @@
       </c>
       <c r="F308" s="14" t="inlineStr">
         <is>
-          <t>נגב / ערבה</t>
+          <t>חיפה / כרמל</t>
         </is>
       </c>
       <c r="G308" s="14" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H308" s="16" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="I308" s="17" t="n">
-        <v>24000</v>
+        <v>8000</v>
       </c>
       <c r="J308" s="17" t="n">
-        <v>2400</v>
+        <v>800</v>
       </c>
       <c r="K308" s="14" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="L308" s="14" t="n">
-        <v>46.8</v>
+        <v>15.6</v>
       </c>
       <c r="M308" s="14" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B309" s="12" t="n">
-        <v>30.29091</v>
+        <v>32.56674</v>
       </c>
       <c r="C309" s="12" t="n">
-        <v>35.09632</v>
+        <v>35.26239</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>675</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
@@ -15133,7 +15127,7 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>נגב / ערבה</t>
+          <t>חיפה / כרמל</t>
         </is>
       </c>
       <c r="G309" t="n">
@@ -15149,7 +15143,7 @@
         <v>800</v>
       </c>
       <c r="K309" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="L309" t="n">
         <v>15.6</v>
@@ -15158,13 +15152,13 @@
     </row>
     <row r="310">
       <c r="A310" s="14" t="n">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="B310" s="15" t="n">
-        <v>30.9957</v>
+        <v>30.91157</v>
       </c>
       <c r="C310" s="15" t="n">
-        <v>34.92368</v>
+        <v>34.84372</v>
       </c>
       <c r="D310" s="14" t="inlineStr">
         <is>
@@ -15173,12 +15167,12 @@
       </c>
       <c r="E310" s="14" t="inlineStr">
         <is>
-          <t>רגיל</t>
+          <t>עוטף עזה</t>
         </is>
       </c>
       <c r="F310" s="14" t="inlineStr">
         <is>
-          <t>נגב / ערבה</t>
+          <t>עוטף עזה / הנגב המערבי</t>
         </is>
       </c>
       <c r="G310" s="14" t="n">
@@ -15203,17 +15197,17 @@
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="B311" s="12" t="n">
-        <v>32.57236</v>
+        <v>29.55534</v>
       </c>
       <c r="C311" s="12" t="n">
-        <v>35.07668</v>
+        <v>34.91334</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>דרך החוגגים</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
@@ -15223,7 +15217,7 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>חיפה / כרמל</t>
+          <t>נגב / ערבה</t>
         </is>
       </c>
       <c r="G311" t="n">
@@ -15248,17 +15242,17 @@
     </row>
     <row r="312">
       <c r="A312" s="14" t="n">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="B312" s="15" t="n">
-        <v>32.56674</v>
+        <v>32.59429</v>
       </c>
       <c r="C312" s="15" t="n">
-        <v>35.26239</v>
+        <v>35.18035</v>
       </c>
       <c r="D312" s="14" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>66</t>
         </is>
       </c>
       <c r="E312" s="14" t="inlineStr">
@@ -15284,7 +15278,7 @@
         <v>800</v>
       </c>
       <c r="K312" s="14" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="L312" s="14" t="n">
         <v>15.6</v>
@@ -15293,27 +15287,27 @@
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="B313" s="12" t="n">
-        <v>30.91157</v>
+        <v>31.00401</v>
       </c>
       <c r="C313" s="12" t="n">
-        <v>34.84372</v>
+        <v>35.27512</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>מעלה תמר</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>עוטף עזה</t>
+          <t>רגיל</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>עוטף עזה / הנגב המערבי</t>
+          <t>נגב / ערבה</t>
         </is>
       </c>
       <c r="G313" t="n">
@@ -15338,17 +15332,17 @@
     </row>
     <row r="314">
       <c r="A314" s="14" t="n">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="B314" s="15" t="n">
-        <v>29.55534</v>
+        <v>30.92485</v>
       </c>
       <c r="C314" s="15" t="n">
-        <v>34.91334</v>
+        <v>35.02487</v>
       </c>
       <c r="D314" s="14" t="inlineStr">
         <is>
-          <t>דרך החוגגים</t>
+          <t>206</t>
         </is>
       </c>
       <c r="E314" s="14" t="inlineStr">
@@ -15383,17 +15377,17 @@
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="B315" s="12" t="n">
-        <v>32.59429</v>
+        <v>32.71419</v>
       </c>
       <c r="C315" s="12" t="n">
-        <v>35.18035</v>
+        <v>35.54642</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>767</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
@@ -15419,7 +15413,7 @@
         <v>800</v>
       </c>
       <c r="K315" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="L315" t="n">
         <v>15.6</v>
@@ -15428,17 +15422,17 @@
     </row>
     <row r="316">
       <c r="A316" s="14" t="n">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="B316" s="15" t="n">
-        <v>31.00401</v>
+        <v>30.93723</v>
       </c>
       <c r="C316" s="15" t="n">
-        <v>35.27512</v>
+        <v>35.11694</v>
       </c>
       <c r="D316" s="14" t="inlineStr">
         <is>
-          <t>מעלה תמר</t>
+          <t>227</t>
         </is>
       </c>
       <c r="E316" s="14" t="inlineStr">
@@ -15473,17 +15467,17 @@
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="B317" s="12" t="n">
-        <v>30.92485</v>
+        <v>30.95248</v>
       </c>
       <c r="C317" s="12" t="n">
-        <v>35.02487</v>
+        <v>35.01187</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>225</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
@@ -15497,38 +15491,38 @@
         </is>
       </c>
       <c r="G317" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H317" s="6" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I317" s="13" t="n">
-        <v>8000</v>
+        <v>4000</v>
       </c>
       <c r="J317" s="13" t="n">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="K317" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="L317" t="n">
-        <v>15.6</v>
+        <v>7.8</v>
       </c>
       <c r="M317" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" s="14" t="n">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="B318" s="15" t="n">
-        <v>32.71419</v>
+        <v>31.01151</v>
       </c>
       <c r="C318" s="15" t="n">
-        <v>35.54642</v>
+        <v>35.07848</v>
       </c>
       <c r="D318" s="14" t="inlineStr">
         <is>
-          <t>767</t>
+          <t>206</t>
         </is>
       </c>
       <c r="E318" s="14" t="inlineStr">
@@ -15538,7 +15532,7 @@
       </c>
       <c r="F318" s="14" t="inlineStr">
         <is>
-          <t>חיפה / כרמל</t>
+          <t>נגב / ערבה</t>
         </is>
       </c>
       <c r="G318" s="14" t="n">
@@ -15563,13 +15557,13 @@
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="B319" s="12" t="n">
-        <v>30.93723</v>
+        <v>30.88774</v>
       </c>
       <c r="C319" s="12" t="n">
-        <v>35.11694</v>
+        <v>35.13939</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -15608,17 +15602,17 @@
     </row>
     <row r="320">
       <c r="A320" s="14" t="n">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="B320" s="15" t="n">
-        <v>30.95248</v>
+        <v>30.9633</v>
       </c>
       <c r="C320" s="15" t="n">
-        <v>35.01187</v>
+        <v>35.04934</v>
       </c>
       <c r="D320" s="14" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>227</t>
         </is>
       </c>
       <c r="E320" s="14" t="inlineStr">
@@ -15632,38 +15626,38 @@
         </is>
       </c>
       <c r="G320" s="14" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H320" s="16" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I320" s="17" t="n">
-        <v>4000</v>
+        <v>8000</v>
       </c>
       <c r="J320" s="17" t="n">
-        <v>400</v>
+        <v>800</v>
       </c>
       <c r="K320" s="14" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="L320" s="14" t="n">
-        <v>7.8</v>
+        <v>15.6</v>
       </c>
       <c r="M320" s="14" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="B321" s="12" t="n">
-        <v>31.01151</v>
+        <v>31.08317</v>
       </c>
       <c r="C321" s="12" t="n">
-        <v>35.07848</v>
+        <v>35.21114</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>258</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
@@ -15695,141 +15689,6 @@
         <v>15.6</v>
       </c>
       <c r="M321" t="inlineStr"/>
-    </row>
-    <row r="322">
-      <c r="A322" s="14" t="n">
-        <v>383</v>
-      </c>
-      <c r="B322" s="15" t="n">
-        <v>30.88774</v>
-      </c>
-      <c r="C322" s="15" t="n">
-        <v>35.13939</v>
-      </c>
-      <c r="D322" s="14" t="inlineStr">
-        <is>
-          <t>227</t>
-        </is>
-      </c>
-      <c r="E322" s="14" t="inlineStr">
-        <is>
-          <t>רגיל</t>
-        </is>
-      </c>
-      <c r="F322" s="14" t="inlineStr">
-        <is>
-          <t>נגב / ערבה</t>
-        </is>
-      </c>
-      <c r="G322" s="14" t="n">
-        <v>20</v>
-      </c>
-      <c r="H322" s="16" t="n">
-        <v>150000</v>
-      </c>
-      <c r="I322" s="17" t="n">
-        <v>8000</v>
-      </c>
-      <c r="J322" s="17" t="n">
-        <v>800</v>
-      </c>
-      <c r="K322" s="14" t="n">
-        <v>80</v>
-      </c>
-      <c r="L322" s="14" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="M322" s="14" t="inlineStr"/>
-    </row>
-    <row r="323">
-      <c r="A323" t="n">
-        <v>384</v>
-      </c>
-      <c r="B323" s="12" t="n">
-        <v>30.9633</v>
-      </c>
-      <c r="C323" s="12" t="n">
-        <v>35.04934</v>
-      </c>
-      <c r="D323" t="inlineStr">
-        <is>
-          <t>227</t>
-        </is>
-      </c>
-      <c r="E323" t="inlineStr">
-        <is>
-          <t>רגיל</t>
-        </is>
-      </c>
-      <c r="F323" t="inlineStr">
-        <is>
-          <t>נגב / ערבה</t>
-        </is>
-      </c>
-      <c r="G323" t="n">
-        <v>20</v>
-      </c>
-      <c r="H323" s="6" t="n">
-        <v>150000</v>
-      </c>
-      <c r="I323" s="13" t="n">
-        <v>8000</v>
-      </c>
-      <c r="J323" s="13" t="n">
-        <v>800</v>
-      </c>
-      <c r="K323" t="n">
-        <v>80</v>
-      </c>
-      <c r="L323" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="M323" t="inlineStr"/>
-    </row>
-    <row r="324">
-      <c r="A324" s="14" t="n">
-        <v>385</v>
-      </c>
-      <c r="B324" s="15" t="n">
-        <v>31.08317</v>
-      </c>
-      <c r="C324" s="15" t="n">
-        <v>35.21114</v>
-      </c>
-      <c r="D324" s="14" t="inlineStr">
-        <is>
-          <t>258</t>
-        </is>
-      </c>
-      <c r="E324" s="14" t="inlineStr">
-        <is>
-          <t>רגיל</t>
-        </is>
-      </c>
-      <c r="F324" s="14" t="inlineStr">
-        <is>
-          <t>נגב / ערבה</t>
-        </is>
-      </c>
-      <c r="G324" s="14" t="n">
-        <v>20</v>
-      </c>
-      <c r="H324" s="16" t="n">
-        <v>150000</v>
-      </c>
-      <c r="I324" s="17" t="n">
-        <v>8000</v>
-      </c>
-      <c r="J324" s="17" t="n">
-        <v>800</v>
-      </c>
-      <c r="K324" s="14" t="n">
-        <v>80</v>
-      </c>
-      <c r="L324" s="14" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="M324" s="14" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -15902,10 +15761,10 @@
         <v>17800000</v>
       </c>
       <c r="D3" t="n">
-        <v>32.6</v>
+        <v>32.9</v>
       </c>
       <c r="E3" t="n">
-        <v>31.5</v>
+        <v>31.8</v>
       </c>
     </row>
     <row r="4">
@@ -15915,16 +15774,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>10200000</v>
+        <v>9700000</v>
       </c>
       <c r="D4" t="n">
-        <v>15.5</v>
+        <v>14.7</v>
       </c>
       <c r="E4" t="n">
-        <v>18</v>
+        <v>17.3</v>
       </c>
     </row>
     <row r="5">
@@ -15940,10 +15799,10 @@
         <v>6850000</v>
       </c>
       <c r="D5" t="n">
-        <v>10.9</v>
+        <v>11</v>
       </c>
       <c r="E5" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="6">
@@ -15959,10 +15818,10 @@
         <v>9600000</v>
       </c>
       <c r="D6" t="n">
-        <v>18.3</v>
+        <v>18.5</v>
       </c>
       <c r="E6" t="n">
-        <v>17</v>
+        <v>17.1</v>
       </c>
     </row>
     <row r="7">
@@ -15978,10 +15837,10 @@
         <v>10350000</v>
       </c>
       <c r="D7" t="n">
-        <v>18.9</v>
+        <v>19.1</v>
       </c>
       <c r="E7" t="n">
-        <v>18.3</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="8">
@@ -15997,10 +15856,10 @@
         <v>1723000</v>
       </c>
       <c r="D8" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="9">
@@ -16010,10 +15869,10 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>56523000</v>
+        <v>56023000</v>
       </c>
     </row>
   </sheetData>
@@ -16102,7 +15961,7 @@
         <v>2900000</v>
       </c>
       <c r="E4" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="5">
@@ -16110,16 +15969,16 @@
         <v>20</v>
       </c>
       <c r="B5" t="n">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>150000</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>27450000</v>
+        <v>27150000</v>
       </c>
       <c r="E5" t="n">
-        <v>56.8</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="6">
@@ -16127,16 +15986,16 @@
         <v>30</v>
       </c>
       <c r="B6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>200000</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>4600000</v>
+        <v>4400000</v>
       </c>
       <c r="E6" t="n">
-        <v>7.1</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="7">
@@ -16153,7 +16012,7 @@
         <v>21500000</v>
       </c>
       <c r="E7" t="n">
-        <v>26.7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8">
@@ -16163,10 +16022,10 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>56523000</v>
+        <v>56023000</v>
       </c>
     </row>
   </sheetData>

--- a/budget_shelters_v2.xlsx
+++ b/budget_shelters_v2.xlsx
@@ -558,7 +558,7 @@
         <v>73000</v>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D6" s="6">
         <f>B6*C6</f>
@@ -573,7 +573,7 @@
         <v>100000</v>
       </c>
       <c r="C7" t="n">
-        <v>29</v>
+        <v>182</v>
       </c>
       <c r="D7" s="6">
         <f>B7*C7</f>
@@ -588,7 +588,7 @@
         <v>150000</v>
       </c>
       <c r="C8" t="n">
-        <v>181</v>
+        <v>31</v>
       </c>
       <c r="D8" s="6">
         <f>B8*C8</f>
@@ -603,7 +603,7 @@
         <v>200000</v>
       </c>
       <c r="C9" t="n">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="D9" s="6">
         <f>B9*C9</f>
@@ -618,7 +618,7 @@
         <v>250000</v>
       </c>
       <c r="C10" t="n">
-        <v>86</v>
+        <v>55</v>
       </c>
       <c r="D10" s="6">
         <f>B10*C10</f>
@@ -875,10 +875,10 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I3" s="13" t="n">
         <v>8000</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="G4" s="14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H4" s="16" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I4" s="17" t="n">
         <v>9000</v>
@@ -969,10 +969,10 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>250000</v>
+        <v>200000</v>
       </c>
       <c r="I5" s="13" t="n">
         <v>20000</v>
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="G6" s="14" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H6" s="16" t="n">
-        <v>250000</v>
+        <v>200000</v>
       </c>
       <c r="I6" s="17" t="n">
         <v>20000</v>
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>200000</v>
+        <v>150000</v>
       </c>
       <c r="I7" s="13" t="n">
         <v>13000</v>
@@ -1157,10 +1157,10 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>200000</v>
+        <v>150000</v>
       </c>
       <c r="I9" s="13" t="n">
         <v>4000</v>
@@ -1204,10 +1204,10 @@
         </is>
       </c>
       <c r="G10" s="14" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H10" s="16" t="n">
-        <v>250000</v>
+        <v>200000</v>
       </c>
       <c r="I10" s="17" t="n">
         <v>8000</v>
@@ -1251,10 +1251,10 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I11" s="13" t="n">
         <v>9000</v>
@@ -1298,10 +1298,10 @@
         </is>
       </c>
       <c r="G12" s="14" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H12" s="16" t="n">
-        <v>200000</v>
+        <v>150000</v>
       </c>
       <c r="I12" s="17" t="n">
         <v>8000</v>
@@ -1345,10 +1345,10 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>250000</v>
+        <v>200000</v>
       </c>
       <c r="I13" s="13" t="n">
         <v>8000</v>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="G16" s="14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H16" s="16" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I16" s="17" t="n">
         <v>8000</v>
@@ -1627,10 +1627,10 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>250000</v>
+        <v>200000</v>
       </c>
       <c r="I19" s="13" t="n">
         <v>8000</v>
@@ -1721,10 +1721,10 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I21" s="13" t="n">
         <v>8000</v>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="G22" s="14" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H22" s="16" t="n">
-        <v>250000</v>
+        <v>200000</v>
       </c>
       <c r="I22" s="17" t="n">
         <v>8000</v>
@@ -1815,10 +1815,10 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>250000</v>
+        <v>200000</v>
       </c>
       <c r="I23" s="13" t="n">
         <v>8000</v>
@@ -1909,10 +1909,10 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I25" s="13" t="n">
         <v>8000</v>
@@ -1956,10 +1956,10 @@
         </is>
       </c>
       <c r="G26" s="14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H26" s="16" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I26" s="17" t="n">
         <v>8000</v>
@@ -2003,10 +2003,10 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>250000</v>
+        <v>200000</v>
       </c>
       <c r="I27" s="13" t="n">
         <v>8000</v>
@@ -2097,10 +2097,10 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>250000</v>
+        <v>200000</v>
       </c>
       <c r="I29" s="13" t="n">
         <v>8000</v>
@@ -2285,10 +2285,10 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>250000</v>
+        <v>200000</v>
       </c>
       <c r="I33" s="13" t="n">
         <v>8000</v>
@@ -2332,10 +2332,10 @@
         </is>
       </c>
       <c r="G34" s="14" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H34" s="16" t="n">
-        <v>250000</v>
+        <v>200000</v>
       </c>
       <c r="I34" s="17" t="n">
         <v>8000</v>
@@ -2379,10 +2379,10 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I35" s="13" t="n">
         <v>8000</v>
@@ -2612,10 +2612,10 @@
         </is>
       </c>
       <c r="G40" s="14" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H40" s="16" t="n">
-        <v>250000</v>
+        <v>200000</v>
       </c>
       <c r="I40" s="17" t="n">
         <v>20000</v>
@@ -2659,10 +2659,10 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>250000</v>
+        <v>200000</v>
       </c>
       <c r="I41" s="13" t="n">
         <v>8000</v>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="G44" s="14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H44" s="16" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I44" s="17" t="n">
         <v>8000</v>
@@ -2847,10 +2847,10 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>250000</v>
+        <v>200000</v>
       </c>
       <c r="I45" s="13" t="n">
         <v>8000</v>
@@ -2894,10 +2894,10 @@
         </is>
       </c>
       <c r="G46" s="14" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H46" s="16" t="n">
-        <v>200000</v>
+        <v>150000</v>
       </c>
       <c r="I46" s="17" t="n">
         <v>8000</v>
@@ -2941,10 +2941,10 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>200000</v>
+        <v>150000</v>
       </c>
       <c r="I47" s="13" t="n">
         <v>8000</v>
@@ -2988,10 +2988,10 @@
         </is>
       </c>
       <c r="G48" s="14" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H48" s="16" t="n">
-        <v>250000</v>
+        <v>200000</v>
       </c>
       <c r="I48" s="17" t="n">
         <v>8000</v>
@@ -3035,10 +3035,10 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H49" s="6" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I49" s="13" t="n">
         <v>8000</v>
@@ -3082,10 +3082,10 @@
         </is>
       </c>
       <c r="G50" s="14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H50" s="16" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I50" s="17" t="n">
         <v>9000</v>
@@ -3176,10 +3176,10 @@
         </is>
       </c>
       <c r="G52" s="14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H52" s="16" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I52" s="17" t="n">
         <v>8500</v>
@@ -3223,10 +3223,10 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H53" s="6" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I53" s="13" t="n">
         <v>9000</v>
@@ -3317,10 +3317,10 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H55" s="6" t="n">
-        <v>250000</v>
+        <v>200000</v>
       </c>
       <c r="I55" s="13" t="n">
         <v>20000</v>
@@ -3411,10 +3411,10 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H57" s="6" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I57" s="13" t="n">
         <v>8500</v>
@@ -3458,10 +3458,10 @@
         </is>
       </c>
       <c r="G58" s="14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H58" s="16" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I58" s="17" t="n">
         <v>8000</v>
@@ -3505,10 +3505,10 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H59" s="6" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I59" s="13" t="n">
         <v>8000</v>
@@ -3597,10 +3597,10 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H61" s="6" t="n">
-        <v>250000</v>
+        <v>200000</v>
       </c>
       <c r="I61" s="13" t="n">
         <v>8000</v>
@@ -3644,10 +3644,10 @@
         </is>
       </c>
       <c r="G62" s="14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H62" s="16" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I62" s="17" t="n">
         <v>9000</v>
@@ -3877,10 +3877,10 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H67" s="6" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I67" s="13" t="n">
         <v>8000</v>
@@ -3924,10 +3924,10 @@
         </is>
       </c>
       <c r="G68" s="14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H68" s="16" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I68" s="17" t="n">
         <v>8000</v>
@@ -3971,10 +3971,10 @@
         </is>
       </c>
       <c r="G69" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H69" s="6" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I69" s="13" t="n">
         <v>8000</v>
@@ -4065,10 +4065,10 @@
         </is>
       </c>
       <c r="G71" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H71" s="6" t="n">
-        <v>250000</v>
+        <v>200000</v>
       </c>
       <c r="I71" s="13" t="n">
         <v>8000</v>
@@ -4112,10 +4112,10 @@
         </is>
       </c>
       <c r="G72" s="14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H72" s="16" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I72" s="17" t="n">
         <v>8000</v>
@@ -4204,10 +4204,10 @@
         </is>
       </c>
       <c r="G74" s="14" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H74" s="16" t="n">
-        <v>200000</v>
+        <v>150000</v>
       </c>
       <c r="I74" s="17" t="n">
         <v>8000</v>
@@ -4345,10 +4345,10 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H77" s="6" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I77" s="13" t="n">
         <v>8000</v>
@@ -4392,10 +4392,10 @@
         </is>
       </c>
       <c r="G78" s="14" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H78" s="16" t="n">
-        <v>250000</v>
+        <v>200000</v>
       </c>
       <c r="I78" s="17" t="n">
         <v>18000</v>
@@ -4439,10 +4439,10 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H79" s="6" t="n">
-        <v>250000</v>
+        <v>200000</v>
       </c>
       <c r="I79" s="13" t="n">
         <v>20000</v>
@@ -4486,10 +4486,10 @@
         </is>
       </c>
       <c r="G80" s="14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H80" s="16" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I80" s="17" t="n">
         <v>8000</v>
@@ -4533,10 +4533,10 @@
         </is>
       </c>
       <c r="G81" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H81" s="6" t="n">
-        <v>200000</v>
+        <v>150000</v>
       </c>
       <c r="I81" s="13" t="n">
         <v>8000</v>
@@ -4580,10 +4580,10 @@
         </is>
       </c>
       <c r="G82" s="14" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H82" s="16" t="n">
-        <v>200000</v>
+        <v>150000</v>
       </c>
       <c r="I82" s="17" t="n">
         <v>8000</v>
@@ -4627,10 +4627,10 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H83" s="6" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I83" s="13" t="n">
         <v>8000</v>
@@ -4766,10 +4766,10 @@
         </is>
       </c>
       <c r="G86" s="14" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H86" s="16" t="n">
-        <v>200000</v>
+        <v>150000</v>
       </c>
       <c r="I86" s="17" t="n">
         <v>8000</v>
@@ -4813,10 +4813,10 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H87" s="6" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I87" s="13" t="n">
         <v>8000</v>
@@ -5001,10 +5001,10 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H91" s="6" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I91" s="13" t="n">
         <v>8000</v>
@@ -5048,10 +5048,10 @@
         </is>
       </c>
       <c r="G92" s="14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H92" s="16" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I92" s="17" t="n">
         <v>8000</v>
@@ -5142,10 +5142,10 @@
         </is>
       </c>
       <c r="G94" s="14" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H94" s="16" t="n">
-        <v>250000</v>
+        <v>200000</v>
       </c>
       <c r="I94" s="17" t="n">
         <v>18000</v>
@@ -5189,10 +5189,10 @@
         </is>
       </c>
       <c r="G95" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H95" s="6" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I95" s="13" t="n">
         <v>8000</v>
@@ -5283,10 +5283,10 @@
         </is>
       </c>
       <c r="G97" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H97" s="6" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I97" s="13" t="n">
         <v>8000</v>
@@ -5377,10 +5377,10 @@
         </is>
       </c>
       <c r="G99" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H99" s="6" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I99" s="13" t="n">
         <v>8000</v>
@@ -5424,10 +5424,10 @@
         </is>
       </c>
       <c r="G100" s="14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H100" s="16" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I100" s="17" t="n">
         <v>8000</v>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="G103" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H103" s="6" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I103" s="13" t="n">
         <v>8000</v>
@@ -5612,10 +5612,10 @@
         </is>
       </c>
       <c r="G104" s="14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H104" s="16" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I104" s="17" t="n">
         <v>8000</v>
@@ -5659,10 +5659,10 @@
         </is>
       </c>
       <c r="G105" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H105" s="6" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I105" s="13" t="n">
         <v>8000</v>
@@ -5845,10 +5845,10 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H109" s="6" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I109" s="13" t="n">
         <v>8000</v>
@@ -5937,10 +5937,10 @@
         </is>
       </c>
       <c r="G111" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H111" s="6" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I111" s="13" t="n">
         <v>8000</v>
@@ -5984,10 +5984,10 @@
         </is>
       </c>
       <c r="G112" s="14" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H112" s="16" t="n">
-        <v>200000</v>
+        <v>150000</v>
       </c>
       <c r="I112" s="17" t="n">
         <v>11000</v>
@@ -6078,10 +6078,10 @@
         </is>
       </c>
       <c r="G114" s="14" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H114" s="16" t="n">
-        <v>200000</v>
+        <v>150000</v>
       </c>
       <c r="I114" s="17" t="n">
         <v>8000</v>
@@ -6125,10 +6125,10 @@
         </is>
       </c>
       <c r="G115" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H115" s="6" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I115" s="13" t="n">
         <v>8000</v>
@@ -6172,10 +6172,10 @@
         </is>
       </c>
       <c r="G116" s="14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H116" s="16" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I116" s="17" t="n">
         <v>8000</v>
@@ -6219,10 +6219,10 @@
         </is>
       </c>
       <c r="G117" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H117" s="6" t="n">
-        <v>100000</v>
+        <v>73000</v>
       </c>
       <c r="I117" s="13" t="n">
         <v>4000</v>
@@ -6266,10 +6266,10 @@
         </is>
       </c>
       <c r="G118" s="14" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H118" s="16" t="n">
-        <v>200000</v>
+        <v>150000</v>
       </c>
       <c r="I118" s="17" t="n">
         <v>8000</v>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="G120" s="14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H120" s="16" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I120" s="17" t="n">
         <v>8000</v>
@@ -6407,10 +6407,10 @@
         </is>
       </c>
       <c r="G121" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H121" s="6" t="n">
-        <v>100000</v>
+        <v>73000</v>
       </c>
       <c r="I121" s="13" t="n">
         <v>4000</v>
@@ -6454,10 +6454,10 @@
         </is>
       </c>
       <c r="G122" s="14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H122" s="16" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I122" s="17" t="n">
         <v>7000</v>
@@ -6501,10 +6501,10 @@
         </is>
       </c>
       <c r="G123" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H123" s="6" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I123" s="13" t="n">
         <v>8000</v>
@@ -6548,10 +6548,10 @@
         </is>
       </c>
       <c r="G124" s="14" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H124" s="16" t="n">
-        <v>200000</v>
+        <v>150000</v>
       </c>
       <c r="I124" s="17" t="n">
         <v>8000</v>
@@ -6642,10 +6642,10 @@
         </is>
       </c>
       <c r="G126" s="14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H126" s="16" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I126" s="17" t="n">
         <v>8000</v>
@@ -6689,10 +6689,10 @@
         </is>
       </c>
       <c r="G127" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H127" s="6" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I127" s="13" t="n">
         <v>8000</v>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="G128" s="14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H128" s="16" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I128" s="17" t="n">
         <v>8000</v>
@@ -6830,10 +6830,10 @@
         </is>
       </c>
       <c r="G130" s="14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H130" s="16" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I130" s="17" t="n">
         <v>8000</v>
@@ -6877,10 +6877,10 @@
         </is>
       </c>
       <c r="G131" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H131" s="6" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I131" s="13" t="n">
         <v>8000</v>
@@ -6924,10 +6924,10 @@
         </is>
       </c>
       <c r="G132" s="14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H132" s="16" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I132" s="17" t="n">
         <v>8000</v>
@@ -7018,10 +7018,10 @@
         </is>
       </c>
       <c r="G134" s="14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H134" s="16" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I134" s="17" t="n">
         <v>8000</v>
@@ -7112,10 +7112,10 @@
         </is>
       </c>
       <c r="G136" s="14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H136" s="16" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I136" s="17" t="n">
         <v>8000</v>
@@ -7159,10 +7159,10 @@
         </is>
       </c>
       <c r="G137" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H137" s="6" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I137" s="13" t="n">
         <v>8000</v>
@@ -7206,10 +7206,10 @@
         </is>
       </c>
       <c r="G138" s="14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H138" s="16" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I138" s="17" t="n">
         <v>8000</v>
@@ -7253,10 +7253,10 @@
         </is>
       </c>
       <c r="G139" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H139" s="6" t="n">
-        <v>250000</v>
+        <v>200000</v>
       </c>
       <c r="I139" s="13" t="n">
         <v>20000</v>
@@ -7300,10 +7300,10 @@
         </is>
       </c>
       <c r="G140" s="14" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H140" s="16" t="n">
-        <v>200000</v>
+        <v>150000</v>
       </c>
       <c r="I140" s="17" t="n">
         <v>8000</v>
@@ -7441,10 +7441,10 @@
         </is>
       </c>
       <c r="G143" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H143" s="6" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I143" s="13" t="n">
         <v>8000</v>
@@ -7488,10 +7488,10 @@
         </is>
       </c>
       <c r="G144" s="14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H144" s="16" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I144" s="17" t="n">
         <v>8000</v>
@@ -7535,10 +7535,10 @@
         </is>
       </c>
       <c r="G145" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H145" s="6" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I145" s="13" t="n">
         <v>8000</v>
@@ -7582,10 +7582,10 @@
         </is>
       </c>
       <c r="G146" s="14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H146" s="16" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I146" s="17" t="n">
         <v>8000</v>
@@ -7629,10 +7629,10 @@
         </is>
       </c>
       <c r="G147" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H147" s="6" t="n">
-        <v>250000</v>
+        <v>200000</v>
       </c>
       <c r="I147" s="13" t="n">
         <v>19000</v>
@@ -7723,10 +7723,10 @@
         </is>
       </c>
       <c r="G149" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H149" s="6" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I149" s="13" t="n">
         <v>8000</v>
@@ -7817,10 +7817,10 @@
         </is>
       </c>
       <c r="G151" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H151" s="6" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I151" s="13" t="n">
         <v>8000</v>
@@ -7909,10 +7909,10 @@
         </is>
       </c>
       <c r="G153" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H153" s="6" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I153" s="13" t="n">
         <v>8000</v>
@@ -8003,10 +8003,10 @@
         </is>
       </c>
       <c r="G155" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H155" s="6" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I155" s="13" t="n">
         <v>8000</v>
@@ -8097,10 +8097,10 @@
         </is>
       </c>
       <c r="G157" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H157" s="6" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I157" s="13" t="n">
         <v>8000</v>
@@ -8144,10 +8144,10 @@
         </is>
       </c>
       <c r="G158" s="14" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H158" s="16" t="n">
-        <v>250000</v>
+        <v>200000</v>
       </c>
       <c r="I158" s="17" t="n">
         <v>18000</v>
@@ -8191,10 +8191,10 @@
         </is>
       </c>
       <c r="G159" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H159" s="6" t="n">
-        <v>250000</v>
+        <v>200000</v>
       </c>
       <c r="I159" s="13" t="n">
         <v>19000</v>
@@ -8238,10 +8238,10 @@
         </is>
       </c>
       <c r="G160" s="14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H160" s="16" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I160" s="17" t="n">
         <v>8000</v>
@@ -8285,10 +8285,10 @@
         </is>
       </c>
       <c r="G161" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H161" s="6" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I161" s="13" t="n">
         <v>8000</v>
@@ -8379,10 +8379,10 @@
         </is>
       </c>
       <c r="G163" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H163" s="6" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I163" s="13" t="n">
         <v>8000</v>
@@ -8426,10 +8426,10 @@
         </is>
       </c>
       <c r="G164" s="14" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H164" s="16" t="n">
-        <v>200000</v>
+        <v>150000</v>
       </c>
       <c r="I164" s="17" t="n">
         <v>11000</v>
@@ -8520,10 +8520,10 @@
         </is>
       </c>
       <c r="G166" s="14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H166" s="16" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I166" s="17" t="n">
         <v>8000</v>
@@ -8661,10 +8661,10 @@
         </is>
       </c>
       <c r="G169" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H169" s="6" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I169" s="13" t="n">
         <v>8000</v>
@@ -8708,10 +8708,10 @@
         </is>
       </c>
       <c r="G170" s="14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H170" s="16" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I170" s="17" t="n">
         <v>8000</v>
@@ -8755,10 +8755,10 @@
         </is>
       </c>
       <c r="G171" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H171" s="6" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I171" s="13" t="n">
         <v>8000</v>
@@ -8800,10 +8800,10 @@
         </is>
       </c>
       <c r="G172" s="14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H172" s="16" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I172" s="17" t="n">
         <v>8000</v>
@@ -8892,10 +8892,10 @@
         </is>
       </c>
       <c r="G174" s="14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H174" s="16" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I174" s="17" t="n">
         <v>8000</v>
@@ -8939,10 +8939,10 @@
         </is>
       </c>
       <c r="G175" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H175" s="6" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I175" s="13" t="n">
         <v>8000</v>
@@ -8984,10 +8984,10 @@
         </is>
       </c>
       <c r="G176" s="14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H176" s="16" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I176" s="17" t="n">
         <v>8000</v>
@@ -9031,10 +9031,10 @@
         </is>
       </c>
       <c r="G177" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H177" s="6" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I177" s="13" t="n">
         <v>6500</v>
@@ -9125,10 +9125,10 @@
         </is>
       </c>
       <c r="G179" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H179" s="6" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I179" s="13" t="n">
         <v>8000</v>
@@ -9172,10 +9172,10 @@
         </is>
       </c>
       <c r="G180" s="14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H180" s="16" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I180" s="17" t="n">
         <v>8000</v>
@@ -9266,10 +9266,10 @@
         </is>
       </c>
       <c r="G182" s="14" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H182" s="16" t="n">
-        <v>100000</v>
+        <v>73000</v>
       </c>
       <c r="I182" s="17" t="n">
         <v>4000</v>
@@ -9407,10 +9407,10 @@
         </is>
       </c>
       <c r="G185" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H185" s="6" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I185" s="13" t="n">
         <v>8000</v>
@@ -9454,10 +9454,10 @@
         </is>
       </c>
       <c r="G186" s="14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H186" s="16" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I186" s="17" t="n">
         <v>8000</v>
@@ -9548,10 +9548,10 @@
         </is>
       </c>
       <c r="G188" s="14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H188" s="16" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I188" s="17" t="n">
         <v>8000</v>
@@ -9593,10 +9593,10 @@
         </is>
       </c>
       <c r="G189" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H189" s="6" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I189" s="13" t="n">
         <v>8000</v>
@@ -9687,10 +9687,10 @@
         </is>
       </c>
       <c r="G191" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H191" s="6" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I191" s="13" t="n">
         <v>8000</v>
@@ -9734,10 +9734,10 @@
         </is>
       </c>
       <c r="G192" s="14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H192" s="16" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I192" s="17" t="n">
         <v>8000</v>
@@ -9781,10 +9781,10 @@
         </is>
       </c>
       <c r="G193" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H193" s="6" t="n">
-        <v>250000</v>
+        <v>200000</v>
       </c>
       <c r="I193" s="13" t="n">
         <v>16000</v>
@@ -9875,10 +9875,10 @@
         </is>
       </c>
       <c r="G195" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H195" s="6" t="n">
-        <v>250000</v>
+        <v>200000</v>
       </c>
       <c r="I195" s="13" t="n">
         <v>19000</v>
@@ -9922,10 +9922,10 @@
         </is>
       </c>
       <c r="G196" s="14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H196" s="16" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I196" s="17" t="n">
         <v>8000</v>
@@ -10016,10 +10016,10 @@
         </is>
       </c>
       <c r="G198" s="14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H198" s="16" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I198" s="17" t="n">
         <v>8000</v>
@@ -10061,10 +10061,10 @@
         </is>
       </c>
       <c r="G199" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H199" s="6" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I199" s="13" t="n">
         <v>7000</v>
@@ -10108,10 +10108,10 @@
         </is>
       </c>
       <c r="G200" s="14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H200" s="16" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I200" s="17" t="n">
         <v>8000</v>
@@ -10155,10 +10155,10 @@
         </is>
       </c>
       <c r="G201" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H201" s="6" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I201" s="13" t="n">
         <v>8000</v>
@@ -10202,10 +10202,10 @@
         </is>
       </c>
       <c r="G202" s="14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H202" s="16" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I202" s="17" t="n">
         <v>8000</v>
@@ -10249,10 +10249,10 @@
         </is>
       </c>
       <c r="G203" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H203" s="6" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I203" s="13" t="n">
         <v>8000</v>
@@ -10296,10 +10296,10 @@
         </is>
       </c>
       <c r="G204" s="14" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H204" s="16" t="n">
-        <v>250000</v>
+        <v>200000</v>
       </c>
       <c r="I204" s="17" t="n">
         <v>16000</v>
@@ -10433,10 +10433,10 @@
         </is>
       </c>
       <c r="G207" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H207" s="6" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I207" s="13" t="n">
         <v>6500</v>
@@ -10480,10 +10480,10 @@
         </is>
       </c>
       <c r="G208" s="14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H208" s="16" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I208" s="17" t="n">
         <v>8000</v>
@@ -10527,10 +10527,10 @@
         </is>
       </c>
       <c r="G209" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H209" s="6" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I209" s="13" t="n">
         <v>8000</v>
@@ -10668,10 +10668,10 @@
         </is>
       </c>
       <c r="G212" s="14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H212" s="16" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I212" s="17" t="n">
         <v>8000</v>
@@ -10715,10 +10715,10 @@
         </is>
       </c>
       <c r="G213" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H213" s="6" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I213" s="13" t="n">
         <v>8000</v>
@@ -10760,10 +10760,10 @@
         </is>
       </c>
       <c r="G214" s="14" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H214" s="16" t="n">
-        <v>100000</v>
+        <v>73000</v>
       </c>
       <c r="I214" s="17" t="n">
         <v>4000</v>
@@ -10807,10 +10807,10 @@
         </is>
       </c>
       <c r="G215" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H215" s="6" t="n">
-        <v>250000</v>
+        <v>200000</v>
       </c>
       <c r="I215" s="13" t="n">
         <v>19000</v>
@@ -10854,10 +10854,10 @@
         </is>
       </c>
       <c r="G216" s="14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H216" s="16" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I216" s="17" t="n">
         <v>8000</v>
@@ -10901,10 +10901,10 @@
         </is>
       </c>
       <c r="G217" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H217" s="6" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I217" s="13" t="n">
         <v>8000</v>
@@ -10948,10 +10948,10 @@
         </is>
       </c>
       <c r="G218" s="14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H218" s="16" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I218" s="17" t="n">
         <v>8000</v>
@@ -10995,10 +10995,10 @@
         </is>
       </c>
       <c r="G219" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H219" s="6" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I219" s="13" t="n">
         <v>8000</v>
@@ -11042,10 +11042,10 @@
         </is>
       </c>
       <c r="G220" s="14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H220" s="16" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I220" s="17" t="n">
         <v>8000</v>
@@ -11089,10 +11089,10 @@
         </is>
       </c>
       <c r="G221" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H221" s="6" t="n">
-        <v>250000</v>
+        <v>200000</v>
       </c>
       <c r="I221" s="13" t="n">
         <v>16000</v>
@@ -11136,10 +11136,10 @@
         </is>
       </c>
       <c r="G222" s="14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H222" s="16" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I222" s="17" t="n">
         <v>8000</v>
@@ -11183,10 +11183,10 @@
         </is>
       </c>
       <c r="G223" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H223" s="6" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I223" s="13" t="n">
         <v>8000</v>
@@ -11275,10 +11275,10 @@
         </is>
       </c>
       <c r="G225" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H225" s="6" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I225" s="13" t="n">
         <v>7000</v>
@@ -11322,10 +11322,10 @@
         </is>
       </c>
       <c r="G226" s="14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H226" s="16" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I226" s="17" t="n">
         <v>8000</v>
@@ -11369,10 +11369,10 @@
         </is>
       </c>
       <c r="G227" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H227" s="6" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I227" s="13" t="n">
         <v>8000</v>
@@ -11414,10 +11414,10 @@
         </is>
       </c>
       <c r="G228" s="14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H228" s="16" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I228" s="17" t="n">
         <v>8000</v>
@@ -11461,10 +11461,10 @@
         </is>
       </c>
       <c r="G229" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H229" s="6" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I229" s="13" t="n">
         <v>8000</v>
@@ -11508,10 +11508,10 @@
         </is>
       </c>
       <c r="G230" s="14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H230" s="16" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I230" s="17" t="n">
         <v>8000</v>
@@ -11555,10 +11555,10 @@
         </is>
       </c>
       <c r="G231" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H231" s="6" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I231" s="13" t="n">
         <v>6500</v>
@@ -11602,10 +11602,10 @@
         </is>
       </c>
       <c r="G232" s="14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H232" s="16" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I232" s="17" t="n">
         <v>8000</v>
@@ -11649,10 +11649,10 @@
         </is>
       </c>
       <c r="G233" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H233" s="6" t="n">
-        <v>100000</v>
+        <v>73000</v>
       </c>
       <c r="I233" s="13" t="n">
         <v>4000</v>
@@ -11696,10 +11696,10 @@
         </is>
       </c>
       <c r="G234" s="14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H234" s="16" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I234" s="17" t="n">
         <v>8000</v>
@@ -11743,10 +11743,10 @@
         </is>
       </c>
       <c r="G235" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H235" s="6" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I235" s="13" t="n">
         <v>8000</v>
@@ -11790,10 +11790,10 @@
         </is>
       </c>
       <c r="G236" s="14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H236" s="16" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I236" s="17" t="n">
         <v>6500</v>
@@ -11837,10 +11837,10 @@
         </is>
       </c>
       <c r="G237" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H237" s="6" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I237" s="13" t="n">
         <v>8000</v>
@@ -11884,10 +11884,10 @@
         </is>
       </c>
       <c r="G238" s="14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H238" s="16" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I238" s="17" t="n">
         <v>8000</v>
@@ -11931,10 +11931,10 @@
         </is>
       </c>
       <c r="G239" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H239" s="6" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I239" s="13" t="n">
         <v>8000</v>
@@ -11978,10 +11978,10 @@
         </is>
       </c>
       <c r="G240" s="14" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H240" s="16" t="n">
-        <v>100000</v>
+        <v>73000</v>
       </c>
       <c r="I240" s="17" t="n">
         <v>4000</v>
@@ -12025,10 +12025,10 @@
         </is>
       </c>
       <c r="G241" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H241" s="6" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I241" s="13" t="n">
         <v>6500</v>
@@ -12072,10 +12072,10 @@
         </is>
       </c>
       <c r="G242" s="14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H242" s="16" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I242" s="17" t="n">
         <v>8000</v>
@@ -12119,10 +12119,10 @@
         </is>
       </c>
       <c r="G243" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H243" s="6" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I243" s="13" t="n">
         <v>6500</v>
@@ -12166,10 +12166,10 @@
         </is>
       </c>
       <c r="G244" s="14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H244" s="16" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I244" s="17" t="n">
         <v>8000</v>
@@ -12213,10 +12213,10 @@
         </is>
       </c>
       <c r="G245" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H245" s="6" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I245" s="13" t="n">
         <v>8000</v>
@@ -12260,10 +12260,10 @@
         </is>
       </c>
       <c r="G246" s="14" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H246" s="16" t="n">
-        <v>100000</v>
+        <v>73000</v>
       </c>
       <c r="I246" s="17" t="n">
         <v>4000</v>
@@ -12542,10 +12542,10 @@
         </is>
       </c>
       <c r="G252" s="14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H252" s="16" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I252" s="17" t="n">
         <v>8000</v>
@@ -12589,10 +12589,10 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H253" s="6" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I253" s="13" t="n">
         <v>8000</v>
@@ -12777,10 +12777,10 @@
         </is>
       </c>
       <c r="G257" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H257" s="6" t="n">
-        <v>250000</v>
+        <v>200000</v>
       </c>
       <c r="I257" s="13" t="n">
         <v>16000</v>
@@ -12824,10 +12824,10 @@
         </is>
       </c>
       <c r="G258" s="14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H258" s="16" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I258" s="17" t="n">
         <v>8000</v>
@@ -12871,10 +12871,10 @@
         </is>
       </c>
       <c r="G259" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H259" s="6" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I259" s="13" t="n">
         <v>8000</v>
@@ -12918,10 +12918,10 @@
         </is>
       </c>
       <c r="G260" s="14" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H260" s="16" t="n">
-        <v>100000</v>
+        <v>73000</v>
       </c>
       <c r="I260" s="17" t="n">
         <v>4000</v>
@@ -12965,10 +12965,10 @@
         </is>
       </c>
       <c r="G261" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H261" s="6" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I261" s="13" t="n">
         <v>8000</v>
@@ -13012,10 +13012,10 @@
         </is>
       </c>
       <c r="G262" s="14" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H262" s="16" t="n">
-        <v>100000</v>
+        <v>73000</v>
       </c>
       <c r="I262" s="17" t="n">
         <v>4000</v>
@@ -13059,10 +13059,10 @@
         </is>
       </c>
       <c r="G263" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H263" s="6" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I263" s="13" t="n">
         <v>7000</v>
@@ -13106,10 +13106,10 @@
         </is>
       </c>
       <c r="G264" s="14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H264" s="16" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I264" s="17" t="n">
         <v>8000</v>
@@ -13151,10 +13151,10 @@
         </is>
       </c>
       <c r="G265" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H265" s="6" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I265" s="13" t="n">
         <v>8000</v>
@@ -13196,10 +13196,10 @@
         </is>
       </c>
       <c r="G266" s="14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H266" s="16" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I266" s="17" t="n">
         <v>8000</v>
@@ -13241,10 +13241,10 @@
         </is>
       </c>
       <c r="G267" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H267" s="6" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I267" s="13" t="n">
         <v>8000</v>
@@ -13421,10 +13421,10 @@
         </is>
       </c>
       <c r="G271" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H271" s="6" t="n">
-        <v>100000</v>
+        <v>73000</v>
       </c>
       <c r="I271" s="13" t="n">
         <v>4000</v>
@@ -13511,10 +13511,10 @@
         </is>
       </c>
       <c r="G273" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H273" s="6" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I273" s="13" t="n">
         <v>8000</v>
@@ -13556,10 +13556,10 @@
         </is>
       </c>
       <c r="G274" s="14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H274" s="16" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I274" s="17" t="n">
         <v>8000</v>
@@ -13601,10 +13601,10 @@
         </is>
       </c>
       <c r="G275" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H275" s="6" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I275" s="13" t="n">
         <v>8000</v>
@@ -13781,10 +13781,10 @@
         </is>
       </c>
       <c r="G279" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H279" s="6" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I279" s="13" t="n">
         <v>8000</v>
@@ -13826,10 +13826,10 @@
         </is>
       </c>
       <c r="G280" s="14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H280" s="16" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I280" s="17" t="n">
         <v>7000</v>
@@ -13871,10 +13871,10 @@
         </is>
       </c>
       <c r="G281" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H281" s="6" t="n">
-        <v>100000</v>
+        <v>73000</v>
       </c>
       <c r="I281" s="13" t="n">
         <v>4000</v>
@@ -13916,10 +13916,10 @@
         </is>
       </c>
       <c r="G282" s="14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H282" s="16" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I282" s="17" t="n">
         <v>8000</v>
@@ -13961,10 +13961,10 @@
         </is>
       </c>
       <c r="G283" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H283" s="6" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I283" s="13" t="n">
         <v>8000</v>
@@ -14051,10 +14051,10 @@
         </is>
       </c>
       <c r="G285" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H285" s="6" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I285" s="13" t="n">
         <v>8000</v>
@@ -14096,10 +14096,10 @@
         </is>
       </c>
       <c r="G286" s="14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H286" s="16" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I286" s="17" t="n">
         <v>8000</v>
@@ -14186,10 +14186,10 @@
         </is>
       </c>
       <c r="G288" s="14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H288" s="16" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I288" s="17" t="n">
         <v>8000</v>
@@ -14231,10 +14231,10 @@
         </is>
       </c>
       <c r="G289" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H289" s="6" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I289" s="13" t="n">
         <v>8000</v>
@@ -14276,10 +14276,10 @@
         </is>
       </c>
       <c r="G290" s="14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H290" s="16" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I290" s="17" t="n">
         <v>8000</v>
@@ -14321,10 +14321,10 @@
         </is>
       </c>
       <c r="G291" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H291" s="6" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I291" s="13" t="n">
         <v>8000</v>
@@ -14366,10 +14366,10 @@
         </is>
       </c>
       <c r="G292" s="14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H292" s="16" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I292" s="17" t="n">
         <v>7000</v>
@@ -14411,10 +14411,10 @@
         </is>
       </c>
       <c r="G293" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H293" s="6" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I293" s="13" t="n">
         <v>8000</v>
@@ -14591,10 +14591,10 @@
         </is>
       </c>
       <c r="G297" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H297" s="6" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I297" s="13" t="n">
         <v>8000</v>
@@ -14636,10 +14636,10 @@
         </is>
       </c>
       <c r="G298" s="14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H298" s="16" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I298" s="17" t="n">
         <v>8000</v>
@@ -14726,10 +14726,10 @@
         </is>
       </c>
       <c r="G300" s="14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H300" s="16" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I300" s="17" t="n">
         <v>8000</v>
@@ -14771,10 +14771,10 @@
         </is>
       </c>
       <c r="G301" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H301" s="6" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I301" s="13" t="n">
         <v>8000</v>
@@ -14816,10 +14816,10 @@
         </is>
       </c>
       <c r="G302" s="14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H302" s="16" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I302" s="17" t="n">
         <v>8000</v>
@@ -14861,10 +14861,10 @@
         </is>
       </c>
       <c r="G303" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H303" s="6" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I303" s="13" t="n">
         <v>8000</v>
@@ -14906,10 +14906,10 @@
         </is>
       </c>
       <c r="G304" s="14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H304" s="16" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I304" s="17" t="n">
         <v>8000</v>
@@ -14996,10 +14996,10 @@
         </is>
       </c>
       <c r="G306" s="14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H306" s="16" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I306" s="17" t="n">
         <v>8000</v>
@@ -15041,10 +15041,10 @@
         </is>
       </c>
       <c r="G307" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H307" s="6" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I307" s="13" t="n">
         <v>8000</v>
@@ -15086,10 +15086,10 @@
         </is>
       </c>
       <c r="G308" s="14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H308" s="16" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I308" s="17" t="n">
         <v>8000</v>
@@ -15131,10 +15131,10 @@
         </is>
       </c>
       <c r="G309" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H309" s="6" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I309" s="13" t="n">
         <v>8000</v>
@@ -15176,10 +15176,10 @@
         </is>
       </c>
       <c r="G310" s="14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H310" s="16" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I310" s="17" t="n">
         <v>8000</v>
@@ -15221,10 +15221,10 @@
         </is>
       </c>
       <c r="G311" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H311" s="6" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I311" s="13" t="n">
         <v>8000</v>
@@ -15266,10 +15266,10 @@
         </is>
       </c>
       <c r="G312" s="14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H312" s="16" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I312" s="17" t="n">
         <v>8000</v>
@@ -15311,10 +15311,10 @@
         </is>
       </c>
       <c r="G313" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H313" s="6" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I313" s="13" t="n">
         <v>8000</v>
@@ -15356,10 +15356,10 @@
         </is>
       </c>
       <c r="G314" s="14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H314" s="16" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I314" s="17" t="n">
         <v>8000</v>
@@ -15401,10 +15401,10 @@
         </is>
       </c>
       <c r="G315" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H315" s="6" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I315" s="13" t="n">
         <v>8000</v>
@@ -15446,10 +15446,10 @@
         </is>
       </c>
       <c r="G316" s="14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H316" s="16" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I316" s="17" t="n">
         <v>8000</v>
@@ -15491,10 +15491,10 @@
         </is>
       </c>
       <c r="G317" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H317" s="6" t="n">
-        <v>100000</v>
+        <v>73000</v>
       </c>
       <c r="I317" s="13" t="n">
         <v>4000</v>
@@ -15536,10 +15536,10 @@
         </is>
       </c>
       <c r="G318" s="14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H318" s="16" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I318" s="17" t="n">
         <v>8000</v>
@@ -15581,10 +15581,10 @@
         </is>
       </c>
       <c r="G319" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H319" s="6" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I319" s="13" t="n">
         <v>8000</v>
@@ -15626,10 +15626,10 @@
         </is>
       </c>
       <c r="G320" s="14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H320" s="16" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I320" s="17" t="n">
         <v>8000</v>
@@ -15671,10 +15671,10 @@
         </is>
       </c>
       <c r="G321" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H321" s="6" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I321" s="13" t="n">
         <v>8000</v>
@@ -15758,13 +15758,13 @@
         <v>105</v>
       </c>
       <c r="C3" s="6" t="n">
-        <v>17800000</v>
+        <v>13911000</v>
       </c>
       <c r="D3" t="n">
         <v>32.9</v>
       </c>
       <c r="E3" t="n">
-        <v>31.8</v>
+        <v>30.8</v>
       </c>
     </row>
     <row r="4">
@@ -15777,13 +15777,13 @@
         <v>47</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>9700000</v>
+        <v>8573000</v>
       </c>
       <c r="D4" t="n">
         <v>14.7</v>
       </c>
       <c r="E4" t="n">
-        <v>17.3</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5">
@@ -15796,13 +15796,13 @@
         <v>35</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>6850000</v>
+        <v>5573000</v>
       </c>
       <c r="D5" t="n">
         <v>11</v>
       </c>
       <c r="E5" t="n">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
     </row>
     <row r="6">
@@ -15815,13 +15815,13 @@
         <v>59</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>9600000</v>
+        <v>7219000</v>
       </c>
       <c r="D6" t="n">
         <v>18.5</v>
       </c>
       <c r="E6" t="n">
-        <v>17.1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
@@ -15834,13 +15834,13 @@
         <v>61</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>10350000</v>
+        <v>8600000</v>
       </c>
       <c r="D7" t="n">
         <v>19.1</v>
       </c>
       <c r="E7" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8">
@@ -15853,13 +15853,13 @@
         <v>12</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>1723000</v>
+        <v>1273000</v>
       </c>
       <c r="D8" t="n">
         <v>3.8</v>
       </c>
       <c r="E8" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="9">
@@ -15872,7 +15872,7 @@
         <v>319</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>56023000</v>
+        <v>45149000</v>
       </c>
     </row>
   </sheetData>
@@ -15935,16 +15935,16 @@
         <v>6</v>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C3" s="6" t="n">
         <v>73000</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>73000</v>
+        <v>949000</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="4">
@@ -15952,16 +15952,16 @@
         <v>12</v>
       </c>
       <c r="B4" t="n">
-        <v>29</v>
+        <v>182</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>100000</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>2900000</v>
+        <v>18200000</v>
       </c>
       <c r="E4" t="n">
-        <v>9.1</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="5">
@@ -15969,16 +15969,16 @@
         <v>20</v>
       </c>
       <c r="B5" t="n">
-        <v>181</v>
+        <v>31</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>150000</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>27150000</v>
+        <v>4650000</v>
       </c>
       <c r="E5" t="n">
-        <v>56.7</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -15986,16 +15986,16 @@
         <v>30</v>
       </c>
       <c r="B6" t="n">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>200000</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>4400000</v>
+        <v>7600000</v>
       </c>
       <c r="E6" t="n">
-        <v>6.9</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="7">
@@ -16003,16 +16003,16 @@
         <v>50</v>
       </c>
       <c r="B7" t="n">
-        <v>86</v>
+        <v>55</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>250000</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>21500000</v>
+        <v>13750000</v>
       </c>
       <c r="E7" t="n">
-        <v>27</v>
+        <v>17.2</v>
       </c>
     </row>
     <row r="8">
@@ -16025,7 +16025,7 @@
         <v>319</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>56023000</v>
+        <v>45149000</v>
       </c>
     </row>
   </sheetData>

--- a/budget_shelters_v2.xlsx
+++ b/budget_shelters_v2.xlsx
@@ -493,7 +493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -558,7 +558,7 @@
         <v>73000</v>
       </c>
       <c r="C6" t="n">
-        <v>13</v>
+        <v>96</v>
       </c>
       <c r="D6" s="6">
         <f>B6*C6</f>
@@ -573,7 +573,7 @@
         <v>100000</v>
       </c>
       <c r="C7" t="n">
-        <v>182</v>
+        <v>95</v>
       </c>
       <c r="D7" s="6">
         <f>B7*C7</f>
@@ -588,7 +588,7 @@
         <v>150000</v>
       </c>
       <c r="C8" t="n">
-        <v>31</v>
+        <v>128</v>
       </c>
       <c r="D8" s="6">
         <f>B8*C8</f>
@@ -596,147 +596,117 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
-        <v>30</v>
-      </c>
-      <c r="B9" s="5" t="n">
-        <v>200000</v>
-      </c>
-      <c r="C9" t="n">
-        <v>38</v>
-      </c>
-      <c r="D9" s="6">
-        <f>B9*C9</f>
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>עלות הון סה"כ</t>
+        </is>
+      </c>
+      <c r="D9" s="7">
+        <f>D6+D7+D8</f>
         <v/>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>50</v>
-      </c>
-      <c r="B10" s="5" t="n">
-        <v>250000</v>
-      </c>
-      <c r="C10" t="n">
-        <v>55</v>
-      </c>
-      <c r="D10" s="6">
-        <f>B10*C10</f>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>פרמטרים נוספים (ניתן לשינוי)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>רזרבה / אי-וודאות (%)</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>עלות תחזוקה שנתית לכל מיגונית (₪)</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>סיכום תקציבי</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>מספר מיגוניות</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>עלות הון (ללא מע"מ)</t>
+        </is>
+      </c>
+      <c r="B17" s="6">
+        <f>D9</f>
         <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>עלות הון סה"כ</t>
-        </is>
-      </c>
-      <c r="D11" s="7">
-        <f>D6+D7+D8+D9+D10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>פרמטרים נוספים (ניתן לשינוי)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>רזרבה / אי-וודאות (%)</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>עלות תחזוקה שנתית לכל מיגונית (₪)</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="n">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>סיכום תקציבי</t>
-        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>מספר מיגוניות</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>319</v>
+          <t>רזרבה</t>
+        </is>
+      </c>
+      <c r="B18" s="6">
+        <f>D9*B12/100</f>
+        <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>עלות הון (ללא מע"מ)</t>
-        </is>
-      </c>
-      <c r="B19" s="6">
-        <f>D11</f>
+          <t>עלות הון כולל רזרבה</t>
+        </is>
+      </c>
+      <c r="B19" s="7">
+        <f>D9*(1+B12/100)</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>רזרבה</t>
+          <t>עלות תחזוקה שנתית (319 מיגוניות)</t>
         </is>
       </c>
       <c r="B20" s="6">
-        <f>D11*B14/100</f>
+        <f>B13*319</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>עלות הון כולל רזרבה</t>
+          <t>עלות כוללת ל-10 שנים</t>
         </is>
       </c>
       <c r="B21" s="7">
-        <f>D11*(1+B14/100)</f>
+        <f>D9*(1+B12/100)+B13*319*10</f>
         <v/>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>עלות תחזוקה שנתית (319 מיגוניות)</t>
-        </is>
-      </c>
-      <c r="B22" s="6">
-        <f>B15*319</f>
-        <v/>
-      </c>
-    </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>עלות כוללת ל-10 שנים</t>
-        </is>
-      </c>
-      <c r="B23" s="7">
-        <f>D11*(1+B14/100)+B15*319*10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="9" t="inlineStr">
+      <c r="A23" s="9" t="inlineStr">
         <is>
           <t>הערות: עלויות ללא מע"מ. מבוסס על אלגוריתם Gonzalez k-center | תקן 5 דקות | 319 מיגוניות | ישראל בלבד (קו ירוק 1967) | קיבולת מחושבת לפי תנועה בשעת שיא בזמן מלחמה (10% מתנועה רגילה)</t>
         </is>
@@ -875,10 +845,10 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>100000</v>
+        <v>73000</v>
       </c>
       <c r="I3" s="13" t="n">
         <v>8000</v>
@@ -922,10 +892,10 @@
         </is>
       </c>
       <c r="G4" s="14" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H4" s="16" t="n">
-        <v>100000</v>
+        <v>73000</v>
       </c>
       <c r="I4" s="17" t="n">
         <v>9000</v>
@@ -969,10 +939,10 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>200000</v>
+        <v>150000</v>
       </c>
       <c r="I5" s="13" t="n">
         <v>20000</v>
@@ -1016,10 +986,10 @@
         </is>
       </c>
       <c r="G6" s="14" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H6" s="16" t="n">
-        <v>200000</v>
+        <v>150000</v>
       </c>
       <c r="I6" s="17" t="n">
         <v>20000</v>
@@ -1110,10 +1080,10 @@
         </is>
       </c>
       <c r="G8" s="14" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H8" s="16" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="I8" s="17" t="n">
         <v>18000</v>
@@ -1157,10 +1127,10 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>150000</v>
+        <v>73000</v>
       </c>
       <c r="I9" s="13" t="n">
         <v>4000</v>
@@ -1204,10 +1174,10 @@
         </is>
       </c>
       <c r="G10" s="14" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="H10" s="16" t="n">
-        <v>200000</v>
+        <v>73000</v>
       </c>
       <c r="I10" s="17" t="n">
         <v>8000</v>
@@ -1251,10 +1221,10 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>100000</v>
+        <v>73000</v>
       </c>
       <c r="I11" s="13" t="n">
         <v>9000</v>
@@ -1298,10 +1268,10 @@
         </is>
       </c>
       <c r="G12" s="14" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="H12" s="16" t="n">
-        <v>150000</v>
+        <v>73000</v>
       </c>
       <c r="I12" s="17" t="n">
         <v>8000</v>
@@ -1345,10 +1315,10 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>200000</v>
+        <v>73000</v>
       </c>
       <c r="I13" s="13" t="n">
         <v>8000</v>
@@ -1392,10 +1362,10 @@
         </is>
       </c>
       <c r="G14" s="14" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H14" s="16" t="n">
-        <v>100000</v>
+        <v>73000</v>
       </c>
       <c r="I14" s="17" t="n">
         <v>7000</v>
@@ -1439,10 +1409,10 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="I15" s="13" t="n">
         <v>30000</v>
@@ -1486,10 +1456,10 @@
         </is>
       </c>
       <c r="G16" s="14" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H16" s="16" t="n">
-        <v>100000</v>
+        <v>73000</v>
       </c>
       <c r="I16" s="17" t="n">
         <v>8000</v>
@@ -1533,10 +1503,10 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="I17" s="13" t="n">
         <v>40000</v>
@@ -1580,10 +1550,10 @@
         </is>
       </c>
       <c r="G18" s="14" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H18" s="16" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="I18" s="17" t="n">
         <v>18000</v>
@@ -1627,10 +1597,10 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>200000</v>
+        <v>73000</v>
       </c>
       <c r="I19" s="13" t="n">
         <v>8000</v>
@@ -1674,10 +1644,10 @@
         </is>
       </c>
       <c r="G20" s="14" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H20" s="16" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="I20" s="17" t="n">
         <v>13000</v>
@@ -1721,10 +1691,10 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>100000</v>
+        <v>73000</v>
       </c>
       <c r="I21" s="13" t="n">
         <v>8000</v>
@@ -1768,10 +1738,10 @@
         </is>
       </c>
       <c r="G22" s="14" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="H22" s="16" t="n">
-        <v>200000</v>
+        <v>73000</v>
       </c>
       <c r="I22" s="17" t="n">
         <v>8000</v>
@@ -1815,10 +1785,10 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>200000</v>
+        <v>73000</v>
       </c>
       <c r="I23" s="13" t="n">
         <v>8000</v>
@@ -1862,10 +1832,10 @@
         </is>
       </c>
       <c r="G24" s="14" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H24" s="16" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="I24" s="17" t="n">
         <v>40000</v>
@@ -1909,10 +1879,10 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>100000</v>
+        <v>73000</v>
       </c>
       <c r="I25" s="13" t="n">
         <v>8000</v>
@@ -1956,10 +1926,10 @@
         </is>
       </c>
       <c r="G26" s="14" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H26" s="16" t="n">
-        <v>100000</v>
+        <v>73000</v>
       </c>
       <c r="I26" s="17" t="n">
         <v>8000</v>
@@ -2003,10 +1973,10 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>200000</v>
+        <v>73000</v>
       </c>
       <c r="I27" s="13" t="n">
         <v>8000</v>
@@ -2050,10 +2020,10 @@
         </is>
       </c>
       <c r="G28" s="14" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H28" s="16" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="I28" s="17" t="n">
         <v>40000</v>
@@ -2097,10 +2067,10 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>200000</v>
+        <v>73000</v>
       </c>
       <c r="I29" s="13" t="n">
         <v>8000</v>
@@ -2144,10 +2114,10 @@
         </is>
       </c>
       <c r="G30" s="14" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H30" s="16" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="I30" s="17" t="n">
         <v>40000</v>
@@ -2191,10 +2161,10 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="I31" s="13" t="n">
         <v>40000</v>
@@ -2238,10 +2208,10 @@
         </is>
       </c>
       <c r="G32" s="14" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H32" s="16" t="n">
-        <v>100000</v>
+        <v>73000</v>
       </c>
       <c r="I32" s="17" t="n">
         <v>7000</v>
@@ -2285,10 +2255,10 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>200000</v>
+        <v>73000</v>
       </c>
       <c r="I33" s="13" t="n">
         <v>8000</v>
@@ -2332,10 +2302,10 @@
         </is>
       </c>
       <c r="G34" s="14" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="H34" s="16" t="n">
-        <v>200000</v>
+        <v>73000</v>
       </c>
       <c r="I34" s="17" t="n">
         <v>8000</v>
@@ -2379,10 +2349,10 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>100000</v>
+        <v>73000</v>
       </c>
       <c r="I35" s="13" t="n">
         <v>8000</v>
@@ -2426,10 +2396,10 @@
         </is>
       </c>
       <c r="G36" s="14" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H36" s="16" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="I36" s="17" t="n">
         <v>30000</v>
@@ -2473,10 +2443,10 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>100000</v>
+        <v>73000</v>
       </c>
       <c r="I37" s="13" t="n">
         <v>7000</v>
@@ -2518,10 +2488,10 @@
         </is>
       </c>
       <c r="G38" s="14" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H38" s="16" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="I38" s="17" t="n">
         <v>13000</v>
@@ -2565,10 +2535,10 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="I39" s="13" t="n">
         <v>13000</v>
@@ -2612,10 +2582,10 @@
         </is>
       </c>
       <c r="G40" s="14" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H40" s="16" t="n">
-        <v>200000</v>
+        <v>150000</v>
       </c>
       <c r="I40" s="17" t="n">
         <v>20000</v>
@@ -2659,10 +2629,10 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>200000</v>
+        <v>73000</v>
       </c>
       <c r="I41" s="13" t="n">
         <v>8000</v>
@@ -2706,10 +2676,10 @@
         </is>
       </c>
       <c r="G42" s="14" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H42" s="16" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="I42" s="17" t="n">
         <v>30000</v>
@@ -2753,10 +2723,10 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="I43" s="13" t="n">
         <v>40000</v>
@@ -2800,10 +2770,10 @@
         </is>
       </c>
       <c r="G44" s="14" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H44" s="16" t="n">
-        <v>100000</v>
+        <v>73000</v>
       </c>
       <c r="I44" s="17" t="n">
         <v>8000</v>
@@ -2847,10 +2817,10 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>200000</v>
+        <v>73000</v>
       </c>
       <c r="I45" s="13" t="n">
         <v>8000</v>
@@ -2894,10 +2864,10 @@
         </is>
       </c>
       <c r="G46" s="14" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="H46" s="16" t="n">
-        <v>150000</v>
+        <v>73000</v>
       </c>
       <c r="I46" s="17" t="n">
         <v>8000</v>
@@ -2941,10 +2911,10 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>150000</v>
+        <v>73000</v>
       </c>
       <c r="I47" s="13" t="n">
         <v>8000</v>
@@ -2988,10 +2958,10 @@
         </is>
       </c>
       <c r="G48" s="14" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="H48" s="16" t="n">
-        <v>200000</v>
+        <v>73000</v>
       </c>
       <c r="I48" s="17" t="n">
         <v>8000</v>
@@ -3035,10 +3005,10 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H49" s="6" t="n">
-        <v>100000</v>
+        <v>73000</v>
       </c>
       <c r="I49" s="13" t="n">
         <v>8000</v>
@@ -3082,10 +3052,10 @@
         </is>
       </c>
       <c r="G50" s="14" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H50" s="16" t="n">
-        <v>100000</v>
+        <v>73000</v>
       </c>
       <c r="I50" s="17" t="n">
         <v>9000</v>
@@ -3129,10 +3099,10 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H51" s="6" t="n">
-        <v>100000</v>
+        <v>73000</v>
       </c>
       <c r="I51" s="13" t="n">
         <v>7000</v>
@@ -3176,10 +3146,10 @@
         </is>
       </c>
       <c r="G52" s="14" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H52" s="16" t="n">
-        <v>100000</v>
+        <v>73000</v>
       </c>
       <c r="I52" s="17" t="n">
         <v>8500</v>
@@ -3223,10 +3193,10 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H53" s="6" t="n">
-        <v>100000</v>
+        <v>73000</v>
       </c>
       <c r="I53" s="13" t="n">
         <v>9000</v>
@@ -3270,10 +3240,10 @@
         </is>
       </c>
       <c r="G54" s="14" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H54" s="16" t="n">
-        <v>200000</v>
+        <v>150000</v>
       </c>
       <c r="I54" s="17" t="n">
         <v>15000</v>
@@ -3317,10 +3287,10 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H55" s="6" t="n">
-        <v>200000</v>
+        <v>150000</v>
       </c>
       <c r="I55" s="13" t="n">
         <v>20000</v>
@@ -3364,10 +3334,10 @@
         </is>
       </c>
       <c r="G56" s="14" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H56" s="16" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="I56" s="17" t="n">
         <v>18000</v>
@@ -3411,10 +3381,10 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H57" s="6" t="n">
-        <v>100000</v>
+        <v>73000</v>
       </c>
       <c r="I57" s="13" t="n">
         <v>8500</v>
@@ -3458,10 +3428,10 @@
         </is>
       </c>
       <c r="G58" s="14" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H58" s="16" t="n">
-        <v>100000</v>
+        <v>73000</v>
       </c>
       <c r="I58" s="17" t="n">
         <v>8000</v>
@@ -3505,10 +3475,10 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H59" s="6" t="n">
-        <v>100000</v>
+        <v>73000</v>
       </c>
       <c r="I59" s="13" t="n">
         <v>8000</v>
@@ -3550,10 +3520,10 @@
         </is>
       </c>
       <c r="G60" s="14" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H60" s="16" t="n">
-        <v>100000</v>
+        <v>73000</v>
       </c>
       <c r="I60" s="17" t="n">
         <v>7000</v>
@@ -3597,10 +3567,10 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="H61" s="6" t="n">
-        <v>200000</v>
+        <v>73000</v>
       </c>
       <c r="I61" s="13" t="n">
         <v>8000</v>
@@ -3644,10 +3614,10 @@
         </is>
       </c>
       <c r="G62" s="14" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H62" s="16" t="n">
-        <v>100000</v>
+        <v>73000</v>
       </c>
       <c r="I62" s="17" t="n">
         <v>9000</v>
@@ -3738,10 +3708,10 @@
         </is>
       </c>
       <c r="G64" s="14" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H64" s="16" t="n">
-        <v>100000</v>
+        <v>73000</v>
       </c>
       <c r="I64" s="17" t="n">
         <v>7000</v>
@@ -3832,10 +3802,10 @@
         </is>
       </c>
       <c r="G66" s="14" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H66" s="16" t="n">
-        <v>100000</v>
+        <v>73000</v>
       </c>
       <c r="I66" s="17" t="n">
         <v>7000</v>
@@ -3877,10 +3847,10 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H67" s="6" t="n">
-        <v>100000</v>
+        <v>73000</v>
       </c>
       <c r="I67" s="13" t="n">
         <v>8000</v>
@@ -3924,10 +3894,10 @@
         </is>
       </c>
       <c r="G68" s="14" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H68" s="16" t="n">
-        <v>100000</v>
+        <v>73000</v>
       </c>
       <c r="I68" s="17" t="n">
         <v>8000</v>
@@ -3971,10 +3941,10 @@
         </is>
       </c>
       <c r="G69" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H69" s="6" t="n">
-        <v>100000</v>
+        <v>73000</v>
       </c>
       <c r="I69" s="13" t="n">
         <v>8000</v>
@@ -4018,10 +3988,10 @@
         </is>
       </c>
       <c r="G70" s="14" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H70" s="16" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="I70" s="17" t="n">
         <v>30000</v>
@@ -4065,10 +4035,10 @@
         </is>
       </c>
       <c r="G71" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="H71" s="6" t="n">
-        <v>200000</v>
+        <v>73000</v>
       </c>
       <c r="I71" s="13" t="n">
         <v>8000</v>
@@ -4112,10 +4082,10 @@
         </is>
       </c>
       <c r="G72" s="14" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H72" s="16" t="n">
-        <v>100000</v>
+        <v>73000</v>
       </c>
       <c r="I72" s="17" t="n">
         <v>8000</v>
@@ -4157,10 +4127,10 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H73" s="6" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="I73" s="13" t="n">
         <v>40000</v>
@@ -4204,10 +4174,10 @@
         </is>
       </c>
       <c r="G74" s="14" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="H74" s="16" t="n">
-        <v>150000</v>
+        <v>73000</v>
       </c>
       <c r="I74" s="17" t="n">
         <v>8000</v>
@@ -4251,10 +4221,10 @@
         </is>
       </c>
       <c r="G75" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H75" s="6" t="n">
-        <v>100000</v>
+        <v>73000</v>
       </c>
       <c r="I75" s="13" t="n">
         <v>4000</v>
@@ -4345,10 +4315,10 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H77" s="6" t="n">
-        <v>100000</v>
+        <v>73000</v>
       </c>
       <c r="I77" s="13" t="n">
         <v>8000</v>
@@ -4392,10 +4362,10 @@
         </is>
       </c>
       <c r="G78" s="14" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H78" s="16" t="n">
-        <v>200000</v>
+        <v>150000</v>
       </c>
       <c r="I78" s="17" t="n">
         <v>18000</v>
@@ -4439,10 +4409,10 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H79" s="6" t="n">
-        <v>200000</v>
+        <v>150000</v>
       </c>
       <c r="I79" s="13" t="n">
         <v>20000</v>
@@ -4486,10 +4456,10 @@
         </is>
       </c>
       <c r="G80" s="14" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H80" s="16" t="n">
-        <v>100000</v>
+        <v>73000</v>
       </c>
       <c r="I80" s="17" t="n">
         <v>8000</v>
@@ -4533,10 +4503,10 @@
         </is>
       </c>
       <c r="G81" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="H81" s="6" t="n">
-        <v>150000</v>
+        <v>73000</v>
       </c>
       <c r="I81" s="13" t="n">
         <v>8000</v>
@@ -4580,10 +4550,10 @@
         </is>
       </c>
       <c r="G82" s="14" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="H82" s="16" t="n">
-        <v>150000</v>
+        <v>73000</v>
       </c>
       <c r="I82" s="17" t="n">
         <v>8000</v>
@@ -4627,10 +4597,10 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H83" s="6" t="n">
-        <v>100000</v>
+        <v>73000</v>
       </c>
       <c r="I83" s="13" t="n">
         <v>8000</v>
@@ -4674,10 +4644,10 @@
         </is>
       </c>
       <c r="G84" s="14" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H84" s="16" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="I84" s="17" t="n">
         <v>18000</v>
@@ -4721,10 +4691,10 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H85" s="6" t="n">
-        <v>100000</v>
+        <v>73000</v>
       </c>
       <c r="I85" s="13" t="n">
         <v>7000</v>
@@ -4766,10 +4736,10 @@
         </is>
       </c>
       <c r="G86" s="14" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="H86" s="16" t="n">
-        <v>150000</v>
+        <v>73000</v>
       </c>
       <c r="I86" s="17" t="n">
         <v>8000</v>
@@ -4813,10 +4783,10 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H87" s="6" t="n">
-        <v>100000</v>
+        <v>73000</v>
       </c>
       <c r="I87" s="13" t="n">
         <v>8000</v>
@@ -4860,10 +4830,10 @@
         </is>
       </c>
       <c r="G88" s="14" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H88" s="16" t="n">
-        <v>100000</v>
+        <v>73000</v>
       </c>
       <c r="I88" s="17" t="n">
         <v>4000</v>
@@ -4954,10 +4924,10 @@
         </is>
       </c>
       <c r="G90" s="14" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H90" s="16" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="I90" s="17" t="n">
         <v>22000</v>
@@ -5001,10 +4971,10 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H91" s="6" t="n">
-        <v>100000</v>
+        <v>73000</v>
       </c>
       <c r="I91" s="13" t="n">
         <v>8000</v>
@@ -5048,10 +5018,10 @@
         </is>
       </c>
       <c r="G92" s="14" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H92" s="16" t="n">
-        <v>100000</v>
+        <v>73000</v>
       </c>
       <c r="I92" s="17" t="n">
         <v>8000</v>
@@ -5095,10 +5065,10 @@
         </is>
       </c>
       <c r="G93" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H93" s="6" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="I93" s="13" t="n">
         <v>13000</v>
@@ -5142,10 +5112,10 @@
         </is>
       </c>
       <c r="G94" s="14" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H94" s="16" t="n">
-        <v>200000</v>
+        <v>150000</v>
       </c>
       <c r="I94" s="17" t="n">
         <v>18000</v>
@@ -5189,10 +5159,10 @@
         </is>
       </c>
       <c r="G95" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H95" s="6" t="n">
-        <v>100000</v>
+        <v>73000</v>
       </c>
       <c r="I95" s="13" t="n">
         <v>8000</v>
@@ -5236,10 +5206,10 @@
         </is>
       </c>
       <c r="G96" s="14" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H96" s="16" t="n">
-        <v>100000</v>
+        <v>73000</v>
       </c>
       <c r="I96" s="17" t="n">
         <v>4000</v>
@@ -5283,10 +5253,10 @@
         </is>
       </c>
       <c r="G97" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H97" s="6" t="n">
-        <v>100000</v>
+        <v>73000</v>
       </c>
       <c r="I97" s="13" t="n">
         <v>8000</v>
@@ -5377,10 +5347,10 @@
         </is>
       </c>
       <c r="G99" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H99" s="6" t="n">
-        <v>100000</v>
+        <v>73000</v>
       </c>
       <c r="I99" s="13" t="n">
         <v>8000</v>
@@ -5424,10 +5394,10 @@
         </is>
       </c>
       <c r="G100" s="14" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H100" s="16" t="n">
-        <v>100000</v>
+        <v>73000</v>
       </c>
       <c r="I100" s="17" t="n">
         <v>8000</v>
@@ -5471,10 +5441,10 @@
         </is>
       </c>
       <c r="G101" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H101" s="6" t="n">
-        <v>200000</v>
+        <v>150000</v>
       </c>
       <c r="I101" s="13" t="n">
         <v>13000</v>
@@ -5518,10 +5488,10 @@
         </is>
       </c>
       <c r="G102" s="14" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H102" s="16" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="I102" s="17" t="n">
         <v>14000</v>
@@ -5565,10 +5535,10 @@
         </is>
       </c>
       <c r="G103" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H103" s="6" t="n">
-        <v>100000</v>
+        <v>73000</v>
       </c>
       <c r="I103" s="13" t="n">
         <v>8000</v>
@@ -5704,10 +5674,10 @@
         </is>
       </c>
       <c r="G106" s="14" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H106" s="16" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="I106" s="17" t="n">
         <v>22000</v>
@@ -5798,10 +5768,10 @@
         </is>
       </c>
       <c r="G108" s="14" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H108" s="16" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="I108" s="17" t="n">
         <v>35000</v>
@@ -5890,10 +5860,10 @@
         </is>
       </c>
       <c r="G110" s="14" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H110" s="16" t="n">
-        <v>100000</v>
+        <v>73000</v>
       </c>
       <c r="I110" s="17" t="n">
         <v>4000</v>
@@ -6031,10 +6001,10 @@
         </is>
       </c>
       <c r="G113" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H113" s="6" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="I113" s="13" t="n">
         <v>13000</v>
@@ -6078,10 +6048,10 @@
         </is>
       </c>
       <c r="G114" s="14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H114" s="16" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I114" s="17" t="n">
         <v>8000</v>
@@ -6266,10 +6236,10 @@
         </is>
       </c>
       <c r="G118" s="14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H118" s="16" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I118" s="17" t="n">
         <v>8000</v>
@@ -6454,10 +6424,10 @@
         </is>
       </c>
       <c r="G122" s="14" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H122" s="16" t="n">
-        <v>100000</v>
+        <v>73000</v>
       </c>
       <c r="I122" s="17" t="n">
         <v>7000</v>
@@ -6548,10 +6518,10 @@
         </is>
       </c>
       <c r="G124" s="14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H124" s="16" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I124" s="17" t="n">
         <v>8000</v>
@@ -6783,10 +6753,10 @@
         </is>
       </c>
       <c r="G129" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H129" s="6" t="n">
-        <v>100000</v>
+        <v>73000</v>
       </c>
       <c r="I129" s="13" t="n">
         <v>4000</v>
@@ -6971,10 +6941,10 @@
         </is>
       </c>
       <c r="G133" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H133" s="6" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="I133" s="13" t="n">
         <v>24000</v>
@@ -7065,10 +7035,10 @@
         </is>
       </c>
       <c r="G135" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H135" s="6" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="I135" s="13" t="n">
         <v>22000</v>
@@ -7253,10 +7223,10 @@
         </is>
       </c>
       <c r="G139" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H139" s="6" t="n">
-        <v>200000</v>
+        <v>150000</v>
       </c>
       <c r="I139" s="13" t="n">
         <v>20000</v>
@@ -7300,10 +7270,10 @@
         </is>
       </c>
       <c r="G140" s="14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H140" s="16" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="I140" s="17" t="n">
         <v>8000</v>
@@ -7394,10 +7364,10 @@
         </is>
       </c>
       <c r="G142" s="14" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H142" s="16" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="I142" s="17" t="n">
         <v>18000</v>
@@ -7629,10 +7599,10 @@
         </is>
       </c>
       <c r="G147" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H147" s="6" t="n">
-        <v>200000</v>
+        <v>150000</v>
       </c>
       <c r="I147" s="13" t="n">
         <v>19000</v>
@@ -7676,10 +7646,10 @@
         </is>
       </c>
       <c r="G148" s="14" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H148" s="16" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="I148" s="17" t="n">
         <v>22000</v>
@@ -7770,10 +7740,10 @@
         </is>
       </c>
       <c r="G150" s="14" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H150" s="16" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="I150" s="17" t="n">
         <v>24000</v>
@@ -7862,10 +7832,10 @@
         </is>
       </c>
       <c r="G152" s="14" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H152" s="16" t="n">
-        <v>200000</v>
+        <v>150000</v>
       </c>
       <c r="I152" s="17" t="n">
         <v>13000</v>
@@ -7956,10 +7926,10 @@
         </is>
       </c>
       <c r="G154" s="14" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H154" s="16" t="n">
-        <v>200000</v>
+        <v>150000</v>
       </c>
       <c r="I154" s="17" t="n">
         <v>13000</v>
@@ -8050,10 +8020,10 @@
         </is>
       </c>
       <c r="G156" s="14" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H156" s="16" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="I156" s="17" t="n">
         <v>24000</v>
@@ -8144,10 +8114,10 @@
         </is>
       </c>
       <c r="G158" s="14" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H158" s="16" t="n">
-        <v>200000</v>
+        <v>150000</v>
       </c>
       <c r="I158" s="17" t="n">
         <v>18000</v>
@@ -8191,10 +8161,10 @@
         </is>
       </c>
       <c r="G159" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H159" s="6" t="n">
-        <v>200000</v>
+        <v>150000</v>
       </c>
       <c r="I159" s="13" t="n">
         <v>19000</v>
@@ -8332,10 +8302,10 @@
         </is>
       </c>
       <c r="G162" s="14" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H162" s="16" t="n">
-        <v>100000</v>
+        <v>73000</v>
       </c>
       <c r="I162" s="17" t="n">
         <v>4000</v>
@@ -8473,10 +8443,10 @@
         </is>
       </c>
       <c r="G165" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H165" s="6" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="I165" s="13" t="n">
         <v>22000</v>
@@ -8567,10 +8537,10 @@
         </is>
       </c>
       <c r="G167" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H167" s="6" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="I167" s="13" t="n">
         <v>24000</v>
@@ -8614,10 +8584,10 @@
         </is>
       </c>
       <c r="G168" s="14" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H168" s="16" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="I168" s="17" t="n">
         <v>22000</v>
@@ -9031,10 +9001,10 @@
         </is>
       </c>
       <c r="G177" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H177" s="6" t="n">
-        <v>100000</v>
+        <v>73000</v>
       </c>
       <c r="I177" s="13" t="n">
         <v>6500</v>
@@ -9078,10 +9048,10 @@
         </is>
       </c>
       <c r="G178" s="14" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H178" s="16" t="n">
-        <v>100000</v>
+        <v>73000</v>
       </c>
       <c r="I178" s="17" t="n">
         <v>4000</v>
@@ -9219,10 +9189,10 @@
         </is>
       </c>
       <c r="G181" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H181" s="6" t="n">
-        <v>200000</v>
+        <v>150000</v>
       </c>
       <c r="I181" s="13" t="n">
         <v>14000</v>
@@ -9360,10 +9330,10 @@
         </is>
       </c>
       <c r="G184" s="14" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H184" s="16" t="n">
-        <v>100000</v>
+        <v>73000</v>
       </c>
       <c r="I184" s="17" t="n">
         <v>4000</v>
@@ -9501,10 +9471,10 @@
         </is>
       </c>
       <c r="G187" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H187" s="6" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="I187" s="13" t="n">
         <v>22000</v>
@@ -9640,10 +9610,10 @@
         </is>
       </c>
       <c r="G190" s="14" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H190" s="16" t="n">
-        <v>100000</v>
+        <v>73000</v>
       </c>
       <c r="I190" s="17" t="n">
         <v>4000</v>
@@ -9781,10 +9751,10 @@
         </is>
       </c>
       <c r="G193" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H193" s="6" t="n">
-        <v>200000</v>
+        <v>150000</v>
       </c>
       <c r="I193" s="13" t="n">
         <v>16000</v>
@@ -9828,10 +9798,10 @@
         </is>
       </c>
       <c r="G194" s="14" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H194" s="16" t="n">
-        <v>200000</v>
+        <v>150000</v>
       </c>
       <c r="I194" s="17" t="n">
         <v>13000</v>
@@ -9875,10 +9845,10 @@
         </is>
       </c>
       <c r="G195" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H195" s="6" t="n">
-        <v>200000</v>
+        <v>150000</v>
       </c>
       <c r="I195" s="13" t="n">
         <v>19000</v>
@@ -9969,10 +9939,10 @@
         </is>
       </c>
       <c r="G197" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H197" s="6" t="n">
-        <v>200000</v>
+        <v>150000</v>
       </c>
       <c r="I197" s="13" t="n">
         <v>13000</v>
@@ -10061,10 +10031,10 @@
         </is>
       </c>
       <c r="G199" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H199" s="6" t="n">
-        <v>100000</v>
+        <v>73000</v>
       </c>
       <c r="I199" s="13" t="n">
         <v>7000</v>
@@ -10296,10 +10266,10 @@
         </is>
       </c>
       <c r="G204" s="14" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H204" s="16" t="n">
-        <v>200000</v>
+        <v>150000</v>
       </c>
       <c r="I204" s="17" t="n">
         <v>16000</v>
@@ -10343,10 +10313,10 @@
         </is>
       </c>
       <c r="G205" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H205" s="6" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="I205" s="13" t="n">
         <v>22000</v>
@@ -10388,10 +10358,10 @@
         </is>
       </c>
       <c r="G206" s="14" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H206" s="16" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="I206" s="17" t="n">
         <v>22000</v>
@@ -10433,10 +10403,10 @@
         </is>
       </c>
       <c r="G207" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H207" s="6" t="n">
-        <v>100000</v>
+        <v>73000</v>
       </c>
       <c r="I207" s="13" t="n">
         <v>6500</v>
@@ -10574,10 +10544,10 @@
         </is>
       </c>
       <c r="G210" s="14" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H210" s="16" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="I210" s="17" t="n">
         <v>24000</v>
@@ -10621,10 +10591,10 @@
         </is>
       </c>
       <c r="G211" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H211" s="6" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="I211" s="13" t="n">
         <v>24000</v>
@@ -10807,10 +10777,10 @@
         </is>
       </c>
       <c r="G215" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H215" s="6" t="n">
-        <v>200000</v>
+        <v>150000</v>
       </c>
       <c r="I215" s="13" t="n">
         <v>19000</v>
@@ -11089,10 +11059,10 @@
         </is>
       </c>
       <c r="G221" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H221" s="6" t="n">
-        <v>200000</v>
+        <v>150000</v>
       </c>
       <c r="I221" s="13" t="n">
         <v>16000</v>
@@ -11230,10 +11200,10 @@
         </is>
       </c>
       <c r="G224" s="14" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H224" s="16" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="I224" s="17" t="n">
         <v>22000</v>
@@ -11275,10 +11245,10 @@
         </is>
       </c>
       <c r="G225" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H225" s="6" t="n">
-        <v>100000</v>
+        <v>73000</v>
       </c>
       <c r="I225" s="13" t="n">
         <v>7000</v>
@@ -11555,10 +11525,10 @@
         </is>
       </c>
       <c r="G231" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H231" s="6" t="n">
-        <v>100000</v>
+        <v>73000</v>
       </c>
       <c r="I231" s="13" t="n">
         <v>6500</v>
@@ -11790,10 +11760,10 @@
         </is>
       </c>
       <c r="G236" s="14" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H236" s="16" t="n">
-        <v>100000</v>
+        <v>73000</v>
       </c>
       <c r="I236" s="17" t="n">
         <v>6500</v>
@@ -12025,10 +11995,10 @@
         </is>
       </c>
       <c r="G241" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H241" s="6" t="n">
-        <v>100000</v>
+        <v>73000</v>
       </c>
       <c r="I241" s="13" t="n">
         <v>6500</v>
@@ -12119,10 +12089,10 @@
         </is>
       </c>
       <c r="G243" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H243" s="6" t="n">
-        <v>100000</v>
+        <v>73000</v>
       </c>
       <c r="I243" s="13" t="n">
         <v>6500</v>
@@ -12307,10 +12277,10 @@
         </is>
       </c>
       <c r="G247" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H247" s="6" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="I247" s="13" t="n">
         <v>22000</v>
@@ -12354,10 +12324,10 @@
         </is>
       </c>
       <c r="G248" s="14" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H248" s="16" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="I248" s="17" t="n">
         <v>22000</v>
@@ -12401,10 +12371,10 @@
         </is>
       </c>
       <c r="G249" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H249" s="6" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="I249" s="13" t="n">
         <v>22000</v>
@@ -12448,10 +12418,10 @@
         </is>
       </c>
       <c r="G250" s="14" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H250" s="16" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="I250" s="17" t="n">
         <v>22000</v>
@@ -12495,10 +12465,10 @@
         </is>
       </c>
       <c r="G251" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H251" s="6" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="I251" s="13" t="n">
         <v>22000</v>
@@ -12683,10 +12653,10 @@
         </is>
       </c>
       <c r="G255" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H255" s="6" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="I255" s="13" t="n">
         <v>24000</v>
@@ -12730,10 +12700,10 @@
         </is>
       </c>
       <c r="G256" s="14" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H256" s="16" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="I256" s="17" t="n">
         <v>24000</v>
@@ -12777,10 +12747,10 @@
         </is>
       </c>
       <c r="G257" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H257" s="6" t="n">
-        <v>200000</v>
+        <v>150000</v>
       </c>
       <c r="I257" s="13" t="n">
         <v>16000</v>
@@ -13059,10 +13029,10 @@
         </is>
       </c>
       <c r="G263" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H263" s="6" t="n">
-        <v>100000</v>
+        <v>73000</v>
       </c>
       <c r="I263" s="13" t="n">
         <v>7000</v>
@@ -13646,10 +13616,10 @@
         </is>
       </c>
       <c r="G276" s="14" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H276" s="16" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="I276" s="17" t="n">
         <v>22000</v>
@@ -13691,10 +13661,10 @@
         </is>
       </c>
       <c r="G277" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H277" s="6" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="I277" s="13" t="n">
         <v>22000</v>
@@ -13736,10 +13706,10 @@
         </is>
       </c>
       <c r="G278" s="14" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H278" s="16" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="I278" s="17" t="n">
         <v>22000</v>
@@ -13826,10 +13796,10 @@
         </is>
       </c>
       <c r="G280" s="14" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H280" s="16" t="n">
-        <v>100000</v>
+        <v>73000</v>
       </c>
       <c r="I280" s="17" t="n">
         <v>7000</v>
@@ -13961,10 +13931,10 @@
         </is>
       </c>
       <c r="G283" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H283" s="6" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I283" s="13" t="n">
         <v>8000</v>
@@ -14006,10 +13976,10 @@
         </is>
       </c>
       <c r="G284" s="14" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H284" s="16" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="I284" s="17" t="n">
         <v>24000</v>
@@ -14051,10 +14021,10 @@
         </is>
       </c>
       <c r="G285" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H285" s="6" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I285" s="13" t="n">
         <v>8000</v>
@@ -14096,10 +14066,10 @@
         </is>
       </c>
       <c r="G286" s="14" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H286" s="16" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I286" s="17" t="n">
         <v>8000</v>
@@ -14141,10 +14111,10 @@
         </is>
       </c>
       <c r="G287" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H287" s="6" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="I287" s="13" t="n">
         <v>22000</v>
@@ -14186,10 +14156,10 @@
         </is>
       </c>
       <c r="G288" s="14" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H288" s="16" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I288" s="17" t="n">
         <v>8000</v>
@@ -14231,10 +14201,10 @@
         </is>
       </c>
       <c r="G289" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H289" s="6" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I289" s="13" t="n">
         <v>8000</v>
@@ -14276,10 +14246,10 @@
         </is>
       </c>
       <c r="G290" s="14" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H290" s="16" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I290" s="17" t="n">
         <v>8000</v>
@@ -14321,10 +14291,10 @@
         </is>
       </c>
       <c r="G291" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H291" s="6" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I291" s="13" t="n">
         <v>8000</v>
@@ -14366,10 +14336,10 @@
         </is>
       </c>
       <c r="G292" s="14" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H292" s="16" t="n">
-        <v>100000</v>
+        <v>73000</v>
       </c>
       <c r="I292" s="17" t="n">
         <v>7000</v>
@@ -14411,10 +14381,10 @@
         </is>
       </c>
       <c r="G293" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H293" s="6" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I293" s="13" t="n">
         <v>8000</v>
@@ -14456,10 +14426,10 @@
         </is>
       </c>
       <c r="G294" s="14" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H294" s="16" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="I294" s="17" t="n">
         <v>22000</v>
@@ -14501,10 +14471,10 @@
         </is>
       </c>
       <c r="G295" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H295" s="6" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="I295" s="13" t="n">
         <v>22000</v>
@@ -14591,10 +14561,10 @@
         </is>
       </c>
       <c r="G297" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H297" s="6" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I297" s="13" t="n">
         <v>8000</v>
@@ -14636,10 +14606,10 @@
         </is>
       </c>
       <c r="G298" s="14" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H298" s="16" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I298" s="17" t="n">
         <v>8000</v>
@@ -14681,10 +14651,10 @@
         </is>
       </c>
       <c r="G299" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H299" s="6" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="I299" s="13" t="n">
         <v>22000</v>
@@ -14726,10 +14696,10 @@
         </is>
       </c>
       <c r="G300" s="14" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H300" s="16" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I300" s="17" t="n">
         <v>8000</v>
@@ -14771,10 +14741,10 @@
         </is>
       </c>
       <c r="G301" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H301" s="6" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I301" s="13" t="n">
         <v>8000</v>
@@ -14816,10 +14786,10 @@
         </is>
       </c>
       <c r="G302" s="14" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H302" s="16" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I302" s="17" t="n">
         <v>8000</v>
@@ -14861,10 +14831,10 @@
         </is>
       </c>
       <c r="G303" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H303" s="6" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I303" s="13" t="n">
         <v>8000</v>
@@ -14906,10 +14876,10 @@
         </is>
       </c>
       <c r="G304" s="14" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H304" s="16" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I304" s="17" t="n">
         <v>8000</v>
@@ -14951,10 +14921,10 @@
         </is>
       </c>
       <c r="G305" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H305" s="6" t="n">
-        <v>250000</v>
+        <v>150000</v>
       </c>
       <c r="I305" s="13" t="n">
         <v>24000</v>
@@ -14996,10 +14966,10 @@
         </is>
       </c>
       <c r="G306" s="14" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H306" s="16" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I306" s="17" t="n">
         <v>8000</v>
@@ -15041,10 +15011,10 @@
         </is>
       </c>
       <c r="G307" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H307" s="6" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I307" s="13" t="n">
         <v>8000</v>
@@ -15086,10 +15056,10 @@
         </is>
       </c>
       <c r="G308" s="14" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H308" s="16" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I308" s="17" t="n">
         <v>8000</v>
@@ -15131,10 +15101,10 @@
         </is>
       </c>
       <c r="G309" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H309" s="6" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I309" s="13" t="n">
         <v>8000</v>
@@ -15176,10 +15146,10 @@
         </is>
       </c>
       <c r="G310" s="14" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H310" s="16" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I310" s="17" t="n">
         <v>8000</v>
@@ -15221,10 +15191,10 @@
         </is>
       </c>
       <c r="G311" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H311" s="6" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I311" s="13" t="n">
         <v>8000</v>
@@ -15266,10 +15236,10 @@
         </is>
       </c>
       <c r="G312" s="14" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H312" s="16" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I312" s="17" t="n">
         <v>8000</v>
@@ -15311,10 +15281,10 @@
         </is>
       </c>
       <c r="G313" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H313" s="6" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I313" s="13" t="n">
         <v>8000</v>
@@ -15356,10 +15326,10 @@
         </is>
       </c>
       <c r="G314" s="14" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H314" s="16" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I314" s="17" t="n">
         <v>8000</v>
@@ -15401,10 +15371,10 @@
         </is>
       </c>
       <c r="G315" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H315" s="6" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I315" s="13" t="n">
         <v>8000</v>
@@ -15446,10 +15416,10 @@
         </is>
       </c>
       <c r="G316" s="14" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H316" s="16" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I316" s="17" t="n">
         <v>8000</v>
@@ -15536,10 +15506,10 @@
         </is>
       </c>
       <c r="G318" s="14" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H318" s="16" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I318" s="17" t="n">
         <v>8000</v>
@@ -15581,10 +15551,10 @@
         </is>
       </c>
       <c r="G319" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H319" s="6" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I319" s="13" t="n">
         <v>8000</v>
@@ -15626,10 +15596,10 @@
         </is>
       </c>
       <c r="G320" s="14" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H320" s="16" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I320" s="17" t="n">
         <v>8000</v>
@@ -15671,10 +15641,10 @@
         </is>
       </c>
       <c r="G321" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H321" s="6" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="I321" s="13" t="n">
         <v>8000</v>
@@ -15758,13 +15728,13 @@
         <v>105</v>
       </c>
       <c r="C3" s="6" t="n">
-        <v>13911000</v>
+        <v>11979000</v>
       </c>
       <c r="D3" t="n">
         <v>32.9</v>
       </c>
       <c r="E3" t="n">
-        <v>30.8</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="4">
@@ -15777,13 +15747,13 @@
         <v>47</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>8573000</v>
+        <v>5445000</v>
       </c>
       <c r="D4" t="n">
         <v>14.7</v>
       </c>
       <c r="E4" t="n">
-        <v>19</v>
+        <v>15.2</v>
       </c>
     </row>
     <row r="5">
@@ -15796,13 +15766,13 @@
         <v>35</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>5573000</v>
+        <v>3445000</v>
       </c>
       <c r="D5" t="n">
         <v>11</v>
       </c>
       <c r="E5" t="n">
-        <v>12.3</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="6">
@@ -15815,13 +15785,13 @@
         <v>59</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>7219000</v>
+        <v>7176000</v>
       </c>
       <c r="D6" t="n">
         <v>18.5</v>
       </c>
       <c r="E6" t="n">
-        <v>16</v>
+        <v>20.1</v>
       </c>
     </row>
     <row r="7">
@@ -15834,13 +15804,13 @@
         <v>61</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>8600000</v>
+        <v>6633000</v>
       </c>
       <c r="D7" t="n">
         <v>19.1</v>
       </c>
       <c r="E7" t="n">
-        <v>19</v>
+        <v>18.6</v>
       </c>
     </row>
     <row r="8">
@@ -15853,13 +15823,13 @@
         <v>12</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>1273000</v>
+        <v>1030000</v>
       </c>
       <c r="D8" t="n">
         <v>3.8</v>
       </c>
       <c r="E8" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="9">
@@ -15872,7 +15842,7 @@
         <v>319</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>45149000</v>
+        <v>35708000</v>
       </c>
     </row>
   </sheetData>
@@ -15886,7 +15856,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -15935,16 +15905,16 @@
         <v>6</v>
       </c>
       <c r="B3" t="n">
-        <v>13</v>
+        <v>96</v>
       </c>
       <c r="C3" s="6" t="n">
         <v>73000</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>949000</v>
+        <v>7008000</v>
       </c>
       <c r="E3" t="n">
-        <v>4.1</v>
+        <v>30.1</v>
       </c>
     </row>
     <row r="4">
@@ -15952,16 +15922,16 @@
         <v>12</v>
       </c>
       <c r="B4" t="n">
-        <v>182</v>
+        <v>95</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>100000</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>18200000</v>
+        <v>9500000</v>
       </c>
       <c r="E4" t="n">
-        <v>57.1</v>
+        <v>29.8</v>
       </c>
     </row>
     <row r="5">
@@ -15969,63 +15939,29 @@
         <v>20</v>
       </c>
       <c r="B5" t="n">
-        <v>31</v>
+        <v>128</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>150000</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>4650000</v>
+        <v>19200000</v>
       </c>
       <c r="E5" t="n">
-        <v>9.699999999999999</v>
+        <v>40.1</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>30</v>
-      </c>
-      <c r="B6" t="n">
-        <v>38</v>
-      </c>
-      <c r="C6" s="6" t="n">
-        <v>200000</v>
-      </c>
-      <c r="D6" s="6" t="n">
-        <v>7600000</v>
-      </c>
-      <c r="E6" t="n">
-        <v>11.9</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>50</v>
-      </c>
-      <c r="B7" t="n">
-        <v>55</v>
-      </c>
-      <c r="C7" s="6" t="n">
-        <v>250000</v>
-      </c>
-      <c r="D7" s="6" t="n">
-        <v>13750000</v>
-      </c>
-      <c r="E7" t="n">
-        <v>17.2</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>סה"כ</t>
         </is>
       </c>
-      <c r="B8" s="4" t="n">
+      <c r="B6" s="4" t="n">
         <v>319</v>
       </c>
-      <c r="D8" s="7" t="n">
-        <v>45149000</v>
+      <c r="D6" s="7" t="n">
+        <v>35708000</v>
       </c>
     </row>
   </sheetData>
